--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -753,7 +753,7 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="V3" t="n">
         <v>200</v>
@@ -849,7 +849,7 @@
         <v>34</v>
       </c>
       <c r="V4" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>141</v>
       </c>
       <c r="U5" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="V5" t="n">
         <v>1000</v>
@@ -1125,7 +1125,7 @@
         <v>139.7</v>
       </c>
       <c r="U7" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="V7" t="n">
         <v>350</v>
@@ -1218,7 +1218,7 @@
         <v>141</v>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V8" t="n">
         <v>9150</v>
@@ -1404,7 +1404,7 @@
         <v>59.2</v>
       </c>
       <c r="U10" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="V10" t="n">
         <v>10</v>
@@ -1497,7 +1497,7 @@
         <v>139.7</v>
       </c>
       <c r="U11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V11" t="n">
         <v>600</v>
@@ -1590,7 +1590,7 @@
         <v>98.2</v>
       </c>
       <c r="U12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V12" t="n">
         <v>800</v>
@@ -1683,7 +1683,7 @@
         <v>98.2</v>
       </c>
       <c r="U13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V13" t="n">
         <v>500</v>
@@ -1869,7 +1869,7 @@
         <v>141</v>
       </c>
       <c r="U15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="V15" t="n">
         <v>1000</v>
@@ -1962,7 +1962,7 @@
         <v>31.8</v>
       </c>
       <c r="U16" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="V16" t="n">
         <v>200</v>
@@ -2055,7 +2055,7 @@
         <v>141</v>
       </c>
       <c r="U17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V17" t="n">
         <v>200</v>
@@ -2148,7 +2148,7 @@
         <v>141</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V18" t="n">
         <v>200</v>
@@ -2182,19 +2182,19 @@
         <v>87</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>41.350681</v>
+        <v>41.365496</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>69.266822</v>
+        <v>69.203898</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>41.350681, 69.266822</t>
+          <t>41.365496, 69.203898</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Джами махалля</t>
+          <t>Бешкурган-4</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2203,30 +2203,30 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4950</v>
+        <v>12971</v>
       </c>
       <c r="M19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="O19" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="P19" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="Q19" t="n">
         <v>0.5</v>
@@ -2235,16 +2235,16 @@
         <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>126</v>
+        <v>313</v>
       </c>
       <c r="T19" t="n">
-        <v>139.7</v>
+        <v>59.2</v>
       </c>
       <c r="U19" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="V19" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.350681,69.266822</t>
+          <t>https://www.google.com/maps?q=41.365496,69.203898</t>
         </is>
       </c>
     </row>
@@ -2275,19 +2275,19 @@
         <v>87</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>41.365496</v>
+        <v>41.350681</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>69.203898</v>
+        <v>69.266822</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>41.365496, 69.203898</t>
+          <t>41.350681, 69.266822</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Бешкурган-4</t>
+          <t>Джами махалля</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2296,30 +2296,30 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>12971</v>
+        <v>4950</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N20" t="n">
+        <v>58</v>
+      </c>
+      <c r="O20" t="n">
         <v>28</v>
       </c>
-      <c r="O20" t="n">
-        <v>11</v>
-      </c>
       <c r="P20" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="Q20" t="n">
         <v>0.5</v>
@@ -2328,16 +2328,16 @@
         <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>313</v>
+        <v>126</v>
       </c>
       <c r="T20" t="n">
-        <v>59.2</v>
+        <v>139.7</v>
       </c>
       <c r="U20" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="V20" t="n">
-        <v>200</v>
+        <v>450</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.365496,69.203898</t>
+          <t>https://www.google.com/maps?q=41.350681,69.266822</t>
         </is>
       </c>
     </row>
@@ -2520,10 +2520,10 @@
         <v>139.7</v>
       </c>
       <c r="U22" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="V22" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>139.7</v>
       </c>
       <c r="U23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V23" t="n">
         <v>350</v>
@@ -2706,7 +2706,7 @@
         <v>59.2</v>
       </c>
       <c r="U24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V24" t="n">
         <v>200</v>
@@ -2799,7 +2799,7 @@
         <v>139.7</v>
       </c>
       <c r="U25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V25" t="n">
         <v>350</v>
@@ -2892,7 +2892,7 @@
         <v>28.3</v>
       </c>
       <c r="U26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V26" t="n">
         <v>350</v>
@@ -2988,7 +2988,7 @@
         <v>2</v>
       </c>
       <c r="V27" t="n">
-        <v>1100</v>
+        <v>2600</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>139.7</v>
       </c>
       <c r="U28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V28" t="n">
         <v>600</v>
@@ -3264,7 +3264,7 @@
         <v>122.7</v>
       </c>
       <c r="U30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V30" t="n">
         <v>550</v>
@@ -3357,10 +3357,10 @@
         <v>98.2</v>
       </c>
       <c r="U31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V31" t="n">
-        <v>900</v>
+        <v>350</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>122.7</v>
       </c>
       <c r="U34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V34" t="n">
         <v>350</v>
@@ -3667,7 +3667,7 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>41.278439</v>
@@ -3729,7 +3729,7 @@
         <v>141</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
@@ -3820,10 +3820,10 @@
         <v>59.2</v>
       </c>
       <c r="U36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V36" t="n">
-        <v>600</v>
+        <v>350</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>139.7</v>
       </c>
       <c r="U38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
         <v>2000</v>
@@ -4099,7 +4099,7 @@
         <v>47.6</v>
       </c>
       <c r="U39" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="V39" t="n">
         <v>220</v>
@@ -4283,7 +4283,7 @@
         <v>31.8</v>
       </c>
       <c r="U41" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="V41" t="n">
         <v>1000</v>
@@ -4376,7 +4376,7 @@
         <v>28.3</v>
       </c>
       <c r="U42" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="V42" t="n">
         <v>500</v>
@@ -4655,7 +4655,7 @@
         <v>47.6</v>
       </c>
       <c r="U45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V45" t="n">
         <v>2</v>
@@ -4841,7 +4841,7 @@
         <v>48.5</v>
       </c>
       <c r="U47" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="V47" t="n">
         <v>1300</v>
@@ -4934,7 +4934,7 @@
         <v>60.2</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
@@ -5025,10 +5025,10 @@
         <v>28.3</v>
       </c>
       <c r="U49" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="V49" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>60.2</v>
       </c>
       <c r="U50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V50" t="n">
         <v>1200</v>
@@ -5211,7 +5211,7 @@
         <v>31.8</v>
       </c>
       <c r="U51" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="V51" t="n">
         <v>200</v>
@@ -5490,10 +5490,10 @@
         <v>59.2</v>
       </c>
       <c r="U54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V54" t="n">
-        <v>23040</v>
+        <v>499</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -5676,9 +5676,11 @@
         <v>139.7</v>
       </c>
       <c r="U56" t="n">
-        <v>1</v>
-      </c>
-      <c r="V56" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="V56" t="n">
+        <v>6000</v>
+      </c>
       <c r="W56" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5767,7 +5769,7 @@
         <v>122.7</v>
       </c>
       <c r="U57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V57" t="n">
         <v>150</v>
@@ -5860,7 +5862,7 @@
         <v>122.7</v>
       </c>
       <c r="U58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V58" t="n">
         <v>150</v>
@@ -5891,7 +5893,7 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D59" s="2" t="n">
         <v>41.174834</v>
@@ -5984,7 +5986,7 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D60" s="2" t="n">
         <v>41.387374</v>
@@ -6046,10 +6048,10 @@
         <v>59.2</v>
       </c>
       <c r="U60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V60" t="n">
-        <v>15120</v>
+        <v>499</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -6232,7 +6234,7 @@
         <v>184.9</v>
       </c>
       <c r="U62" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V62" t="n">
         <v>18</v>
@@ -6325,7 +6327,7 @@
         <v>213.9</v>
       </c>
       <c r="U63" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V63" t="n">
         <v>100</v>
@@ -6356,7 +6358,7 @@
         <v>13</v>
       </c>
       <c r="C64" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D64" s="2" t="n">
         <v>41.387864</v>
@@ -6418,7 +6420,7 @@
         <v>270.6</v>
       </c>
       <c r="U64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V64" t="n">
         <v>600</v>
@@ -6602,11 +6604,9 @@
         <v>213.9</v>
       </c>
       <c r="U66" t="n">
-        <v>1</v>
-      </c>
-      <c r="V66" t="n">
-        <v>1400</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6884,7 +6884,7 @@
         <v>3</v>
       </c>
       <c r="V69" t="n">
-        <v>1925</v>
+        <v>499</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
@@ -6974,11 +6974,9 @@
         <v>270.6</v>
       </c>
       <c r="U70" t="n">
-        <v>1</v>
-      </c>
-      <c r="V70" t="n">
-        <v>250</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7186,7 +7184,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C73" t="n">
         <v>77</v>
@@ -7368,7 +7366,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C75" t="n">
         <v>77</v>
@@ -7923,7 +7921,7 @@
         <v>30</v>
       </c>
       <c r="C81" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D81" s="2" t="n">
         <v>41.417442</v>
@@ -8197,7 +8195,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C84" t="n">
         <v>77</v>
@@ -8841,7 +8839,7 @@
         <v>23</v>
       </c>
       <c r="C91" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D91" s="2" t="n">
         <v>41.160793</v>
@@ -9477,7 +9475,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C98" t="n">
         <v>77</v>
@@ -10853,7 +10851,7 @@
         <v>22</v>
       </c>
       <c r="C113" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D113" s="2" t="n">
         <v>41.088745</v>
@@ -11578,7 +11576,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C121" t="n">
         <v>77</v>
@@ -12193,7 +12191,7 @@
         <v>55.2</v>
       </c>
       <c r="U127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V127" t="inlineStr"/>
       <c r="W127" t="inlineStr">
@@ -12586,7 +12584,7 @@
         <v>45</v>
       </c>
       <c r="C132" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D132" s="2" t="n">
         <v>41.007896</v>
@@ -13405,7 +13403,7 @@
         <v>57</v>
       </c>
       <c r="C141" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D141" s="2" t="n">
         <v>41.014259</v>
@@ -13769,7 +13767,7 @@
         <v>56</v>
       </c>
       <c r="C145" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D145" s="2" t="n">
         <v>40.856143</v>
@@ -14286,11 +14284,9 @@
         <v>55.2</v>
       </c>
       <c r="U150" t="n">
-        <v>1</v>
-      </c>
-      <c r="V150" t="n">
-        <v>500</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V150" t="inlineStr"/>
       <c r="W150" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -14496,20 +14492,20 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C153" t="n">
         <v>59</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>40.855744</v>
+        <v>40.85233</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>68.918626</v>
+        <v>68.91854499999999</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>40.855744, 68.918626</t>
+          <t>40.852330, 68.918545</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -14523,10 +14519,10 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J153" t="n">
-        <v>43.1</v>
+        <v>43.4</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
@@ -14534,7 +14530,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>2917</v>
+        <v>3338</v>
       </c>
       <c r="M153" t="n">
         <v>1</v>
@@ -14576,7 +14572,7 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.855744,68.918626</t>
+          <t>https://www.google.com/maps?q=40.852330,68.918545</t>
         </is>
       </c>
     </row>
@@ -14863,7 +14859,7 @@
         <v>54</v>
       </c>
       <c r="C157" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D157" s="2" t="n">
         <v>40.960514</v>
@@ -15500,7 +15496,7 @@
         <v>1</v>
       </c>
       <c r="C164" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D164" s="2" t="n">
         <v>41.669921</v>
@@ -15952,7 +15948,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C169" t="n">
         <v>59</v>
@@ -17229,7 +17225,7 @@
         <v>2</v>
       </c>
       <c r="C183" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D183" s="2" t="n">
         <v>41.018669</v>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,7 +660,7 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V2" t="n">
         <v>220</v>
@@ -753,7 +753,7 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V3" t="n">
         <v>200</v>
@@ -846,7 +846,7 @@
         <v>28.3</v>
       </c>
       <c r="U4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="V4" t="n">
         <v>450</v>
@@ -939,10 +939,10 @@
         <v>141</v>
       </c>
       <c r="U5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V5" t="n">
-        <v>1000</v>
+        <v>918</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>122.7</v>
       </c>
       <c r="U7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V7" t="n">
         <v>150</v>
@@ -1218,7 +1218,7 @@
         <v>139.7</v>
       </c>
       <c r="U8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V8" t="n">
         <v>350</v>
@@ -1311,7 +1311,7 @@
         <v>141</v>
       </c>
       <c r="U9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V9" t="n">
         <v>5400</v>
@@ -1404,7 +1404,7 @@
         <v>59.2</v>
       </c>
       <c r="U10" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="V10" t="n">
         <v>450</v>
@@ -1590,7 +1590,7 @@
         <v>98.2</v>
       </c>
       <c r="U12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V12" t="n">
         <v>500</v>
@@ -1683,7 +1683,7 @@
         <v>98.2</v>
       </c>
       <c r="U13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V13" t="n">
         <v>900</v>
@@ -1779,7 +1779,7 @@
         <v>14</v>
       </c>
       <c r="V14" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>31.8</v>
       </c>
       <c r="U15" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="V15" t="n">
         <v>200</v>
@@ -1965,7 +1965,7 @@
         <v>30</v>
       </c>
       <c r="V16" t="n">
-        <v>1000</v>
+        <v>918</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>141</v>
       </c>
       <c r="U17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V17" t="n">
         <v>200</v>
@@ -2148,7 +2148,7 @@
         <v>59.2</v>
       </c>
       <c r="U18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V18" t="n">
         <v>200</v>
@@ -2241,7 +2241,7 @@
         <v>141</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
         <v>200</v>
@@ -2427,7 +2427,7 @@
         <v>139.7</v>
       </c>
       <c r="U21" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="V21" t="n">
         <v>700</v>
@@ -2613,7 +2613,7 @@
         <v>59.2</v>
       </c>
       <c r="U23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V23" t="n">
         <v>200</v>
@@ -2706,10 +2706,10 @@
         <v>122.7</v>
       </c>
       <c r="U24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V24" t="n">
-        <v>2000</v>
+        <v>350</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>139.7</v>
       </c>
       <c r="U25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V25" t="n">
         <v>350</v>
@@ -2830,7 +2830,7 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>41.370618</v>
@@ -2892,10 +2892,10 @@
         <v>139.7</v>
       </c>
       <c r="U26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V26" t="n">
-        <v>600</v>
+        <v>350</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>139.7</v>
       </c>
       <c r="U27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V27" t="n">
         <v>450</v>
@@ -3171,10 +3171,10 @@
         <v>28.3</v>
       </c>
       <c r="U29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V29" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3355,10 +3355,10 @@
         <v>139.7</v>
       </c>
       <c r="U31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V31" t="n">
-        <v>600</v>
+        <v>350</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3634,10 +3634,10 @@
         <v>141</v>
       </c>
       <c r="U34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V34" t="n">
-        <v>1200</v>
+        <v>1872</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>98.2</v>
       </c>
       <c r="U36" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V36" t="n">
         <v>500</v>
@@ -3913,7 +3913,7 @@
         <v>59.2</v>
       </c>
       <c r="U37" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V37" t="n">
         <v>350</v>
@@ -4099,7 +4099,7 @@
         <v>47.6</v>
       </c>
       <c r="U39" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="V39" t="n">
         <v>220</v>
@@ -4195,7 +4195,7 @@
         <v>3</v>
       </c>
       <c r="V40" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -4378,10 +4378,10 @@
         <v>31.8</v>
       </c>
       <c r="U42" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -4471,10 +4471,10 @@
         <v>28.3</v>
       </c>
       <c r="U43" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="V43" t="n">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>28.3</v>
       </c>
       <c r="U44" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V44" t="n">
         <v>400</v>
@@ -4657,7 +4657,7 @@
         <v>47.6</v>
       </c>
       <c r="U45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V45" t="n">
         <v>2</v>
@@ -4841,7 +4841,7 @@
         <v>28.3</v>
       </c>
       <c r="U47" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V47" t="n">
         <v>400</v>
@@ -5027,7 +5027,7 @@
         <v>28.3</v>
       </c>
       <c r="U49" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V49" t="n">
         <v>450</v>
@@ -5120,9 +5120,11 @@
         <v>60.2</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1500</v>
+      </c>
       <c r="W50" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5304,7 +5306,7 @@
         <v>31.8</v>
       </c>
       <c r="U52" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="V52" t="n">
         <v>200</v>
@@ -5397,10 +5399,10 @@
         <v>60.2</v>
       </c>
       <c r="U53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V53" t="n">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -5490,10 +5492,10 @@
         <v>48.5</v>
       </c>
       <c r="U54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V54" t="n">
-        <v>1200</v>
+        <v>8000</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -6048,9 +6050,11 @@
         <v>141</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1500</v>
+      </c>
       <c r="W60" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6139,7 +6143,7 @@
         <v>139.7</v>
       </c>
       <c r="U61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V61" t="n">
         <v>3500</v>
@@ -6232,11 +6236,9 @@
         <v>184.9</v>
       </c>
       <c r="U62" t="n">
-        <v>1</v>
-      </c>
-      <c r="V62" t="n">
-        <v>1100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6325,7 +6327,7 @@
         <v>184.9</v>
       </c>
       <c r="U63" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V63" t="n">
         <v>18</v>
@@ -6418,7 +6420,7 @@
         <v>213.9</v>
       </c>
       <c r="U64" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V64" t="n">
         <v>100</v>
@@ -6511,7 +6513,7 @@
         <v>270.6</v>
       </c>
       <c r="U65" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V65" t="n">
         <v>600</v>
@@ -6697,11 +6699,9 @@
         <v>213.9</v>
       </c>
       <c r="U67" t="n">
-        <v>1</v>
-      </c>
-      <c r="V67" t="n">
-        <v>1400</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6790,7 +6790,7 @@
         <v>270.6</v>
       </c>
       <c r="U68" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V68" t="n">
         <v>100</v>
@@ -6883,7 +6883,7 @@
         <v>270.6</v>
       </c>
       <c r="U69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr">
@@ -7187,7 +7187,7 @@
         <v>22</v>
       </c>
       <c r="C73" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D73" s="2" t="n">
         <v>41.402834</v>
@@ -8723,7 +8723,7 @@
         <v>184.9</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" t="inlineStr">
@@ -9819,11 +9819,9 @@
         <v>184.9</v>
       </c>
       <c r="U101" t="n">
-        <v>1</v>
-      </c>
-      <c r="V101" t="n">
-        <v>600</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V101" t="inlineStr"/>
       <c r="W101" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -9912,11 +9910,9 @@
         <v>184.9</v>
       </c>
       <c r="U102" t="n">
-        <v>1</v>
-      </c>
-      <c r="V102" t="n">
-        <v>600</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V102" t="inlineStr"/>
       <c r="W102" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -11132,7 +11128,7 @@
         <v>16</v>
       </c>
       <c r="C116" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D116" s="2" t="n">
         <v>41.02079</v>
@@ -13044,7 +13040,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C137" t="n">
         <v>44</v>
@@ -13226,7 +13222,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C139" t="n">
         <v>44</v>
@@ -13687,25 +13683,25 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C144" t="n">
         <v>45</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>40.81467</v>
+        <v>40.810243</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>69.22759000000001</v>
+        <v>69.282393</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>40.814670, 69.227590</t>
+          <t>40.810243, 69.282393</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ачмайли</t>
+          <t>Каракуйли</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -13714,10 +13710,10 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="J144" t="n">
-        <v>39</v>
+        <v>39.3</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -13725,10 +13721,10 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>1538</v>
+        <v>1602</v>
       </c>
       <c r="M144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N144" t="n">
         <v>0</v>
@@ -13737,7 +13733,7 @@
         <v>0</v>
       </c>
       <c r="P144" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q144" t="n">
         <v>5</v>
@@ -13762,12 +13758,12 @@
       </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.814670,69.227590</t>
+          <t>https://www.google.com/maps?q=40.810243,69.282393</t>
         </is>
       </c>
     </row>
@@ -13778,25 +13774,25 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="C145" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>40.810243</v>
+        <v>40.805776</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>69.282393</v>
+        <v>69.246951</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>40.810243, 69.282393</t>
+          <t>40.805776, 69.246951</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Каракуйли</t>
+          <t>Ачмайли</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -13805,10 +13801,10 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J145" t="n">
-        <v>39.3</v>
+        <v>39.9</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
@@ -13816,7 +13812,7 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>1602</v>
+        <v>2059</v>
       </c>
       <c r="M145" t="n">
         <v>0</v>
@@ -13858,7 +13854,7 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.810243,69.282393</t>
+          <t>https://www.google.com/maps?q=40.805776,69.246951</t>
         </is>
       </c>
     </row>
@@ -13869,25 +13865,25 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C146" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>40.805776</v>
+        <v>41.601553</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>69.246951</v>
+        <v>69.87878000000001</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>40.805776, 69.246951</t>
+          <t>41.601553, 69.878780</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ачмайли</t>
+          <t>Каранккуль</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -13896,18 +13892,18 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J146" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Букинский район</t>
+          <t>Бостанлыкский район</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>2059</v>
+        <v>1524</v>
       </c>
       <c r="M146" t="n">
         <v>0</v>
@@ -13931,7 +13927,7 @@
         <v>0</v>
       </c>
       <c r="T146" t="n">
-        <v>39.6</v>
+        <v>147.5</v>
       </c>
       <c r="U146" t="n">
         <v>0</v>
@@ -13949,7 +13945,7 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.805776,69.246951</t>
+          <t>https://www.google.com/maps?q=41.601553,69.878780</t>
         </is>
       </c>
     </row>
@@ -13960,25 +13956,25 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="C147" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>41.601553</v>
+        <v>40.964208</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>69.87878000000001</v>
+        <v>68.862195</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>41.601553, 69.878780</t>
+          <t>40.964208, 68.862195</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Каранккуль</t>
+          <t>Алмазар</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -13987,18 +13983,18 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="J147" t="n">
         <v>40</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Бостанлыкский район</t>
+          <t>Чиназский район</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>1524</v>
+        <v>3416</v>
       </c>
       <c r="M147" t="n">
         <v>0</v>
@@ -14010,7 +14006,7 @@
         <v>0</v>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q147" t="n">
         <v>5</v>
@@ -14022,7 +14018,7 @@
         <v>0</v>
       </c>
       <c r="T147" t="n">
-        <v>147.5</v>
+        <v>59.7</v>
       </c>
       <c r="U147" t="n">
         <v>0</v>
@@ -14035,12 +14031,12 @@
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.601553,69.878780</t>
+          <t>https://www.google.com/maps?q=40.964208,68.862195</t>
         </is>
       </c>
     </row>
@@ -14051,45 +14047,45 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="C148" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>40.964208</v>
+        <v>40.906695</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>68.862195</v>
+        <v>69.81593100000001</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>40.964208, 68.862195</t>
+          <t>40.906695, 69.815931</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Алмазар</t>
+          <t>Нурабад</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J148" t="n">
-        <v>40</v>
+        <v>41.2</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Чиназский район</t>
+          <t>Ахангаранский район</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>3416</v>
+        <v>2251</v>
       </c>
       <c r="M148" t="n">
         <v>0</v>
@@ -14101,7 +14097,7 @@
         <v>0</v>
       </c>
       <c r="P148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q148" t="n">
         <v>5</v>
@@ -14113,12 +14109,14 @@
         <v>0</v>
       </c>
       <c r="T148" t="n">
-        <v>59.7</v>
+        <v>55.2</v>
       </c>
       <c r="U148" t="n">
-        <v>0</v>
-      </c>
-      <c r="V148" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V148" t="n">
+        <v>500</v>
+      </c>
       <c r="W148" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -14126,12 +14124,12 @@
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.964208,68.862195</t>
+          <t>https://www.google.com/maps?q=40.906695,69.815931</t>
         </is>
       </c>
     </row>
@@ -14142,25 +14140,25 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C149" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>40.906695</v>
+        <v>40.862328</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>69.81593100000001</v>
+        <v>68.934483</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>40.906695, 69.815931</t>
+          <t>40.862328, 68.934483</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Нурабад</t>
+          <t>Дустабад (Солдатский)</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -14169,21 +14167,21 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J149" t="n">
-        <v>41.2</v>
+        <v>41.7</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Ахангаранский район</t>
+          <t>Куйичирчикский район</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>2251</v>
+        <v>2450</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N149" t="n">
         <v>0</v>
@@ -14192,7 +14190,7 @@
         <v>0</v>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q149" t="n">
         <v>5</v>
@@ -14204,14 +14202,12 @@
         <v>0</v>
       </c>
       <c r="T149" t="n">
-        <v>55.2</v>
+        <v>63.5</v>
       </c>
       <c r="U149" t="n">
-        <v>1</v>
-      </c>
-      <c r="V149" t="n">
-        <v>500</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V149" t="inlineStr"/>
       <c r="W149" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -14219,12 +14215,12 @@
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.906695,69.815931</t>
+          <t>https://www.google.com/maps?q=40.862328,68.934483</t>
         </is>
       </c>
     </row>
@@ -14235,20 +14231,20 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C150" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>40.862328</v>
+        <v>40.85233</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>68.934483</v>
+        <v>68.91854499999999</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>40.862328, 68.934483</t>
+          <t>40.852330, 68.918545</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -14262,10 +14258,10 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J150" t="n">
-        <v>41.7</v>
+        <v>43.4</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -14273,7 +14269,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>2450</v>
+        <v>3338</v>
       </c>
       <c r="M150" t="n">
         <v>1</v>
@@ -14315,7 +14311,7 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.862328,68.934483</t>
+          <t>https://www.google.com/maps?q=40.852330,68.918545</t>
         </is>
       </c>
     </row>
@@ -14326,37 +14322,37 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="C151" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>40.85233</v>
+        <v>40.915214</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>68.91854499999999</v>
+        <v>68.82572999999999</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>40.852330, 68.918545</t>
+          <t>40.915214, 68.825730</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Дустабад (Солдатский)</t>
+          <t>Кушек</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J151" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
@@ -14364,10 +14360,10 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>3338</v>
+        <v>1258</v>
       </c>
       <c r="M151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
         <v>0</v>
@@ -14376,7 +14372,7 @@
         <v>0</v>
       </c>
       <c r="P151" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q151" t="n">
         <v>5</v>
@@ -14401,12 +14397,12 @@
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.852330,68.918545</t>
+          <t>https://www.google.com/maps?q=40.915214,68.825730</t>
         </is>
       </c>
     </row>
@@ -14965,7 +14961,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C158" t="n">
         <v>44</v>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,10 +660,10 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V2" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="V3" t="n">
         <v>200</v>
@@ -846,10 +846,10 @@
         <v>28.3</v>
       </c>
       <c r="U4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="V4" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>141</v>
       </c>
       <c r="U6" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="V6" t="n">
         <v>918</v>
@@ -1125,7 +1125,7 @@
         <v>139.7</v>
       </c>
       <c r="U7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V7" t="n">
         <v>100</v>
@@ -1218,7 +1218,7 @@
         <v>139.7</v>
       </c>
       <c r="U8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V8" t="n">
         <v>350</v>
@@ -1314,7 +1314,7 @@
         <v>6</v>
       </c>
       <c r="V9" t="n">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>59.2</v>
       </c>
       <c r="U10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="V10" t="n">
         <v>450</v>
@@ -1500,7 +1500,7 @@
         <v>7</v>
       </c>
       <c r="V11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>141</v>
       </c>
       <c r="U12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V12" t="n">
         <v>500</v>
@@ -1683,7 +1683,7 @@
         <v>98.2</v>
       </c>
       <c r="U13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V13" t="n">
         <v>500</v>
@@ -1776,10 +1776,10 @@
         <v>98.2</v>
       </c>
       <c r="U14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V14" t="n">
-        <v>1300</v>
+        <v>900</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>31.8</v>
       </c>
       <c r="U15" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V15" t="n">
         <v>200</v>
@@ -1962,7 +1962,7 @@
         <v>98.2</v>
       </c>
       <c r="U16" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="V16" t="n">
         <v>800</v>
@@ -2055,7 +2055,7 @@
         <v>98.2</v>
       </c>
       <c r="U17" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="V17" t="n">
         <v>700</v>
@@ -2148,7 +2148,7 @@
         <v>59.2</v>
       </c>
       <c r="U18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V18" t="n">
         <v>200</v>
@@ -2241,7 +2241,7 @@
         <v>139.7</v>
       </c>
       <c r="U19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V19" t="n">
         <v>450</v>
@@ -2334,7 +2334,7 @@
         <v>48.5</v>
       </c>
       <c r="U20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V20" t="n">
         <v>1000</v>
@@ -2520,7 +2520,7 @@
         <v>139.7</v>
       </c>
       <c r="U22" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="V22" t="n">
         <v>700</v>
@@ -2554,19 +2554,19 @@
         <v>84</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>41.355449</v>
+        <v>41.228735</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>69.286761</v>
+        <v>69.200014</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>41.355449, 69.286761</t>
+          <t>41.228735, 69.200014</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Юнусабад-1</t>
+          <t>Сергели-5A</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2575,45 +2575,45 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>10097</v>
+        <v>7101</v>
       </c>
       <c r="M23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="O23" t="n">
+        <v>10</v>
+      </c>
+      <c r="P23" t="n">
         <v>20</v>
-      </c>
-      <c r="P23" t="n">
-        <v>38</v>
       </c>
       <c r="Q23" t="n">
         <v>0.5</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>522</v>
       </c>
       <c r="T23" t="n">
-        <v>139.7</v>
+        <v>122.7</v>
       </c>
       <c r="U23" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V23" t="n">
         <v>350</v>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.355449,69.286761</t>
+          <t>https://www.google.com/maps?q=41.228735,69.200014</t>
         </is>
       </c>
     </row>
@@ -2647,19 +2647,19 @@
         <v>84</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>41.228735</v>
+        <v>41.355449</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>69.200014</v>
+        <v>69.286761</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>41.228735, 69.200014</t>
+          <t>41.355449, 69.286761</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Сергели-5A</t>
+          <t>Юнусабад-1</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2668,45 +2668,45 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>7101</v>
+        <v>10097</v>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N24" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="O24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="P24" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="Q24" t="n">
         <v>0.5</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>522</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>122.7</v>
+        <v>139.7</v>
       </c>
       <c r="U24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V24" t="n">
         <v>350</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.228735,69.200014</t>
+          <t>https://www.google.com/maps?q=41.355449,69.286761</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
         <v>98.2</v>
       </c>
       <c r="U25" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="V25" t="n">
         <v>500</v>
@@ -2892,7 +2892,7 @@
         <v>59.2</v>
       </c>
       <c r="U26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V26" t="n">
         <v>200</v>
@@ -2985,7 +2985,7 @@
         <v>139.7</v>
       </c>
       <c r="U27" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V27" t="n">
         <v>350</v>
@@ -3078,7 +3078,7 @@
         <v>139.7</v>
       </c>
       <c r="U28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V28" t="n">
         <v>300</v>
@@ -3171,7 +3171,7 @@
         <v>141</v>
       </c>
       <c r="U29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V29" t="n">
         <v>200</v>
@@ -3264,7 +3264,7 @@
         <v>141</v>
       </c>
       <c r="U30" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V30" t="n">
         <v>200</v>
@@ -3482,19 +3482,19 @@
         <v>79</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>41.280376</v>
+        <v>41.382952</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>69.367574</v>
+        <v>69.279659</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>41.280376, 69.367574</t>
+          <t>41.382952, 69.279659</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>58а Военный городок</t>
+          <t>Юнусабад-10</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3503,30 +3503,30 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>9556</v>
+        <v>8693</v>
       </c>
       <c r="M33" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N33" t="n">
+        <v>24</v>
+      </c>
+      <c r="O33" t="n">
         <v>11</v>
       </c>
-      <c r="O33" t="n">
-        <v>7</v>
-      </c>
       <c r="P33" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="Q33" t="n">
         <v>0.5</v>
@@ -3538,13 +3538,13 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>141</v>
+        <v>139.7</v>
       </c>
       <c r="U33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V33" t="n">
-        <v>1500</v>
+        <v>600</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.280376,69.367574</t>
+          <t>https://www.google.com/maps?q=41.382952,69.279659</t>
         </is>
       </c>
     </row>
@@ -3575,19 +3575,19 @@
         <v>79</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>41.382952</v>
+        <v>41.280376</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>69.279659</v>
+        <v>69.367574</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>41.382952, 69.279659</t>
+          <t>41.280376, 69.367574</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Юнусабад-10</t>
+          <t>58а Военный городок</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3596,30 +3596,30 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8693</v>
+        <v>9556</v>
       </c>
       <c r="M34" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N34" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="O34" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="P34" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="Q34" t="n">
         <v>0.5</v>
@@ -3631,13 +3631,13 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>139.7</v>
+        <v>141</v>
       </c>
       <c r="U34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V34" t="n">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.382952,69.279659</t>
+          <t>https://www.google.com/maps?q=41.280376,69.367574</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
         <v>141</v>
       </c>
       <c r="U35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V35" t="n">
         <v>200</v>
@@ -3820,7 +3820,7 @@
         <v>139.7</v>
       </c>
       <c r="U36" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V36" t="n">
         <v>300</v>
@@ -3913,7 +3913,7 @@
         <v>28.3</v>
       </c>
       <c r="U37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V37" t="n">
         <v>350</v>
@@ -4006,7 +4006,7 @@
         <v>122.7</v>
       </c>
       <c r="U38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V38" t="n">
         <v>550</v>
@@ -4099,7 +4099,7 @@
         <v>98.2</v>
       </c>
       <c r="U39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V39" t="n">
         <v>300</v>
@@ -4192,7 +4192,7 @@
         <v>59.2</v>
       </c>
       <c r="U40" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="V40" t="n">
         <v>250</v>
@@ -4285,11 +4285,9 @@
         <v>98.2</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
-      </c>
-      <c r="V41" t="n">
-        <v>3876</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4378,10 +4376,10 @@
         <v>47.6</v>
       </c>
       <c r="U42" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="V42" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -4564,7 +4562,7 @@
         <v>98.2</v>
       </c>
       <c r="U44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V44" t="n">
         <v>800</v>
@@ -4657,9 +4655,11 @@
         <v>184.9</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V45" t="n">
+        <v>250</v>
+      </c>
       <c r="W45" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4841,7 +4841,7 @@
         <v>31.8</v>
       </c>
       <c r="U47" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V47" t="n">
         <v>1000</v>
@@ -4934,7 +4934,7 @@
         <v>28.3</v>
       </c>
       <c r="U48" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="V48" t="n">
         <v>250</v>
@@ -5027,7 +5027,7 @@
         <v>139.7</v>
       </c>
       <c r="U49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V49" t="n">
         <v>2000</v>
@@ -5120,10 +5120,10 @@
         <v>28.3</v>
       </c>
       <c r="U50" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V50" t="n">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -5304,10 +5304,10 @@
         <v>28.3</v>
       </c>
       <c r="U52" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="V52" t="n">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>31.8</v>
       </c>
       <c r="U54" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="V54" t="n">
         <v>200</v>
@@ -5583,10 +5583,10 @@
         <v>60.2</v>
       </c>
       <c r="U55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V55" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>3</v>
       </c>
       <c r="V57" t="n">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -5862,10 +5862,10 @@
         <v>139.7</v>
       </c>
       <c r="U58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V58" t="n">
-        <v>1200</v>
+        <v>3500</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -6234,9 +6234,11 @@
         <v>184.9</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V62" t="n">
+        <v>250</v>
+      </c>
       <c r="W62" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6418,7 +6420,7 @@
         <v>213.9</v>
       </c>
       <c r="U64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V64" t="n">
         <v>100</v>
@@ -6514,7 +6516,7 @@
         <v>7</v>
       </c>
       <c r="V65" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -6697,7 +6699,7 @@
         <v>270.6</v>
       </c>
       <c r="U67" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V67" t="n">
         <v>100</v>
@@ -6821,7 +6823,7 @@
         <v>46</v>
       </c>
       <c r="C69" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D69" s="2" t="n">
         <v>41.394942</v>
@@ -7158,9 +7160,11 @@
         <v>270.6</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
-      </c>
-      <c r="V72" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V72" t="n">
+        <v>250</v>
+      </c>
       <c r="W72" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7340,7 +7344,7 @@
         <v>270.6</v>
       </c>
       <c r="U74" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V74" t="n">
         <v>1925</v>
@@ -8169,10 +8173,10 @@
         <v>270.6</v>
       </c>
       <c r="U83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V83" t="n">
-        <v>1200</v>
+        <v>1925</v>
       </c>
       <c r="W83" t="inlineStr">
         <is>
@@ -8197,10 +8201,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C84" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D84" s="2" t="n">
         <v>41.417442</v>
@@ -8448,9 +8452,11 @@
         <v>270.6</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
-      </c>
-      <c r="V86" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V86" t="n">
+        <v>250</v>
+      </c>
       <c r="W86" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -9451,11 +9457,9 @@
         <v>270.6</v>
       </c>
       <c r="U97" t="n">
-        <v>1</v>
-      </c>
-      <c r="V97" t="n">
-        <v>1200</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V97" t="inlineStr"/>
       <c r="W97" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -9661,7 +9665,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C100" t="n">
         <v>75</v>
@@ -10305,7 +10309,7 @@
         <v>53</v>
       </c>
       <c r="C107" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D107" s="2" t="n">
         <v>41.451813</v>
@@ -12585,7 +12589,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C132" t="n">
         <v>44</v>
@@ -14321,7 +14325,7 @@
         <v>24</v>
       </c>
       <c r="C151" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D151" s="2" t="n">
         <v>40.906695</v>
@@ -15050,7 +15054,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C159" t="n">
         <v>44</v>
@@ -16691,7 +16695,7 @@
         <v>41</v>
       </c>
       <c r="C177" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D177" s="2" t="n">
         <v>41.022127</v>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -639,7 +639,7 @@
         <v>15</v>
       </c>
       <c r="N2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O2" t="n">
         <v>21</v>
@@ -660,7 +660,7 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V2" t="n">
         <v>70</v>
@@ -753,10 +753,10 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="V3" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -846,10 +846,10 @@
         <v>141</v>
       </c>
       <c r="U4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V4" t="n">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>7</v>
       </c>
       <c r="N5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O5" t="n">
         <v>16</v>
@@ -939,7 +939,7 @@
         <v>28.3</v>
       </c>
       <c r="U5" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="V5" t="n">
         <v>450</v>
@@ -1066,19 +1066,19 @@
         <v>92</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>41.302375</v>
+        <v>41.204808</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>69.289134</v>
+        <v>69.199336</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>41.302375, 69.289134</t>
+          <t>41.204808, 69.199336</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Айбек</t>
+          <t>Гульшанабад махалля</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1087,30 +1087,30 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>13591</v>
+        <v>8833</v>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="O7" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="P7" t="n">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="Q7" t="n">
         <v>0.5</v>
@@ -1119,16 +1119,16 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>448</v>
+        <v>13000</v>
       </c>
       <c r="T7" t="n">
-        <v>141</v>
+        <v>122.7</v>
       </c>
       <c r="U7" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>918</v>
+        <v>550</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.302375,69.289134</t>
+          <t>https://www.google.com/maps?q=41.204808,69.199336</t>
         </is>
       </c>
     </row>
@@ -1159,19 +1159,19 @@
         <v>92</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>41.204808</v>
+        <v>41.302375</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>69.199336</v>
+        <v>69.289134</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>41.204808, 69.199336</t>
+          <t>41.302375, 69.289134</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Гульшанабад махалля</t>
+          <t>Айбек</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1180,30 +1180,30 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>8833</v>
+        <v>13591</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="O8" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="P8" t="n">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="Q8" t="n">
         <v>0.5</v>
@@ -1212,16 +1212,16 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>13000</v>
+        <v>448</v>
       </c>
       <c r="T8" t="n">
-        <v>122.7</v>
+        <v>141</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="V8" t="n">
-        <v>2100</v>
+        <v>918</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.204808,69.199336</t>
+          <t>https://www.google.com/maps?q=41.302375,69.289134</t>
         </is>
       </c>
     </row>
@@ -1311,10 +1311,10 @@
         <v>122.7</v>
       </c>
       <c r="U9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V9" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>139.7</v>
       </c>
       <c r="U10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="V10" t="n">
         <v>350</v>
@@ -1497,7 +1497,7 @@
         <v>59.2</v>
       </c>
       <c r="U11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V11" t="n">
         <v>450</v>
@@ -1590,7 +1590,7 @@
         <v>139.7</v>
       </c>
       <c r="U12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V12" t="n">
         <v>600</v>
@@ -1683,7 +1683,7 @@
         <v>141</v>
       </c>
       <c r="U13" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="V13" t="n">
         <v>500</v>
@@ -1776,7 +1776,7 @@
         <v>98.2</v>
       </c>
       <c r="U14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V14" t="n">
         <v>500</v>
@@ -1869,10 +1869,10 @@
         <v>98.2</v>
       </c>
       <c r="U15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V15" t="n">
-        <v>1300</v>
+        <v>800</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -1962,10 +1962,10 @@
         <v>98.2</v>
       </c>
       <c r="U16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="V16" t="n">
-        <v>650</v>
+        <v>1000</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>7</v>
       </c>
       <c r="N18" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O18" t="n">
         <v>21</v>
@@ -2148,10 +2148,10 @@
         <v>31.8</v>
       </c>
       <c r="U18" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="V18" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2241,10 +2241,10 @@
         <v>98.2</v>
       </c>
       <c r="U19" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="V19" t="n">
-        <v>918</v>
+        <v>700</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2334,10 +2334,10 @@
         <v>59.2</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V20" t="n">
-        <v>1100</v>
+        <v>200</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2427,10 +2427,10 @@
         <v>141</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V21" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
         <v>48.5</v>
       </c>
       <c r="U22" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V22" t="n">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>139.7</v>
       </c>
       <c r="U23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V23" t="n">
         <v>450</v>
@@ -2706,7 +2706,7 @@
         <v>47.6</v>
       </c>
       <c r="U24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V24" t="n">
         <v>550</v>
@@ -2831,19 +2831,19 @@
         <v>85</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>41.355449</v>
+        <v>41.31798</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>69.286761</v>
+        <v>69.27772899999999</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>41.355449, 69.286761</t>
+          <t>41.317980, 69.277729</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Юнусабад-1</t>
+          <t>Кашгар (Ц-4)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2863,19 +2863,19 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>10097</v>
+        <v>6739</v>
       </c>
       <c r="M26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="O26" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="P26" t="n">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="Q26" t="n">
         <v>0.5</v>
@@ -2890,10 +2890,10 @@
         <v>139.7</v>
       </c>
       <c r="U26" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="V26" t="n">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.355449,69.286761</t>
+          <t>https://www.google.com/maps?q=41.317980,69.277729</t>
         </is>
       </c>
     </row>
@@ -2924,19 +2924,19 @@
         <v>85</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>41.31798</v>
+        <v>41.355449</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>69.27772899999999</v>
+        <v>69.286761</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>41.317980, 69.277729</t>
+          <t>41.355449, 69.286761</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Кашгар (Ц-4)</t>
+          <t>Юнусабад-1</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2956,19 +2956,19 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>6739</v>
+        <v>10097</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="O27" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="P27" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="Q27" t="n">
         <v>0.5</v>
@@ -2983,10 +2983,10 @@
         <v>139.7</v>
       </c>
       <c r="U27" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="V27" t="n">
-        <v>700</v>
+        <v>350</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.317980,69.277729</t>
+          <t>https://www.google.com/maps?q=41.355449,69.286761</t>
         </is>
       </c>
     </row>
@@ -3076,10 +3076,10 @@
         <v>59.2</v>
       </c>
       <c r="U28" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V28" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>139.7</v>
       </c>
       <c r="U29" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="V29" t="n">
         <v>300</v>
@@ -3203,19 +3203,19 @@
         <v>84</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>41.343261</v>
+        <v>41.23913</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>69.29827400000001</v>
+        <v>69.19240499999999</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>41.343261, 69.298274</t>
+          <t>41.239130, 69.192405</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Атчапар-1 махалля</t>
+          <t>Янги Чаштепа</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3224,45 +3224,45 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>8030</v>
+        <v>3046</v>
       </c>
       <c r="M30" t="n">
+        <v>9</v>
+      </c>
+      <c r="N30" t="n">
+        <v>14</v>
+      </c>
+      <c r="O30" t="n">
         <v>7</v>
       </c>
-      <c r="N30" t="n">
-        <v>49</v>
-      </c>
-      <c r="O30" t="n">
-        <v>19</v>
-      </c>
       <c r="P30" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="Q30" t="n">
         <v>0.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T30" t="n">
-        <v>139.7</v>
+        <v>28.3</v>
       </c>
       <c r="U30" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="V30" t="n">
         <v>350</v>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.343261,69.298274</t>
+          <t>https://www.google.com/maps?q=41.239130,69.192405</t>
         </is>
       </c>
     </row>
@@ -3296,19 +3296,19 @@
         <v>84</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>41.23913</v>
+        <v>41.343261</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>69.19240499999999</v>
+        <v>69.29827400000001</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>41.239130, 69.192405</t>
+          <t>41.343261, 69.298274</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Янги Чаштепа</t>
+          <t>Атчапар-1 махалля</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3317,48 +3317,48 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3046</v>
+        <v>8030</v>
       </c>
       <c r="M31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N31" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="O31" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="P31" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="Q31" t="n">
         <v>0.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>28.3</v>
+        <v>139.7</v>
       </c>
       <c r="U31" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="V31" t="n">
-        <v>2000</v>
+        <v>350</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.239130,69.192405</t>
+          <t>https://www.google.com/maps?q=41.343261,69.298274</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
         <v>141</v>
       </c>
       <c r="U32" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="V32" t="n">
         <v>500</v>
@@ -3541,7 +3541,7 @@
         <v>141</v>
       </c>
       <c r="U33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V33" t="n">
         <v>1400</v>
@@ -3725,7 +3725,7 @@
         <v>139.7</v>
       </c>
       <c r="U35" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V35" t="n">
         <v>600</v>
@@ -3818,7 +3818,7 @@
         <v>139.7</v>
       </c>
       <c r="U36" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V36" t="n">
         <v>300</v>
@@ -3911,7 +3911,7 @@
         <v>141</v>
       </c>
       <c r="U37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V37" t="n">
         <v>500</v>
@@ -4004,11 +4004,9 @@
         <v>141</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1800</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4097,7 +4095,7 @@
         <v>141</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
@@ -4188,10 +4186,10 @@
         <v>98.2</v>
       </c>
       <c r="U40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V40" t="n">
-        <v>3876</v>
+        <v>800</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -4260,7 +4258,7 @@
         <v>4</v>
       </c>
       <c r="N41" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O41" t="n">
         <v>4</v>
@@ -4281,10 +4279,10 @@
         <v>28.3</v>
       </c>
       <c r="U41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V41" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -4377,7 +4375,7 @@
         <v>18</v>
       </c>
       <c r="V42" t="n">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -4467,10 +4465,10 @@
         <v>98.2</v>
       </c>
       <c r="U43" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="V43" t="n">
-        <v>1800</v>
+        <v>800</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -4498,7 +4496,7 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>41.286991</v>
@@ -4539,7 +4537,7 @@
         <v>9</v>
       </c>
       <c r="N44" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="O44" t="n">
         <v>21</v>
@@ -4560,7 +4558,7 @@
         <v>47.6</v>
       </c>
       <c r="U44" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V44" t="n">
         <v>70</v>
@@ -4837,9 +4835,11 @@
         <v>139.7</v>
       </c>
       <c r="U47" t="n">
-        <v>1</v>
-      </c>
-      <c r="V47" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="V47" t="n">
+        <v>2000</v>
+      </c>
       <c r="W47" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4928,7 +4928,7 @@
         <v>31.8</v>
       </c>
       <c r="U48" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="V48" t="n">
         <v>500</v>
@@ -5112,10 +5112,10 @@
         <v>28.3</v>
       </c>
       <c r="U50" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="V50" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -5205,10 +5205,10 @@
         <v>59.2</v>
       </c>
       <c r="U51" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V51" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>9</v>
       </c>
       <c r="N53" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O53" t="n">
         <v>18</v>
@@ -5484,10 +5484,10 @@
         <v>48.5</v>
       </c>
       <c r="U54" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V54" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>8</v>
       </c>
       <c r="N55" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O55" t="n">
         <v>17</v>
@@ -5577,7 +5577,7 @@
         <v>28.3</v>
       </c>
       <c r="U55" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="V55" t="n">
         <v>450</v>
@@ -5670,7 +5670,7 @@
         <v>60.2</v>
       </c>
       <c r="U56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V56" t="n">
         <v>1500</v>
@@ -5704,19 +5704,19 @@
         <v>71</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>41.366713</v>
+        <v>41.270832</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>69.23165299999999</v>
+        <v>69.23679199999999</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>41.366713, 69.231653</t>
+          <t>41.270832, 69.236792</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Каракамыш 1/4</t>
+          <t>Дилбулак махалля</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5725,30 +5725,30 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Яккасарайский район</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>5172</v>
+        <v>11138</v>
       </c>
       <c r="M57" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N57" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="O57" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P57" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="Q57" t="n">
         <v>0.5</v>
@@ -5760,13 +5760,13 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>59.2</v>
+        <v>31.8</v>
       </c>
       <c r="U57" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="V57" t="n">
-        <v>499</v>
+        <v>350</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.366713,69.231653</t>
+          <t>https://www.google.com/maps?q=41.270832,69.236792</t>
         </is>
       </c>
     </row>
@@ -5797,19 +5797,19 @@
         <v>71</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>41.270832</v>
+        <v>41.366713</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>69.23679199999999</v>
+        <v>69.23165299999999</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>41.270832, 69.236792</t>
+          <t>41.366713, 69.231653</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Дилбулак махалля</t>
+          <t>Каракамыш 1/4</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5818,30 +5818,30 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Яккасарайский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>11138</v>
+        <v>5172</v>
       </c>
       <c r="M58" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N58" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="O58" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P58" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="Q58" t="n">
         <v>0.5</v>
@@ -5853,10 +5853,10 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>31.8</v>
+        <v>59.2</v>
       </c>
       <c r="U58" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="V58" t="n">
         <v>200</v>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.270832,69.236792</t>
+          <t>https://www.google.com/maps?q=41.366713,69.231653</t>
         </is>
       </c>
     </row>
@@ -5949,7 +5949,7 @@
         <v>139.7</v>
       </c>
       <c r="U59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V59" t="n">
         <v>1200</v>
@@ -6042,10 +6042,10 @@
         <v>60.2</v>
       </c>
       <c r="U60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V60" t="n">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -6135,10 +6135,10 @@
         <v>122.7</v>
       </c>
       <c r="U61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V61" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C63" t="n">
         <v>86</v>
@@ -6321,10 +6321,10 @@
         <v>270.6</v>
       </c>
       <c r="U63" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V63" t="n">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>184.9</v>
       </c>
       <c r="U65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V65" t="n">
         <v>200</v>
@@ -6600,7 +6600,7 @@
         <v>213.9</v>
       </c>
       <c r="U66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V66" t="n">
         <v>100</v>
@@ -7245,7 +7245,7 @@
         <v>270.6</v>
       </c>
       <c r="U73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V73" t="n">
         <v>3500</v>
@@ -7338,7 +7338,7 @@
         <v>270.6</v>
       </c>
       <c r="U74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr">
@@ -7706,7 +7706,7 @@
         <v>213.9</v>
       </c>
       <c r="U78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V78" t="n">
         <v>1000</v>
@@ -7890,10 +7890,10 @@
         <v>213.9</v>
       </c>
       <c r="U80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V80" t="n">
-        <v>1100</v>
+        <v>3000</v>
       </c>
       <c r="W80" t="inlineStr">
         <is>
@@ -10363,10 +10363,10 @@
         <v>40.8</v>
       </c>
       <c r="U107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V107" t="n">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="W107" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C120" t="n">
         <v>86</v>
@@ -11916,9 +11916,11 @@
         <v>37.9</v>
       </c>
       <c r="U124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V124" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V124" t="n">
+        <v>350</v>
+      </c>
       <c r="W124" t="inlineStr">
         <is>
           <t>рекомендуемая</t>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Места под ПВЗ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Места под ПВЗ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Места под ПВЗ'!$A$1:$Y$183</definedName>
@@ -753,10 +753,10 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="V3" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>141</v>
       </c>
       <c r="U4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V4" t="n">
         <v>1400</v>
@@ -939,7 +939,7 @@
         <v>28.3</v>
       </c>
       <c r="U5" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="V5" t="n">
         <v>450</v>
@@ -1032,7 +1032,7 @@
         <v>141</v>
       </c>
       <c r="U6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="V6" t="n">
         <v>918</v>
@@ -1125,7 +1125,7 @@
         <v>122.7</v>
       </c>
       <c r="U7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V7" t="n">
         <v>150</v>
@@ -1311,10 +1311,10 @@
         <v>139.7</v>
       </c>
       <c r="U9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V9" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1404,10 +1404,10 @@
         <v>139.7</v>
       </c>
       <c r="U10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V10" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1497,10 +1497,10 @@
         <v>59.2</v>
       </c>
       <c r="U11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V11" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1776,10 +1776,10 @@
         <v>98.2</v>
       </c>
       <c r="U14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="V14" t="n">
-        <v>1300</v>
+        <v>800</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1869,10 +1869,10 @@
         <v>98.2</v>
       </c>
       <c r="U15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V15" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>31.8</v>
       </c>
       <c r="U16" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="V16" t="n">
         <v>500</v>
@@ -2055,7 +2055,7 @@
         <v>98.2</v>
       </c>
       <c r="U17" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="V17" t="n">
         <v>700</v>
@@ -2148,7 +2148,7 @@
         <v>48.5</v>
       </c>
       <c r="U18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V18" t="n">
         <v>1400</v>
@@ -2244,7 +2244,7 @@
         <v>17</v>
       </c>
       <c r="V19" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>59.2</v>
       </c>
       <c r="U20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V20" t="n">
         <v>200</v>
@@ -2520,7 +2520,7 @@
         <v>47.6</v>
       </c>
       <c r="U22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V22" t="n">
         <v>550</v>
@@ -2704,7 +2704,7 @@
         <v>139.7</v>
       </c>
       <c r="U24" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="V24" t="n">
         <v>700</v>
@@ -2797,7 +2797,7 @@
         <v>139.7</v>
       </c>
       <c r="U25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V25" t="n">
         <v>350</v>
@@ -3076,7 +3076,7 @@
         <v>141</v>
       </c>
       <c r="U28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V28" t="n">
         <v>500</v>
@@ -3169,7 +3169,7 @@
         <v>28.3</v>
       </c>
       <c r="U29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V29" t="n">
         <v>350</v>
@@ -3353,10 +3353,10 @@
         <v>139.7</v>
       </c>
       <c r="U31" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V31" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>139.7</v>
       </c>
       <c r="U32" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V32" t="n">
         <v>300</v>
@@ -3723,9 +3723,11 @@
         <v>98.2</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
-      </c>
-      <c r="V35" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="V35" t="n">
+        <v>800</v>
+      </c>
       <c r="W35" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3814,9 +3816,11 @@
         <v>98.2</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V36" t="n">
+        <v>3876</v>
+      </c>
       <c r="W36" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3908,7 +3912,7 @@
         <v>16</v>
       </c>
       <c r="V37" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -3998,7 +4002,7 @@
         <v>59.2</v>
       </c>
       <c r="U38" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="V38" t="n">
         <v>250</v>
@@ -4091,7 +4095,7 @@
         <v>122.7</v>
       </c>
       <c r="U39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V39" t="n">
         <v>350</v>
@@ -4184,7 +4188,7 @@
         <v>47.6</v>
       </c>
       <c r="U40" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="V40" t="n">
         <v>70</v>
@@ -4461,7 +4465,7 @@
         <v>59.2</v>
       </c>
       <c r="U43" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V43" t="n">
         <v>200</v>
@@ -4554,10 +4558,10 @@
         <v>31.8</v>
       </c>
       <c r="U44" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="V44" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -4647,7 +4651,7 @@
         <v>28.3</v>
       </c>
       <c r="U45" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="V45" t="n">
         <v>250</v>
@@ -4833,7 +4837,7 @@
         <v>139.7</v>
       </c>
       <c r="U47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V47" t="n">
         <v>500</v>
@@ -4926,7 +4930,7 @@
         <v>28.3</v>
       </c>
       <c r="U48" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="V48" t="n">
         <v>350</v>
@@ -5019,10 +5023,10 @@
         <v>47.6</v>
       </c>
       <c r="U49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V49" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -5112,7 +5116,7 @@
         <v>28.3</v>
       </c>
       <c r="U50" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="V50" t="n">
         <v>450</v>
@@ -5205,10 +5209,10 @@
         <v>48.5</v>
       </c>
       <c r="U51" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V51" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -5298,7 +5302,7 @@
         <v>122.7</v>
       </c>
       <c r="U52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V52" t="n">
         <v>150</v>
@@ -5391,7 +5395,7 @@
         <v>31.8</v>
       </c>
       <c r="U53" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="V53" t="n">
         <v>500</v>
@@ -5852,7 +5856,7 @@
         <v>59.2</v>
       </c>
       <c r="U58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V58" t="n">
         <v>499</v>
@@ -5945,7 +5949,7 @@
         <v>122.7</v>
       </c>
       <c r="U59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V59" t="n">
         <v>180</v>
@@ -6041,7 +6045,7 @@
         <v>2</v>
       </c>
       <c r="V60" t="n">
-        <v>2</v>
+        <v>450</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -6222,7 +6226,7 @@
         <v>184.9</v>
       </c>
       <c r="U62" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V62" t="n">
         <v>200</v>
@@ -6315,10 +6319,10 @@
         <v>213.9</v>
       </c>
       <c r="U63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V63" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -6408,10 +6412,10 @@
         <v>270.6</v>
       </c>
       <c r="U64" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V64" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -6501,10 +6505,10 @@
         <v>270.6</v>
       </c>
       <c r="U65" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V65" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -6964,7 +6968,7 @@
         <v>184.9</v>
       </c>
       <c r="U70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr">
@@ -7146,7 +7150,7 @@
         <v>270.6</v>
       </c>
       <c r="U72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V72" t="n">
         <v>3500</v>
@@ -7239,7 +7243,7 @@
         <v>270.6</v>
       </c>
       <c r="U73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V73" t="inlineStr"/>
       <c r="W73" t="inlineStr">
@@ -7789,7 +7793,7 @@
         <v>213.9</v>
       </c>
       <c r="U79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V79" t="n">
         <v>1000</v>
@@ -7978,7 +7982,7 @@
         <v>1</v>
       </c>
       <c r="V81" t="n">
-        <v>1100</v>
+        <v>3000</v>
       </c>
       <c r="W81" t="inlineStr">
         <is>
@@ -8068,9 +8072,11 @@
         <v>270.6</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
-      </c>
-      <c r="V82" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V82" t="n">
+        <v>1200</v>
+      </c>
       <c r="W82" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8344,7 +8350,7 @@
         <v>2</v>
       </c>
       <c r="V85" t="n">
-        <v>1100</v>
+        <v>3000</v>
       </c>
       <c r="W85" t="inlineStr">
         <is>
@@ -8798,7 +8804,7 @@
         <v>184.9</v>
       </c>
       <c r="U90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr">
@@ -8889,11 +8895,9 @@
         <v>213.9</v>
       </c>
       <c r="U91" t="n">
-        <v>1</v>
-      </c>
-      <c r="V91" t="n">
-        <v>1100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V91" t="inlineStr"/>
       <c r="W91" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -9073,7 +9077,7 @@
         <v>184.9</v>
       </c>
       <c r="U93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V93" t="inlineStr"/>
       <c r="W93" t="inlineStr">
@@ -9528,9 +9532,11 @@
         <v>270.6</v>
       </c>
       <c r="U98" t="n">
-        <v>0</v>
-      </c>
-      <c r="V98" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V98" t="n">
+        <v>1200</v>
+      </c>
       <c r="W98" t="inlineStr">
         <is>
           <t>рекомендуемая</t>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Места под ПВЗ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Места под ПВЗ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Места под ПВЗ'!$A$1:$Y$183</definedName>
@@ -598,7 +598,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>41.275234</v>
@@ -636,7 +636,7 @@
         <v>14985</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N2" t="n">
         <v>57</v>
@@ -660,7 +660,7 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V2" t="n">
         <v>70</v>
@@ -729,7 +729,7 @@
         <v>11954</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
         <v>38</v>
@@ -753,10 +753,10 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="V3" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>12156</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
         <v>20</v>
@@ -846,7 +846,7 @@
         <v>141</v>
       </c>
       <c r="U4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V4" t="n">
         <v>1400</v>
@@ -915,7 +915,7 @@
         <v>17457</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N5" t="n">
         <v>48</v>
@@ -939,7 +939,7 @@
         <v>28.3</v>
       </c>
       <c r="U5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="V5" t="n">
         <v>450</v>
@@ -970,7 +970,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>41.302375</v>
@@ -1008,7 +1008,7 @@
         <v>13591</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N6" t="n">
         <v>45</v>
@@ -1032,7 +1032,7 @@
         <v>141</v>
       </c>
       <c r="U6" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="V6" t="n">
         <v>918</v>
@@ -1101,7 +1101,7 @@
         <v>11740</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
         <v>14</v>
@@ -1194,7 +1194,7 @@
         <v>10538</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
         <v>52</v>
@@ -1218,7 +1218,7 @@
         <v>139.7</v>
       </c>
       <c r="U8" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="V8" t="n">
         <v>350</v>
@@ -1287,7 +1287,7 @@
         <v>13166</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N9" t="n">
         <v>28</v>
@@ -1345,19 +1345,19 @@
         <v>90</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>41.367635</v>
+        <v>41.345911</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>69.275244</v>
+        <v>69.246887</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>41.367635, 69.275244</t>
+          <t>41.345911, 69.246887</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Туркистан махалля</t>
+          <t>Карасарай махалля</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1366,30 +1366,30 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>15593</v>
+        <v>14912</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="N10" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="O10" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="P10" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q10" t="n">
         <v>0.5</v>
@@ -1398,16 +1398,16 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>438</v>
+        <v>252</v>
       </c>
       <c r="T10" t="n">
-        <v>139.7</v>
+        <v>59.2</v>
       </c>
       <c r="U10" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="V10" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.367635,69.275244</t>
+          <t>https://www.google.com/maps?q=41.345911,69.246887</t>
         </is>
       </c>
     </row>
@@ -1438,19 +1438,19 @@
         <v>90</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>41.345911</v>
+        <v>41.367635</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>69.246887</v>
+        <v>69.275244</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>41.345911, 69.246887</t>
+          <t>41.367635, 69.275244</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Карасарай махалля</t>
+          <t>Туркистан махалля</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1459,30 +1459,30 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>14912</v>
+        <v>15593</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N11" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="O11" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="P11" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Q11" t="n">
         <v>0.5</v>
@@ -1491,16 +1491,16 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>252</v>
+        <v>438</v>
       </c>
       <c r="T11" t="n">
-        <v>59.2</v>
+        <v>139.7</v>
       </c>
       <c r="U11" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="V11" t="n">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.345911,69.246887</t>
+          <t>https://www.google.com/maps?q=41.367635,69.275244</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
         <v>8891</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N12" t="n">
         <v>34</v>
@@ -1590,7 +1590,7 @@
         <v>141</v>
       </c>
       <c r="U12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="V12" t="n">
         <v>500</v>
@@ -1624,19 +1624,19 @@
         <v>89</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>41.332561</v>
+        <v>41.309964</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>69.321702</v>
+        <v>69.34079800000001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>41.332561, 69.321702</t>
+          <t>41.309964, 69.340798</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Буюк Ипак Йули махалля</t>
+          <t>Авайхан махалля</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1656,37 +1656,37 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4166</v>
+        <v>9976</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N13" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P13" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="Q13" t="n">
         <v>0.5</v>
       </c>
       <c r="R13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>1970</v>
+        <v>500</v>
       </c>
       <c r="T13" t="n">
         <v>98.2</v>
       </c>
       <c r="U13" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="V13" t="n">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.332561,69.321702</t>
+          <t>https://www.google.com/maps?q=41.309964,69.340798</t>
         </is>
       </c>
     </row>
@@ -1714,22 +1714,22 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>41.349362</v>
+        <v>41.332561</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>69.33805099999999</v>
+        <v>69.321702</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>41.349362, 69.338051</t>
+          <t>41.332561, 69.321702</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ялангач (Высоковольтный)</t>
+          <t>Буюк Ипак Йули махалля</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1749,37 +1749,37 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>13228</v>
+        <v>4166</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="O14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P14" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="Q14" t="n">
         <v>0.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S14" t="n">
-        <v>558</v>
+        <v>1970</v>
       </c>
       <c r="T14" t="n">
         <v>98.2</v>
       </c>
       <c r="U14" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="V14" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.349362,69.338051</t>
+          <t>https://www.google.com/maps?q=41.332561,69.321702</t>
         </is>
       </c>
     </row>
@@ -1810,19 +1810,19 @@
         <v>88</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>41.309964</v>
+        <v>41.349362</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>69.34079800000001</v>
+        <v>69.33805099999999</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41.309964, 69.340798</t>
+          <t>41.349362, 69.338051</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Авайхан махалля</t>
+          <t>Ялангач (Высоковольтный)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1842,19 +1842,19 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>9976</v>
+        <v>13228</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N15" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="O15" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="P15" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="Q15" t="n">
         <v>0.5</v>
@@ -1863,16 +1863,16 @@
         <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>500</v>
+        <v>558</v>
       </c>
       <c r="T15" t="n">
         <v>98.2</v>
       </c>
       <c r="U15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V15" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.309964,69.340798</t>
+          <t>https://www.google.com/maps?q=41.349362,69.338051</t>
         </is>
       </c>
     </row>
@@ -1938,10 +1938,10 @@
         <v>7882</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N16" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O16" t="n">
         <v>21</v>
@@ -1962,10 +1962,10 @@
         <v>31.8</v>
       </c>
       <c r="U16" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="V16" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>41.314123</v>
@@ -2031,7 +2031,7 @@
         <v>6403</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
         <v>50</v>
@@ -2055,10 +2055,10 @@
         <v>98.2</v>
       </c>
       <c r="U17" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="V17" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2089,19 +2089,19 @@
         <v>87</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>41.271165</v>
+        <v>41.283946</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>69.311927</v>
+        <v>69.359775</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>41.271165, 69.311927</t>
+          <t>41.283946, 69.359775</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ок Уй махалля</t>
+          <t>Авиасозлар-1</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2110,30 +2110,30 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Мирабадский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>10553</v>
+        <v>13526</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N18" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P18" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Q18" t="n">
         <v>0.5</v>
@@ -2142,16 +2142,16 @@
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>726</v>
+        <v>480</v>
       </c>
       <c r="T18" t="n">
-        <v>48.5</v>
+        <v>141</v>
       </c>
       <c r="U18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V18" t="n">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.271165,69.311927</t>
+          <t>https://www.google.com/maps?q=41.283946,69.359775</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
         <v>4950</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N19" t="n">
         <v>58</v>
@@ -2241,10 +2241,10 @@
         <v>139.7</v>
       </c>
       <c r="U19" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V19" t="n">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2275,19 +2275,19 @@
         <v>86</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>41.365496</v>
+        <v>41.271165</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>69.203898</v>
+        <v>69.311927</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>41.365496, 69.203898</t>
+          <t>41.271165, 69.311927</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Бешкурган-4</t>
+          <t>Ок Уй махалля</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2296,30 +2296,30 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Мирабадский район</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>12971</v>
+        <v>10553</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="O20" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="P20" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="Q20" t="n">
         <v>0.5</v>
@@ -2328,16 +2328,16 @@
         <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>313</v>
+        <v>726</v>
       </c>
       <c r="T20" t="n">
-        <v>59.2</v>
+        <v>48.5</v>
       </c>
       <c r="U20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V20" t="n">
-        <v>200</v>
+        <v>1400</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.365496,69.203898</t>
+          <t>https://www.google.com/maps?q=41.271165,69.311927</t>
         </is>
       </c>
     </row>
@@ -2368,19 +2368,19 @@
         <v>86</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>41.283946</v>
+        <v>41.365496</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>69.359775</v>
+        <v>69.203898</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>41.283946, 69.359775</t>
+          <t>41.365496, 69.203898</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Авиасозлар-1</t>
+          <t>Бешкурган-4</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2389,30 +2389,30 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>13526</v>
+        <v>12971</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
+        <v>28</v>
+      </c>
+      <c r="O21" t="n">
+        <v>11</v>
+      </c>
+      <c r="P21" t="n">
         <v>9</v>
-      </c>
-      <c r="O21" t="n">
-        <v>6</v>
-      </c>
-      <c r="P21" t="n">
-        <v>16</v>
       </c>
       <c r="Q21" t="n">
         <v>0.5</v>
@@ -2421,16 +2421,16 @@
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>480</v>
+        <v>313</v>
       </c>
       <c r="T21" t="n">
-        <v>141</v>
+        <v>59.2</v>
       </c>
       <c r="U21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V21" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.283946,69.359775</t>
+          <t>https://www.google.com/maps?q=41.365496,69.203898</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
         <v>3023</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N22" t="n">
         <v>27</v>
@@ -2520,7 +2520,7 @@
         <v>47.6</v>
       </c>
       <c r="U22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V22" t="n">
         <v>550</v>
@@ -2589,7 +2589,7 @@
         <v>8381</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N23" t="n">
         <v>11</v>
@@ -2680,7 +2680,7 @@
         <v>6739</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
         <v>59</v>
@@ -2704,7 +2704,7 @@
         <v>139.7</v>
       </c>
       <c r="U24" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="V24" t="n">
         <v>700</v>
@@ -2773,7 +2773,7 @@
         <v>10097</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N25" t="n">
         <v>49</v>
@@ -2866,7 +2866,7 @@
         <v>6689</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N26" t="n">
         <v>45</v>
@@ -2959,7 +2959,7 @@
         <v>8030</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N27" t="n">
         <v>49</v>
@@ -2983,7 +2983,7 @@
         <v>139.7</v>
       </c>
       <c r="U27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V27" t="n">
         <v>350</v>
@@ -3052,7 +3052,7 @@
         <v>9024</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N28" t="n">
         <v>24</v>
@@ -3076,10 +3076,10 @@
         <v>141</v>
       </c>
       <c r="U28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V28" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3145,10 +3145,10 @@
         <v>2020</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O29" t="n">
         <v>6</v>
@@ -3238,7 +3238,7 @@
         <v>7413</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N30" t="n">
         <v>23</v>
@@ -3294,19 +3294,19 @@
         <v>80</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>41.382952</v>
+        <v>41.384298</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>69.279659</v>
+        <v>69.29950700000001</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>41.382952, 69.279659</t>
+          <t>41.384298, 69.299507</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Юнусабад-10</t>
+          <t>Орзулар</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3326,16 +3326,16 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>8693</v>
+        <v>9262</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N31" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="O31" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="P31" t="n">
         <v>27</v>
@@ -3353,10 +3353,10 @@
         <v>139.7</v>
       </c>
       <c r="U31" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="V31" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.382952,69.279659</t>
+          <t>https://www.google.com/maps?q=41.384298,69.299507</t>
         </is>
       </c>
     </row>
@@ -3387,19 +3387,19 @@
         <v>80</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>41.384298</v>
+        <v>41.382952</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>69.29950700000001</v>
+        <v>69.279659</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>41.384298, 69.299507</t>
+          <t>41.382952, 69.279659</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Орзулар</t>
+          <t>Юнусабад-10</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3419,16 +3419,16 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>9262</v>
+        <v>8693</v>
       </c>
       <c r="M32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="O32" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P32" t="n">
         <v>27</v>
@@ -3446,10 +3446,10 @@
         <v>139.7</v>
       </c>
       <c r="U32" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="V32" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.384298,69.299507</t>
+          <t>https://www.google.com/maps?q=41.382952,69.279659</t>
         </is>
       </c>
     </row>
@@ -3480,19 +3480,19 @@
         <v>80</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>41.211644</v>
+        <v>41.25868</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>69.19953</v>
+        <v>69.339223</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>41.211644, 69.199530</t>
+          <t>41.258680, 69.339223</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Сергели-9А</t>
+          <t>Аханграбо (Панельный)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3501,30 +3501,30 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>19654</v>
+        <v>8057</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N33" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O33" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P33" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q33" t="n">
         <v>0.5</v>
@@ -3536,14 +3536,12 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>122.7</v>
+        <v>141</v>
       </c>
       <c r="U33" t="n">
-        <v>4</v>
-      </c>
-      <c r="V33" t="n">
-        <v>550</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3556,7 +3554,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.211644,69.199530</t>
+          <t>https://www.google.com/maps?q=41.258680,69.339223</t>
         </is>
       </c>
     </row>
@@ -3573,19 +3571,19 @@
         <v>80</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>41.25868</v>
+        <v>41.211644</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>69.339223</v>
+        <v>69.19953</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>41.258680, 69.339223</t>
+          <t>41.211644, 69.199530</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Аханграбо (Панельный)</t>
+          <t>Сергели-9А</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3594,30 +3592,30 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8057</v>
+        <v>19654</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O34" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P34" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q34" t="n">
         <v>0.5</v>
@@ -3629,12 +3627,14 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>141</v>
+        <v>122.7</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="V34" t="n">
+        <v>550</v>
+      </c>
       <c r="W34" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.258680,69.339223</t>
+          <t>https://www.google.com/maps?q=41.211644,69.199530</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>41.338502</v>
@@ -3699,7 +3699,7 @@
         <v>9666</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N35" t="n">
         <v>29</v>
@@ -3792,7 +3792,7 @@
         <v>13244</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N36" t="n">
         <v>20</v>
@@ -3885,7 +3885,7 @@
         <v>6442</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N37" t="n">
         <v>34</v>
@@ -3909,10 +3909,10 @@
         <v>98.2</v>
       </c>
       <c r="U37" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V37" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>10288</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N38" t="n">
         <v>52</v>
@@ -4002,10 +4002,10 @@
         <v>59.2</v>
       </c>
       <c r="U38" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="V38" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4036,19 +4036,19 @@
         <v>77</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>41.232153</v>
+        <v>41.286991</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>69.20011100000001</v>
+        <v>69.19375700000001</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>41.232153, 69.200111</t>
+          <t>41.286991, 69.193757</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Янги Чаштепа</t>
+          <t>Чиланзар Г 9А</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4057,48 +4057,48 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2145</v>
+        <v>16603</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N39" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="O39" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="P39" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="Q39" t="n">
         <v>0.5</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>314</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>122.7</v>
+        <v>47.6</v>
       </c>
       <c r="U39" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="V39" t="n">
-        <v>350</v>
+        <v>70</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.232153,69.200111</t>
+          <t>https://www.google.com/maps?q=41.286991,69.193757</t>
         </is>
       </c>
     </row>
@@ -4129,19 +4129,19 @@
         <v>77</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>41.286991</v>
+        <v>41.232153</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>69.19375700000001</v>
+        <v>69.20011100000001</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>41.286991, 69.193757</t>
+          <t>41.232153, 69.200111</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Чиланзар Г 9А</t>
+          <t>Янги Чаштепа</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4150,48 +4150,48 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>16603</v>
+        <v>2145</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N40" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="O40" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="P40" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="Q40" t="n">
         <v>0.5</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="T40" t="n">
-        <v>47.6</v>
+        <v>122.7</v>
       </c>
       <c r="U40" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="V40" t="n">
-        <v>70</v>
+        <v>350</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.286991,69.193757</t>
+          <t>https://www.google.com/maps?q=41.232153,69.200111</t>
         </is>
       </c>
     </row>
@@ -4222,51 +4222,51 @@
         <v>75</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>41.401782</v>
+        <v>41.358376</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>69.458556</v>
+        <v>69.219533</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>41.401782, 69.458556</t>
+          <t>41.358376, 69.219533</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Улугбек</t>
+          <t>Каракамыш 2/1</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3473</v>
+        <v>10654</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N41" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="O41" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="P41" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="Q41" t="n">
         <v>0.5</v>
@@ -4278,12 +4278,14 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>213.9</v>
+        <v>59.2</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="V41" t="n">
+        <v>200</v>
+      </c>
       <c r="W41" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4296,7 +4298,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.401782,69.458556</t>
+          <t>https://www.google.com/maps?q=41.358376,69.219533</t>
         </is>
       </c>
     </row>
@@ -4348,7 +4350,7 @@
         <v>2816</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
         <v>15</v>
@@ -4406,51 +4408,51 @@
         <v>75</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>41.358376</v>
+        <v>41.401782</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>69.219533</v>
+        <v>69.458556</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>41.358376, 69.219533</t>
+          <t>41.401782, 69.458556</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Каракамыш 2/1</t>
+          <t>Улугбек</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>10654</v>
+        <v>3473</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="O43" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="P43" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="Q43" t="n">
         <v>0.5</v>
@@ -4462,14 +4464,12 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>59.2</v>
+        <v>213.9</v>
       </c>
       <c r="U43" t="n">
-        <v>13</v>
-      </c>
-      <c r="V43" t="n">
-        <v>200</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.358376,69.219533</t>
+          <t>https://www.google.com/maps?q=41.401782,69.458556</t>
         </is>
       </c>
     </row>
@@ -4534,7 +4534,7 @@
         <v>11879</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N44" t="n">
         <v>48</v>
@@ -4558,10 +4558,10 @@
         <v>31.8</v>
       </c>
       <c r="U44" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="V44" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>12235</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N45" t="n">
         <v>46</v>
@@ -4651,10 +4651,10 @@
         <v>28.3</v>
       </c>
       <c r="U45" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="V45" t="n">
-        <v>250</v>
+        <v>800</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>8230</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N46" t="n">
         <v>28</v>
@@ -4778,51 +4778,51 @@
         <v>73</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>41.390081</v>
+        <v>41.265528</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>69.26402400000001</v>
+        <v>69.149665</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>41.390081, 69.264024</t>
+          <t>41.265528, 69.149665</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Дустамабад</t>
+          <t>Чиланзар-31</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2632</v>
+        <v>10778</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="N47" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="O47" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="Q47" t="n">
         <v>0.5</v>
@@ -4834,13 +4834,13 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>139.7</v>
+        <v>47.6</v>
       </c>
       <c r="U47" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V47" t="n">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.390081,69.264024</t>
+          <t>https://www.google.com/maps?q=41.265528,69.149665</t>
         </is>
       </c>
     </row>
@@ -4906,10 +4906,10 @@
         <v>10663</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N48" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O48" t="n">
         <v>18</v>
@@ -4961,54 +4961,54 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>41.265528</v>
+        <v>41.390081</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>69.149665</v>
+        <v>69.26402400000001</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>41.265528, 69.149665</t>
+          <t>41.390081, 69.264024</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Чиланзар-31</t>
+          <t>Дустамабад</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>10778</v>
+        <v>2632</v>
       </c>
       <c r="M49" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="O49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="P49" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="Q49" t="n">
         <v>0.5</v>
@@ -5020,13 +5020,13 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>47.6</v>
+        <v>139.7</v>
       </c>
       <c r="U49" t="n">
         <v>4</v>
       </c>
       <c r="V49" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.265528,69.149665</t>
+          <t>https://www.google.com/maps?q=41.390081,69.264024</t>
         </is>
       </c>
     </row>
@@ -5057,19 +5057,19 @@
         <v>72</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>41.283152</v>
+        <v>41.254507</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>69.217376</v>
+        <v>69.37862699999999</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>41.283152, 69.217376</t>
+          <t>41.254507, 69.378627</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Чиланзар-4</t>
+          <t>Сувсоз-2 (Водник)</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5078,30 +5078,30 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>8748</v>
+        <v>10644</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N50" t="n">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="O50" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="P50" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="Q50" t="n">
         <v>0.5</v>
@@ -5113,13 +5113,13 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>28.3</v>
+        <v>60.2</v>
       </c>
       <c r="U50" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="V50" t="n">
-        <v>450</v>
+        <v>1500</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.283152,69.217376</t>
+          <t>https://www.google.com/maps?q=41.254507,69.378627</t>
         </is>
       </c>
     </row>
@@ -5150,19 +5150,19 @@
         <v>72</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>41.283644</v>
+        <v>41.283152</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>69.28462</v>
+        <v>69.217376</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>41.283644, 69.284620</t>
+          <t>41.283152, 69.217376</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Сарыкулька</t>
+          <t>Чиланзар-4</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5171,30 +5171,30 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Мирабадский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>5986</v>
+        <v>8748</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N51" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="O51" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="P51" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="Q51" t="n">
         <v>0.5</v>
@@ -5206,13 +5206,13 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>48.5</v>
+        <v>28.3</v>
       </c>
       <c r="U51" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="V51" t="n">
-        <v>2000</v>
+        <v>450</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.283644,69.284620</t>
+          <t>https://www.google.com/maps?q=41.283152,69.217376</t>
         </is>
       </c>
     </row>
@@ -5243,19 +5243,19 @@
         <v>72</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>41.20054</v>
+        <v>41.283644</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>69.246605</v>
+        <v>69.28462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>41.200540, 69.246605</t>
+          <t>41.283644, 69.284620</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Дарьябуйи махалля</t>
+          <t>Сарыкулька</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5264,30 +5264,30 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Мирабадский район</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2723</v>
+        <v>5986</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N52" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="O52" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P52" t="n">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="Q52" t="n">
         <v>0.5</v>
@@ -5299,13 +5299,13 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>122.7</v>
+        <v>48.5</v>
       </c>
       <c r="U52" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="V52" t="n">
-        <v>150</v>
+        <v>1500</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.200540,69.246605</t>
+          <t>https://www.google.com/maps?q=41.283644,69.284620</t>
         </is>
       </c>
     </row>
@@ -5333,22 +5333,22 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>41.270832</v>
+        <v>41.20054</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>69.23679199999999</v>
+        <v>69.246605</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>41.270832, 69.236792</t>
+          <t>41.200540, 69.246605</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Дилбулак махалля</t>
+          <t>Дарьябуйи махалля</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5357,30 +5357,30 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Яккасарайский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>11138</v>
+        <v>2723</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N53" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="O53" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="Q53" t="n">
         <v>0.5</v>
@@ -5392,13 +5392,13 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>31.8</v>
+        <v>122.7</v>
       </c>
       <c r="U53" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="V53" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.270832,69.236792</t>
+          <t>https://www.google.com/maps?q=41.200540,69.246605</t>
         </is>
       </c>
     </row>
@@ -5464,7 +5464,7 @@
         <v>4072</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N54" t="n">
         <v>12</v>
@@ -5520,19 +5520,19 @@
         <v>71</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>41.252288</v>
+        <v>41.270832</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>69.315309</v>
+        <v>69.23679199999999</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>41.252288, 69.315309</t>
+          <t>41.270832, 69.236792</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Билимдан махалля</t>
+          <t>Дилбулак махалля</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5541,30 +5541,30 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Мирабадский район</t>
+          <t>Яккасарайский район</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>9192</v>
+        <v>11138</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N55" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="O55" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P55" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="Q55" t="n">
         <v>0.5</v>
@@ -5576,12 +5576,14 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>48.5</v>
+        <v>31.8</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="V55" t="n">
+        <v>350</v>
+      </c>
       <c r="W55" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5594,7 +5596,7 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.252288,69.315309</t>
+          <t>https://www.google.com/maps?q=41.270832,69.236792</t>
         </is>
       </c>
     </row>
@@ -5608,54 +5610,54 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>41.228062</v>
+        <v>41.252288</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>69.330381</v>
+        <v>69.315309</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>41.228062, 69.330381</t>
+          <t>41.252288, 69.315309</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Бектемир</t>
+          <t>Билимдан махалля</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>район города</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Мирабадский район</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>4317</v>
+        <v>9192</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N56" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P56" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="Q56" t="n">
         <v>0.5</v>
@@ -5667,14 +5669,12 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>60.2</v>
+        <v>48.5</v>
       </c>
       <c r="U56" t="n">
-        <v>2</v>
-      </c>
-      <c r="V56" t="n">
-        <v>90</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.228062,69.330381</t>
+          <t>https://www.google.com/maps?q=41.252288,69.315309</t>
         </is>
       </c>
     </row>
@@ -5704,28 +5704,28 @@
         <v>70</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>41.254507</v>
+        <v>41.228062</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>69.37862699999999</v>
+        <v>69.330381</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>41.254507, 69.378627</t>
+          <t>41.228062, 69.330381</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Сувсоз-2 (Водник)</t>
+          <t>Бектемир</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>район города</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5736,19 +5736,19 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>10644</v>
+        <v>4317</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O57" t="n">
         <v>2</v>
       </c>
       <c r="P57" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="Q57" t="n">
         <v>0.5</v>
@@ -5766,7 +5766,7 @@
         <v>2</v>
       </c>
       <c r="V57" t="n">
-        <v>1500</v>
+        <v>90</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.254507,69.378627</t>
+          <t>https://www.google.com/maps?q=41.228062,69.330381</t>
         </is>
       </c>
     </row>
@@ -5794,22 +5794,22 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>41.378753</v>
+        <v>41.185516</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>69.228041</v>
+        <v>69.226426</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>41.378753, 69.228041</t>
+          <t>41.185516, 69.226426</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ахил махалля</t>
+          <t>Чартак махалля</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5818,30 +5818,30 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3771</v>
+        <v>2980</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N58" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="O58" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q58" t="n">
         <v>0.5</v>
@@ -5853,13 +5853,13 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>59.2</v>
+        <v>122.7</v>
       </c>
       <c r="U58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V58" t="n">
-        <v>499</v>
+        <v>300</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.378753,69.228041</t>
+          <t>https://www.google.com/maps?q=41.185516,69.226426</t>
         </is>
       </c>
     </row>
@@ -5887,22 +5887,22 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>41.185516</v>
+        <v>41.378753</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>69.226426</v>
+        <v>69.228041</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>41.185516, 69.226426</t>
+          <t>41.378753, 69.228041</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Чартак махалля</t>
+          <t>Ахил махалля</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5911,30 +5911,30 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2980</v>
+        <v>3771</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N59" t="n">
+        <v>14</v>
+      </c>
+      <c r="O59" t="n">
+        <v>6</v>
+      </c>
+      <c r="P59" t="n">
         <v>4</v>
-      </c>
-      <c r="O59" t="n">
-        <v>3</v>
-      </c>
-      <c r="P59" t="n">
-        <v>3</v>
       </c>
       <c r="Q59" t="n">
         <v>0.5</v>
@@ -5946,13 +5946,13 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>122.7</v>
+        <v>59.2</v>
       </c>
       <c r="U59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V59" t="n">
-        <v>180</v>
+        <v>499</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.185516,69.226426</t>
+          <t>https://www.google.com/maps?q=41.378753,69.228041</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D60" s="2" t="n">
         <v>41.277832</v>
@@ -6018,7 +6018,7 @@
         <v>1699</v>
       </c>
       <c r="M60" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N60" t="n">
         <v>7</v>
@@ -6042,10 +6042,10 @@
         <v>184.9</v>
       </c>
       <c r="U60" t="n">
+        <v>3</v>
+      </c>
+      <c r="V60" t="n">
         <v>2</v>
-      </c>
-      <c r="V60" t="n">
-        <v>450</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>1782</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N61" t="n">
         <v>8</v>
@@ -6161,7 +6161,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C62" t="n">
         <v>83</v>
@@ -6202,7 +6202,7 @@
         <v>1929</v>
       </c>
       <c r="M62" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N62" t="n">
         <v>18</v>
@@ -6226,7 +6226,7 @@
         <v>184.9</v>
       </c>
       <c r="U62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V62" t="n">
         <v>200</v>
@@ -6257,7 +6257,7 @@
         <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D63" s="2" t="n">
         <v>41.359471</v>
@@ -6295,7 +6295,7 @@
         <v>3879</v>
       </c>
       <c r="M63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N63" t="n">
         <v>18</v>
@@ -6388,7 +6388,7 @@
         <v>1950</v>
       </c>
       <c r="M64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N64" t="n">
         <v>22</v>
@@ -6481,7 +6481,7 @@
         <v>3068</v>
       </c>
       <c r="M65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N65" t="n">
         <v>12</v>
@@ -6505,7 +6505,7 @@
         <v>270.6</v>
       </c>
       <c r="U65" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V65" t="n">
         <v>200</v>
@@ -6533,7 +6533,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C66" t="n">
         <v>72</v>
@@ -6574,7 +6574,7 @@
         <v>1357</v>
       </c>
       <c r="M66" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N66" t="n">
         <v>5</v>
@@ -6667,7 +6667,7 @@
         <v>4778</v>
       </c>
       <c r="M67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N67" t="n">
         <v>11</v>
@@ -6719,10 +6719,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C68" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D68" s="2" t="n">
         <v>41.361522</v>
@@ -6760,7 +6760,7 @@
         <v>1892</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N68" t="n">
         <v>6</v>
@@ -6810,25 +6810,25 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C69" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>41.356066</v>
+        <v>41.296704</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>69.15611800000001</v>
+        <v>69.12679199999999</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>41.356066, 69.156118</t>
+          <t>41.296704, 69.126792</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Чигатай</t>
+          <t>Харакат</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6837,49 +6837,47 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>1</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2418</v>
+        <v>2861</v>
       </c>
       <c r="M69" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="N69" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q69" t="n">
         <v>5</v>
       </c>
       <c r="R69" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S69" t="n">
-        <v>3190</v>
+        <v>6708</v>
       </c>
       <c r="T69" t="n">
-        <v>270.6</v>
+        <v>184.9</v>
       </c>
       <c r="U69" t="n">
         <v>1</v>
       </c>
-      <c r="V69" t="n">
-        <v>250</v>
-      </c>
+      <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6892,7 +6890,7 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.356066,69.156118</t>
+          <t>https://www.google.com/maps?q=41.296704,69.126792</t>
         </is>
       </c>
     </row>
@@ -6909,19 +6907,19 @@
         <v>84</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>41.296704</v>
+        <v>41.356066</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>69.12679199999999</v>
+        <v>69.15611800000001</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>41.296704, 69.126792</t>
+          <t>41.356066, 69.156118</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Харакат</t>
+          <t>Чигатай</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6930,47 +6928,49 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>1</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2861</v>
+        <v>2418</v>
       </c>
       <c r="M70" t="n">
         <v>4</v>
       </c>
       <c r="N70" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="O70" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P70" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
         <v>5</v>
       </c>
       <c r="R70" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S70" t="n">
-        <v>6708</v>
+        <v>3190</v>
       </c>
       <c r="T70" t="n">
-        <v>184.9</v>
+        <v>270.6</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
-      </c>
-      <c r="V70" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V70" t="n">
+        <v>250</v>
+      </c>
       <c r="W70" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.296704,69.126792</t>
+          <t>https://www.google.com/maps?q=41.356066,69.156118</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C71" t="n">
         <v>74</v>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C72" t="n">
         <v>80</v>
@@ -7153,7 +7153,7 @@
         <v>5</v>
       </c>
       <c r="V72" t="n">
-        <v>3500</v>
+        <v>1860</v>
       </c>
       <c r="W72" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C73" t="n">
         <v>76</v>
@@ -7243,7 +7243,7 @@
         <v>270.6</v>
       </c>
       <c r="U73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V73" t="inlineStr"/>
       <c r="W73" t="inlineStr">
@@ -7272,7 +7272,7 @@
         <v>58</v>
       </c>
       <c r="C74" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D74" s="2" t="n">
         <v>41.316805</v>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C75" t="n">
         <v>76</v>
@@ -7451,7 +7451,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C76" t="n">
         <v>81</v>
@@ -7492,7 +7492,7 @@
         <v>2081</v>
       </c>
       <c r="M76" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N76" t="n">
         <v>11</v>
@@ -7544,7 +7544,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C77" t="n">
         <v>78</v>
@@ -7637,7 +7637,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C78" t="n">
         <v>77</v>
@@ -7678,7 +7678,7 @@
         <v>1727</v>
       </c>
       <c r="M78" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N78" t="n">
         <v>7</v>
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C79" t="n">
         <v>75</v>
@@ -7821,7 +7821,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C80" t="n">
         <v>74</v>
@@ -7955,7 +7955,7 @@
         <v>4623</v>
       </c>
       <c r="M81" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N81" t="n">
         <v>11</v>
@@ -7979,10 +7979,10 @@
         <v>213.9</v>
       </c>
       <c r="U81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V81" t="n">
-        <v>3000</v>
+        <v>1100</v>
       </c>
       <c r="W81" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>4</v>
       </c>
       <c r="C82" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D82" s="2" t="n">
         <v>41.403254</v>
@@ -8072,7 +8072,7 @@
         <v>270.6</v>
       </c>
       <c r="U82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V82" t="n">
         <v>1200</v>
@@ -8100,7 +8100,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C83" t="n">
         <v>79</v>
@@ -8191,7 +8191,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C84" t="n">
         <v>77</v>
@@ -8256,9 +8256,11 @@
         <v>270.6</v>
       </c>
       <c r="U84" t="n">
-        <v>0</v>
-      </c>
-      <c r="V84" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V84" t="n">
+        <v>600</v>
+      </c>
       <c r="W84" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8282,10 +8284,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C85" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D85" s="2" t="n">
         <v>41.392035</v>
@@ -8347,10 +8349,10 @@
         <v>213.9</v>
       </c>
       <c r="U85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V85" t="n">
-        <v>3000</v>
+        <v>1100</v>
       </c>
       <c r="W85" t="inlineStr">
         <is>
@@ -8375,7 +8377,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C86" t="n">
         <v>75</v>
@@ -8466,7 +8468,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C87" t="n">
         <v>77</v>
@@ -8557,7 +8559,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C88" t="n">
         <v>74</v>
@@ -8651,7 +8653,7 @@
         <v>48</v>
       </c>
       <c r="C89" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D89" s="2" t="n">
         <v>41.378499</v>
@@ -8739,10 +8741,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C90" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D90" s="2" t="n">
         <v>41.314067</v>
@@ -8804,7 +8806,7 @@
         <v>184.9</v>
       </c>
       <c r="U90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr">
@@ -8830,7 +8832,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C91" t="n">
         <v>72</v>
@@ -8895,9 +8897,11 @@
         <v>213.9</v>
       </c>
       <c r="U91" t="n">
-        <v>0</v>
-      </c>
-      <c r="V91" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V91" t="n">
+        <v>1100</v>
+      </c>
       <c r="W91" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8921,7 +8925,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C92" t="n">
         <v>80</v>
@@ -9012,7 +9016,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C93" t="n">
         <v>74</v>
@@ -9077,7 +9081,7 @@
         <v>184.9</v>
       </c>
       <c r="U93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V93" t="inlineStr"/>
       <c r="W93" t="inlineStr">
@@ -9194,7 +9198,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C95" t="n">
         <v>77</v>
@@ -9285,10 +9289,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C96" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D96" s="2" t="n">
         <v>41.425276</v>
@@ -9376,7 +9380,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C97" t="n">
         <v>79</v>
@@ -9467,7 +9471,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C98" t="n">
         <v>79</v>
@@ -9560,7 +9564,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C99" t="n">
         <v>78</v>
@@ -9651,7 +9655,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C100" t="n">
         <v>85</v>
@@ -9742,7 +9746,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C101" t="n">
         <v>79</v>
@@ -9833,7 +9837,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C102" t="n">
         <v>75</v>
@@ -9924,7 +9928,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C103" t="n">
         <v>77</v>
@@ -9989,11 +9993,9 @@
         <v>184.9</v>
       </c>
       <c r="U103" t="n">
-        <v>1</v>
-      </c>
-      <c r="V103" t="n">
-        <v>600</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V103" t="inlineStr"/>
       <c r="W103" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -10017,7 +10019,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C104" t="n">
         <v>74</v>
@@ -10082,11 +10084,9 @@
         <v>184.9</v>
       </c>
       <c r="U104" t="n">
-        <v>1</v>
-      </c>
-      <c r="V104" t="n">
-        <v>600</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V104" t="inlineStr"/>
       <c r="W104" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -10110,10 +10110,10 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C105" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D105" s="2" t="n">
         <v>41.434386</v>
@@ -10292,7 +10292,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C107" t="n">
         <v>81</v>
@@ -10383,7 +10383,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C108" t="n">
         <v>79</v>
@@ -10474,7 +10474,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C109" t="n">
         <v>81</v>
@@ -10567,25 +10567,25 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="C110" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>41.109247</v>
+        <v>41.115948</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>69.09017900000001</v>
+        <v>69.098242</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>41.109247, 69.090179</t>
+          <t>41.115948, 69.098242</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ниязбаш</t>
+          <t>Тахтакуприк</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -10594,10 +10594,10 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J110" t="n">
-        <v>12.6</v>
+        <v>11.5</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -10605,19 +10605,19 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2626</v>
+        <v>1767</v>
       </c>
       <c r="M110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
         <v>5</v>
@@ -10642,12 +10642,12 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.109247,69.090179</t>
+          <t>https://www.google.com/maps?q=41.115948,69.098242</t>
         </is>
       </c>
     </row>
@@ -10658,10 +10658,10 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C111" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D111" s="2" t="n">
         <v>41.463685</v>
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C112" t="n">
         <v>75</v>
@@ -10840,20 +10840,20 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="C113" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>41.039505</v>
+        <v>41.039806</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>69.35615300000001</v>
+        <v>69.340406</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>41.039505, 69.356153</t>
+          <t>41.039806, 69.340406</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -10867,7 +10867,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J113" t="n">
         <v>13.6</v>
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2818</v>
+        <v>1871</v>
       </c>
       <c r="M113" t="n">
         <v>0</v>
@@ -10905,11 +10905,9 @@
         <v>134.2</v>
       </c>
       <c r="U113" t="n">
-        <v>1</v>
-      </c>
-      <c r="V113" t="n">
-        <v>500</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V113" t="inlineStr"/>
       <c r="W113" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -10922,7 +10920,7 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.039505,69.356153</t>
+          <t>https://www.google.com/maps?q=41.039806,69.340406</t>
         </is>
       </c>
     </row>
@@ -10933,20 +10931,20 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C114" t="n">
         <v>79</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>41.088745</v>
+        <v>41.099129</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>69.089637</v>
+        <v>69.082027</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>41.088745, 69.089637</t>
+          <t>41.099129, 69.082027</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -10960,10 +10958,10 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J114" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -10971,19 +10969,19 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2111</v>
+        <v>2756</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q114" t="n">
         <v>5</v>
@@ -11008,12 +11006,12 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.088745,69.089637</t>
+          <t>https://www.google.com/maps?q=41.099129,69.082027</t>
         </is>
       </c>
     </row>
@@ -11024,7 +11022,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C115" t="n">
         <v>83</v>
@@ -11115,7 +11113,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C116" t="n">
         <v>81</v>
@@ -11206,10 +11204,10 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C117" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D117" s="2" t="n">
         <v>41.13231</v>
@@ -11297,7 +11295,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C118" t="n">
         <v>76</v>
@@ -11388,10 +11386,10 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C119" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D119" s="2" t="n">
         <v>41.091305</v>
@@ -11570,7 +11568,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C121" t="n">
         <v>76</v>
@@ -11635,11 +11633,9 @@
         <v>147.5</v>
       </c>
       <c r="U121" t="n">
-        <v>1</v>
-      </c>
-      <c r="V121" t="n">
-        <v>1600</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V121" t="inlineStr"/>
       <c r="W121" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -11757,7 +11753,7 @@
         <v>33</v>
       </c>
       <c r="C123" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D123" s="2" t="n">
         <v>40.914676</v>
@@ -11848,7 +11844,7 @@
         <v>6</v>
       </c>
       <c r="C124" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D124" s="2" t="n">
         <v>41.613627</v>
@@ -12001,11 +11997,9 @@
         <v>147.5</v>
       </c>
       <c r="U125" t="n">
-        <v>1</v>
-      </c>
-      <c r="V125" t="n">
-        <v>1600</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V125" t="inlineStr"/>
       <c r="W125" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -12393,7 +12387,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C130" t="n">
         <v>47</v>
@@ -12757,7 +12751,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C134" t="n">
         <v>49</v>
@@ -12939,7 +12933,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C136" t="n">
         <v>56</v>
@@ -13030,7 +13024,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C137" t="n">
         <v>52</v>
@@ -13212,7 +13206,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C139" t="n">
         <v>59</v>
@@ -13305,10 +13299,10 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C140" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D140" s="2" t="n">
         <v>40.847834</v>
@@ -13489,10 +13483,10 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C142" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D142" s="2" t="n">
         <v>40.82914</v>
@@ -13580,7 +13574,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C143" t="n">
         <v>52</v>
@@ -13671,7 +13665,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C144" t="n">
         <v>59</v>
@@ -13853,7 +13847,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C146" t="n">
         <v>56</v>
@@ -14100,11 +14094,9 @@
         <v>55.2</v>
       </c>
       <c r="U148" t="n">
-        <v>1</v>
-      </c>
-      <c r="V148" t="n">
-        <v>500</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V148" t="inlineStr"/>
       <c r="W148" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -14583,7 +14575,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C154" t="n">
         <v>49</v>
@@ -14674,10 +14666,10 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C155" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D155" s="2" t="n">
         <v>40.941452</v>
@@ -14768,7 +14760,7 @@
         <v>45</v>
       </c>
       <c r="C156" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D156" s="2" t="n">
         <v>41.622198</v>
@@ -15043,7 +15035,7 @@
         <v>20</v>
       </c>
       <c r="C159" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D159" s="2" t="n">
         <v>40.9246</v>
@@ -15222,7 +15214,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C161" t="n">
         <v>52</v>
@@ -15498,7 +15490,7 @@
         <v>46</v>
       </c>
       <c r="C164" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D164" s="2" t="n">
         <v>41.005644</v>
@@ -15768,7 +15760,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C167" t="n">
         <v>57</v>
@@ -16405,7 +16397,7 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C174" t="n">
         <v>57</v>
@@ -16590,7 +16582,7 @@
         <v>58</v>
       </c>
       <c r="C176" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D176" s="2" t="n">
         <v>40.988777</v>
@@ -16769,7 +16761,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C178" t="n">
         <v>56</v>
@@ -17227,7 +17219,7 @@
         <v>1</v>
       </c>
       <c r="C183" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D183" s="2" t="n">
         <v>40.252947</v>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,7 +660,7 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V2" t="n">
         <v>70</v>
@@ -753,7 +753,7 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="V3" t="n">
         <v>500</v>
@@ -1125,10 +1125,10 @@
         <v>139.7</v>
       </c>
       <c r="U7" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="V7" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1311,10 +1311,10 @@
         <v>122.7</v>
       </c>
       <c r="U9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V9" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>59.2</v>
       </c>
       <c r="U10" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="V10" t="n">
         <v>450</v>
@@ -1590,10 +1590,10 @@
         <v>139.7</v>
       </c>
       <c r="U12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V12" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>141</v>
       </c>
       <c r="U13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V13" t="n">
         <v>500</v>
@@ -1776,7 +1776,7 @@
         <v>98.2</v>
       </c>
       <c r="U14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V14" t="n">
         <v>500</v>
@@ -1810,19 +1810,19 @@
         <v>88</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>41.349362</v>
+        <v>41.284507</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>69.33805099999999</v>
+        <v>69.237188</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41.349362, 69.338051</t>
+          <t>41.284507, 69.237188</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ялангач (Высоковольтный)</t>
+          <t>Ракат махалля</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1831,30 +1831,30 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Яккасарайский район</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>13228</v>
+        <v>7882</v>
       </c>
       <c r="M15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N15" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="O15" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="P15" t="n">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="Q15" t="n">
         <v>0.5</v>
@@ -1863,16 +1863,16 @@
         <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>558</v>
+        <v>312</v>
       </c>
       <c r="T15" t="n">
-        <v>98.2</v>
+        <v>31.8</v>
       </c>
       <c r="U15" t="n">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="V15" t="n">
-        <v>850</v>
+        <v>350</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.349362,69.338051</t>
+          <t>https://www.google.com/maps?q=41.284507,69.237188</t>
         </is>
       </c>
     </row>
@@ -1903,19 +1903,19 @@
         <v>88</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>41.284507</v>
+        <v>41.349362</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>69.237188</v>
+        <v>69.33805099999999</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>41.284507, 69.237188</t>
+          <t>41.349362, 69.338051</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ракат махалля</t>
+          <t>Ялангач (Высоковольтный)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1924,30 +1924,30 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Яккасарайский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>7882</v>
+        <v>13228</v>
       </c>
       <c r="M16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="O16" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="Q16" t="n">
         <v>0.5</v>
@@ -1956,16 +1956,16 @@
         <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>312</v>
+        <v>558</v>
       </c>
       <c r="T16" t="n">
-        <v>31.8</v>
+        <v>98.2</v>
       </c>
       <c r="U16" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="V16" t="n">
-        <v>500</v>
+        <v>850</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.284507,69.237188</t>
+          <t>https://www.google.com/maps?q=41.349362,69.338051</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
         <v>98.2</v>
       </c>
       <c r="U17" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="V17" t="n">
         <v>500</v>
@@ -2241,7 +2241,7 @@
         <v>139.7</v>
       </c>
       <c r="U19" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="V19" t="n">
         <v>450</v>
@@ -2427,7 +2427,7 @@
         <v>141</v>
       </c>
       <c r="U21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
         <v>900</v>
@@ -2520,7 +2520,7 @@
         <v>48.5</v>
       </c>
       <c r="U22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V22" t="n">
         <v>1400</v>
@@ -2706,7 +2706,7 @@
         <v>139.7</v>
       </c>
       <c r="U24" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="V24" t="n">
         <v>700</v>
@@ -2802,7 +2802,7 @@
         <v>21</v>
       </c>
       <c r="V25" t="n">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>98.2</v>
       </c>
       <c r="U27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="V27" t="n">
         <v>500</v>
@@ -3076,7 +3076,7 @@
         <v>59.2</v>
       </c>
       <c r="U28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V28" t="n">
         <v>200</v>
@@ -3172,7 +3172,7 @@
         <v>26</v>
       </c>
       <c r="V29" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>139.7</v>
       </c>
       <c r="U30" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="V30" t="n">
         <v>300</v>
@@ -3293,7 +3293,7 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>41.291531</v>
@@ -3355,10 +3355,10 @@
         <v>141</v>
       </c>
       <c r="U31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V31" t="n">
-        <v>900</v>
+        <v>875</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3448,10 +3448,10 @@
         <v>122.7</v>
       </c>
       <c r="U32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V32" t="n">
-        <v>350</v>
+        <v>1400</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -3725,10 +3725,10 @@
         <v>139.7</v>
       </c>
       <c r="U35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V35" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>139.7</v>
       </c>
       <c r="U36" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V36" t="n">
         <v>300</v>
@@ -3849,7 +3849,7 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>41.277558</v>
@@ -3911,7 +3911,7 @@
         <v>141</v>
       </c>
       <c r="U37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V37" t="n">
         <v>900</v>
@@ -4007,7 +4007,7 @@
         <v>6</v>
       </c>
       <c r="V38" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4097,9 +4097,11 @@
         <v>141</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
-      </c>
-      <c r="V39" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="V39" t="n">
+        <v>10</v>
+      </c>
       <c r="W39" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4281,10 +4283,10 @@
         <v>98.2</v>
       </c>
       <c r="U41" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V41" t="n">
-        <v>3876</v>
+        <v>10</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -4374,7 +4376,7 @@
         <v>47.6</v>
       </c>
       <c r="U42" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="V42" t="n">
         <v>70</v>
@@ -4558,10 +4560,10 @@
         <v>98.2</v>
       </c>
       <c r="U44" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="V44" t="n">
-        <v>850</v>
+        <v>10</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -4651,10 +4653,10 @@
         <v>98.2</v>
       </c>
       <c r="U45" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V45" t="n">
-        <v>650</v>
+        <v>10</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -4744,11 +4746,9 @@
         <v>184.9</v>
       </c>
       <c r="U46" t="n">
-        <v>2</v>
-      </c>
-      <c r="V46" t="n">
-        <v>250</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4837,7 +4837,7 @@
         <v>59.2</v>
       </c>
       <c r="U47" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V47" t="n">
         <v>200</v>
@@ -4868,7 +4868,7 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>41.190855</v>
@@ -4964,19 +4964,19 @@
         <v>74</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>41.360502</v>
+        <v>41.299391</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>69.381956</v>
+        <v>69.26531</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>41.360502, 69.381956</t>
+          <t>41.299391, 69.265310</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Мунавваркары махалля</t>
+          <t>Багсарай махалля</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4985,30 +4985,30 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Яккасарайский район</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>7210</v>
+        <v>11879</v>
       </c>
       <c r="M49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N49" t="n">
+        <v>48</v>
+      </c>
+      <c r="O49" t="n">
         <v>19</v>
       </c>
-      <c r="O49" t="n">
-        <v>9</v>
-      </c>
       <c r="P49" t="n">
-        <v>6</v>
+        <v>102</v>
       </c>
       <c r="Q49" t="n">
         <v>0.5</v>
@@ -5020,13 +5020,13 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>98.2</v>
+        <v>31.8</v>
       </c>
       <c r="U49" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="V49" t="n">
-        <v>3876</v>
+        <v>500</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.360502,69.381956</t>
+          <t>https://www.google.com/maps?q=41.299391,69.265310</t>
         </is>
       </c>
     </row>
@@ -5057,19 +5057,19 @@
         <v>74</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>41.299391</v>
+        <v>41.360502</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>69.26531</v>
+        <v>69.381956</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>41.299391, 69.265310</t>
+          <t>41.360502, 69.381956</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Багсарай махалля</t>
+          <t>Мунавваркары махалля</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5078,30 +5078,30 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Яккасарайский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>11879</v>
+        <v>7210</v>
       </c>
       <c r="M50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="O50" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="P50" t="n">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="Q50" t="n">
         <v>0.5</v>
@@ -5113,13 +5113,13 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>31.8</v>
+        <v>98.2</v>
       </c>
       <c r="U50" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="V50" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.299391,69.265310</t>
+          <t>https://www.google.com/maps?q=41.360502,69.381956</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
         <v>139.7</v>
       </c>
       <c r="U52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V52" t="n">
         <v>500</v>
@@ -5486,7 +5486,7 @@
         <v>28.3</v>
       </c>
       <c r="U54" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V54" t="n">
         <v>350</v>
@@ -5582,7 +5582,7 @@
         <v>6</v>
       </c>
       <c r="V55" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -5858,10 +5858,10 @@
         <v>60.2</v>
       </c>
       <c r="U58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V58" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -5951,10 +5951,10 @@
         <v>31.8</v>
       </c>
       <c r="U59" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="V59" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>139.7</v>
       </c>
       <c r="U60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V60" t="n">
         <v>500</v>
@@ -6137,10 +6137,10 @@
         <v>122.7</v>
       </c>
       <c r="U61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V61" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>184.9</v>
       </c>
       <c r="U62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V62" t="n">
         <v>200</v>
@@ -6323,7 +6323,7 @@
         <v>213.9</v>
       </c>
       <c r="U63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V63" t="n">
         <v>100</v>
@@ -6416,10 +6416,10 @@
         <v>270.6</v>
       </c>
       <c r="U64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V64" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -6509,11 +6509,9 @@
         <v>184.9</v>
       </c>
       <c r="U65" t="n">
-        <v>1</v>
-      </c>
-      <c r="V65" t="n">
-        <v>250</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6695,7 +6693,7 @@
         <v>270.6</v>
       </c>
       <c r="U67" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V67" t="n">
         <v>100</v>
@@ -7364,7 +7362,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C75" t="n">
         <v>71</v>
@@ -7704,11 +7702,9 @@
         <v>270.6</v>
       </c>
       <c r="U78" t="n">
-        <v>1</v>
-      </c>
-      <c r="V78" t="n">
-        <v>250</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7981,7 +7977,7 @@
         <v>213.9</v>
       </c>
       <c r="U81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V81" t="n">
         <v>1000</v>
@@ -8074,10 +8070,10 @@
         <v>213.9</v>
       </c>
       <c r="U82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V82" t="n">
-        <v>1100</v>
+        <v>3000</v>
       </c>
       <c r="W82" t="inlineStr">
         <is>
@@ -8260,11 +8256,9 @@
         <v>270.6</v>
       </c>
       <c r="U84" t="n">
-        <v>1</v>
-      </c>
-      <c r="V84" t="n">
-        <v>600</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8291,7 +8285,7 @@
         <v>33</v>
       </c>
       <c r="C85" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D85" s="2" t="n">
         <v>41.377685</v>
@@ -8899,11 +8893,9 @@
         <v>213.9</v>
       </c>
       <c r="U91" t="n">
-        <v>1</v>
-      </c>
-      <c r="V91" t="n">
-        <v>1100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V91" t="inlineStr"/>
       <c r="W91" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -9657,7 +9649,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C100" t="n">
         <v>75</v>
@@ -10387,7 +10379,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C108" t="n">
         <v>71</v>
@@ -11572,7 +11564,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C121" t="n">
         <v>75</v>
@@ -12213,7 +12205,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C128" t="n">
         <v>57</v>
@@ -13032,7 +13024,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C137" t="n">
         <v>49</v>
@@ -13370,9 +13362,11 @@
         <v>37.9</v>
       </c>
       <c r="U140" t="n">
-        <v>0</v>
-      </c>
-      <c r="V140" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V140" t="n">
+        <v>1800</v>
+      </c>
       <c r="W140" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -13461,9 +13455,11 @@
         <v>37.9</v>
       </c>
       <c r="U141" t="n">
-        <v>0</v>
-      </c>
-      <c r="V141" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V141" t="n">
+        <v>1800</v>
+      </c>
       <c r="W141" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -13487,7 +13483,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C142" t="n">
         <v>49</v>
@@ -13643,9 +13639,11 @@
         <v>37.9</v>
       </c>
       <c r="U143" t="n">
-        <v>0</v>
-      </c>
-      <c r="V143" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V143" t="n">
+        <v>1800</v>
+      </c>
       <c r="W143" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -14763,7 +14761,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C156" t="n">
         <v>61</v>
@@ -16039,10 +16037,10 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C170" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D170" s="2" t="n">
         <v>41.120414</v>
@@ -16315,7 +16313,7 @@
         <v>33</v>
       </c>
       <c r="C173" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D173" s="2" t="n">
         <v>40.976114</v>
@@ -16858,7 +16856,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C179" t="n">
         <v>61</v>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Места под ПВЗ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Места под ПВЗ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Места под ПВЗ'!$A$1:$Y$183</definedName>
@@ -598,7 +598,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>41.275234</v>
@@ -636,7 +636,7 @@
         <v>14985</v>
       </c>
       <c r="M2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>57</v>
@@ -660,7 +660,7 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V2" t="n">
         <v>70</v>
@@ -729,7 +729,7 @@
         <v>10558</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>31</v>
@@ -753,7 +753,7 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="V3" t="n">
         <v>1100</v>
@@ -784,22 +784,22 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>41.298608</v>
+        <v>41.302375</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>69.213863</v>
+        <v>69.289134</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>41.298608, 69.213863</t>
+          <t>41.302375, 69.289134</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Чарх Камалан-3 махалля</t>
+          <t>Айбек</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -808,48 +808,48 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>17457</v>
+        <v>13591</v>
       </c>
       <c r="M4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O4" t="n">
         <v>16</v>
       </c>
       <c r="P4" t="n">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="Q4" t="n">
         <v>0.5</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>781</v>
+        <v>448</v>
       </c>
       <c r="T4" t="n">
-        <v>28.3</v>
+        <v>141</v>
       </c>
       <c r="U4" t="n">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="V4" t="n">
-        <v>500</v>
+        <v>918</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.298608,69.213863</t>
+          <t>https://www.google.com/maps?q=41.302375,69.289134</t>
         </is>
       </c>
     </row>
@@ -880,19 +880,19 @@
         <v>91</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>41.302375</v>
+        <v>41.298608</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>69.289134</v>
+        <v>69.213863</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>41.302375, 69.289134</t>
+          <t>41.298608, 69.213863</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Айбек</t>
+          <t>Чарх Камалан-3 махалля</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -901,48 +901,48 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>13591</v>
+        <v>17457</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O5" t="n">
         <v>16</v>
       </c>
       <c r="P5" t="n">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="Q5" t="n">
         <v>0.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>448</v>
+        <v>781</v>
       </c>
       <c r="T5" t="n">
-        <v>141</v>
+        <v>28.3</v>
       </c>
       <c r="U5" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="V5" t="n">
-        <v>918</v>
+        <v>500</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.302375,69.289134</t>
+          <t>https://www.google.com/maps?q=41.298608,69.213863</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
         <v>12156</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>20</v>
@@ -1063,7 +1063,7 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>41.329729</v>
@@ -1101,7 +1101,7 @@
         <v>10538</v>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>52</v>
@@ -1125,10 +1125,10 @@
         <v>139.7</v>
       </c>
       <c r="U7" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V7" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1159,19 +1159,19 @@
         <v>90</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>41.353226</v>
+        <v>41.204808</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>69.31441100000001</v>
+        <v>69.199336</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>41.353226, 69.314411</t>
+          <t>41.204808, 69.199336</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Атчапар-2 махалля</t>
+          <t>Гульшанабад махалля</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1180,48 +1180,48 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5180</v>
+        <v>8833</v>
       </c>
       <c r="M8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="O8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P8" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="Q8" t="n">
         <v>0.5</v>
       </c>
       <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>13000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>122.7</v>
+      </c>
+      <c r="U8" t="n">
         <v>2</v>
       </c>
-      <c r="S8" t="n">
-        <v>4200</v>
-      </c>
-      <c r="T8" t="n">
-        <v>139.7</v>
-      </c>
-      <c r="U8" t="n">
-        <v>7</v>
-      </c>
       <c r="V8" t="n">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.353226,69.314411</t>
+          <t>https://www.google.com/maps?q=41.204808,69.199336</t>
         </is>
       </c>
     </row>
@@ -1252,19 +1252,19 @@
         <v>90</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>41.204808</v>
+        <v>41.353226</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>69.199336</v>
+        <v>69.31441100000001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>41.204808, 69.199336</t>
+          <t>41.353226, 69.314411</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Гульшанабад махалля</t>
+          <t>Атчапар-2 махалля</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1273,48 +1273,48 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>8833</v>
+        <v>5180</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="O9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="P9" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="Q9" t="n">
         <v>0.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>13000</v>
+        <v>4200</v>
       </c>
       <c r="T9" t="n">
-        <v>122.7</v>
+        <v>139.7</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V9" t="n">
-        <v>1400</v>
+        <v>350</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.204808,69.199336</t>
+          <t>https://www.google.com/maps?q=41.353226,69.314411</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>11740</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>14</v>
@@ -1435,7 +1435,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>41.345911</v>
@@ -1473,7 +1473,7 @@
         <v>14912</v>
       </c>
       <c r="M11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>50</v>
@@ -1566,7 +1566,7 @@
         <v>15593</v>
       </c>
       <c r="M12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>35</v>
@@ -1590,10 +1590,10 @@
         <v>139.7</v>
       </c>
       <c r="U12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V12" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>8891</v>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>34</v>
@@ -1683,7 +1683,7 @@
         <v>141</v>
       </c>
       <c r="U13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="V13" t="n">
         <v>500</v>
@@ -1714,7 +1714,7 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>41.309964</v>
@@ -1752,7 +1752,7 @@
         <v>9976</v>
       </c>
       <c r="M14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>31</v>
@@ -1776,7 +1776,7 @@
         <v>98.2</v>
       </c>
       <c r="U14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V14" t="n">
         <v>500</v>
@@ -1845,10 +1845,10 @@
         <v>7882</v>
       </c>
       <c r="M15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O15" t="n">
         <v>21</v>
@@ -1938,7 +1938,7 @@
         <v>13228</v>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>28</v>
@@ -1962,10 +1962,10 @@
         <v>98.2</v>
       </c>
       <c r="U16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="V16" t="n">
-        <v>850</v>
+        <v>1000</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -1996,19 +1996,19 @@
         <v>86</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>41.335981</v>
+        <v>41.337616</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>69.321806</v>
+        <v>69.32581399999999</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>41.335981, 69.321806</t>
+          <t>41.337616, 69.325814</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Буюк Ипак Йули махалля</t>
+          <t>Буз-1 (Черданцева)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2028,19 +2028,19 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5082</v>
+        <v>5401</v>
       </c>
       <c r="M17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q17" t="n">
         <v>0.5</v>
@@ -2055,7 +2055,7 @@
         <v>98.2</v>
       </c>
       <c r="U17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V17" t="n">
         <v>500</v>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.335981,69.321806</t>
+          <t>https://www.google.com/maps?q=41.337616,69.325814</t>
         </is>
       </c>
     </row>
@@ -2089,19 +2089,19 @@
         <v>86</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>41.365403</v>
+        <v>41.314123</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>69.393992</v>
+        <v>69.301356</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>41.365403, 69.393992</t>
+          <t>41.314123, 69.301356</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ТТЗ-4</t>
+          <t>Ирригатор массив</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2110,30 +2110,30 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>13404</v>
+        <v>6403</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="O18" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="P18" t="n">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="Q18" t="n">
         <v>0.5</v>
@@ -2142,16 +2142,16 @@
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>1200</v>
+        <v>220</v>
       </c>
       <c r="T18" t="n">
-        <v>213.9</v>
+        <v>98.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="V18" t="n">
-        <v>1400</v>
+        <v>500</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.365403,69.393992</t>
+          <t>https://www.google.com/maps?q=41.314123,69.301356</t>
         </is>
       </c>
     </row>
@@ -2182,19 +2182,19 @@
         <v>86</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>41.314123</v>
+        <v>41.365403</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>69.301356</v>
+        <v>69.393992</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>41.314123, 69.301356</t>
+          <t>41.365403, 69.393992</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ирригатор массив</t>
+          <t>ТТЗ-4</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2203,30 +2203,30 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>6403</v>
+        <v>13404</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="O19" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="P19" t="n">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="n">
         <v>0.5</v>
@@ -2235,16 +2235,16 @@
         <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>220</v>
+        <v>1200</v>
       </c>
       <c r="T19" t="n">
-        <v>98.2</v>
+        <v>213.9</v>
       </c>
       <c r="U19" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="V19" t="n">
-        <v>500</v>
+        <v>1400</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.314123,69.301356</t>
+          <t>https://www.google.com/maps?q=41.365403,69.393992</t>
         </is>
       </c>
     </row>
@@ -2275,19 +2275,19 @@
         <v>85</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>41.350681</v>
+        <v>41.355303</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>69.266822</v>
+        <v>69.294676</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>41.350681, 69.266822</t>
+          <t>41.355303, 69.294676</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Джами махалля</t>
+          <t>Юнусабад махалля</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2307,19 +2307,19 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4950</v>
+        <v>5016</v>
       </c>
       <c r="M20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="O20" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="P20" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="Q20" t="n">
         <v>0.5</v>
@@ -2328,16 +2328,16 @@
         <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>126</v>
+        <v>350</v>
       </c>
       <c r="T20" t="n">
         <v>139.7</v>
       </c>
       <c r="U20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V20" t="n">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.350681,69.266822</t>
+          <t>https://www.google.com/maps?q=41.355303,69.294676</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
         <v>12971</v>
       </c>
       <c r="M21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>28</v>
@@ -2427,7 +2427,7 @@
         <v>59.2</v>
       </c>
       <c r="U21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V21" t="n">
         <v>570</v>
@@ -2461,19 +2461,19 @@
         <v>85</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>41.283946</v>
+        <v>41.350681</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>69.359775</v>
+        <v>69.266822</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>41.283946, 69.359775</t>
+          <t>41.350681, 69.266822</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Авиасозлар-1</t>
+          <t>Джами махалля</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2482,30 +2482,30 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>13526</v>
+        <v>4950</v>
       </c>
       <c r="M22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="O22" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="P22" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="Q22" t="n">
         <v>0.5</v>
@@ -2514,16 +2514,16 @@
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>480</v>
+        <v>126</v>
       </c>
       <c r="T22" t="n">
-        <v>141</v>
+        <v>139.7</v>
       </c>
       <c r="U22" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="V22" t="n">
-        <v>900</v>
+        <v>450</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.283946,69.359775</t>
+          <t>https://www.google.com/maps?q=41.350681,69.266822</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
         <v>10553</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>12</v>
@@ -2613,7 +2613,7 @@
         <v>48.5</v>
       </c>
       <c r="U23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V23" t="n">
         <v>1400</v>
@@ -2647,19 +2647,19 @@
         <v>84</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>41.311064</v>
+        <v>41.32587</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>69.186525</v>
+        <v>69.31358299999999</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>41.311064, 69.186525</t>
+          <t>41.325870, 69.313583</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Пахтакор махалля</t>
+          <t>Янги Алмачи махалля</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2668,48 +2668,48 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3023</v>
+        <v>3115</v>
       </c>
       <c r="M24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="O24" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P24" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="Q24" t="n">
         <v>0.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>1735</v>
+        <v>759</v>
       </c>
       <c r="T24" t="n">
-        <v>47.6</v>
+        <v>98.2</v>
       </c>
       <c r="U24" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="V24" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.311064,69.186525</t>
+          <t>https://www.google.com/maps?q=41.325870,69.313583</t>
         </is>
       </c>
     </row>
@@ -2737,22 +2737,22 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>41.31798</v>
+        <v>41.283946</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>69.27772899999999</v>
+        <v>69.359775</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>41.317980, 69.277729</t>
+          <t>41.283946, 69.359775</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Кашгар (Ц-4)</t>
+          <t>Авиасозлар-1</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2761,48 +2761,48 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>6739</v>
+        <v>13526</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="O25" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="P25" t="n">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="Q25" t="n">
         <v>0.5</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="T25" t="n">
-        <v>139.7</v>
+        <v>141</v>
       </c>
       <c r="U25" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="V25" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.317980,69.277729</t>
+          <t>https://www.google.com/maps?q=41.283946,69.359775</t>
         </is>
       </c>
     </row>
@@ -2830,22 +2830,22 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>41.355449</v>
+        <v>41.311064</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>69.286761</v>
+        <v>69.186525</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>41.355449, 69.286761</t>
+          <t>41.311064, 69.186525</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Юнусабад-1</t>
+          <t>Пахтакор махалля</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2854,45 +2854,45 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>10097</v>
+        <v>3023</v>
       </c>
       <c r="M26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="O26" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="P26" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="Q26" t="n">
         <v>0.5</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1777</v>
       </c>
       <c r="T26" t="n">
-        <v>139.7</v>
+        <v>47.6</v>
       </c>
       <c r="U26" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="V26" t="n">
         <v>600</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.355449,69.286761</t>
+          <t>https://www.google.com/maps?q=41.311064,69.186525</t>
         </is>
       </c>
     </row>
@@ -2926,19 +2926,19 @@
         <v>83</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>41.24277</v>
+        <v>41.31798</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>69.36640199999999</v>
+        <v>69.27772899999999</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>41.242770, 69.366402</t>
+          <t>41.317980, 69.277729</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Абай махалля</t>
+          <t>Кашгар (Ц-4)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2947,47 +2947,49 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>8381</v>
+        <v>6739</v>
       </c>
       <c r="M27" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="O27" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="P27" t="n">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="Q27" t="n">
         <v>0.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>828</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>60.2</v>
+        <v>139.7</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="V27" t="n">
+        <v>700</v>
+      </c>
       <c r="W27" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3000,7 +3002,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.242770,69.366402</t>
+          <t>https://www.google.com/maps?q=41.317980,69.277729</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3054,7 @@
         <v>7101</v>
       </c>
       <c r="M28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>15</v>
@@ -3076,7 +3078,7 @@
         <v>122.7</v>
       </c>
       <c r="U28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V28" t="n">
         <v>350</v>
@@ -3107,22 +3109,22 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>41.322155</v>
+        <v>41.296436</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>69.3293</v>
+        <v>69.332471</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>41.322155, 69.329300</t>
+          <t>41.296436, 69.332471</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Алмачи махалля</t>
+          <t>Куксарай махалля</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3131,30 +3133,30 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>8916</v>
+        <v>4067</v>
       </c>
       <c r="M29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="O29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P29" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="Q29" t="n">
         <v>0.5</v>
@@ -3163,13 +3165,13 @@
         <v>1</v>
       </c>
       <c r="S29" t="n">
-        <v>80</v>
+        <v>488</v>
       </c>
       <c r="T29" t="n">
-        <v>98.2</v>
+        <v>141</v>
       </c>
       <c r="U29" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="V29" t="n">
         <v>500</v>
@@ -3186,7 +3188,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.322155,69.329300</t>
+          <t>https://www.google.com/maps?q=41.296436,69.332471</t>
         </is>
       </c>
     </row>
@@ -3203,19 +3205,19 @@
         <v>82</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>41.343199</v>
+        <v>41.370618</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>69.207222</v>
+        <v>69.29909600000001</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>41.343199, 69.207222</t>
+          <t>41.370618, 69.299096</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>массив Ниязова</t>
+          <t>Юнусабад 13-й квартал</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3231,41 +3233,41 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>6689</v>
+        <v>22705</v>
       </c>
       <c r="M30" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="O30" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="P30" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="Q30" t="n">
         <v>0.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>59.2</v>
+        <v>139.7</v>
       </c>
       <c r="U30" t="n">
         <v>16</v>
       </c>
       <c r="V30" t="n">
-        <v>570</v>
+        <v>350</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3279,7 +3281,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.343199,69.207222</t>
+          <t>https://www.google.com/maps?q=41.370618,69.299096</t>
         </is>
       </c>
     </row>
@@ -3296,19 +3298,19 @@
         <v>82</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>41.343261</v>
+        <v>41.24277</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>69.29827400000001</v>
+        <v>69.36640199999999</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>41.343261, 69.298274</t>
+          <t>41.242770, 69.366402</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Атчапар-1 махалля</t>
+          <t>Абай махалля</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3317,49 +3319,47 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>8030</v>
+        <v>8381</v>
       </c>
       <c r="M31" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="O31" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="P31" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="Q31" t="n">
         <v>0.5</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>828</v>
       </c>
       <c r="T31" t="n">
-        <v>139.7</v>
+        <v>60.2</v>
       </c>
       <c r="U31" t="n">
-        <v>29</v>
-      </c>
-      <c r="V31" t="n">
-        <v>500</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.343261,69.298274</t>
+          <t>https://www.google.com/maps?q=41.242770,69.366402</t>
         </is>
       </c>
     </row>
@@ -3389,19 +3389,19 @@
         <v>82</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>41.370618</v>
+        <v>41.343199</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>69.29909600000001</v>
+        <v>69.207222</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>41.370618, 69.299096</t>
+          <t>41.343199, 69.207222</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Юнусабад 13-й квартал</t>
+          <t>массив Ниязова</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3417,41 +3417,41 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>22705</v>
+        <v>6689</v>
       </c>
       <c r="M32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O32" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="P32" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="Q32" t="n">
         <v>0.5</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="T32" t="n">
-        <v>139.7</v>
+        <v>59.2</v>
       </c>
       <c r="U32" t="n">
         <v>17</v>
       </c>
       <c r="V32" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.370618,69.299096</t>
+          <t>https://www.google.com/maps?q=41.343199,69.207222</t>
         </is>
       </c>
     </row>
@@ -3479,22 +3479,22 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>41.291531</v>
+        <v>41.341478</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>69.320454</v>
+        <v>69.302179</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>41.291531, 69.320454</t>
+          <t>41.341478, 69.302179</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ширинабад махалля</t>
+          <t>Атчапар-1 махалля</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3503,48 +3503,48 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5303</v>
+        <v>5652</v>
       </c>
       <c r="M33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="O33" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P33" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="Q33" t="n">
         <v>0.5</v>
       </c>
       <c r="R33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>141</v>
+        <v>139.7</v>
       </c>
       <c r="U33" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="V33" t="n">
-        <v>875</v>
+        <v>350</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.291531,69.320454</t>
+          <t>https://www.google.com/maps?q=41.341478,69.302179</t>
         </is>
       </c>
     </row>
@@ -3575,19 +3575,19 @@
         <v>79</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>41.260613</v>
+        <v>41.318137</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>69.327422</v>
+        <v>69.360837</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>41.260613, 69.327422</t>
+          <t>41.318137, 69.360837</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Бунёдкор махалля</t>
+          <t>Гульзарабад махалля</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3607,28 +3607,28 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3292</v>
+        <v>7413</v>
       </c>
       <c r="M34" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="O34" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P34" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="Q34" t="n">
         <v>0.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>141</v>
@@ -3637,7 +3637,7 @@
         <v>3</v>
       </c>
       <c r="V34" t="n">
-        <v>1400</v>
+        <v>650</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.260613,69.327422</t>
+          <t>https://www.google.com/maps?q=41.318137,69.360837</t>
         </is>
       </c>
     </row>
@@ -3668,19 +3668,19 @@
         <v>79</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>41.318137</v>
+        <v>41.260613</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>69.360837</v>
+        <v>69.327422</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>41.318137, 69.360837</t>
+          <t>41.260613, 69.327422</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Гульзарабад махалля</t>
+          <t>Бунёдкор махалля</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3700,28 +3700,28 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>7413</v>
+        <v>3292</v>
       </c>
       <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>15</v>
+      </c>
+      <c r="O35" t="n">
         <v>5</v>
       </c>
-      <c r="N35" t="n">
-        <v>23</v>
-      </c>
-      <c r="O35" t="n">
-        <v>12</v>
-      </c>
       <c r="P35" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="Q35" t="n">
         <v>0.5</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="T35" t="n">
         <v>141</v>
@@ -3730,7 +3730,7 @@
         <v>3</v>
       </c>
       <c r="V35" t="n">
-        <v>650</v>
+        <v>1400</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.318137,69.360837</t>
+          <t>https://www.google.com/maps?q=41.260613,69.327422</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
         <v>8693</v>
       </c>
       <c r="M36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N36" t="n">
         <v>24</v>
@@ -3823,7 +3823,7 @@
         <v>4</v>
       </c>
       <c r="V36" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -3889,10 +3889,10 @@
         <v>2020</v>
       </c>
       <c r="M37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O37" t="n">
         <v>6</v>
@@ -3913,7 +3913,7 @@
         <v>28.3</v>
       </c>
       <c r="U37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V37" t="n">
         <v>350</v>
@@ -3982,7 +3982,7 @@
         <v>9262</v>
       </c>
       <c r="M38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N38" t="n">
         <v>19</v>
@@ -4009,7 +4009,7 @@
         <v>11</v>
       </c>
       <c r="V38" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>7484</v>
       </c>
       <c r="M39" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>18</v>
@@ -4099,7 +4099,7 @@
         <v>141</v>
       </c>
       <c r="U39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V39" t="n">
         <v>875</v>
@@ -4168,7 +4168,7 @@
         <v>10288</v>
       </c>
       <c r="M40" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>52</v>
@@ -4192,7 +4192,7 @@
         <v>59.2</v>
       </c>
       <c r="U40" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V40" t="n">
         <v>250</v>
@@ -4261,7 +4261,7 @@
         <v>16603</v>
       </c>
       <c r="M41" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>60</v>
@@ -4285,7 +4285,7 @@
         <v>47.6</v>
       </c>
       <c r="U41" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="V41" t="n">
         <v>70</v>
@@ -4354,7 +4354,7 @@
         <v>5737</v>
       </c>
       <c r="M42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>23</v>
@@ -4378,7 +4378,7 @@
         <v>141</v>
       </c>
       <c r="U42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V42" t="n">
         <v>10</v>
@@ -4447,7 +4447,7 @@
         <v>10881</v>
       </c>
       <c r="M43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>23</v>
@@ -4502,22 +4502,22 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>41.250058</v>
+        <v>41.323641</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>69.342911</v>
+        <v>69.341219</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>41.250058, 69.342911</t>
+          <t>41.323641, 69.341219</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Аханграбо (Панельный)</t>
+          <t>Катта Алтынтепа махалля</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4526,30 +4526,30 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4446</v>
+        <v>6442</v>
       </c>
       <c r="M44" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="O44" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="P44" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q44" t="n">
         <v>0.5</v>
@@ -4561,12 +4561,14 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>141</v>
+        <v>98.2</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="V44" t="n">
+        <v>500</v>
+      </c>
       <c r="W44" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4579,7 +4581,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.250058,69.342911</t>
+          <t>https://www.google.com/maps?q=41.323641,69.341219</t>
         </is>
       </c>
     </row>
@@ -4596,19 +4598,19 @@
         <v>75</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>41.343858</v>
+        <v>41.250058</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>69.357677</v>
+        <v>69.342911</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>41.343858, 69.357677</t>
+          <t>41.250058, 69.342911</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Буз-2 (Черданцева)</t>
+          <t>Аханграбо (Панельный)</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4617,30 +4619,30 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>5378</v>
+        <v>4446</v>
       </c>
       <c r="M45" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="O45" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="P45" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q45" t="n">
         <v>0.5</v>
@@ -4652,14 +4654,12 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>98.2</v>
+        <v>141</v>
       </c>
       <c r="U45" t="n">
-        <v>13</v>
-      </c>
-      <c r="V45" t="n">
-        <v>10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.343858,69.357677</t>
+          <t>https://www.google.com/maps?q=41.250058,69.342911</t>
         </is>
       </c>
     </row>
@@ -4689,19 +4689,19 @@
         <v>75</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>41.332115</v>
+        <v>41.343858</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>69.345438</v>
+        <v>69.357677</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>41.332115, 69.345438</t>
+          <t>41.343858, 69.357677</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Академгородок</t>
+          <t>Буз-2 (Черданцева)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4721,19 +4721,19 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>4353</v>
+        <v>5378</v>
       </c>
       <c r="M46" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O46" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P46" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="Q46" t="n">
         <v>0.5</v>
@@ -4748,7 +4748,7 @@
         <v>98.2</v>
       </c>
       <c r="U46" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V46" t="n">
         <v>10</v>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.332115,69.345438</t>
+          <t>https://www.google.com/maps?q=41.343858,69.357677</t>
         </is>
       </c>
     </row>
@@ -4817,7 +4817,7 @@
         <v>11879</v>
       </c>
       <c r="M47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
         <v>48</v>
@@ -4841,7 +4841,7 @@
         <v>31.8</v>
       </c>
       <c r="U47" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="V47" t="n">
         <v>500</v>
@@ -4910,7 +4910,7 @@
         <v>10654</v>
       </c>
       <c r="M48" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
         <v>36</v>
@@ -4934,7 +4934,7 @@
         <v>59.2</v>
       </c>
       <c r="U48" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V48" t="n">
         <v>570</v>
@@ -5003,7 +5003,7 @@
         <v>12235</v>
       </c>
       <c r="M49" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
         <v>46</v>
@@ -5027,7 +5027,7 @@
         <v>28.3</v>
       </c>
       <c r="U49" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V49" t="n">
         <v>250</v>
@@ -5096,7 +5096,7 @@
         <v>2530</v>
       </c>
       <c r="M50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N50" t="n">
         <v>21</v>
@@ -5122,7 +5122,9 @@
       <c r="U50" t="n">
         <v>1</v>
       </c>
-      <c r="V50" t="inlineStr"/>
+      <c r="V50" t="n">
+        <v>250</v>
+      </c>
       <c r="W50" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5149,7 +5151,7 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D51" s="2" t="n">
         <v>41.271397</v>
@@ -5187,10 +5189,10 @@
         <v>10663</v>
       </c>
       <c r="M51" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O51" t="n">
         <v>18</v>
@@ -5211,7 +5213,7 @@
         <v>28.3</v>
       </c>
       <c r="U51" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="V51" t="n">
         <v>350</v>
@@ -5245,19 +5247,19 @@
         <v>72</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>41.265528</v>
+        <v>41.376688</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>69.149665</v>
+        <v>69.24778499999999</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>41.265528, 69.149665</t>
+          <t>41.376688, 69.247785</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Чиланзар-31</t>
+          <t>Ибрагим-Ата махалля</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5266,30 +5268,30 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>10778</v>
+        <v>2816</v>
       </c>
       <c r="M52" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="O52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P52" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="Q52" t="n">
         <v>0.5</v>
@@ -5301,13 +5303,13 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>47.6</v>
+        <v>139.7</v>
       </c>
       <c r="U52" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V52" t="n">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -5321,7 +5323,7 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.265528,69.149665</t>
+          <t>https://www.google.com/maps?q=41.376688,69.247785</t>
         </is>
       </c>
     </row>
@@ -5373,10 +5375,10 @@
         <v>8748</v>
       </c>
       <c r="M53" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O53" t="n">
         <v>17</v>
@@ -5431,19 +5433,19 @@
         <v>72</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>41.376688</v>
+        <v>41.265528</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>69.24778499999999</v>
+        <v>69.149665</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>41.376688, 69.247785</t>
+          <t>41.265528, 69.149665</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ибрагим-Ата махалля</t>
+          <t>Чиланзар-31</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5452,30 +5454,30 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2816</v>
+        <v>10778</v>
       </c>
       <c r="M54" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N54" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="O54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="Q54" t="n">
         <v>0.5</v>
@@ -5487,13 +5489,13 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>139.7</v>
+        <v>47.6</v>
       </c>
       <c r="U54" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="V54" t="n">
-        <v>1120</v>
+        <v>2</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -5507,7 +5509,7 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.376688,69.247785</t>
+          <t>https://www.google.com/maps?q=41.265528,69.149665</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5614,7 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>41.283644</v>
@@ -5650,7 +5652,7 @@
         <v>5986</v>
       </c>
       <c r="M56" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
         <v>33</v>
@@ -5674,7 +5676,7 @@
         <v>48.5</v>
       </c>
       <c r="U56" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V56" t="n">
         <v>1500</v>
@@ -5743,10 +5745,10 @@
         <v>11138</v>
       </c>
       <c r="M57" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O57" t="n">
         <v>12</v>
@@ -5767,7 +5769,7 @@
         <v>31.8</v>
       </c>
       <c r="U57" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="V57" t="n">
         <v>350</v>
@@ -5798,54 +5800,54 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>41.254507</v>
+        <v>41.390081</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>69.37862699999999</v>
+        <v>69.26402400000001</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>41.254507, 69.378627</t>
+          <t>41.390081, 69.264024</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Сувсоз-2 (Водник)</t>
+          <t>Дустамабад</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>10644</v>
+        <v>2632</v>
       </c>
       <c r="M58" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N58" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q58" t="n">
         <v>0.5</v>
@@ -5857,13 +5859,13 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>60.2</v>
+        <v>139.7</v>
       </c>
       <c r="U58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V58" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -5877,7 +5879,7 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.254507,69.378627</t>
+          <t>https://www.google.com/maps?q=41.390081,69.264024</t>
         </is>
       </c>
     </row>
@@ -5894,51 +5896,51 @@
         <v>68</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>41.390081</v>
+        <v>41.254507</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>69.26402400000001</v>
+        <v>69.37862699999999</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>41.390081, 69.264024</t>
+          <t>41.254507, 69.378627</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Дустамабад</t>
+          <t>Сувсоз-2 (Водник)</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2632</v>
+        <v>10644</v>
       </c>
       <c r="M59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q59" t="n">
         <v>0.5</v>
@@ -5950,13 +5952,13 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>139.7</v>
+        <v>60.2</v>
       </c>
       <c r="U59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V59" t="n">
-        <v>1120</v>
+        <v>1500</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -5970,7 +5972,7 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.390081,69.264024</t>
+          <t>https://www.google.com/maps?q=41.254507,69.378627</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6024,7 @@
         <v>6883</v>
       </c>
       <c r="M60" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
         <v>14</v>
@@ -6115,7 +6117,7 @@
         <v>4317</v>
       </c>
       <c r="M61" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
         <v>7</v>
@@ -6142,7 +6144,7 @@
         <v>2</v>
       </c>
       <c r="V61" t="n">
-        <v>90</v>
+        <v>220</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -6167,7 +6169,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C62" t="n">
         <v>85</v>
@@ -6208,7 +6210,7 @@
         <v>4927</v>
       </c>
       <c r="M62" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
         <v>17</v>
@@ -6232,11 +6234,9 @@
         <v>184.9</v>
       </c>
       <c r="U62" t="n">
-        <v>1</v>
-      </c>
-      <c r="V62" t="n">
-        <v>1100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6325,10 +6325,10 @@
         <v>63.5</v>
       </c>
       <c r="U63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V63" t="n">
-        <v>12000</v>
+        <v>300</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>1929</v>
       </c>
       <c r="M64" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N64" t="n">
         <v>18</v>
@@ -6487,7 +6487,7 @@
         <v>3879</v>
       </c>
       <c r="M65" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N65" t="n">
         <v>18</v>
@@ -6502,16 +6502,16 @@
         <v>5</v>
       </c>
       <c r="R65" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="S65" t="n">
-        <v>20455</v>
+        <v>21037</v>
       </c>
       <c r="T65" t="n">
         <v>213.9</v>
       </c>
       <c r="U65" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V65" t="n">
         <v>250</v>
@@ -6580,7 +6580,7 @@
         <v>1950</v>
       </c>
       <c r="M66" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N66" t="n">
         <v>22</v>
@@ -6595,19 +6595,19 @@
         <v>5</v>
       </c>
       <c r="R66" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S66" t="n">
-        <v>19140</v>
+        <v>19490</v>
       </c>
       <c r="T66" t="n">
         <v>270.6</v>
       </c>
       <c r="U66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V66" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>13</v>
       </c>
       <c r="C67" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D67" s="2" t="n">
         <v>41.36099</v>
@@ -6673,7 +6673,7 @@
         <v>2226</v>
       </c>
       <c r="M67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N67" t="n">
         <v>16</v>
@@ -6697,9 +6697,11 @@
         <v>184.9</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
-      </c>
-      <c r="V67" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V67" t="n">
+        <v>250</v>
+      </c>
       <c r="W67" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6726,7 +6728,7 @@
         <v>10</v>
       </c>
       <c r="C68" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D68" s="2" t="n">
         <v>41.370609</v>
@@ -6764,7 +6766,7 @@
         <v>3110</v>
       </c>
       <c r="M68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
         <v>15</v>
@@ -6816,7 +6818,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C69" t="n">
         <v>85</v>
@@ -6857,7 +6859,7 @@
         <v>3499</v>
       </c>
       <c r="M69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N69" t="n">
         <v>15</v>
@@ -6872,19 +6874,19 @@
         <v>5</v>
       </c>
       <c r="R69" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S69" t="n">
-        <v>19360</v>
+        <v>19710</v>
       </c>
       <c r="T69" t="n">
         <v>270.6</v>
       </c>
       <c r="U69" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V69" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
@@ -6909,7 +6911,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C70" t="n">
         <v>69</v>
@@ -6950,7 +6952,7 @@
         <v>1357</v>
       </c>
       <c r="M70" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N70" t="n">
         <v>5</v>
@@ -7043,7 +7045,7 @@
         <v>4778</v>
       </c>
       <c r="M71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N71" t="n">
         <v>11</v>
@@ -7095,10 +7097,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C72" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D72" s="2" t="n">
         <v>41.361522</v>
@@ -7136,7 +7138,7 @@
         <v>1892</v>
       </c>
       <c r="M72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
         <v>6</v>
@@ -7186,10 +7188,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="C73" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D73" s="2" t="n">
         <v>41.324284</v>
@@ -7242,10 +7244,10 @@
         <v>5</v>
       </c>
       <c r="R73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S73" t="n">
-        <v>650</v>
+        <v>1673</v>
       </c>
       <c r="T73" t="n">
         <v>151.7</v>
@@ -7342,7 +7344,7 @@
         <v>270.6</v>
       </c>
       <c r="U74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V74" t="n">
         <v>1860</v>
@@ -7370,7 +7372,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C75" t="n">
         <v>73</v>
@@ -7435,7 +7437,7 @@
         <v>270.6</v>
       </c>
       <c r="U75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr">
@@ -7461,10 +7463,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="C76" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D76" s="2" t="n">
         <v>41.316805</v>
@@ -7517,10 +7519,10 @@
         <v>5</v>
       </c>
       <c r="R76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S76" t="n">
-        <v>350</v>
+        <v>1373</v>
       </c>
       <c r="T76" t="n">
         <v>151.7</v>
@@ -7552,7 +7554,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C77" t="n">
         <v>73</v>
@@ -7643,7 +7645,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C78" t="n">
         <v>74</v>
@@ -7708,9 +7710,11 @@
         <v>184.9</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
-      </c>
-      <c r="V78" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V78" t="n">
+        <v>2600</v>
+      </c>
       <c r="W78" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7734,10 +7738,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C79" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D79" s="2" t="n">
         <v>41.33418</v>
@@ -7775,7 +7779,7 @@
         <v>1727</v>
       </c>
       <c r="M79" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N79" t="n">
         <v>7</v>
@@ -7790,10 +7794,10 @@
         <v>5</v>
       </c>
       <c r="R79" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S79" t="n">
-        <v>6488</v>
+        <v>6530</v>
       </c>
       <c r="T79" t="n">
         <v>184.9</v>
@@ -7825,10 +7829,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C80" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D80" s="2" t="n">
         <v>41.399172</v>
@@ -7918,10 +7922,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C81" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D81" s="2" t="n">
         <v>41.401398</v>
@@ -7983,7 +7987,7 @@
         <v>213.9</v>
       </c>
       <c r="U81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V81" t="n">
         <v>1000</v>
@@ -8052,7 +8056,7 @@
         <v>4623</v>
       </c>
       <c r="M82" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N82" t="n">
         <v>11</v>
@@ -8067,10 +8071,10 @@
         <v>5</v>
       </c>
       <c r="R82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S82" t="n">
-        <v>14355</v>
+        <v>14705</v>
       </c>
       <c r="T82" t="n">
         <v>213.9</v>
@@ -8169,10 +8173,10 @@
         <v>270.6</v>
       </c>
       <c r="U83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V83" t="n">
-        <v>1200</v>
+        <v>1860</v>
       </c>
       <c r="W83" t="inlineStr">
         <is>
@@ -8197,7 +8201,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C84" t="n">
         <v>75</v>
@@ -8383,7 +8387,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C86" t="n">
         <v>69</v>
@@ -8565,7 +8569,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C88" t="n">
         <v>74</v>
@@ -8656,10 +8660,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C89" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D89" s="2" t="n">
         <v>41.378499</v>
@@ -8846,19 +8850,19 @@
         <v>69</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>41.444142</v>
+        <v>41.202356</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>69.479776</v>
+        <v>69.14398</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>41.444142, 69.479776</t>
+          <t>41.202356, 69.143980</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Сасбага</t>
+          <t>Куёшли (Солнечный)</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8867,47 +8871,49 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>3.1</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1883</v>
+        <v>1820</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q91" t="n">
         <v>5</v>
       </c>
       <c r="R91" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S91" t="n">
-        <v>129</v>
+        <v>16256</v>
       </c>
       <c r="T91" t="n">
-        <v>213.9</v>
+        <v>184.9</v>
       </c>
       <c r="U91" t="n">
-        <v>0</v>
-      </c>
-      <c r="V91" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="V91" t="n">
+        <v>3</v>
+      </c>
       <c r="W91" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8915,12 +8921,12 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.444142,69.479776</t>
+          <t>https://www.google.com/maps?q=41.202356,69.143980</t>
         </is>
       </c>
     </row>
@@ -9022,7 +9028,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C93" t="n">
         <v>70</v>
@@ -9204,10 +9210,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C95" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D95" s="2" t="n">
         <v>41.425276</v>
@@ -9295,7 +9301,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C96" t="n">
         <v>76</v>
@@ -9392,19 +9398,19 @@
         <v>76</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>41.404809</v>
+        <v>41.412151</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>69.391277</v>
+        <v>69.177485</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>41.404809, 69.391277</t>
+          <t>41.412151, 69.177485</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Уткир</t>
+          <t>Сагбан</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9420,35 +9426,35 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1919</v>
+        <v>2486</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q97" t="n">
         <v>5</v>
       </c>
       <c r="R97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S97" t="n">
-        <v>1398</v>
+        <v>1519</v>
       </c>
       <c r="T97" t="n">
-        <v>213.9</v>
+        <v>270.6</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
@@ -9461,12 +9467,12 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.404809,69.391277</t>
+          <t>https://www.google.com/maps?q=41.412151,69.177485</t>
         </is>
       </c>
     </row>
@@ -9477,25 +9483,25 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C98" t="n">
         <v>75</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>41.412151</v>
+        <v>41.404809</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>69.177485</v>
+        <v>69.391277</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>41.412151, 69.177485</t>
+          <t>41.404809, 69.391277</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Сагбан</t>
+          <t>Уткир</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -9511,42 +9517,40 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2486</v>
+        <v>1919</v>
       </c>
       <c r="M98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
         <v>5</v>
       </c>
       <c r="R98" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S98" t="n">
-        <v>1519</v>
+        <v>1398</v>
       </c>
       <c r="T98" t="n">
-        <v>270.6</v>
+        <v>213.9</v>
       </c>
       <c r="U98" t="n">
-        <v>1</v>
-      </c>
-      <c r="V98" t="n">
-        <v>1200</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V98" t="inlineStr"/>
       <c r="W98" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -9554,12 +9558,12 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.412151,69.177485</t>
+          <t>https://www.google.com/maps?q=41.404809,69.391277</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9665,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C100" t="n">
         <v>76</v>
@@ -9752,7 +9756,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C101" t="n">
         <v>73</v>
@@ -9843,7 +9847,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C102" t="n">
         <v>74</v>
@@ -9934,7 +9938,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C103" t="n">
         <v>71</v>
@@ -10116,10 +10120,10 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C105" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D105" s="2" t="n">
         <v>41.451813</v>
@@ -10207,7 +10211,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C106" t="n">
         <v>76</v>
@@ -10298,7 +10302,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C107" t="n">
         <v>69</v>
@@ -10389,7 +10393,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C108" t="n">
         <v>69</v>
@@ -10480,7 +10484,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C109" t="n">
         <v>70</v>
@@ -10571,7 +10575,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C110" t="n">
         <v>75</v>
@@ -10662,7 +10666,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C111" t="n">
         <v>77</v>
@@ -10753,7 +10757,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C112" t="n">
         <v>72</v>
@@ -10844,7 +10848,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C113" t="n">
         <v>71</v>
@@ -10935,7 +10939,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C114" t="n">
         <v>77</v>
@@ -11026,7 +11030,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C115" t="n">
         <v>70</v>
@@ -11299,7 +11303,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C118" t="n">
         <v>74</v>
@@ -11390,7 +11394,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C119" t="n">
         <v>85</v>
@@ -11572,10 +11576,10 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C121" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D121" s="2" t="n">
         <v>41.570059</v>
@@ -12122,7 +12126,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C127" t="n">
         <v>66</v>
@@ -12304,7 +12308,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C129" t="n">
         <v>56</v>
@@ -12941,7 +12945,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C136" t="n">
         <v>59</v>
@@ -13578,7 +13582,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C143" t="n">
         <v>59</v>
@@ -13671,7 +13675,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C144" t="n">
         <v>54</v>
@@ -13858,7 +13862,7 @@
         <v>7</v>
       </c>
       <c r="C146" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D146" s="2" t="n">
         <v>40.836137</v>
@@ -14585,7 +14589,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C154" t="n">
         <v>54</v>
@@ -14676,7 +14680,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C155" t="n">
         <v>56</v>
@@ -15497,7 +15501,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C164" t="n">
         <v>59</v>
@@ -16501,7 +16505,7 @@
         <v>28</v>
       </c>
       <c r="C175" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D175" s="2" t="n">
         <v>40.985763</v>
@@ -16953,7 +16957,7 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C180" t="n">
         <v>66</v>
@@ -17229,7 +17233,7 @@
         <v>1</v>
       </c>
       <c r="C183" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D183" s="2" t="n">
         <v>40.252947</v>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -598,7 +598,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>41.275234</v>
@@ -636,7 +636,7 @@
         <v>14985</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N2" t="n">
         <v>57</v>
@@ -729,7 +729,7 @@
         <v>10558</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
         <v>31</v>
@@ -787,19 +787,19 @@
         <v>91</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>41.302375</v>
+        <v>41.298608</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>69.289134</v>
+        <v>69.213863</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>41.302375, 69.289134</t>
+          <t>41.298608, 69.213863</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Айбек</t>
+          <t>Чарх Камалан-3 махалля</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -808,48 +808,48 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>13591</v>
+        <v>17457</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N4" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O4" t="n">
         <v>16</v>
       </c>
       <c r="P4" t="n">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="Q4" t="n">
         <v>0.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>448</v>
+        <v>781</v>
       </c>
       <c r="T4" t="n">
-        <v>141</v>
+        <v>28.3</v>
       </c>
       <c r="U4" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="V4" t="n">
-        <v>918</v>
+        <v>500</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.302375,69.289134</t>
+          <t>https://www.google.com/maps?q=41.298608,69.213863</t>
         </is>
       </c>
     </row>
@@ -880,19 +880,19 @@
         <v>91</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>41.298608</v>
+        <v>41.302375</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>69.213863</v>
+        <v>69.289134</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>41.298608, 69.213863</t>
+          <t>41.302375, 69.289134</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Чарх Камалан-3 махалля</t>
+          <t>Айбек</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -901,48 +901,48 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>17457</v>
+        <v>13591</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O5" t="n">
         <v>16</v>
       </c>
       <c r="P5" t="n">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="Q5" t="n">
         <v>0.5</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>781</v>
+        <v>448</v>
       </c>
       <c r="T5" t="n">
-        <v>28.3</v>
+        <v>141</v>
       </c>
       <c r="U5" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="V5" t="n">
-        <v>500</v>
+        <v>918</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.298608,69.213863</t>
+          <t>https://www.google.com/maps?q=41.302375,69.289134</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
         <v>12156</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
         <v>20</v>
@@ -1063,7 +1063,7 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>41.329729</v>
@@ -1101,7 +1101,7 @@
         <v>10538</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
         <v>52</v>
@@ -1159,19 +1159,19 @@
         <v>90</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>41.204808</v>
+        <v>41.353226</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>69.199336</v>
+        <v>69.31441100000001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>41.204808, 69.199336</t>
+          <t>41.353226, 69.314411</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Гульшанабад махалля</t>
+          <t>Атчапар-2 махалля</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1180,48 +1180,48 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>8833</v>
+        <v>5180</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N8" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="O8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="P8" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="Q8" t="n">
         <v>0.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>13000</v>
+        <v>4200</v>
       </c>
       <c r="T8" t="n">
-        <v>122.7</v>
+        <v>139.7</v>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V8" t="n">
-        <v>1400</v>
+        <v>350</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.204808,69.199336</t>
+          <t>https://www.google.com/maps?q=41.353226,69.314411</t>
         </is>
       </c>
     </row>
@@ -1252,19 +1252,19 @@
         <v>90</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>41.353226</v>
+        <v>41.204808</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>69.31441100000001</v>
+        <v>69.199336</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>41.353226, 69.314411</t>
+          <t>41.204808, 69.199336</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Атчапар-2 махалля</t>
+          <t>Гульшанабад махалля</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1273,48 +1273,48 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5180</v>
+        <v>8833</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="O9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P9" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="Q9" t="n">
         <v>0.5</v>
       </c>
       <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>13000</v>
+      </c>
+      <c r="T9" t="n">
+        <v>122.7</v>
+      </c>
+      <c r="U9" t="n">
         <v>2</v>
       </c>
-      <c r="S9" t="n">
-        <v>4200</v>
-      </c>
-      <c r="T9" t="n">
-        <v>139.7</v>
-      </c>
-      <c r="U9" t="n">
-        <v>9</v>
-      </c>
       <c r="V9" t="n">
-        <v>350</v>
+        <v>1400</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.353226,69.314411</t>
+          <t>https://www.google.com/maps?q=41.204808,69.199336</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>11740</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
         <v>14</v>
@@ -1473,7 +1473,7 @@
         <v>14912</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N11" t="n">
         <v>50</v>
@@ -1566,7 +1566,7 @@
         <v>15593</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N12" t="n">
         <v>35</v>
@@ -1659,7 +1659,7 @@
         <v>8891</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N13" t="n">
         <v>34</v>
@@ -1714,7 +1714,7 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>41.309964</v>
@@ -1752,7 +1752,7 @@
         <v>9976</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N14" t="n">
         <v>31</v>
@@ -1845,10 +1845,10 @@
         <v>7882</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N15" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O15" t="n">
         <v>21</v>
@@ -1938,7 +1938,7 @@
         <v>13228</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N16" t="n">
         <v>28</v>
@@ -1996,19 +1996,19 @@
         <v>86</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>41.337616</v>
+        <v>41.335981</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>69.32581399999999</v>
+        <v>69.321806</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>41.337616, 69.325814</t>
+          <t>41.335981, 69.321806</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Буз-1 (Черданцева)</t>
+          <t>Буюк Ипак Йули махалля</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2028,19 +2028,19 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5401</v>
+        <v>5082</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N17" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q17" t="n">
         <v>0.5</v>
@@ -2055,7 +2055,7 @@
         <v>98.2</v>
       </c>
       <c r="U17" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V17" t="n">
         <v>500</v>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.337616,69.325814</t>
+          <t>https://www.google.com/maps?q=41.335981,69.321806</t>
         </is>
       </c>
     </row>
@@ -2089,19 +2089,19 @@
         <v>86</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>41.314123</v>
+        <v>41.365403</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>69.301356</v>
+        <v>69.393992</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>41.314123, 69.301356</t>
+          <t>41.365403, 69.393992</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ирригатор массив</t>
+          <t>ТТЗ-4</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2110,30 +2110,30 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6403</v>
+        <v>13404</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="O18" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="P18" t="n">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="Q18" t="n">
         <v>0.5</v>
@@ -2142,16 +2142,16 @@
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>220</v>
+        <v>1200</v>
       </c>
       <c r="T18" t="n">
-        <v>98.2</v>
+        <v>213.9</v>
       </c>
       <c r="U18" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="V18" t="n">
-        <v>500</v>
+        <v>1400</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.314123,69.301356</t>
+          <t>https://www.google.com/maps?q=41.365403,69.393992</t>
         </is>
       </c>
     </row>
@@ -2182,19 +2182,19 @@
         <v>86</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>41.365403</v>
+        <v>41.314123</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>69.393992</v>
+        <v>69.301356</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>41.365403, 69.393992</t>
+          <t>41.314123, 69.301356</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ТТЗ-4</t>
+          <t>Ирригатор массив</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2203,30 +2203,30 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>13404</v>
+        <v>6403</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="O19" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="P19" t="n">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="Q19" t="n">
         <v>0.5</v>
@@ -2235,16 +2235,16 @@
         <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>1200</v>
+        <v>220</v>
       </c>
       <c r="T19" t="n">
-        <v>213.9</v>
+        <v>98.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="V19" t="n">
-        <v>1400</v>
+        <v>500</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.365403,69.393992</t>
+          <t>https://www.google.com/maps?q=41.314123,69.301356</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
         <v>5016</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
         <v>49</v>
@@ -2368,19 +2368,19 @@
         <v>85</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>41.365496</v>
+        <v>41.350681</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>69.203898</v>
+        <v>69.266822</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>41.365496, 69.203898</t>
+          <t>41.350681, 69.266822</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Бешкурган-4</t>
+          <t>Джами махалля</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2389,30 +2389,30 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>12971</v>
+        <v>4950</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N21" t="n">
+        <v>58</v>
+      </c>
+      <c r="O21" t="n">
         <v>28</v>
       </c>
-      <c r="O21" t="n">
-        <v>11</v>
-      </c>
       <c r="P21" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="Q21" t="n">
         <v>0.5</v>
@@ -2421,16 +2421,16 @@
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>313</v>
+        <v>126</v>
       </c>
       <c r="T21" t="n">
-        <v>59.2</v>
+        <v>139.7</v>
       </c>
       <c r="U21" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="V21" t="n">
-        <v>570</v>
+        <v>450</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.365496,69.203898</t>
+          <t>https://www.google.com/maps?q=41.350681,69.266822</t>
         </is>
       </c>
     </row>
@@ -2461,19 +2461,19 @@
         <v>85</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>41.350681</v>
+        <v>41.365496</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>69.266822</v>
+        <v>69.203898</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>41.350681, 69.266822</t>
+          <t>41.365496, 69.203898</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Джами махалля</t>
+          <t>Бешкурган-4</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2482,30 +2482,30 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4950</v>
+        <v>12971</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="O22" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="P22" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="Q22" t="n">
         <v>0.5</v>
@@ -2514,16 +2514,16 @@
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>126</v>
+        <v>313</v>
       </c>
       <c r="T22" t="n">
-        <v>139.7</v>
+        <v>59.2</v>
       </c>
       <c r="U22" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="V22" t="n">
-        <v>450</v>
+        <v>570</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.350681,69.266822</t>
+          <t>https://www.google.com/maps?q=41.365496,69.203898</t>
         </is>
       </c>
     </row>
@@ -2554,19 +2554,19 @@
         <v>84</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>41.271165</v>
+        <v>41.283946</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>69.311927</v>
+        <v>69.359775</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>41.271165, 69.311927</t>
+          <t>41.283946, 69.359775</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ок Уй махалля</t>
+          <t>Авиасозлар-1</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2575,30 +2575,30 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Мирабадский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>10553</v>
+        <v>13526</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N23" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P23" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Q23" t="n">
         <v>0.5</v>
@@ -2607,16 +2607,16 @@
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>726</v>
+        <v>480</v>
       </c>
       <c r="T23" t="n">
-        <v>48.5</v>
+        <v>141</v>
       </c>
       <c r="U23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V23" t="n">
-        <v>1400</v>
+        <v>900</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.271165,69.311927</t>
+          <t>https://www.google.com/maps?q=41.283946,69.359775</t>
         </is>
       </c>
     </row>
@@ -2647,19 +2647,19 @@
         <v>84</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>41.32587</v>
+        <v>41.271165</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>69.31358299999999</v>
+        <v>69.311927</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>41.325870, 69.313583</t>
+          <t>41.271165, 69.311927</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Янги Алмачи махалля</t>
+          <t>Ок Уй махалля</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2668,48 +2668,48 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Мирабадский район</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3115</v>
+        <v>10553</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="O24" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="P24" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="Q24" t="n">
         <v>0.5</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>759</v>
+        <v>726</v>
       </c>
       <c r="T24" t="n">
-        <v>98.2</v>
+        <v>48.5</v>
       </c>
       <c r="U24" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="V24" t="n">
-        <v>500</v>
+        <v>1400</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.325870,69.313583</t>
+          <t>https://www.google.com/maps?q=41.271165,69.311927</t>
         </is>
       </c>
     </row>
@@ -2740,19 +2740,19 @@
         <v>84</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>41.283946</v>
+        <v>41.311064</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>69.359775</v>
+        <v>69.186525</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>41.283946, 69.359775</t>
+          <t>41.311064, 69.186525</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Авиасозлар-1</t>
+          <t>Пахтакор махалля</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2768,41 +2768,41 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>13526</v>
+        <v>3023</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N25" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="O25" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="P25" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q25" t="n">
         <v>0.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
-        <v>480</v>
+        <v>1777</v>
       </c>
       <c r="T25" t="n">
-        <v>141</v>
+        <v>47.6</v>
       </c>
       <c r="U25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V25" t="n">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.283946,69.359775</t>
+          <t>https://www.google.com/maps?q=41.311064,69.186525</t>
         </is>
       </c>
     </row>
@@ -2830,22 +2830,22 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>41.311064</v>
+        <v>41.31798</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>69.186525</v>
+        <v>69.27772899999999</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>41.311064, 69.186525</t>
+          <t>41.317980, 69.277729</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Пахтакор махалля</t>
+          <t>Кашгар (Ц-4)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2854,48 +2854,48 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3023</v>
+        <v>6739</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="O26" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="P26" t="n">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="Q26" t="n">
         <v>0.5</v>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1777</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>47.6</v>
+        <v>139.7</v>
       </c>
       <c r="U26" t="n">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="V26" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.311064,69.186525</t>
+          <t>https://www.google.com/maps?q=41.317980,69.277729</t>
         </is>
       </c>
     </row>
@@ -2926,19 +2926,19 @@
         <v>83</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>41.31798</v>
+        <v>41.24277</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>69.27772899999999</v>
+        <v>69.36640199999999</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>41.317980, 69.277729</t>
+          <t>41.242770, 69.366402</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Кашгар (Ц-4)</t>
+          <t>Абай махалля</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2947,49 +2947,47 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>6739</v>
+        <v>8381</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N27" t="n">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="O27" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="P27" t="n">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="Q27" t="n">
         <v>0.5</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>828</v>
       </c>
       <c r="T27" t="n">
-        <v>139.7</v>
+        <v>60.2</v>
       </c>
       <c r="U27" t="n">
-        <v>58</v>
-      </c>
-      <c r="V27" t="n">
-        <v>700</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3002,7 +3000,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.317980,69.277729</t>
+          <t>https://www.google.com/maps?q=41.242770,69.366402</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3052,7 @@
         <v>7101</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N28" t="n">
         <v>15</v>
@@ -3112,19 +3110,19 @@
         <v>82</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>41.296436</v>
+        <v>41.322155</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>69.332471</v>
+        <v>69.3293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>41.296436, 69.332471</t>
+          <t>41.322155, 69.329300</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Куксарай махалля</t>
+          <t>Алмачи махалля</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3133,30 +3131,30 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4067</v>
+        <v>8916</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N29" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="O29" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P29" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="Q29" t="n">
         <v>0.5</v>
@@ -3165,13 +3163,13 @@
         <v>1</v>
       </c>
       <c r="S29" t="n">
-        <v>488</v>
+        <v>80</v>
       </c>
       <c r="T29" t="n">
-        <v>141</v>
+        <v>98.2</v>
       </c>
       <c r="U29" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="V29" t="n">
         <v>500</v>
@@ -3188,7 +3186,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.296436,69.332471</t>
+          <t>https://www.google.com/maps?q=41.322155,69.329300</t>
         </is>
       </c>
     </row>
@@ -3205,19 +3203,19 @@
         <v>82</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>41.370618</v>
+        <v>41.296436</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>69.29909600000001</v>
+        <v>69.332471</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>41.370618, 69.299096</t>
+          <t>41.296436, 69.332471</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Юнусабад 13-й квартал</t>
+          <t>Куксарай махалля</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3226,48 +3224,48 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>22705</v>
+        <v>4067</v>
       </c>
       <c r="M30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N30" t="n">
+        <v>25</v>
+      </c>
+      <c r="O30" t="n">
+        <v>14</v>
+      </c>
+      <c r="P30" t="n">
         <v>33</v>
-      </c>
-      <c r="O30" t="n">
-        <v>13</v>
-      </c>
-      <c r="P30" t="n">
-        <v>31</v>
       </c>
       <c r="Q30" t="n">
         <v>0.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>488</v>
       </c>
       <c r="T30" t="n">
-        <v>139.7</v>
+        <v>141</v>
       </c>
       <c r="U30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V30" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3281,7 +3279,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.370618,69.299096</t>
+          <t>https://www.google.com/maps?q=41.296436,69.332471</t>
         </is>
       </c>
     </row>
@@ -3298,19 +3296,19 @@
         <v>82</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>41.24277</v>
+        <v>41.343199</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>69.36640199999999</v>
+        <v>69.207222</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>41.242770, 69.366402</t>
+          <t>41.343199, 69.207222</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Абай махалля</t>
+          <t>массив Ниязова</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3319,30 +3317,30 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>8381</v>
+        <v>6689</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N31" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="O31" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="P31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Q31" t="n">
         <v>0.5</v>
@@ -3351,15 +3349,17 @@
         <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>828</v>
+        <v>96</v>
       </c>
       <c r="T31" t="n">
-        <v>60.2</v>
+        <v>59.2</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="V31" t="n">
+        <v>500</v>
+      </c>
       <c r="W31" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.242770,69.366402</t>
+          <t>https://www.google.com/maps?q=41.343199,69.207222</t>
         </is>
       </c>
     </row>
@@ -3389,19 +3389,19 @@
         <v>82</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>41.343199</v>
+        <v>41.370618</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>69.207222</v>
+        <v>69.29909600000001</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>41.343199, 69.207222</t>
+          <t>41.370618, 69.299096</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>массив Ниязова</t>
+          <t>Юнусабад 13-й квартал</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3417,41 +3417,41 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>6689</v>
+        <v>22705</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N32" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="O32" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="P32" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="Q32" t="n">
         <v>0.5</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>59.2</v>
+        <v>139.7</v>
       </c>
       <c r="U32" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V32" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.343199,69.207222</t>
+          <t>https://www.google.com/maps?q=41.370618,69.299096</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
         <v>5652</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N33" t="n">
         <v>49</v>
@@ -3575,19 +3575,19 @@
         <v>79</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>41.318137</v>
+        <v>41.260613</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>69.360837</v>
+        <v>69.327422</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>41.318137, 69.360837</t>
+          <t>41.260613, 69.327422</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Гульзарабад махалля</t>
+          <t>Бунёдкор махалля</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3607,28 +3607,28 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>7413</v>
+        <v>3292</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N34" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="O34" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="P34" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="Q34" t="n">
         <v>0.5</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="T34" t="n">
         <v>141</v>
@@ -3637,7 +3637,7 @@
         <v>3</v>
       </c>
       <c r="V34" t="n">
-        <v>650</v>
+        <v>1400</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.318137,69.360837</t>
+          <t>https://www.google.com/maps?q=41.260613,69.327422</t>
         </is>
       </c>
     </row>
@@ -3668,19 +3668,19 @@
         <v>79</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>41.260613</v>
+        <v>41.318137</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>69.327422</v>
+        <v>69.360837</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>41.260613, 69.327422</t>
+          <t>41.318137, 69.360837</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Бунёдкор махалля</t>
+          <t>Гульзарабад махалля</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3700,28 +3700,28 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3292</v>
+        <v>7413</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N35" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="O35" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P35" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="Q35" t="n">
         <v>0.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>141</v>
@@ -3730,7 +3730,7 @@
         <v>3</v>
       </c>
       <c r="V35" t="n">
-        <v>1400</v>
+        <v>650</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.260613,69.327422</t>
+          <t>https://www.google.com/maps?q=41.318137,69.360837</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
         <v>8693</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N36" t="n">
         <v>24</v>
@@ -3889,10 +3889,10 @@
         <v>2020</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N37" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O37" t="n">
         <v>6</v>
@@ -3982,7 +3982,7 @@
         <v>9262</v>
       </c>
       <c r="M38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N38" t="n">
         <v>19</v>
@@ -4075,7 +4075,7 @@
         <v>7484</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N39" t="n">
         <v>18</v>
@@ -4168,7 +4168,7 @@
         <v>10288</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N40" t="n">
         <v>52</v>
@@ -4261,7 +4261,7 @@
         <v>16603</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N41" t="n">
         <v>60</v>
@@ -4354,7 +4354,7 @@
         <v>5737</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N42" t="n">
         <v>23</v>
@@ -4447,7 +4447,7 @@
         <v>10881</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N43" t="n">
         <v>23</v>
@@ -4502,22 +4502,22 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>41.323641</v>
+        <v>41.250058</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>69.341219</v>
+        <v>69.342911</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>41.323641, 69.341219</t>
+          <t>41.250058, 69.342911</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Катта Алтынтепа махалля</t>
+          <t>Аханграбо (Панельный)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4526,30 +4526,30 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>6442</v>
+        <v>4446</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N44" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="O44" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="P44" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Q44" t="n">
         <v>0.5</v>
@@ -4561,14 +4561,12 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>98.2</v>
+        <v>141</v>
       </c>
       <c r="U44" t="n">
-        <v>23</v>
-      </c>
-      <c r="V44" t="n">
-        <v>500</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4581,7 +4579,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.323641,69.341219</t>
+          <t>https://www.google.com/maps?q=41.250058,69.342911</t>
         </is>
       </c>
     </row>
@@ -4598,19 +4596,19 @@
         <v>75</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>41.250058</v>
+        <v>41.343858</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>69.342911</v>
+        <v>69.357677</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>41.250058, 69.342911</t>
+          <t>41.343858, 69.357677</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Аханграбо (Панельный)</t>
+          <t>Буз-2 (Черданцева)</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4619,30 +4617,30 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>4446</v>
+        <v>5378</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N45" t="n">
+        <v>35</v>
+      </c>
+      <c r="O45" t="n">
         <v>16</v>
       </c>
-      <c r="O45" t="n">
-        <v>7</v>
-      </c>
       <c r="P45" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q45" t="n">
         <v>0.5</v>
@@ -4654,12 +4652,14 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>141</v>
+        <v>98.2</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="V45" t="n">
+        <v>10</v>
+      </c>
       <c r="W45" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.250058,69.342911</t>
+          <t>https://www.google.com/maps?q=41.343858,69.357677</t>
         </is>
       </c>
     </row>
@@ -4689,19 +4689,19 @@
         <v>75</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>41.343858</v>
+        <v>41.332115</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>69.357677</v>
+        <v>69.345438</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>41.343858, 69.357677</t>
+          <t>41.332115, 69.345438</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Буз-2 (Черданцева)</t>
+          <t>Академгородок</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4721,19 +4721,19 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>5378</v>
+        <v>4353</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N46" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O46" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P46" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Q46" t="n">
         <v>0.5</v>
@@ -4748,7 +4748,7 @@
         <v>98.2</v>
       </c>
       <c r="U46" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="V46" t="n">
         <v>10</v>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.343858,69.357677</t>
+          <t>https://www.google.com/maps?q=41.332115,69.345438</t>
         </is>
       </c>
     </row>
@@ -4817,7 +4817,7 @@
         <v>11879</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N47" t="n">
         <v>48</v>
@@ -4910,7 +4910,7 @@
         <v>10654</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N48" t="n">
         <v>36</v>
@@ -5003,7 +5003,7 @@
         <v>12235</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N49" t="n">
         <v>46</v>
@@ -5096,7 +5096,7 @@
         <v>2530</v>
       </c>
       <c r="M50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N50" t="n">
         <v>21</v>
@@ -5151,7 +5151,7 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D51" s="2" t="n">
         <v>41.271397</v>
@@ -5189,10 +5189,10 @@
         <v>10663</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N51" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O51" t="n">
         <v>18</v>
@@ -5247,19 +5247,19 @@
         <v>72</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>41.376688</v>
+        <v>41.265528</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>69.24778499999999</v>
+        <v>69.149665</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>41.376688, 69.247785</t>
+          <t>41.265528, 69.149665</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ибрагим-Ата махалля</t>
+          <t>Чиланзар-31</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5268,30 +5268,30 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2816</v>
+        <v>10778</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N52" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="O52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P52" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="Q52" t="n">
         <v>0.5</v>
@@ -5303,13 +5303,13 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>139.7</v>
+        <v>47.6</v>
       </c>
       <c r="U52" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V52" t="n">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.376688,69.247785</t>
+          <t>https://www.google.com/maps?q=41.265528,69.149665</t>
         </is>
       </c>
     </row>
@@ -5375,10 +5375,10 @@
         <v>8748</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N53" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O53" t="n">
         <v>17</v>
@@ -5433,19 +5433,19 @@
         <v>72</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>41.265528</v>
+        <v>41.376688</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>69.149665</v>
+        <v>69.24778499999999</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>41.265528, 69.149665</t>
+          <t>41.376688, 69.247785</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Чиланзар-31</t>
+          <t>Ибрагим-Ата махалля</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5454,30 +5454,30 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>10778</v>
+        <v>2816</v>
       </c>
       <c r="M54" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="O54" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P54" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="Q54" t="n">
         <v>0.5</v>
@@ -5489,13 +5489,13 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>47.6</v>
+        <v>139.7</v>
       </c>
       <c r="U54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V54" t="n">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.265528,69.149665</t>
+          <t>https://www.google.com/maps?q=41.376688,69.247785</t>
         </is>
       </c>
     </row>
@@ -5614,7 +5614,7 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>41.283644</v>
@@ -5652,7 +5652,7 @@
         <v>5986</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N56" t="n">
         <v>33</v>
@@ -5745,10 +5745,10 @@
         <v>11138</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N57" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O57" t="n">
         <v>12</v>
@@ -5800,54 +5800,54 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>41.390081</v>
+        <v>41.254507</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>69.26402400000001</v>
+        <v>69.37862699999999</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>41.390081, 69.264024</t>
+          <t>41.254507, 69.378627</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Дустамабад</t>
+          <t>Сувсоз-2 (Водник)</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2632</v>
+        <v>10644</v>
       </c>
       <c r="M58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N58" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O58" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q58" t="n">
         <v>0.5</v>
@@ -5859,13 +5859,13 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>139.7</v>
+        <v>60.2</v>
       </c>
       <c r="U58" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V58" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.390081,69.264024</t>
+          <t>https://www.google.com/maps?q=41.254507,69.378627</t>
         </is>
       </c>
     </row>
@@ -5896,51 +5896,51 @@
         <v>68</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>41.254507</v>
+        <v>41.390081</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>69.37862699999999</v>
+        <v>69.26402400000001</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>41.254507, 69.378627</t>
+          <t>41.390081, 69.264024</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Сувсоз-2 (Водник)</t>
+          <t>Дустамабад</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>10644</v>
+        <v>2632</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N59" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q59" t="n">
         <v>0.5</v>
@@ -5952,13 +5952,13 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>60.2</v>
+        <v>139.7</v>
       </c>
       <c r="U59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V59" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.254507,69.378627</t>
+          <t>https://www.google.com/maps?q=41.390081,69.264024</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6024,7 @@
         <v>6883</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N60" t="n">
         <v>14</v>
@@ -6117,7 +6117,7 @@
         <v>4317</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N61" t="n">
         <v>7</v>
@@ -6210,7 +6210,7 @@
         <v>4927</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N62" t="n">
         <v>17</v>
@@ -6394,7 +6394,7 @@
         <v>1929</v>
       </c>
       <c r="M64" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N64" t="n">
         <v>18</v>
@@ -6487,7 +6487,7 @@
         <v>3879</v>
       </c>
       <c r="M65" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N65" t="n">
         <v>18</v>
@@ -6580,7 +6580,7 @@
         <v>1950</v>
       </c>
       <c r="M66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N66" t="n">
         <v>22</v>
@@ -6635,7 +6635,7 @@
         <v>13</v>
       </c>
       <c r="C67" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D67" s="2" t="n">
         <v>41.36099</v>
@@ -6673,7 +6673,7 @@
         <v>2226</v>
       </c>
       <c r="M67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N67" t="n">
         <v>16</v>
@@ -6728,7 +6728,7 @@
         <v>10</v>
       </c>
       <c r="C68" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D68" s="2" t="n">
         <v>41.370609</v>
@@ -6766,7 +6766,7 @@
         <v>3110</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N68" t="n">
         <v>15</v>
@@ -6859,7 +6859,7 @@
         <v>3499</v>
       </c>
       <c r="M69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N69" t="n">
         <v>15</v>
@@ -6911,7 +6911,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C70" t="n">
         <v>69</v>
@@ -6952,7 +6952,7 @@
         <v>1357</v>
       </c>
       <c r="M70" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N70" t="n">
         <v>5</v>
@@ -7045,7 +7045,7 @@
         <v>4778</v>
       </c>
       <c r="M71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N71" t="n">
         <v>11</v>
@@ -7100,7 +7100,7 @@
         <v>28</v>
       </c>
       <c r="C72" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D72" s="2" t="n">
         <v>41.361522</v>
@@ -7138,7 +7138,7 @@
         <v>1892</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N72" t="n">
         <v>6</v>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C73" t="n">
         <v>76</v>
@@ -7738,10 +7738,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C79" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D79" s="2" t="n">
         <v>41.33418</v>
@@ -7779,7 +7779,7 @@
         <v>1727</v>
       </c>
       <c r="M79" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N79" t="n">
         <v>7</v>
@@ -7832,7 +7832,7 @@
         <v>40</v>
       </c>
       <c r="C80" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D80" s="2" t="n">
         <v>41.399172</v>
@@ -7922,10 +7922,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C81" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D81" s="2" t="n">
         <v>41.401398</v>
@@ -8056,7 +8056,7 @@
         <v>4623</v>
       </c>
       <c r="M82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N82" t="n">
         <v>11</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C84" t="n">
         <v>75</v>
@@ -8478,7 +8478,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C87" t="n">
         <v>73</v>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C88" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D88" s="2" t="n">
         <v>41.380099</v>
@@ -8660,10 +8660,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C89" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D89" s="2" t="n">
         <v>41.378499</v>
@@ -8844,7 +8844,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C91" t="n">
         <v>69</v>
@@ -9119,7 +9119,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C94" t="n">
         <v>73</v>
@@ -9210,10 +9210,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C95" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D95" s="2" t="n">
         <v>41.425276</v>
@@ -9301,7 +9301,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C96" t="n">
         <v>76</v>
@@ -9392,25 +9392,25 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C97" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>41.412151</v>
+        <v>41.404809</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>69.177485</v>
+        <v>69.391277</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>41.412151, 69.177485</t>
+          <t>41.404809, 69.391277</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Сагбан</t>
+          <t>Уткир</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9426,35 +9426,35 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2486</v>
+        <v>1919</v>
       </c>
       <c r="M97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
         <v>5</v>
       </c>
       <c r="R97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S97" t="n">
-        <v>1519</v>
+        <v>1398</v>
       </c>
       <c r="T97" t="n">
-        <v>270.6</v>
+        <v>213.9</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
@@ -9467,12 +9467,12 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.412151,69.177485</t>
+          <t>https://www.google.com/maps?q=41.404809,69.391277</t>
         </is>
       </c>
     </row>
@@ -9489,19 +9489,19 @@
         <v>75</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>41.404809</v>
+        <v>41.412151</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>69.391277</v>
+        <v>69.177485</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>41.404809, 69.391277</t>
+          <t>41.412151, 69.177485</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Уткир</t>
+          <t>Сагбан</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -9517,35 +9517,35 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1919</v>
+        <v>2486</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q98" t="n">
         <v>5</v>
       </c>
       <c r="R98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S98" t="n">
-        <v>1398</v>
+        <v>1519</v>
       </c>
       <c r="T98" t="n">
-        <v>213.9</v>
+        <v>270.6</v>
       </c>
       <c r="U98" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.404809,69.391277</t>
+          <t>https://www.google.com/maps?q=41.412151,69.177485</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C100" t="n">
         <v>76</v>
@@ -9756,7 +9756,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C101" t="n">
         <v>73</v>
@@ -9847,7 +9847,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C102" t="n">
         <v>74</v>
@@ -10032,7 +10032,7 @@
         <v>9</v>
       </c>
       <c r="C104" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D104" s="2" t="n">
         <v>41.434386</v>
@@ -10123,7 +10123,7 @@
         <v>46</v>
       </c>
       <c r="C105" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D105" s="2" t="n">
         <v>41.451813</v>
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C106" t="n">
         <v>76</v>
@@ -10302,7 +10302,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C107" t="n">
         <v>69</v>
@@ -10575,7 +10575,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C110" t="n">
         <v>75</v>
@@ -10666,7 +10666,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C111" t="n">
         <v>77</v>
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C114" t="n">
         <v>77</v>
@@ -11303,7 +11303,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C118" t="n">
         <v>74</v>
@@ -11485,7 +11485,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C120" t="n">
         <v>69</v>
@@ -11579,7 +11579,7 @@
         <v>41</v>
       </c>
       <c r="C121" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D121" s="2" t="n">
         <v>41.570059</v>
@@ -12308,7 +12308,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C129" t="n">
         <v>56</v>
@@ -13582,7 +13582,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C143" t="n">
         <v>59</v>
@@ -13675,7 +13675,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C144" t="n">
         <v>54</v>
@@ -13862,7 +13862,7 @@
         <v>7</v>
       </c>
       <c r="C146" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D146" s="2" t="n">
         <v>40.836137</v>
@@ -14589,7 +14589,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C154" t="n">
         <v>54</v>
@@ -14680,7 +14680,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C155" t="n">
         <v>56</v>
@@ -15501,7 +15501,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C164" t="n">
         <v>59</v>
@@ -16505,7 +16505,7 @@
         <v>28</v>
       </c>
       <c r="C175" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D175" s="2" t="n">
         <v>40.985763</v>
@@ -17233,7 +17233,7 @@
         <v>1</v>
       </c>
       <c r="C183" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D183" s="2" t="n">
         <v>40.252947</v>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,10 +660,10 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V2" t="n">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="V3" t="n">
         <v>1100</v>
@@ -846,7 +846,7 @@
         <v>141</v>
       </c>
       <c r="U4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V4" t="n">
         <v>1400</v>
@@ -939,7 +939,7 @@
         <v>28.3</v>
       </c>
       <c r="U5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V5" t="n">
         <v>500</v>
@@ -1032,10 +1032,10 @@
         <v>122.7</v>
       </c>
       <c r="U6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V6" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>141</v>
       </c>
       <c r="U7" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="V7" t="n">
         <v>918</v>
@@ -1218,10 +1218,10 @@
         <v>139.7</v>
       </c>
       <c r="U8" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="V8" t="n">
-        <v>700</v>
+        <v>350</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>13</v>
       </c>
       <c r="V9" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>139.7</v>
       </c>
       <c r="U10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V10" t="n">
         <v>500</v>
@@ -1497,10 +1497,10 @@
         <v>59.2</v>
       </c>
       <c r="U11" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="V11" t="n">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         <v>141</v>
       </c>
       <c r="U12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="V12" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         <v>98.2</v>
       </c>
       <c r="U13" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="V13" t="n">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>22</v>
       </c>
       <c r="V14" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1962,10 +1962,10 @@
         <v>213.9</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V16" t="n">
-        <v>500</v>
+        <v>1400</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>31.8</v>
       </c>
       <c r="U17" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="V17" t="n">
         <v>350</v>
@@ -2148,10 +2148,10 @@
         <v>98.2</v>
       </c>
       <c r="U18" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="V18" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>47.6</v>
       </c>
       <c r="U19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V19" t="n">
         <v>600</v>
@@ -2334,10 +2334,10 @@
         <v>59.2</v>
       </c>
       <c r="U20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
-        <v>570</v>
+        <v>1200</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>141</v>
       </c>
       <c r="U21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V21" t="n">
         <v>900</v>
@@ -2520,7 +2520,7 @@
         <v>139.7</v>
       </c>
       <c r="U22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="V22" t="n">
         <v>450</v>
@@ -2613,10 +2613,10 @@
         <v>122.7</v>
       </c>
       <c r="U23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V23" t="n">
-        <v>1400</v>
+        <v>350</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -2706,10 +2706,10 @@
         <v>141</v>
       </c>
       <c r="U24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="V24" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>139.7</v>
       </c>
       <c r="U25" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="V25" t="n">
         <v>700</v>
@@ -2892,10 +2892,10 @@
         <v>139.7</v>
       </c>
       <c r="U26" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="V26" t="n">
-        <v>600</v>
+        <v>350</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -2985,10 +2985,10 @@
         <v>59.2</v>
       </c>
       <c r="U27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V27" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3078,10 +3078,10 @@
         <v>139.7</v>
       </c>
       <c r="U28" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="V28" t="n">
-        <v>1200</v>
+        <v>350</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>7</v>
       </c>
       <c r="V29" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>141</v>
       </c>
       <c r="U30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V30" t="n">
         <v>1400</v>
@@ -3357,10 +3357,10 @@
         <v>141</v>
       </c>
       <c r="U31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V31" t="n">
-        <v>650</v>
+        <v>1100</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>139.7</v>
       </c>
       <c r="U32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V32" t="n">
         <v>500</v>
@@ -3822,7 +3822,7 @@
         <v>141</v>
       </c>
       <c r="U36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V36" t="n">
         <v>10</v>
@@ -3915,7 +3915,7 @@
         <v>98.2</v>
       </c>
       <c r="U37" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V37" t="n">
         <v>10</v>
@@ -4008,10 +4008,10 @@
         <v>98.2</v>
       </c>
       <c r="U38" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="V38" t="n">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4101,10 +4101,10 @@
         <v>59.2</v>
       </c>
       <c r="U39" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="V39" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -4287,10 +4287,10 @@
         <v>47.6</v>
       </c>
       <c r="U41" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="V41" t="n">
-        <v>350</v>
+        <v>70</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>98.2</v>
       </c>
       <c r="U42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V42" t="n">
         <v>10</v>
@@ -4473,7 +4473,7 @@
         <v>139.7</v>
       </c>
       <c r="U43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V43" t="n">
         <v>500</v>
@@ -4657,7 +4657,7 @@
         <v>31.8</v>
       </c>
       <c r="U45" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="V45" t="n">
         <v>500</v>
@@ -4843,10 +4843,10 @@
         <v>28.3</v>
       </c>
       <c r="U47" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="V47" t="n">
-        <v>550</v>
+        <v>1092</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -4936,11 +4936,9 @@
         <v>59.2</v>
       </c>
       <c r="U48" t="n">
-        <v>2</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1100</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5032,7 +5030,7 @@
         <v>7</v>
       </c>
       <c r="V49" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -5122,7 +5120,7 @@
         <v>28.3</v>
       </c>
       <c r="U50" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="V50" t="n">
         <v>350</v>
@@ -5308,7 +5306,7 @@
         <v>139.7</v>
       </c>
       <c r="U52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V52" t="n">
         <v>500</v>
@@ -5401,10 +5399,10 @@
         <v>48.5</v>
       </c>
       <c r="U53" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V53" t="n">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -5494,10 +5492,10 @@
         <v>122.7</v>
       </c>
       <c r="U54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V54" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -5587,7 +5585,7 @@
         <v>28.3</v>
       </c>
       <c r="U55" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="V55" t="n">
         <v>500</v>
@@ -5864,7 +5862,7 @@
         <v>31.8</v>
       </c>
       <c r="U58" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="V58" t="n">
         <v>350</v>
@@ -6050,10 +6048,10 @@
         <v>59.2</v>
       </c>
       <c r="U60" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V60" t="n">
-        <v>499</v>
+        <v>1200</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -6143,10 +6141,10 @@
         <v>184.9</v>
       </c>
       <c r="U61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V61" t="n">
-        <v>2</v>
+        <v>1200</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -6236,10 +6234,10 @@
         <v>213.9</v>
       </c>
       <c r="U62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V62" t="n">
-        <v>500</v>
+        <v>1400</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -6329,10 +6327,10 @@
         <v>270.6</v>
       </c>
       <c r="U63" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V63" t="n">
-        <v>800</v>
+        <v>750</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -6792,7 +6790,7 @@
         <v>184.9</v>
       </c>
       <c r="U68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V68" t="n">
         <v>600</v>
@@ -6888,7 +6886,7 @@
         <v>7</v>
       </c>
       <c r="V69" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
@@ -6978,10 +6976,10 @@
         <v>270.6</v>
       </c>
       <c r="U70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V70" t="n">
-        <v>499</v>
+        <v>840</v>
       </c>
       <c r="W70" t="inlineStr">
         <is>
@@ -7071,7 +7069,7 @@
         <v>184.9</v>
       </c>
       <c r="U71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr">
@@ -7256,7 +7254,7 @@
         <v>3</v>
       </c>
       <c r="V73" t="n">
-        <v>1860</v>
+        <v>840</v>
       </c>
       <c r="W73" t="inlineStr">
         <is>
@@ -7346,7 +7344,7 @@
         <v>270.6</v>
       </c>
       <c r="U74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr">
@@ -7803,11 +7801,9 @@
         <v>184.9</v>
       </c>
       <c r="U79" t="n">
-        <v>1</v>
-      </c>
-      <c r="V79" t="n">
-        <v>2600</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V79" t="inlineStr"/>
       <c r="W79" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7896,7 +7892,7 @@
         <v>213.9</v>
       </c>
       <c r="U80" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V80" t="n">
         <v>1000</v>
@@ -8362,7 +8358,7 @@
         <v>1</v>
       </c>
       <c r="V85" t="n">
-        <v>1860</v>
+        <v>840</v>
       </c>
       <c r="W85" t="inlineStr">
         <is>
@@ -8545,7 +8541,7 @@
         <v>213.9</v>
       </c>
       <c r="U87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V87" t="n">
         <v>1100</v>
@@ -8638,7 +8634,7 @@
         <v>184.9</v>
       </c>
       <c r="U88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr">

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,7 +660,7 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V2" t="n">
         <v>70</v>
@@ -753,10 +753,10 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V3" t="n">
-        <v>1100</v>
+        <v>1265</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>141</v>
       </c>
       <c r="U4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V4" t="n">
         <v>1400</v>
@@ -939,7 +939,7 @@
         <v>28.3</v>
       </c>
       <c r="U5" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="V5" t="n">
         <v>500</v>
@@ -1032,7 +1032,7 @@
         <v>122.7</v>
       </c>
       <c r="U6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V6" t="n">
         <v>150</v>
@@ -1311,7 +1311,7 @@
         <v>139.7</v>
       </c>
       <c r="U9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V9" t="n">
         <v>300</v>
@@ -1497,7 +1497,7 @@
         <v>59.2</v>
       </c>
       <c r="U11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V11" t="n">
         <v>400</v>
@@ -1590,7 +1590,7 @@
         <v>141</v>
       </c>
       <c r="U12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V12" t="n">
         <v>500</v>
@@ -1683,10 +1683,10 @@
         <v>98.2</v>
       </c>
       <c r="U13" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="V13" t="n">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>98.2</v>
       </c>
       <c r="U14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V14" t="n">
         <v>500</v>
@@ -1962,10 +1962,10 @@
         <v>213.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V16" t="n">
-        <v>1400</v>
+        <v>500</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2055,10 +2055,10 @@
         <v>31.8</v>
       </c>
       <c r="U17" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="V17" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>69</v>
       </c>
       <c r="V18" t="n">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2241,10 +2241,10 @@
         <v>47.6</v>
       </c>
       <c r="U19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V19" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2334,10 +2334,10 @@
         <v>59.2</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V20" t="n">
-        <v>1200</v>
+        <v>570</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>141</v>
       </c>
       <c r="U21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V21" t="n">
         <v>900</v>
@@ -2520,7 +2520,7 @@
         <v>139.7</v>
       </c>
       <c r="U22" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="V22" t="n">
         <v>450</v>
@@ -2613,7 +2613,7 @@
         <v>122.7</v>
       </c>
       <c r="U23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V23" t="n">
         <v>350</v>
@@ -2706,7 +2706,7 @@
         <v>141</v>
       </c>
       <c r="U24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V24" t="n">
         <v>500</v>
@@ -2799,7 +2799,7 @@
         <v>139.7</v>
       </c>
       <c r="U25" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="V25" t="n">
         <v>700</v>
@@ -2892,7 +2892,7 @@
         <v>139.7</v>
       </c>
       <c r="U26" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="V26" t="n">
         <v>350</v>
@@ -2985,10 +2985,10 @@
         <v>59.2</v>
       </c>
       <c r="U27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V27" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>139.7</v>
       </c>
       <c r="U28" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="V28" t="n">
         <v>350</v>
@@ -3171,7 +3171,7 @@
         <v>28.3</v>
       </c>
       <c r="U29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V29" t="n">
         <v>350</v>
@@ -3264,7 +3264,7 @@
         <v>141</v>
       </c>
       <c r="U30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V30" t="n">
         <v>1400</v>
@@ -3360,7 +3360,7 @@
         <v>3</v>
       </c>
       <c r="V31" t="n">
-        <v>1100</v>
+        <v>650</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>139.7</v>
       </c>
       <c r="U32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V32" t="n">
         <v>500</v>
@@ -3636,7 +3636,7 @@
         <v>141</v>
       </c>
       <c r="U34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V34" t="n">
         <v>900</v>
@@ -3732,7 +3732,7 @@
         <v>2</v>
       </c>
       <c r="V35" t="n">
-        <v>1400</v>
+        <v>450</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>141</v>
       </c>
       <c r="U36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V36" t="n">
         <v>10</v>
@@ -3915,7 +3915,7 @@
         <v>98.2</v>
       </c>
       <c r="U37" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V37" t="n">
         <v>10</v>
@@ -4008,7 +4008,7 @@
         <v>98.2</v>
       </c>
       <c r="U38" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="V38" t="n">
         <v>500</v>
@@ -4101,10 +4101,10 @@
         <v>59.2</v>
       </c>
       <c r="U39" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="V39" t="n">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>98.2</v>
       </c>
       <c r="U42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V42" t="n">
         <v>10</v>
@@ -4657,7 +4657,7 @@
         <v>31.8</v>
       </c>
       <c r="U45" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="V45" t="n">
         <v>500</v>
@@ -4843,10 +4843,10 @@
         <v>28.3</v>
       </c>
       <c r="U47" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V47" t="n">
-        <v>1092</v>
+        <v>250</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -5027,10 +5027,10 @@
         <v>47.6</v>
       </c>
       <c r="U49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V49" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>28.3</v>
       </c>
       <c r="U50" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="V50" t="n">
         <v>350</v>
@@ -5306,7 +5306,7 @@
         <v>139.7</v>
       </c>
       <c r="U52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V52" t="n">
         <v>500</v>
@@ -5399,7 +5399,7 @@
         <v>48.5</v>
       </c>
       <c r="U53" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="V53" t="n">
         <v>1500</v>
@@ -5492,7 +5492,7 @@
         <v>122.7</v>
       </c>
       <c r="U54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V54" t="n">
         <v>150</v>
@@ -5585,7 +5585,7 @@
         <v>28.3</v>
       </c>
       <c r="U55" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="V55" t="n">
         <v>500</v>
@@ -5862,10 +5862,10 @@
         <v>31.8</v>
       </c>
       <c r="U58" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="V58" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -5955,10 +5955,10 @@
         <v>60.2</v>
       </c>
       <c r="U59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V59" t="n">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>59.2</v>
       </c>
       <c r="U60" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V60" t="n">
         <v>1200</v>
@@ -6144,7 +6144,7 @@
         <v>1</v>
       </c>
       <c r="V61" t="n">
-        <v>1200</v>
+        <v>2</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -6234,10 +6234,10 @@
         <v>213.9</v>
       </c>
       <c r="U62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V62" t="n">
-        <v>1400</v>
+        <v>500</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>270.6</v>
       </c>
       <c r="U63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V63" t="n">
         <v>750</v>
@@ -6790,7 +6790,7 @@
         <v>184.9</v>
       </c>
       <c r="U68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V68" t="n">
         <v>600</v>
@@ -6883,7 +6883,7 @@
         <v>270.6</v>
       </c>
       <c r="U69" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V69" t="n">
         <v>300</v>
@@ -6979,7 +6979,7 @@
         <v>1</v>
       </c>
       <c r="V70" t="n">
-        <v>840</v>
+        <v>1860</v>
       </c>
       <c r="W70" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>3</v>
       </c>
       <c r="V73" t="n">
-        <v>840</v>
+        <v>1860</v>
       </c>
       <c r="W73" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>270.6</v>
       </c>
       <c r="U74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr">
@@ -7801,9 +7801,11 @@
         <v>184.9</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
-      </c>
-      <c r="V79" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V79" t="n">
+        <v>2600</v>
+      </c>
       <c r="W79" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8169,7 +8171,7 @@
         <v>213.9</v>
       </c>
       <c r="U83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V83" t="n">
         <v>1100</v>
@@ -8355,10 +8357,10 @@
         <v>270.6</v>
       </c>
       <c r="U85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V85" t="n">
-        <v>840</v>
+        <v>1200</v>
       </c>
       <c r="W85" t="inlineStr">
         <is>
@@ -9544,9 +9546,11 @@
         <v>270.6</v>
       </c>
       <c r="U98" t="n">
-        <v>0</v>
-      </c>
-      <c r="V98" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V98" t="n">
+        <v>1200</v>
+      </c>
       <c r="W98" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -12193,7 +12197,7 @@
         <v>55.2</v>
       </c>
       <c r="U127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V127" t="inlineStr"/>
       <c r="W127" t="inlineStr">

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,7 +660,7 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V2" t="n">
         <v>70</v>
@@ -753,10 +753,10 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="V3" t="n">
-        <v>1265</v>
+        <v>1100</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         <v>28.3</v>
       </c>
       <c r="U5" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="V5" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>141</v>
       </c>
       <c r="U7" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="V7" t="n">
         <v>918</v>
@@ -1218,7 +1218,7 @@
         <v>139.7</v>
       </c>
       <c r="U8" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="V8" t="n">
         <v>350</v>
@@ -1311,7 +1311,7 @@
         <v>139.7</v>
       </c>
       <c r="U9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V9" t="n">
         <v>300</v>
@@ -1404,7 +1404,7 @@
         <v>139.7</v>
       </c>
       <c r="U10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V10" t="n">
         <v>500</v>
@@ -1497,7 +1497,7 @@
         <v>59.2</v>
       </c>
       <c r="U11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V11" t="n">
         <v>400</v>
@@ -1590,10 +1590,10 @@
         <v>141</v>
       </c>
       <c r="U12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="V12" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>21</v>
       </c>
       <c r="V14" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>12</v>
       </c>
       <c r="V15" t="n">
-        <v>850</v>
+        <v>1000</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2055,10 +2055,10 @@
         <v>31.8</v>
       </c>
       <c r="U17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="V17" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>98.2</v>
       </c>
       <c r="U18" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V18" t="n">
         <v>650</v>
@@ -2244,7 +2244,7 @@
         <v>11</v>
       </c>
       <c r="V19" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>141</v>
       </c>
       <c r="U21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V21" t="n">
         <v>900</v>
@@ -2520,7 +2520,7 @@
         <v>139.7</v>
       </c>
       <c r="U22" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="V22" t="n">
         <v>450</v>
@@ -2616,7 +2616,7 @@
         <v>4</v>
       </c>
       <c r="V23" t="n">
-        <v>350</v>
+        <v>1400</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>17</v>
       </c>
       <c r="V24" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>139.7</v>
       </c>
       <c r="U25" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="V25" t="n">
         <v>700</v>
@@ -3078,7 +3078,7 @@
         <v>139.7</v>
       </c>
       <c r="U28" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="V28" t="n">
         <v>350</v>
@@ -3174,7 +3174,7 @@
         <v>6</v>
       </c>
       <c r="V29" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>3</v>
       </c>
       <c r="V31" t="n">
-        <v>650</v>
+        <v>1100</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>139.7</v>
       </c>
       <c r="U32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V32" t="n">
         <v>500</v>
@@ -3636,7 +3636,7 @@
         <v>141</v>
       </c>
       <c r="U34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V34" t="n">
         <v>900</v>
@@ -3729,7 +3729,7 @@
         <v>122.7</v>
       </c>
       <c r="U35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V35" t="n">
         <v>450</v>
@@ -3822,7 +3822,7 @@
         <v>141</v>
       </c>
       <c r="U36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V36" t="n">
         <v>10</v>
@@ -3915,7 +3915,7 @@
         <v>98.2</v>
       </c>
       <c r="U37" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V37" t="n">
         <v>10</v>
@@ -4008,10 +4008,10 @@
         <v>98.2</v>
       </c>
       <c r="U38" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="V38" t="n">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>59.2</v>
       </c>
       <c r="U39" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="V39" t="n">
         <v>250</v>
@@ -4287,7 +4287,7 @@
         <v>47.6</v>
       </c>
       <c r="U41" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="V41" t="n">
         <v>70</v>
@@ -4380,7 +4380,7 @@
         <v>98.2</v>
       </c>
       <c r="U42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V42" t="n">
         <v>10</v>
@@ -4657,7 +4657,7 @@
         <v>31.8</v>
       </c>
       <c r="U45" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="V45" t="n">
         <v>500</v>
@@ -4750,10 +4750,10 @@
         <v>122.7</v>
       </c>
       <c r="U46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V46" t="n">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>28.3</v>
       </c>
       <c r="U47" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V47" t="n">
         <v>250</v>
@@ -5120,7 +5120,7 @@
         <v>28.3</v>
       </c>
       <c r="U50" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="V50" t="n">
         <v>350</v>
@@ -5306,7 +5306,7 @@
         <v>139.7</v>
       </c>
       <c r="U52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V52" t="n">
         <v>500</v>
@@ -5585,10 +5585,10 @@
         <v>28.3</v>
       </c>
       <c r="U55" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="V55" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -5862,10 +5862,10 @@
         <v>31.8</v>
       </c>
       <c r="U58" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V58" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>59.2</v>
       </c>
       <c r="U60" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V60" t="n">
         <v>1200</v>
@@ -6141,7 +6141,7 @@
         <v>184.9</v>
       </c>
       <c r="U61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V61" t="n">
         <v>2</v>
@@ -6327,7 +6327,7 @@
         <v>270.6</v>
       </c>
       <c r="U63" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V63" t="n">
         <v>750</v>
@@ -6420,7 +6420,7 @@
         <v>184.9</v>
       </c>
       <c r="U64" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V64" t="n">
         <v>200</v>
@@ -6790,10 +6790,10 @@
         <v>184.9</v>
       </c>
       <c r="U68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V68" t="n">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>270.6</v>
       </c>
       <c r="U69" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V69" t="n">
         <v>300</v>
@@ -6976,10 +6976,10 @@
         <v>270.6</v>
       </c>
       <c r="U70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V70" t="n">
-        <v>1860</v>
+        <v>840</v>
       </c>
       <c r="W70" t="inlineStr">
         <is>
@@ -7251,10 +7251,10 @@
         <v>270.6</v>
       </c>
       <c r="U73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V73" t="n">
-        <v>1860</v>
+        <v>840</v>
       </c>
       <c r="W73" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>270.6</v>
       </c>
       <c r="U74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr">
@@ -8078,7 +8078,7 @@
         <v>213.9</v>
       </c>
       <c r="U82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V82" t="n">
         <v>1000</v>
@@ -8174,7 +8174,7 @@
         <v>1</v>
       </c>
       <c r="V83" t="n">
-        <v>1100</v>
+        <v>3000</v>
       </c>
       <c r="W83" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>184.9</v>
       </c>
       <c r="U84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V84" t="n">
         <v>1840</v>
@@ -8357,10 +8357,10 @@
         <v>270.6</v>
       </c>
       <c r="U85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V85" t="n">
-        <v>1200</v>
+        <v>840</v>
       </c>
       <c r="W85" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         <v>2</v>
       </c>
       <c r="V87" t="n">
-        <v>1100</v>
+        <v>3000</v>
       </c>
       <c r="W87" t="inlineStr">
         <is>
@@ -11647,11 +11647,9 @@
         <v>147.5</v>
       </c>
       <c r="U121" t="n">
-        <v>1</v>
-      </c>
-      <c r="V121" t="n">
-        <v>1600</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V121" t="inlineStr"/>
       <c r="W121" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -12013,11 +12011,9 @@
         <v>147.5</v>
       </c>
       <c r="U125" t="n">
-        <v>1</v>
-      </c>
-      <c r="V125" t="n">
-        <v>1600</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V125" t="inlineStr"/>
       <c r="W125" t="inlineStr">
         <is>
           <t>рекомендуемая</t>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -598,7 +598,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>41.275234</v>
@@ -645,7 +645,7 @@
         <v>21</v>
       </c>
       <c r="P2" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0.5</v>
@@ -660,7 +660,7 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="V2" t="n">
         <v>70</v>
@@ -738,7 +738,7 @@
         <v>12</v>
       </c>
       <c r="P3" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0.5</v>
@@ -753,10 +753,10 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="V3" t="n">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -787,19 +787,19 @@
         <v>93</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>41.284988</v>
+        <v>41.298608</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>69.304435</v>
+        <v>69.213863</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>41.284988, 69.304435</t>
+          <t>41.298608, 69.213863</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Пулемас (Шумиловский городок)</t>
+          <t>Чарх Камалан-3 махалля</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -808,48 +808,48 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>12156</v>
+        <v>17457</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N4" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="O4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P4" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0.5</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>2507</v>
+        <v>781</v>
       </c>
       <c r="T4" t="n">
-        <v>141</v>
+        <v>28.3</v>
       </c>
       <c r="U4" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="V4" t="n">
-        <v>1400</v>
+        <v>500</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.284988,69.304435</t>
+          <t>https://www.google.com/maps?q=41.298608,69.213863</t>
         </is>
       </c>
     </row>
@@ -880,19 +880,19 @@
         <v>92</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>41.298608</v>
+        <v>41.284988</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>69.213863</v>
+        <v>69.304435</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>41.298608, 69.213863</t>
+          <t>41.284988, 69.304435</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Чарх Камалан-3 махалля</t>
+          <t>Пулемас (Шумиловский городок)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -901,48 +901,48 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>17457</v>
+        <v>12156</v>
       </c>
       <c r="M5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="O5" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="P5" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0.5</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S5" t="n">
-        <v>781</v>
+        <v>2507</v>
       </c>
       <c r="T5" t="n">
-        <v>28.3</v>
+        <v>141</v>
       </c>
       <c r="U5" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="V5" t="n">
-        <v>900</v>
+        <v>1990</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.298608,69.213863</t>
+          <t>https://www.google.com/maps?q=41.284988,69.304435</t>
         </is>
       </c>
     </row>
@@ -970,22 +970,22 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>41.206165</v>
+        <v>41.329729</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>69.219122</v>
+        <v>69.289952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41.206165, 69.219122</t>
+          <t>41.329729, 69.289952</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Сергели-1</t>
+          <t>Буюк Туран махалля</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -994,30 +994,30 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>11740</v>
+        <v>10538</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="O6" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="P6" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0.5</v>
@@ -1026,16 +1026,16 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>2510</v>
+        <v>399</v>
       </c>
       <c r="T6" t="n">
-        <v>122.7</v>
+        <v>139.7</v>
       </c>
       <c r="U6" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="V6" t="n">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.206165,69.219122</t>
+          <t>https://www.google.com/maps?q=41.329729,69.289952</t>
         </is>
       </c>
     </row>
@@ -1063,22 +1063,22 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>41.302375</v>
+        <v>41.206165</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>69.289134</v>
+        <v>69.219122</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>41.302375, 69.289134</t>
+          <t>41.206165, 69.219122</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Айбек</t>
+          <t>Сергели-1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1087,30 +1087,30 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>13591</v>
+        <v>11740</v>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="O7" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="P7" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0.5</v>
@@ -1119,16 +1119,16 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>448</v>
+        <v>2510</v>
       </c>
       <c r="T7" t="n">
-        <v>141</v>
+        <v>122.7</v>
       </c>
       <c r="U7" t="n">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="V7" t="n">
-        <v>918</v>
+        <v>150</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.302375,69.289134</t>
+          <t>https://www.google.com/maps?q=41.206165,69.219122</t>
         </is>
       </c>
     </row>
@@ -1159,19 +1159,19 @@
         <v>91</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>41.329729</v>
+        <v>41.345911</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>69.289952</v>
+        <v>69.246887</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>41.329729, 69.289952</t>
+          <t>41.345911, 69.246887</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Буюк Туран махалля</t>
+          <t>Карасарай махалля</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1180,30 +1180,30 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>10538</v>
+        <v>14912</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N8" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="O8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P8" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0.5</v>
@@ -1212,16 +1212,16 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>399</v>
+        <v>252</v>
       </c>
       <c r="T8" t="n">
-        <v>139.7</v>
+        <v>59.2</v>
       </c>
       <c r="U8" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="V8" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.329729,69.289952</t>
+          <t>https://www.google.com/maps?q=41.345911,69.246887</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
         <v>10</v>
       </c>
       <c r="P9" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
         <v>0.5</v>
@@ -1311,10 +1311,10 @@
         <v>139.7</v>
       </c>
       <c r="U9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V9" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1342,22 +1342,22 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>41.367635</v>
+        <v>41.302375</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>69.275244</v>
+        <v>69.289134</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>41.367635, 69.275244</t>
+          <t>41.302375, 69.289134</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Туркистан махалля</t>
+          <t>Айбек</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1366,30 +1366,30 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>15593</v>
+        <v>13591</v>
       </c>
       <c r="M10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="O10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P10" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0.5</v>
@@ -1398,16 +1398,16 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="T10" t="n">
-        <v>139.7</v>
+        <v>141</v>
       </c>
       <c r="U10" t="n">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="V10" t="n">
-        <v>500</v>
+        <v>918</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.367635,69.275244</t>
+          <t>https://www.google.com/maps?q=41.302375,69.289134</t>
         </is>
       </c>
     </row>
@@ -1438,19 +1438,19 @@
         <v>90</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>41.345911</v>
+        <v>41.367635</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>69.246887</v>
+        <v>69.275244</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>41.345911, 69.246887</t>
+          <t>41.367635, 69.275244</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Карасарай махалля</t>
+          <t>Туркистан махалля</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1459,30 +1459,30 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>14912</v>
+        <v>15593</v>
       </c>
       <c r="M11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N11" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="O11" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="P11" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0.5</v>
@@ -1491,16 +1491,16 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>252</v>
+        <v>438</v>
       </c>
       <c r="T11" t="n">
-        <v>59.2</v>
+        <v>139.7</v>
       </c>
       <c r="U11" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="V11" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.345911,69.246887</t>
+          <t>https://www.google.com/maps?q=41.367635,69.275244</t>
         </is>
       </c>
     </row>
@@ -1531,19 +1531,19 @@
         <v>90</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>41.308626</v>
+        <v>41.335981</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>69.32097400000001</v>
+        <v>69.321806</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>41.308626, 69.320974</t>
+          <t>41.335981, 69.321806</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Риёзи (Чизельный)</t>
+          <t>Буюк Ипак Йули махалля</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1552,48 +1552,48 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>8891</v>
+        <v>5082</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0.5</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>742</v>
+        <v>1600</v>
       </c>
       <c r="T12" t="n">
-        <v>141</v>
+        <v>98.2</v>
       </c>
       <c r="U12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="V12" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.308626,69.320974</t>
+          <t>https://www.google.com/maps?q=41.335981,69.321806</t>
         </is>
       </c>
     </row>
@@ -1624,19 +1624,19 @@
         <v>89</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>41.332561</v>
+        <v>41.349362</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>69.321702</v>
+        <v>69.33805099999999</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>41.332561, 69.321702</t>
+          <t>41.349362, 69.338051</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Буюк Ипак Йули махалля</t>
+          <t>Ялангач (Высоковольтный)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1656,37 +1656,37 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4166</v>
+        <v>13228</v>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N13" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="O13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="P13" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
         <v>0.5</v>
       </c>
       <c r="R13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>1970</v>
+        <v>558</v>
       </c>
       <c r="T13" t="n">
         <v>98.2</v>
       </c>
       <c r="U13" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="V13" t="n">
-        <v>650</v>
+        <v>850</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.332561,69.321702</t>
+          <t>https://www.google.com/maps?q=41.349362,69.338051</t>
         </is>
       </c>
     </row>
@@ -1717,19 +1717,19 @@
         <v>89</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>41.309964</v>
+        <v>41.365403</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>69.34079800000001</v>
+        <v>69.393992</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>41.309964, 69.340798</t>
+          <t>41.365403, 69.393992</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Авайхан махалля</t>
+          <t>ТТЗ-4</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1738,30 +1738,30 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>9976</v>
+        <v>13404</v>
       </c>
       <c r="M14" t="n">
+        <v>3</v>
+      </c>
+      <c r="N14" t="n">
+        <v>16</v>
+      </c>
+      <c r="O14" t="n">
         <v>8</v>
       </c>
-      <c r="N14" t="n">
-        <v>31</v>
-      </c>
-      <c r="O14" t="n">
-        <v>16</v>
-      </c>
       <c r="P14" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0.5</v>
@@ -1770,17 +1770,17 @@
         <v>1</v>
       </c>
       <c r="S14" t="n">
+        <v>1200</v>
+      </c>
+      <c r="T14" t="n">
+        <v>213.9</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
         <v>500</v>
       </c>
-      <c r="T14" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>21</v>
-      </c>
-      <c r="V14" t="n">
-        <v>600</v>
-      </c>
       <c r="W14" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.309964,69.340798</t>
+          <t>https://www.google.com/maps?q=41.365403,69.393992</t>
         </is>
       </c>
     </row>
@@ -1810,19 +1810,19 @@
         <v>89</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>41.349362</v>
+        <v>41.309964</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>69.33805099999999</v>
+        <v>69.34079800000001</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41.349362, 69.338051</t>
+          <t>41.309964, 69.340798</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ялангач (Высоковольтный)</t>
+          <t>Авайхан махалля</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1842,19 +1842,19 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>13228</v>
+        <v>9976</v>
       </c>
       <c r="M15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N15" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="O15" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="P15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0.5</v>
@@ -1863,16 +1863,16 @@
         <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>558</v>
+        <v>500</v>
       </c>
       <c r="T15" t="n">
         <v>98.2</v>
       </c>
       <c r="U15" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="V15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.349362,69.338051</t>
+          <t>https://www.google.com/maps?q=41.309964,69.340798</t>
         </is>
       </c>
     </row>
@@ -1903,19 +1903,19 @@
         <v>89</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>41.365403</v>
+        <v>41.308626</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>69.393992</v>
+        <v>69.32097400000001</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>41.365403, 69.393992</t>
+          <t>41.308626, 69.320974</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ТТЗ-4</t>
+          <t>Риёзи (Чизельный)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1931,38 +1931,38 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>13404</v>
+        <v>8891</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="O16" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="P16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
-        <v>1200</v>
+        <v>742</v>
       </c>
       <c r="T16" t="n">
-        <v>213.9</v>
+        <v>141</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="V16" t="n">
         <v>500</v>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.365403,69.393992</t>
+          <t>https://www.google.com/maps?q=41.308626,69.320974</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
         <v>21</v>
       </c>
       <c r="P17" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0.5</v>
@@ -2055,10 +2055,10 @@
         <v>31.8</v>
       </c>
       <c r="U17" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="V17" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2089,19 +2089,19 @@
         <v>88</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>41.314123</v>
+        <v>41.311064</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>69.301356</v>
+        <v>69.186525</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>41.314123, 69.301356</t>
+          <t>41.311064, 69.186525</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ирригатор массив</t>
+          <t>Пахтакор махалля</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2110,48 +2110,48 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6403</v>
+        <v>3023</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N18" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="O18" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="P18" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>220</v>
+        <v>1777</v>
       </c>
       <c r="T18" t="n">
-        <v>98.2</v>
+        <v>47.6</v>
       </c>
       <c r="U18" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="V18" t="n">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.314123,69.301356</t>
+          <t>https://www.google.com/maps?q=41.311064,69.186525</t>
         </is>
       </c>
     </row>
@@ -2182,19 +2182,19 @@
         <v>87</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>41.311064</v>
+        <v>41.365496</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>69.186525</v>
+        <v>69.203898</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>41.311064, 69.186525</t>
+          <t>41.365496, 69.203898</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Пахтакор махалля</t>
+          <t>Бешкурган-4</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2203,48 +2203,48 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3023</v>
+        <v>12971</v>
       </c>
       <c r="M19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O19" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0.5</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>1777</v>
+        <v>313</v>
       </c>
       <c r="T19" t="n">
-        <v>47.6</v>
+        <v>59.2</v>
       </c>
       <c r="U19" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="V19" t="n">
-        <v>600</v>
+        <v>570</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.311064,69.186525</t>
+          <t>https://www.google.com/maps?q=41.365496,69.203898</t>
         </is>
       </c>
     </row>
@@ -2275,19 +2275,19 @@
         <v>87</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>41.365496</v>
+        <v>41.314123</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>69.203898</v>
+        <v>69.301356</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>41.365496, 69.203898</t>
+          <t>41.314123, 69.301356</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Бешкурган-4</t>
+          <t>Ирригатор массив</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2296,30 +2296,30 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>12971</v>
+        <v>6403</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="O20" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="P20" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0.5</v>
@@ -2328,16 +2328,16 @@
         <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>313</v>
+        <v>220</v>
       </c>
       <c r="T20" t="n">
-        <v>59.2</v>
+        <v>98.2</v>
       </c>
       <c r="U20" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="V20" t="n">
-        <v>570</v>
+        <v>500</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.365496,69.203898</t>
+          <t>https://www.google.com/maps?q=41.314123,69.301356</t>
         </is>
       </c>
     </row>
@@ -2368,19 +2368,19 @@
         <v>87</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>41.283946</v>
+        <v>41.350681</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>69.359775</v>
+        <v>69.266822</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>41.283946, 69.359775</t>
+          <t>41.350681, 69.266822</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Авиасозлар-1</t>
+          <t>Джами махалля</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2389,30 +2389,30 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>13526</v>
+        <v>4950</v>
       </c>
       <c r="M21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N21" t="n">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="O21" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="P21" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0.5</v>
@@ -2421,16 +2421,16 @@
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>480</v>
+        <v>126</v>
       </c>
       <c r="T21" t="n">
-        <v>141</v>
+        <v>139.7</v>
       </c>
       <c r="U21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V21" t="n">
-        <v>900</v>
+        <v>450</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.283946,69.359775</t>
+          <t>https://www.google.com/maps?q=41.350681,69.266822</t>
         </is>
       </c>
     </row>
@@ -2458,22 +2458,22 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>41.350681</v>
+        <v>41.283946</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>69.266822</v>
+        <v>69.359775</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>41.350681, 69.266822</t>
+          <t>41.283946, 69.359775</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Джами махалля</t>
+          <t>Авиасозлар-1</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2482,30 +2482,30 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4950</v>
+        <v>13526</v>
       </c>
       <c r="M22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N22" t="n">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="O22" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="P22" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0.5</v>
@@ -2514,16 +2514,16 @@
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>126</v>
+        <v>480</v>
       </c>
       <c r="T22" t="n">
-        <v>139.7</v>
+        <v>141</v>
       </c>
       <c r="U22" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="V22" t="n">
-        <v>450</v>
+        <v>900</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.350681,69.266822</t>
+          <t>https://www.google.com/maps?q=41.283946,69.359775</t>
         </is>
       </c>
     </row>
@@ -2554,19 +2554,19 @@
         <v>86</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>41.228735</v>
+        <v>41.296436</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>69.200014</v>
+        <v>69.332471</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>41.228735, 69.200014</t>
+          <t>41.296436, 69.332471</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Сергели-5A</t>
+          <t>Куксарай махалля</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2575,48 +2575,48 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>7101</v>
+        <v>4067</v>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N23" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="O23" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="P23" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0.5</v>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>522</v>
+        <v>488</v>
       </c>
       <c r="T23" t="n">
-        <v>122.7</v>
+        <v>141</v>
       </c>
       <c r="U23" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="V23" t="n">
-        <v>1400</v>
+        <v>500</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.228735,69.200014</t>
+          <t>https://www.google.com/maps?q=41.296436,69.332471</t>
         </is>
       </c>
     </row>
@@ -2647,19 +2647,19 @@
         <v>86</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>41.296436</v>
+        <v>41.228735</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>69.332471</v>
+        <v>69.200014</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>41.296436, 69.332471</t>
+          <t>41.228735, 69.200014</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Куксарай махалля</t>
+          <t>Сергели-5A</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2668,48 +2668,48 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4067</v>
+        <v>7101</v>
       </c>
       <c r="M24" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="O24" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>488</v>
+        <v>522</v>
       </c>
       <c r="T24" t="n">
-        <v>141</v>
+        <v>122.7</v>
       </c>
       <c r="U24" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="V24" t="n">
-        <v>600</v>
+        <v>350</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.296436,69.332471</t>
+          <t>https://www.google.com/maps?q=41.228735,69.200014</t>
         </is>
       </c>
     </row>
@@ -2740,19 +2740,19 @@
         <v>85</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>41.31798</v>
+        <v>41.355449</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>69.27772899999999</v>
+        <v>69.286761</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>41.317980, 69.277729</t>
+          <t>41.355449, 69.286761</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Кашгар (Ц-4)</t>
+          <t>Юнусабад-1</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2772,19 +2772,19 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>6739</v>
+        <v>10097</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N25" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="O25" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="P25" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0.5</v>
@@ -2799,10 +2799,10 @@
         <v>139.7</v>
       </c>
       <c r="U25" t="n">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="V25" t="n">
-        <v>700</v>
+        <v>350</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.317980,69.277729</t>
+          <t>https://www.google.com/maps?q=41.355449,69.286761</t>
         </is>
       </c>
     </row>
@@ -2833,19 +2833,19 @@
         <v>85</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>41.355449</v>
+        <v>41.343199</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>69.286761</v>
+        <v>69.207222</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>41.355449, 69.286761</t>
+          <t>41.343199, 69.207222</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Юнусабад-1</t>
+          <t>массив Ниязова</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2854,48 +2854,48 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>10097</v>
+        <v>6689</v>
       </c>
       <c r="M26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N26" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="O26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P26" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0.5</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="T26" t="n">
-        <v>139.7</v>
+        <v>59.2</v>
       </c>
       <c r="U26" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="V26" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.355449,69.286761</t>
+          <t>https://www.google.com/maps?q=41.343199,69.207222</t>
         </is>
       </c>
     </row>
@@ -2923,22 +2923,22 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>41.343199</v>
+        <v>41.31798</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>69.207222</v>
+        <v>69.27772899999999</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>41.343199, 69.207222</t>
+          <t>41.317980, 69.277729</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>массив Ниязова</t>
+          <t>Кашгар (Ц-4)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2954,41 +2954,41 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>6689</v>
+        <v>6739</v>
       </c>
       <c r="M27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="O27" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="P27" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>59.2</v>
+        <v>139.7</v>
       </c>
       <c r="U27" t="n">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="V27" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.343199,69.207222</t>
+          <t>https://www.google.com/maps?q=41.317980,69.277729</t>
         </is>
       </c>
     </row>
@@ -3016,22 +3016,22 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>41.343261</v>
+        <v>41.322155</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>69.29827400000001</v>
+        <v>69.3293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>41.343261, 69.298274</t>
+          <t>41.322155, 69.329300</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Атчапар-1 махалля</t>
+          <t>Алмачи махалля</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3040,48 +3040,48 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>8030</v>
+        <v>8916</v>
       </c>
       <c r="M28" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N28" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="O28" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="P28" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0.5</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="T28" t="n">
-        <v>139.7</v>
+        <v>98.2</v>
       </c>
       <c r="U28" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="V28" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.343261,69.298274</t>
+          <t>https://www.google.com/maps?q=41.322155,69.329300</t>
         </is>
       </c>
     </row>
@@ -3109,22 +3109,22 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>41.247466</v>
+        <v>41.343261</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>69.204497</v>
+        <v>69.29827400000001</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>41.247466, 69.204497</t>
+          <t>41.343261, 69.298274</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Тирсакабад махалля</t>
+          <t>Атчапар-1 махалля</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3133,48 +3133,48 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2020</v>
+        <v>8030</v>
       </c>
       <c r="M29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N29" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="O29" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="P29" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0.5</v>
       </c>
       <c r="R29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>28.3</v>
+        <v>139.7</v>
       </c>
       <c r="U29" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="V29" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.247466,69.204497</t>
+          <t>https://www.google.com/maps?q=41.343261,69.298274</t>
         </is>
       </c>
     </row>
@@ -3202,22 +3202,22 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>41.2728</v>
+        <v>41.247466</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>69.31593100000001</v>
+        <v>69.204497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>41.272800, 69.315931</t>
+          <t>41.247466, 69.204497</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Мухтар Ашрафи улица</t>
+          <t>Тирсакабад махалля</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3226,48 +3226,48 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>11334</v>
+        <v>2020</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P30" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="T30" t="n">
-        <v>141</v>
+        <v>28.3</v>
       </c>
       <c r="U30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V30" t="n">
-        <v>1400</v>
+        <v>350</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.272800,69.315931</t>
+          <t>https://www.google.com/maps?q=41.247466,69.204497</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>41.318137</v>
@@ -3336,13 +3336,13 @@
         <v>5</v>
       </c>
       <c r="N31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P31" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0.5</v>
@@ -3357,7 +3357,7 @@
         <v>141</v>
       </c>
       <c r="U31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V31" t="n">
         <v>1100</v>
@@ -3435,7 +3435,7 @@
         <v>11</v>
       </c>
       <c r="P32" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0.5</v>
@@ -3450,7 +3450,7 @@
         <v>139.7</v>
       </c>
       <c r="U32" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V32" t="n">
         <v>500</v>
@@ -3528,7 +3528,7 @@
         <v>6</v>
       </c>
       <c r="P33" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0.5</v>
@@ -3577,19 +3577,19 @@
         <v>81</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>41.277558</v>
+        <v>41.2728</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>69.335848</v>
+        <v>69.31593100000001</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>41.277558, 69.335848</t>
+          <t>41.272800, 69.315931</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Хосиятли махалля</t>
+          <t>Мухтар Ашрафи улица</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3609,19 +3609,19 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>7484</v>
+        <v>11334</v>
       </c>
       <c r="M34" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N34" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="O34" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P34" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0.5</v>
@@ -3636,10 +3636,10 @@
         <v>141</v>
       </c>
       <c r="U34" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V34" t="n">
-        <v>900</v>
+        <v>2000</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.277558,69.335848</t>
+          <t>https://www.google.com/maps?q=41.272800,69.315931</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>41.211644</v>
+        <v>41.277558</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>69.19953</v>
+        <v>69.335848</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>41.211644, 69.199530</t>
+          <t>41.277558, 69.335848</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Сергели-9А</t>
+          <t>Хосиятли махалля</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3691,30 +3691,30 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>19654</v>
+        <v>7484</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N35" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O35" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P35" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0.5</v>
@@ -3726,13 +3726,13 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>122.7</v>
+        <v>141</v>
       </c>
       <c r="U35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V35" t="n">
-        <v>450</v>
+        <v>4830</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.211644,69.199530</t>
+          <t>https://www.google.com/maps?q=41.277558,69.335848</t>
         </is>
       </c>
     </row>
@@ -3801,13 +3801,13 @@
         <v>6</v>
       </c>
       <c r="N36" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O36" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P36" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0.5</v>
@@ -3825,7 +3825,7 @@
         <v>4</v>
       </c>
       <c r="V36" t="n">
-        <v>10</v>
+        <v>600</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -3853,22 +3853,22 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>41.346824</v>
+        <v>41.211644</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>69.38152599999999</v>
+        <v>69.19953</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>41.346824, 69.381526</t>
+          <t>41.211644, 69.199530</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ахмада Югнаки (Солнечный)</t>
+          <t>Сергели-9А</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3877,30 +3877,30 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>10881</v>
+        <v>19654</v>
       </c>
       <c r="M37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N37" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O37" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P37" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0.5</v>
@@ -3912,13 +3912,13 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>98.2</v>
+        <v>122.7</v>
       </c>
       <c r="U37" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="V37" t="n">
-        <v>10</v>
+        <v>450</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.346824,69.381526</t>
+          <t>https://www.google.com/maps?q=41.211644,69.199530</t>
         </is>
       </c>
     </row>
@@ -3949,19 +3949,19 @@
         <v>79</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>41.323641</v>
+        <v>41.346824</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>69.341219</v>
+        <v>69.38152599999999</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>41.323641, 69.341219</t>
+          <t>41.346824, 69.381526</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Катта Алтынтепа махалля</t>
+          <t>Ахмада Югнаки (Солнечный)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3981,19 +3981,19 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>6442</v>
+        <v>10881</v>
       </c>
       <c r="M38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N38" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="O38" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="P38" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0.5</v>
@@ -4008,10 +4008,10 @@
         <v>98.2</v>
       </c>
       <c r="U38" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="V38" t="n">
-        <v>650</v>
+        <v>250</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.323641,69.341219</t>
+          <t>https://www.google.com/maps?q=41.346824,69.381526</t>
         </is>
       </c>
     </row>
@@ -4039,7 +4039,7 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>41.334298</v>
@@ -4086,7 +4086,7 @@
         <v>24</v>
       </c>
       <c r="P39" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0.5</v>
@@ -4101,7 +4101,7 @@
         <v>59.2</v>
       </c>
       <c r="U39" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="V39" t="n">
         <v>250</v>
@@ -4135,19 +4135,19 @@
         <v>78</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>41.278439</v>
+        <v>41.348912</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>69.379378</v>
+        <v>69.361794</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>41.278439, 69.379378</t>
+          <t>41.348912, 69.361794</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Нурмухаммедов</t>
+          <t>Феруза-2</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4156,30 +4156,30 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>5429</v>
+        <v>6046</v>
       </c>
       <c r="M40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N40" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="O40" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="P40" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
         <v>0.5</v>
@@ -4191,13 +4191,13 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>141</v>
+        <v>98.2</v>
       </c>
       <c r="U40" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="V40" t="n">
-        <v>1500</v>
+        <v>250</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.278439,69.379378</t>
+          <t>https://www.google.com/maps?q=41.348912,69.361794</t>
         </is>
       </c>
     </row>
@@ -4228,19 +4228,19 @@
         <v>78</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>41.286991</v>
+        <v>41.29219</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>69.19375700000001</v>
+        <v>69.189949</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>41.286991, 69.193757</t>
+          <t>41.292190, 69.189949</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Чиланзар Г 9А</t>
+          <t>Чиланзар-14</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4260,19 +4260,19 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>16603</v>
+        <v>22515</v>
       </c>
       <c r="M41" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N41" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="O41" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P41" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0.5</v>
@@ -4287,7 +4287,7 @@
         <v>47.6</v>
       </c>
       <c r="U41" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="V41" t="n">
         <v>70</v>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.286991,69.193757</t>
+          <t>https://www.google.com/maps?q=41.292190,69.189949</t>
         </is>
       </c>
     </row>
@@ -4318,22 +4318,22 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>41.348912</v>
+        <v>41.278439</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>69.361794</v>
+        <v>69.379378</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>41.348912, 69.361794</t>
+          <t>41.278439, 69.379378</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Феруза-2</t>
+          <t>Нурмухаммедов</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4342,30 +4342,30 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>6046</v>
+        <v>5429</v>
       </c>
       <c r="M42" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N42" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="O42" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="P42" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0.5</v>
@@ -4377,13 +4377,13 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>98.2</v>
+        <v>141</v>
       </c>
       <c r="U42" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="V42" t="n">
-        <v>10</v>
+        <v>1500</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.348912,69.361794</t>
+          <t>https://www.google.com/maps?q=41.278439,69.379378</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4411,7 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>41.376688</v>
@@ -4458,7 +4458,7 @@
         <v>9</v>
       </c>
       <c r="P43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0.5</v>
@@ -4595,22 +4595,22 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>41.299391</v>
+        <v>41.265528</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>69.26531</v>
+        <v>69.149665</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>41.299391, 69.265310</t>
+          <t>41.265528, 69.149665</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Багсарай махалля</t>
+          <t>Чиланзар-31</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4619,30 +4619,30 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Яккасарайский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>11879</v>
+        <v>10778</v>
       </c>
       <c r="M45" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="N45" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="O45" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>102</v>
+        <v>11</v>
       </c>
       <c r="Q45" t="n">
         <v>0.5</v>
@@ -4654,13 +4654,13 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>31.8</v>
+        <v>47.6</v>
       </c>
       <c r="U45" t="n">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="V45" t="n">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.299391,69.265310</t>
+          <t>https://www.google.com/maps?q=41.265528,69.149665</t>
         </is>
       </c>
     </row>
@@ -4691,19 +4691,19 @@
         <v>74</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>41.189216</v>
+        <v>41.358935</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>69.210739</v>
+        <v>69.187873</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>41.189216, 69.210739</t>
+          <t>41.358935, 69.187873</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Зарбдор махалля</t>
+          <t>Беруни махалля</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4712,30 +4712,30 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>7571</v>
+        <v>8230</v>
       </c>
       <c r="M46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N46" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="O46" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0.5</v>
@@ -4747,14 +4747,12 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>122.7</v>
+        <v>59.2</v>
       </c>
       <c r="U46" t="n">
-        <v>3</v>
-      </c>
-      <c r="V46" t="n">
-        <v>450</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4767,7 +4765,7 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.189216,69.210739</t>
+          <t>https://www.google.com/maps?q=41.358935,69.187873</t>
         </is>
       </c>
     </row>
@@ -4784,19 +4782,19 @@
         <v>74</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>41.310079</v>
+        <v>41.189216</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>69.24188599999999</v>
+        <v>69.210739</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>41.310079, 69.241886</t>
+          <t>41.189216, 69.210739</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Алмазар массив</t>
+          <t>Зарбдор махалля</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4805,30 +4803,30 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>12235</v>
+        <v>7571</v>
       </c>
       <c r="M47" t="n">
+        <v>2</v>
+      </c>
+      <c r="N47" t="n">
         <v>6</v>
       </c>
-      <c r="N47" t="n">
-        <v>46</v>
-      </c>
       <c r="O47" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="P47" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0.5</v>
@@ -4840,13 +4838,13 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>28.3</v>
+        <v>122.7</v>
       </c>
       <c r="U47" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="V47" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -4860,7 +4858,7 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.310079,69.241886</t>
+          <t>https://www.google.com/maps?q=41.189216,69.210739</t>
         </is>
       </c>
     </row>
@@ -4874,22 +4872,22 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>41.358935</v>
+        <v>41.271397</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>69.187873</v>
+        <v>69.20517700000001</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>41.358935, 69.187873</t>
+          <t>41.271397, 69.205177</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Беруни махалля</t>
+          <t>Наккашлык</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4898,30 +4896,30 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>8230</v>
+        <v>10663</v>
       </c>
       <c r="M48" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N48" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="O48" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="P48" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0.5</v>
@@ -4933,12 +4931,14 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>59.2</v>
+        <v>28.3</v>
       </c>
       <c r="U48" t="n">
-        <v>1</v>
-      </c>
-      <c r="V48" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="V48" t="n">
+        <v>500</v>
+      </c>
       <c r="W48" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.358935,69.187873</t>
+          <t>https://www.google.com/maps?q=41.271397,69.205177</t>
         </is>
       </c>
     </row>
@@ -4965,22 +4965,22 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>41.265528</v>
+        <v>41.299391</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>69.149665</v>
+        <v>69.26531</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>41.265528, 69.149665</t>
+          <t>41.299391, 69.265310</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Чиланзар-31</t>
+          <t>Багсарай махалля</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4989,30 +4989,30 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Яккасарайский район</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>10778</v>
+        <v>11879</v>
       </c>
       <c r="M49" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="N49" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="O49" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="P49" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0.5</v>
@@ -5024,13 +5024,13 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>47.6</v>
+        <v>31.8</v>
       </c>
       <c r="U49" t="n">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="V49" t="n">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.265528,69.149665</t>
+          <t>https://www.google.com/maps?q=41.299391,69.265310</t>
         </is>
       </c>
     </row>
@@ -5061,19 +5061,19 @@
         <v>73</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>41.271397</v>
+        <v>41.310079</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>69.20517700000001</v>
+        <v>69.24188599999999</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>41.271397, 69.205177</t>
+          <t>41.310079, 69.241886</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Наккашлык</t>
+          <t>Алмазар массив</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5093,19 +5093,19 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>10663</v>
+        <v>12235</v>
       </c>
       <c r="M50" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N50" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="O50" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P50" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0.5</v>
@@ -5120,10 +5120,10 @@
         <v>28.3</v>
       </c>
       <c r="U50" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="V50" t="n">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.271397,69.205177</t>
+          <t>https://www.google.com/maps?q=41.310079,69.241886</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
         <v>3</v>
       </c>
       <c r="P51" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0.5</v>
@@ -5244,54 +5244,54 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>41.390081</v>
+        <v>41.283152</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>69.26402400000001</v>
+        <v>69.217376</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>41.390081, 69.264024</t>
+          <t>41.283152, 69.217376</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Дустамабад</t>
+          <t>Чиланзар-4</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2632</v>
+        <v>8748</v>
       </c>
       <c r="M52" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N52" t="n">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="O52" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="P52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0.5</v>
@@ -5303,10 +5303,10 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>139.7</v>
+        <v>28.3</v>
       </c>
       <c r="U52" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="V52" t="n">
         <v>500</v>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.390081,69.264024</t>
+          <t>https://www.google.com/maps?q=41.283152,69.217376</t>
         </is>
       </c>
     </row>
@@ -5337,54 +5337,54 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>41.283644</v>
+        <v>41.390081</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>69.28462</v>
+        <v>69.26402400000001</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>41.283644, 69.284620</t>
+          <t>41.390081, 69.264024</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Сарыкулька</t>
+          <t>Дустамабад</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Мирабадский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>5986</v>
+        <v>2632</v>
       </c>
       <c r="M53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N53" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="O53" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P53" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0.5</v>
@@ -5396,13 +5396,13 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>48.5</v>
+        <v>139.7</v>
       </c>
       <c r="U53" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="V53" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.283644,69.284620</t>
+          <t>https://www.google.com/maps?q=41.390081,69.264024</t>
         </is>
       </c>
     </row>
@@ -5477,7 +5477,7 @@
         <v>8</v>
       </c>
       <c r="P54" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0.5</v>
@@ -5492,7 +5492,7 @@
         <v>122.7</v>
       </c>
       <c r="U54" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V54" t="n">
         <v>150</v>
@@ -5523,54 +5523,54 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>41.283152</v>
+        <v>41.238019</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>69.217376</v>
+        <v>69.346493</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>41.283152, 69.217376</t>
+          <t>41.238019, 69.346493</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Чиланзар-4</t>
+          <t>Бузаучи</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>8748</v>
+        <v>4072</v>
       </c>
       <c r="M55" t="n">
         <v>8</v>
       </c>
       <c r="N55" t="n">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="O55" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="P55" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0.5</v>
@@ -5582,14 +5582,12 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>28.3</v>
+        <v>60.2</v>
       </c>
       <c r="U55" t="n">
-        <v>26</v>
-      </c>
-      <c r="V55" t="n">
-        <v>700</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5602,7 +5600,7 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.283152,69.217376</t>
+          <t>https://www.google.com/maps?q=41.238019,69.346493</t>
         </is>
       </c>
     </row>
@@ -5616,54 +5614,54 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>41.238019</v>
+        <v>41.283644</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>69.346493</v>
+        <v>69.28462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>41.238019, 69.346493</t>
+          <t>41.283644, 69.284620</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Бузаучи</t>
+          <t>Сарыкулька</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Мирабадский район</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>4072</v>
+        <v>5986</v>
       </c>
       <c r="M56" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N56" t="n">
+        <v>33</v>
+      </c>
+      <c r="O56" t="n">
         <v>12</v>
       </c>
-      <c r="O56" t="n">
-        <v>3</v>
-      </c>
       <c r="P56" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
         <v>0.5</v>
@@ -5675,12 +5673,14 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>60.2</v>
+        <v>48.5</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="V56" t="n">
+        <v>500</v>
+      </c>
       <c r="W56" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.238019,69.346493</t>
+          <t>https://www.google.com/maps?q=41.283644,69.284620</t>
         </is>
       </c>
     </row>
@@ -5707,7 +5707,7 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D57" s="2" t="n">
         <v>41.252288</v>
@@ -5754,7 +5754,7 @@
         <v>4</v>
       </c>
       <c r="P57" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0.5</v>
@@ -5803,51 +5803,51 @@
         <v>71</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>41.270832</v>
+        <v>41.228062</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>69.23679199999999</v>
+        <v>69.330381</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>41.270832, 69.236792</t>
+          <t>41.228062, 69.330381</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Дилбулак махалля</t>
+          <t>Бектемир</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>район города</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Яккасарайский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>11138</v>
+        <v>4317</v>
       </c>
       <c r="M58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N58" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="O58" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="P58" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
         <v>0.5</v>
@@ -5859,13 +5859,13 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>31.8</v>
+        <v>60.2</v>
       </c>
       <c r="U58" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="V58" t="n">
-        <v>350</v>
+        <v>90</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.270832,69.236792</t>
+          <t>https://www.google.com/maps?q=41.228062,69.330381</t>
         </is>
       </c>
     </row>
@@ -5896,51 +5896,51 @@
         <v>71</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>41.228062</v>
+        <v>41.267555</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>69.330381</v>
+        <v>69.22878900000001</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>41.228062, 69.330381</t>
+          <t>41.267555, 69.228789</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Бектемир</t>
+          <t>Яккасарай махалля</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>район города</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Яккасарайский район</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>4317</v>
+        <v>9446</v>
       </c>
       <c r="M59" t="n">
         <v>6</v>
       </c>
       <c r="N59" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="O59" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="P59" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0.5</v>
@@ -5952,13 +5952,13 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>60.2</v>
+        <v>31.8</v>
       </c>
       <c r="U59" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="V59" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.228062,69.330381</t>
+          <t>https://www.google.com/maps?q=41.267555,69.228789</t>
         </is>
       </c>
     </row>
@@ -5989,19 +5989,19 @@
         <v>70</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>41.368494</v>
+        <v>41.272327</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>69.227745</v>
+        <v>69.24869700000001</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>41.368494, 69.227745</t>
+          <t>41.272327, 69.248697</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Янги Ташкент махалля</t>
+          <t>Башлык</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6010,30 +6010,30 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Яккасарайский район</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2965</v>
+        <v>9907</v>
       </c>
       <c r="M60" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N60" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="O60" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="P60" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>0.5</v>
@@ -6045,13 +6045,13 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>59.2</v>
+        <v>31.8</v>
       </c>
       <c r="U60" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="V60" t="n">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.368494,69.227745</t>
+          <t>https://www.google.com/maps?q=41.272327,69.248697</t>
         </is>
       </c>
     </row>
@@ -6082,51 +6082,51 @@
         <v>70</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>41.277832</v>
+        <v>41.368494</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>69.130234</v>
+        <v>69.227745</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>41.277832, 69.130234</t>
+          <t>41.368494, 69.227745</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Дамачи</t>
+          <t>Янги Ташкент махалля</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1699</v>
+        <v>2965</v>
       </c>
       <c r="M61" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N61" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="O61" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="P61" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
         <v>0.5</v>
@@ -6138,13 +6138,13 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>184.9</v>
+        <v>59.2</v>
       </c>
       <c r="U61" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V61" t="n">
-        <v>2</v>
+        <v>1200</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.277832,69.130234</t>
+          <t>https://www.google.com/maps?q=41.368494,69.227745</t>
         </is>
       </c>
     </row>
@@ -6219,7 +6219,7 @@
         <v>8</v>
       </c>
       <c r="P62" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>5</v>
@@ -6234,7 +6234,7 @@
         <v>213.9</v>
       </c>
       <c r="U62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V62" t="n">
         <v>500</v>
@@ -6265,7 +6265,7 @@
         <v>6</v>
       </c>
       <c r="C63" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D63" s="2" t="n">
         <v>41.388009</v>
@@ -6312,7 +6312,7 @@
         <v>9</v>
       </c>
       <c r="P63" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>5</v>
@@ -6327,7 +6327,7 @@
         <v>270.6</v>
       </c>
       <c r="U63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V63" t="n">
         <v>750</v>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C64" t="n">
         <v>84</v>
@@ -6405,7 +6405,7 @@
         <v>9</v>
       </c>
       <c r="P64" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="Q64" t="n">
         <v>5</v>
@@ -6420,7 +6420,7 @@
         <v>184.9</v>
       </c>
       <c r="U64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V64" t="n">
         <v>200</v>
@@ -6451,7 +6451,7 @@
         <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D65" s="2" t="n">
         <v>41.359471</v>
@@ -6498,7 +6498,7 @@
         <v>6</v>
       </c>
       <c r="P65" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Q65" t="n">
         <v>5</v>
@@ -6634,7 +6634,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C67" t="n">
         <v>83</v>
@@ -6684,7 +6684,7 @@
         <v>7</v>
       </c>
       <c r="P67" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>5</v>
@@ -6699,9 +6699,11 @@
         <v>213.9</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
-      </c>
-      <c r="V67" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1300</v>
+      </c>
       <c r="W67" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6775,7 +6777,7 @@
         <v>4</v>
       </c>
       <c r="P68" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q68" t="n">
         <v>5</v>
@@ -6793,7 +6795,7 @@
         <v>1</v>
       </c>
       <c r="V68" t="n">
-        <v>2400</v>
+        <v>600</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
@@ -6868,7 +6870,7 @@
         <v>6</v>
       </c>
       <c r="P69" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Q69" t="n">
         <v>5</v>
@@ -6883,10 +6885,10 @@
         <v>270.6</v>
       </c>
       <c r="U69" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V69" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
@@ -6911,7 +6913,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C70" t="n">
         <v>87</v>
@@ -6961,7 +6963,7 @@
         <v>4</v>
       </c>
       <c r="P70" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q70" t="n">
         <v>5</v>
@@ -7054,7 +7056,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Q71" t="n">
         <v>5</v>
@@ -7095,74 +7097,76 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C72" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>41.324284</v>
+        <v>41.374181</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>69.483728</v>
+        <v>69.382386</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>41.324284, 69.483728</t>
+          <t>41.374181, 69.382386</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Китай-Тепа</t>
+          <t>ТТЗ-4</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>1.1</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Юкоричирчикский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1851</v>
+        <v>2023</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q72" t="n">
         <v>5</v>
       </c>
       <c r="R72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S72" t="n">
-        <v>1673</v>
+        <v>2347</v>
       </c>
       <c r="T72" t="n">
-        <v>151.7</v>
+        <v>213.9</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
-      </c>
-      <c r="V72" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V72" t="n">
+        <v>500</v>
+      </c>
       <c r="W72" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7170,12 +7174,12 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.324284,69.483728</t>
+          <t>https://www.google.com/maps?q=41.374181,69.382386</t>
         </is>
       </c>
     </row>
@@ -7186,76 +7190,74 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C73" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>41.402834</v>
+        <v>41.324284</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>69.220811</v>
+        <v>69.483728</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>41.402834, 69.220811</t>
+          <t>41.324284, 69.483728</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Абдурахманов</t>
+          <t>Китай-Тепа</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J73" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Юкоричирчикский район</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2527</v>
+        <v>1851</v>
       </c>
       <c r="M73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
         <v>5</v>
       </c>
       <c r="R73" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S73" t="n">
-        <v>2480</v>
+        <v>1673</v>
       </c>
       <c r="T73" t="n">
-        <v>270.6</v>
+        <v>151.7</v>
       </c>
       <c r="U73" t="n">
-        <v>4</v>
-      </c>
-      <c r="V73" t="n">
-        <v>840</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V73" t="inlineStr"/>
       <c r="W73" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7263,12 +7265,12 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.402834,69.220811</t>
+          <t>https://www.google.com/maps?q=41.324284,69.483728</t>
         </is>
       </c>
     </row>
@@ -7279,25 +7281,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C74" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>41.401834</v>
+        <v>41.402834</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>69.276258</v>
+        <v>69.220811</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>41.401834, 69.276258</t>
+          <t>41.402834, 69.220811</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Дустамабад</t>
+          <t>Абдурахманов</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7306,7 +7308,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>1.2</v>
@@ -7317,36 +7319,38 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2226</v>
+        <v>2527</v>
       </c>
       <c r="M74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
       </c>
       <c r="P74" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q74" t="n">
         <v>5</v>
       </c>
       <c r="R74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="S74" t="n">
-        <v>12149</v>
+        <v>2480</v>
       </c>
       <c r="T74" t="n">
         <v>270.6</v>
       </c>
       <c r="U74" t="n">
-        <v>2</v>
-      </c>
-      <c r="V74" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="V74" t="n">
+        <v>840</v>
+      </c>
       <c r="W74" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7359,7 +7363,7 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.401834,69.276258</t>
+          <t>https://www.google.com/maps?q=41.402834,69.220811</t>
         </is>
       </c>
     </row>
@@ -7370,72 +7374,72 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C75" t="n">
         <v>76</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>41.316805</v>
+        <v>41.401834</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>69.51514299999999</v>
+        <v>69.276258</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>41.316805, 69.515143</t>
+          <t>41.401834, 69.276258</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Янгибазар</t>
+          <t>Дустамабад</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J75" t="n">
         <v>1.2</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Юкоричирчикский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2621</v>
+        <v>2226</v>
       </c>
       <c r="M75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N75" t="n">
         <v>2</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
       </c>
       <c r="R75" t="n">
+        <v>10</v>
+      </c>
+      <c r="S75" t="n">
+        <v>12149</v>
+      </c>
+      <c r="T75" t="n">
+        <v>270.6</v>
+      </c>
+      <c r="U75" t="n">
         <v>2</v>
-      </c>
-      <c r="S75" t="n">
-        <v>1373</v>
-      </c>
-      <c r="T75" t="n">
-        <v>151.7</v>
-      </c>
-      <c r="U75" t="n">
-        <v>0</v>
       </c>
       <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr">
@@ -7450,7 +7454,7 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.316805,69.515143</t>
+          <t>https://www.google.com/maps?q=41.401834,69.276258</t>
         </is>
       </c>
     </row>
@@ -7461,69 +7465,69 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C76" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>41.276459</v>
+        <v>41.316805</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>69.110428</v>
+        <v>69.51514299999999</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>41.276459, 69.110428</t>
+          <t>41.316805, 69.515143</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Мевазар</t>
+          <t>Янгибазар</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J76" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Юкоричирчикский район</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2345</v>
+        <v>2621</v>
       </c>
       <c r="M76" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q76" t="n">
         <v>5</v>
       </c>
       <c r="R76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S76" t="n">
-        <v>4564</v>
+        <v>1373</v>
       </c>
       <c r="T76" t="n">
-        <v>184.9</v>
+        <v>151.7</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -7541,7 +7545,7 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.276459,69.110428</t>
+          <t>https://www.google.com/maps?q=41.316805,69.515143</t>
         </is>
       </c>
     </row>
@@ -7552,25 +7556,25 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C77" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>41.375967</v>
+        <v>41.276459</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>69.37848099999999</v>
+        <v>69.110428</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>41.375967, 69.378481</t>
+          <t>41.276459, 69.110428</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ялангач</t>
+          <t>Мевазар</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -7579,49 +7583,47 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2081</v>
+        <v>2345</v>
       </c>
       <c r="M77" t="n">
         <v>4</v>
       </c>
       <c r="N77" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q77" t="n">
         <v>5</v>
       </c>
       <c r="R77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S77" t="n">
-        <v>2347</v>
+        <v>4564</v>
       </c>
       <c r="T77" t="n">
-        <v>213.9</v>
+        <v>184.9</v>
       </c>
       <c r="U77" t="n">
-        <v>1</v>
-      </c>
-      <c r="V77" t="n">
-        <v>1400</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V77" t="inlineStr"/>
       <c r="W77" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7634,7 +7636,7 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.375967,69.378481</t>
+          <t>https://www.google.com/maps?q=41.276459,69.110428</t>
         </is>
       </c>
     </row>
@@ -7645,7 +7647,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C78" t="n">
         <v>76</v>
@@ -7829,10 +7831,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C80" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D80" s="2" t="n">
         <v>41.399761</v>
@@ -7879,7 +7881,7 @@
         <v>2</v>
       </c>
       <c r="P80" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
         <v>5</v>
@@ -7894,7 +7896,7 @@
         <v>213.9</v>
       </c>
       <c r="U80" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V80" t="n">
         <v>1000</v>
@@ -7972,7 +7974,7 @@
         <v>4</v>
       </c>
       <c r="P81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
         <v>5</v>
@@ -8013,7 +8015,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C82" t="n">
         <v>76</v>
@@ -8156,7 +8158,7 @@
         <v>4</v>
       </c>
       <c r="P83" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q83" t="n">
         <v>5</v>
@@ -8199,10 +8201,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C84" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D84" s="2" t="n">
         <v>41.241734</v>
@@ -8249,7 +8251,7 @@
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Q84" t="n">
         <v>5</v>
@@ -8264,7 +8266,7 @@
         <v>184.9</v>
       </c>
       <c r="U84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V84" t="n">
         <v>1840</v>
@@ -8292,7 +8294,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C85" t="n">
         <v>87</v>
@@ -8357,7 +8359,7 @@
         <v>270.6</v>
       </c>
       <c r="U85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V85" t="n">
         <v>840</v>
@@ -8571,10 +8573,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C88" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D88" s="2" t="n">
         <v>41.308872</v>
@@ -8621,7 +8623,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q88" t="n">
         <v>5</v>
@@ -8753,7 +8755,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C90" t="n">
         <v>76</v>
@@ -8847,7 +8849,7 @@
         <v>42</v>
       </c>
       <c r="C91" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D91" s="2" t="n">
         <v>41.380099</v>
@@ -8909,9 +8911,11 @@
         <v>213.9</v>
       </c>
       <c r="U91" t="n">
-        <v>0</v>
-      </c>
-      <c r="V91" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V91" t="n">
+        <v>1300</v>
+      </c>
       <c r="W91" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8935,7 +8939,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C92" t="n">
         <v>76</v>
@@ -9117,7 +9121,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C94" t="n">
         <v>81</v>
@@ -9393,7 +9397,7 @@
         <v>33</v>
       </c>
       <c r="C97" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D97" s="2" t="n">
         <v>41.358385</v>
@@ -9546,11 +9550,9 @@
         <v>270.6</v>
       </c>
       <c r="U98" t="n">
-        <v>1</v>
-      </c>
-      <c r="V98" t="n">
-        <v>1200</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V98" t="inlineStr"/>
       <c r="W98" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -9847,7 +9849,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C102" t="n">
         <v>76</v>
@@ -10211,7 +10213,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C106" t="n">
         <v>82</v>
@@ -10393,10 +10395,10 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C108" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D108" s="2" t="n">
         <v>41.445785</v>
@@ -10763,7 +10765,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C112" t="n">
         <v>81</v>
@@ -10854,7 +10856,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C113" t="n">
         <v>76</v>
@@ -10945,7 +10947,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C114" t="n">
         <v>81</v>
@@ -11036,10 +11038,10 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C115" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D115" s="2" t="n">
         <v>41.039806</v>
@@ -11086,7 +11088,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q115" t="n">
         <v>5</v>
@@ -11127,7 +11129,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C116" t="n">
         <v>80</v>
@@ -11218,7 +11220,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C117" t="n">
         <v>83</v>
@@ -11309,7 +11311,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C118" t="n">
         <v>81</v>
@@ -11359,7 +11361,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q118" t="n">
         <v>5</v>
@@ -11400,7 +11402,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C119" t="n">
         <v>76</v>
@@ -11582,7 +11584,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C121" t="n">
         <v>76</v>
@@ -11632,7 +11634,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q121" t="n">
         <v>5</v>
@@ -11949,7 +11951,7 @@
         <v>2</v>
       </c>
       <c r="C125" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D125" s="2" t="n">
         <v>41.56088</v>
@@ -11996,7 +11998,7 @@
         <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q125" t="n">
         <v>5</v>
@@ -12313,7 +12315,7 @@
         <v>3</v>
       </c>
       <c r="C129" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D129" s="2" t="n">
         <v>41.572586</v>
@@ -12360,7 +12362,7 @@
         <v>0</v>
       </c>
       <c r="P129" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q129" t="n">
         <v>5</v>
@@ -13285,11 +13287,9 @@
         <v>37.9</v>
       </c>
       <c r="U139" t="n">
-        <v>1</v>
-      </c>
-      <c r="V139" t="n">
-        <v>1800</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V139" t="inlineStr"/>
       <c r="W139" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -13378,11 +13378,9 @@
         <v>37.9</v>
       </c>
       <c r="U140" t="n">
-        <v>1</v>
-      </c>
-      <c r="V140" t="n">
-        <v>1800</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V140" t="inlineStr"/>
       <c r="W140" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -13653,11 +13651,9 @@
         <v>37.9</v>
       </c>
       <c r="U143" t="n">
-        <v>1</v>
-      </c>
-      <c r="V143" t="n">
-        <v>1800</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V143" t="inlineStr"/>
       <c r="W143" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -14045,7 +14041,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C148" t="n">
         <v>49</v>
@@ -15048,7 +15044,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C159" t="n">
         <v>49</v>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -846,7 +846,7 @@
         <v>48.5</v>
       </c>
       <c r="U4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V4" t="n">
         <v>1400</v>
@@ -939,7 +939,7 @@
         <v>98.2</v>
       </c>
       <c r="U5" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="V5" t="n">
         <v>500</v>
@@ -1032,7 +1032,7 @@
         <v>139.7</v>
       </c>
       <c r="U6" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="V6" t="n">
         <v>350</v>
@@ -1125,7 +1125,7 @@
         <v>98.2</v>
       </c>
       <c r="U7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="V7" t="n">
         <v>650</v>
@@ -1311,10 +1311,10 @@
         <v>139.7</v>
       </c>
       <c r="U9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V9" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>48.5</v>
       </c>
       <c r="U11" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="V11" t="n">
         <v>700</v>
@@ -1590,7 +1590,7 @@
         <v>98.2</v>
       </c>
       <c r="U12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="V12" t="n">
         <v>500</v>
@@ -1683,7 +1683,7 @@
         <v>31.8</v>
       </c>
       <c r="U13" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="V13" t="n">
         <v>500</v>
@@ -1776,10 +1776,10 @@
         <v>141</v>
       </c>
       <c r="U14" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="V14" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>141</v>
       </c>
       <c r="U15" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="V15" t="n">
         <v>500</v>
@@ -1962,7 +1962,7 @@
         <v>59.2</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V16" t="n">
         <v>570</v>
@@ -2055,7 +2055,7 @@
         <v>139.7</v>
       </c>
       <c r="U17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="V17" t="n">
         <v>450</v>
@@ -2148,7 +2148,7 @@
         <v>122.7</v>
       </c>
       <c r="U18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V18" t="n">
         <v>350</v>
@@ -2241,7 +2241,7 @@
         <v>98.2</v>
       </c>
       <c r="U19" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="V19" t="n">
         <v>500</v>
@@ -2334,7 +2334,7 @@
         <v>98.2</v>
       </c>
       <c r="U20" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="V20" t="n">
         <v>500</v>
@@ -2427,7 +2427,7 @@
         <v>139.7</v>
       </c>
       <c r="U21" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="V21" t="n">
         <v>700</v>
@@ -2520,7 +2520,7 @@
         <v>139.7</v>
       </c>
       <c r="U22" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="V22" t="n">
         <v>350</v>
@@ -2613,7 +2613,7 @@
         <v>59.2</v>
       </c>
       <c r="U23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V23" t="n">
         <v>500</v>
@@ -2706,7 +2706,7 @@
         <v>139.7</v>
       </c>
       <c r="U24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="V24" t="n">
         <v>300</v>
@@ -2799,10 +2799,10 @@
         <v>139.7</v>
       </c>
       <c r="U25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V25" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>141</v>
       </c>
       <c r="U26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V26" t="n">
         <v>10</v>
@@ -2985,7 +2985,7 @@
         <v>28.3</v>
       </c>
       <c r="U27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V27" t="n">
         <v>350</v>
@@ -3078,7 +3078,7 @@
         <v>122.7</v>
       </c>
       <c r="U28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V28" t="n">
         <v>450</v>
@@ -3262,7 +3262,7 @@
         <v>98.2</v>
       </c>
       <c r="U30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V30" t="n">
         <v>10</v>
@@ -3358,7 +3358,7 @@
         <v>8</v>
       </c>
       <c r="V31" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>98.2</v>
       </c>
       <c r="U34" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V34" t="n">
         <v>10</v>
@@ -3727,10 +3727,10 @@
         <v>139.7</v>
       </c>
       <c r="U35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V35" t="n">
-        <v>500</v>
+        <v>1120</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>47.6</v>
       </c>
       <c r="U38" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="V38" t="n">
         <v>70</v>
@@ -4190,10 +4190,10 @@
         <v>139.7</v>
       </c>
       <c r="U40" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V40" t="n">
-        <v>500</v>
+        <v>1120</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>28.3</v>
       </c>
       <c r="U42" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="V42" t="n">
         <v>500</v>
@@ -4562,7 +4562,7 @@
         <v>48.5</v>
       </c>
       <c r="U44" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="V44" t="n">
         <v>500</v>
@@ -4655,10 +4655,10 @@
         <v>31.8</v>
       </c>
       <c r="U45" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="V45" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
         <v>28.3</v>
       </c>
       <c r="U46" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="V46" t="n">
         <v>500</v>
@@ -5025,7 +5025,7 @@
         <v>59.2</v>
       </c>
       <c r="U49" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V49" t="n">
         <v>1200</v>
@@ -5302,7 +5302,7 @@
         <v>31.8</v>
       </c>
       <c r="U52" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="V52" t="n">
         <v>500</v>
@@ -6040,7 +6040,7 @@
         <v>28.3</v>
       </c>
       <c r="U60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V60" t="n">
         <v>350</v>
@@ -6410,7 +6410,7 @@
         <v>184.9</v>
       </c>
       <c r="U64" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V64" t="n">
         <v>200</v>
@@ -6503,7 +6503,7 @@
         <v>213.9</v>
       </c>
       <c r="U65" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V65" t="n">
         <v>250</v>
@@ -6596,9 +6596,11 @@
         <v>184.9</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V66" t="n">
+        <v>250</v>
+      </c>
       <c r="W66" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6690,7 +6692,7 @@
         <v>1</v>
       </c>
       <c r="V67" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
@@ -6780,7 +6782,7 @@
         <v>184.9</v>
       </c>
       <c r="U68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V68" t="n">
         <v>600</v>
@@ -6873,7 +6875,7 @@
         <v>270.6</v>
       </c>
       <c r="U69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V69" t="n">
         <v>300</v>
@@ -7334,7 +7336,7 @@
         <v>270.6</v>
       </c>
       <c r="U74" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V74" t="n">
         <v>840</v>
@@ -7791,9 +7793,11 @@
         <v>270.6</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
-      </c>
-      <c r="V79" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V79" t="n">
+        <v>250</v>
+      </c>
       <c r="W79" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7882,9 +7886,11 @@
         <v>184.9</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
-      </c>
-      <c r="V80" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V80" t="n">
+        <v>2600</v>
+      </c>
       <c r="W80" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7973,7 +7979,7 @@
         <v>213.9</v>
       </c>
       <c r="U81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V81" t="n">
         <v>1000</v>
@@ -8157,7 +8163,7 @@
         <v>213.9</v>
       </c>
       <c r="U83" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V83" t="n">
         <v>1000</v>
@@ -8250,7 +8256,7 @@
         <v>213.9</v>
       </c>
       <c r="U84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V84" t="n">
         <v>1100</v>
@@ -8622,7 +8628,7 @@
         <v>213.9</v>
       </c>
       <c r="U88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V88" t="n">
         <v>1100</v>
@@ -8991,7 +8997,7 @@
         <v>1</v>
       </c>
       <c r="V92" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="W92" t="inlineStr">
         <is>
@@ -10628,7 +10634,7 @@
         <v>40.8</v>
       </c>
       <c r="U110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V110" t="n">
         <v>4068</v>
@@ -14824,9 +14830,11 @@
         <v>147.5</v>
       </c>
       <c r="U156" t="n">
-        <v>0</v>
-      </c>
-      <c r="V156" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V156" t="n">
+        <v>140</v>
+      </c>
       <c r="W156" t="inlineStr">
         <is>
           <t>рекомендуемая</t>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -598,7 +598,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>41.275234</v>
@@ -645,7 +645,7 @@
         <v>21</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="Q2" t="n">
         <v>0.5</v>
@@ -738,7 +738,7 @@
         <v>12</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="Q3" t="n">
         <v>0.5</v>
@@ -784,7 +784,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>41.273095</v>
@@ -831,7 +831,7 @@
         <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="Q4" t="n">
         <v>0.5</v>
@@ -849,7 +849,7 @@
         <v>8</v>
       </c>
       <c r="V4" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -877,22 +877,22 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>41.335981</v>
+        <v>41.302521</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>69.321806</v>
+        <v>69.281226</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>41.335981, 69.321806</t>
+          <t>41.302521, 69.281226</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Буюк Ипак Йули махалля</t>
+          <t>Айбек</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -901,48 +901,48 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Мирабадский район</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5082</v>
+        <v>6299</v>
       </c>
       <c r="M5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="Q5" t="n">
         <v>0.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>1600</v>
+        <v>610</v>
       </c>
       <c r="T5" t="n">
-        <v>98.2</v>
+        <v>48.5</v>
       </c>
       <c r="U5" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="V5" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.335981,69.321806</t>
+          <t>https://www.google.com/maps?q=41.302521,69.281226</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>41.329729</v>
@@ -1017,7 +1017,7 @@
         <v>23</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="Q6" t="n">
         <v>0.5</v>
@@ -1032,7 +1032,7 @@
         <v>139.7</v>
       </c>
       <c r="U6" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="V6" t="n">
         <v>350</v>
@@ -1066,19 +1066,19 @@
         <v>91</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>41.347726</v>
+        <v>41.332561</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>69.334041</v>
+        <v>69.321702</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>41.347726, 69.334041</t>
+          <t>41.332561, 69.321702</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Навнихол махалля</t>
+          <t>Буюк Ипак Йули махалля</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1098,37 +1098,37 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>8650</v>
+        <v>4166</v>
       </c>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
+        <v>33</v>
+      </c>
+      <c r="O7" t="n">
+        <v>15</v>
+      </c>
+      <c r="P7" t="n">
         <v>24</v>
-      </c>
-      <c r="O7" t="n">
-        <v>9</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>0.5</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>1122</v>
+        <v>1970</v>
       </c>
       <c r="T7" t="n">
         <v>98.2</v>
       </c>
       <c r="U7" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="V7" t="n">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.347726,69.334041</t>
+          <t>https://www.google.com/maps?q=41.332561,69.321702</t>
         </is>
       </c>
     </row>
@@ -1159,19 +1159,19 @@
         <v>91</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>41.365403</v>
+        <v>41.367635</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>69.393992</v>
+        <v>69.275244</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>41.365403, 69.393992</t>
+          <t>41.367635, 69.275244</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ТТЗ-4</t>
+          <t>Туркистан махалля</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1187,23 +1187,23 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>13404</v>
+        <v>15593</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N8" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="Q8" t="n">
         <v>0.5</v>
@@ -1212,16 +1212,16 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>1200</v>
+        <v>438</v>
       </c>
       <c r="T8" t="n">
-        <v>213.9</v>
+        <v>139.7</v>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="V8" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.365403,69.393992</t>
+          <t>https://www.google.com/maps?q=41.367635,69.275244</t>
         </is>
       </c>
     </row>
@@ -1252,19 +1252,19 @@
         <v>91</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>41.367635</v>
+        <v>41.347726</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>69.275244</v>
+        <v>69.334041</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>41.367635, 69.275244</t>
+          <t>41.347726, 69.334041</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Туркистан махалля</t>
+          <t>Навнихол махалля</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1273,48 +1273,48 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>15593</v>
+        <v>8650</v>
       </c>
       <c r="M9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N9" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="O9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q9" t="n">
         <v>0.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>438</v>
+        <v>1122</v>
       </c>
       <c r="T9" t="n">
-        <v>139.7</v>
+        <v>98.2</v>
       </c>
       <c r="U9" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="V9" t="n">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.367635,69.275244</t>
+          <t>https://www.google.com/maps?q=41.347726,69.334041</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>41.345911</v>
+        <v>41.309964</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>69.246887</v>
+        <v>69.34079800000001</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>41.345911, 69.246887</t>
+          <t>41.309964, 69.340798</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Карасарай махалля</t>
+          <t>Авайхан махалля</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1366,30 +1366,30 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>14912</v>
+        <v>9976</v>
       </c>
       <c r="M10" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N10" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="O10" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="Q10" t="n">
         <v>0.5</v>
@@ -1398,16 +1398,16 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>252</v>
+        <v>500</v>
       </c>
       <c r="T10" t="n">
-        <v>59.2</v>
+        <v>98.2</v>
       </c>
       <c r="U10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.345911,69.246887</t>
+          <t>https://www.google.com/maps?q=41.309964,69.340798</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1435,22 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>41.302521</v>
+        <v>41.365403</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>69.281226</v>
+        <v>69.393992</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>41.302521, 69.281226</t>
+          <t>41.365403, 69.393992</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Айбек</t>
+          <t>ТТЗ-4</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1459,48 +1459,48 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Мирабадский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>6299</v>
+        <v>13404</v>
       </c>
       <c r="M11" t="n">
+        <v>3</v>
+      </c>
+      <c r="N11" t="n">
+        <v>16</v>
+      </c>
+      <c r="O11" t="n">
+        <v>8</v>
+      </c>
+      <c r="P11" t="n">
         <v>4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>46</v>
-      </c>
-      <c r="O11" t="n">
-        <v>18</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0.5</v>
       </c>
       <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1200</v>
+      </c>
+      <c r="T11" t="n">
+        <v>213.9</v>
+      </c>
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="S11" t="n">
-        <v>610</v>
-      </c>
-      <c r="T11" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>72</v>
-      </c>
       <c r="V11" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.302521,69.281226</t>
+          <t>https://www.google.com/maps?q=41.365403,69.393992</t>
         </is>
       </c>
     </row>
@@ -1531,19 +1531,19 @@
         <v>90</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>41.309964</v>
+        <v>41.345911</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>69.34079800000001</v>
+        <v>69.246887</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>41.309964, 69.340798</t>
+          <t>41.345911, 69.246887</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Авайхан махалля</t>
+          <t>Карасарай махалля</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1552,30 +1552,30 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>9976</v>
+        <v>14912</v>
       </c>
       <c r="M12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N12" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="O12" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="Q12" t="n">
         <v>0.5</v>
@@ -1584,16 +1584,16 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>500</v>
+        <v>252</v>
       </c>
       <c r="T12" t="n">
-        <v>98.2</v>
+        <v>59.2</v>
       </c>
       <c r="U12" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="V12" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.309964,69.340798</t>
+          <t>https://www.google.com/maps?q=41.345911,69.246887</t>
         </is>
       </c>
     </row>
@@ -1624,19 +1624,19 @@
         <v>90</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>41.284507</v>
+        <v>41.293314</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>69.237188</v>
+        <v>69.316553</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>41.284507, 69.237188</t>
+          <t>41.293314, 69.316553</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ракат махалля</t>
+          <t>Ширинабад махалля</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1645,45 +1645,45 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Яккасарайский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>7882</v>
+        <v>6723</v>
       </c>
       <c r="M13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="O13" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="Q13" t="n">
         <v>0.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>312</v>
+        <v>664</v>
       </c>
       <c r="T13" t="n">
-        <v>31.8</v>
+        <v>141</v>
       </c>
       <c r="U13" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="V13" t="n">
         <v>500</v>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.284507,69.237188</t>
+          <t>https://www.google.com/maps?q=41.293314,69.316553</t>
         </is>
       </c>
     </row>
@@ -1714,22 +1714,22 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>41.293314</v>
+        <v>41.308774</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>69.316553</v>
+        <v>69.31306499999999</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>41.293314, 69.316553</t>
+          <t>41.308774, 69.313065</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ширинабад махалля</t>
+          <t>Машинасозлар (Ташсельмаш)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1749,34 +1749,34 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6723</v>
+        <v>6677</v>
       </c>
       <c r="M14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="O14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="Q14" t="n">
         <v>0.5</v>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>664</v>
+        <v>446</v>
       </c>
       <c r="T14" t="n">
         <v>141</v>
       </c>
       <c r="U14" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="V14" t="n">
         <v>500</v>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.293314,69.316553</t>
+          <t>https://www.google.com/maps?q=41.308774,69.313065</t>
         </is>
       </c>
     </row>
@@ -1810,19 +1810,19 @@
         <v>89</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>41.308774</v>
+        <v>41.284507</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>69.31306499999999</v>
+        <v>69.237188</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41.308774, 69.313065</t>
+          <t>41.284507, 69.237188</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Машинасозлар (Ташсельмаш)</t>
+          <t>Ракат махалля</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1838,23 +1838,23 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Яккасарайский район</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6677</v>
+        <v>7882</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N15" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="O15" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="Q15" t="n">
         <v>0.5</v>
@@ -1863,13 +1863,13 @@
         <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>446</v>
+        <v>312</v>
       </c>
       <c r="T15" t="n">
-        <v>141</v>
+        <v>31.8</v>
       </c>
       <c r="U15" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="V15" t="n">
         <v>500</v>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.308774,69.313065</t>
+          <t>https://www.google.com/maps?q=41.284507,69.237188</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
         <v>11</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q16" t="n">
         <v>0.5</v>
@@ -1962,10 +1962,10 @@
         <v>59.2</v>
       </c>
       <c r="U16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V16" t="n">
-        <v>570</v>
+        <v>200</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -1996,19 +1996,19 @@
         <v>88</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>41.350681</v>
+        <v>41.228735</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>69.266822</v>
+        <v>69.200014</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>41.350681, 69.266822</t>
+          <t>41.228735, 69.200014</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Джами махалля</t>
+          <t>Сергели-5A</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2017,48 +2017,48 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4950</v>
+        <v>7101</v>
       </c>
       <c r="M17" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="O17" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q17" t="n">
         <v>0.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
-        <v>126</v>
+        <v>522</v>
       </c>
       <c r="T17" t="n">
-        <v>139.7</v>
+        <v>122.7</v>
       </c>
       <c r="U17" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="V17" t="n">
-        <v>450</v>
+        <v>1400</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.350681,69.266822</t>
+          <t>https://www.google.com/maps?q=41.228735,69.200014</t>
         </is>
       </c>
     </row>
@@ -2089,19 +2089,19 @@
         <v>88</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>41.228735</v>
+        <v>41.350681</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>69.200014</v>
+        <v>69.266822</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>41.228735, 69.200014</t>
+          <t>41.350681, 69.266822</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Сергели-5A</t>
+          <t>Джами махалля</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2110,48 +2110,48 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>7101</v>
+        <v>4950</v>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N18" t="n">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="O18" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Q18" t="n">
         <v>0.5</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>522</v>
+        <v>126</v>
       </c>
       <c r="T18" t="n">
-        <v>122.7</v>
+        <v>139.7</v>
       </c>
       <c r="U18" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="V18" t="n">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.228735,69.200014</t>
+          <t>https://www.google.com/maps?q=41.350681,69.266822</t>
         </is>
       </c>
     </row>
@@ -2179,22 +2179,22 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>41.324234</v>
+        <v>41.31798</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>69.309575</v>
+        <v>69.27772899999999</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>41.324234, 69.309575</t>
+          <t>41.317980, 69.277729</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Янги Алмачи махалля</t>
+          <t>Кашгар (Ц-4)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2203,48 +2203,48 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3778</v>
+        <v>6739</v>
       </c>
       <c r="M19" t="n">
         <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="O19" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q19" t="n">
         <v>0.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>98.2</v>
+        <v>139.7</v>
       </c>
       <c r="U19" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="V19" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.324234,69.309575</t>
+          <t>https://www.google.com/maps?q=41.317980,69.277729</t>
         </is>
       </c>
     </row>
@@ -2272,22 +2272,22 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>41.322155</v>
+        <v>41.351883</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>69.3293</v>
+        <v>69.294573</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>41.322155, 69.329300</t>
+          <t>41.351883, 69.294573</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Алмачи махалля</t>
+          <t>Атчапар-1 махалля</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2296,48 +2296,48 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>8916</v>
+        <v>7012</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="O20" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Q20" t="n">
         <v>0.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>98.2</v>
+        <v>139.7</v>
       </c>
       <c r="U20" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="V20" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.322155,69.329300</t>
+          <t>https://www.google.com/maps?q=41.351883,69.294573</t>
         </is>
       </c>
     </row>
@@ -2365,22 +2365,22 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>41.31798</v>
+        <v>41.370618</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>69.27772899999999</v>
+        <v>69.29909600000001</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>41.317980, 69.277729</t>
+          <t>41.370618, 69.299096</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Кашгар (Ц-4)</t>
+          <t>Юнусабад 13-й квартал</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2400,19 +2400,19 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6739</v>
+        <v>22705</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="O21" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="Q21" t="n">
         <v>0.5</v>
@@ -2427,10 +2427,10 @@
         <v>139.7</v>
       </c>
       <c r="U21" t="n">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="V21" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.317980,69.277729</t>
+          <t>https://www.google.com/maps?q=41.370618,69.299096</t>
         </is>
       </c>
     </row>
@@ -2458,22 +2458,22 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>41.351883</v>
+        <v>41.348398</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>69.294573</v>
+        <v>69.203411</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>41.351883, 69.294573</t>
+          <t>41.348398, 69.203411</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Атчапар-1 махалля</t>
+          <t>Вузгородок</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2482,48 +2482,48 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>7012</v>
+        <v>3326</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N22" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q22" t="n">
         <v>0.5</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="T22" t="n">
-        <v>139.7</v>
+        <v>59.2</v>
       </c>
       <c r="U22" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="V22" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.351883,69.294573</t>
+          <t>https://www.google.com/maps?q=41.348398,69.203411</t>
         </is>
       </c>
     </row>
@@ -2551,22 +2551,22 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>41.348398</v>
+        <v>41.382952</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>69.203411</v>
+        <v>69.279659</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>41.348398, 69.203411</t>
+          <t>41.382952, 69.279659</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Вузгородок</t>
+          <t>Юнусабад-10</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2582,41 +2582,41 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3326</v>
+        <v>8693</v>
       </c>
       <c r="M23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="O23" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Q23" t="n">
         <v>0.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>59.2</v>
+        <v>139.7</v>
       </c>
       <c r="U23" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V23" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.348398,69.203411</t>
+          <t>https://www.google.com/maps?q=41.382952,69.279659</t>
         </is>
       </c>
     </row>
@@ -2644,22 +2644,22 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>41.370618</v>
+        <v>41.252524</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>69.29909600000001</v>
+        <v>69.20859299999999</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>41.370618, 69.299096</t>
+          <t>41.252524, 69.208593</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Юнусабад 13-й квартал</t>
+          <t>ЖК "Домбрабад Тауерс"</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2668,48 +2668,48 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>22705</v>
+        <v>2199</v>
       </c>
       <c r="M24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="O24" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q24" t="n">
         <v>0.5</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="T24" t="n">
-        <v>139.7</v>
+        <v>28.3</v>
       </c>
       <c r="U24" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="V24" t="n">
-        <v>300</v>
+        <v>1500</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.370618,69.299096</t>
+          <t>https://www.google.com/maps?q=41.252524,69.208593</t>
         </is>
       </c>
     </row>
@@ -2737,22 +2737,22 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>41.382952</v>
+        <v>41.331512</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>69.279659</v>
+        <v>69.37708600000001</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>41.382952, 69.279659</t>
+          <t>41.331512, 69.377086</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Юнусабад-10</t>
+          <t>Карасу-4</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2761,30 +2761,30 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>8693</v>
+        <v>5737</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N25" t="n">
         <v>24</v>
       </c>
       <c r="O25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q25" t="n">
         <v>0.5</v>
@@ -2796,13 +2796,13 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>139.7</v>
+        <v>141</v>
       </c>
       <c r="U25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V25" t="n">
-        <v>700</v>
+        <v>10</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.382952,69.279659</t>
+          <t>https://www.google.com/maps?q=41.331512,69.377086</t>
         </is>
       </c>
     </row>
@@ -2830,22 +2830,22 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>41.331512</v>
+        <v>41.211644</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>69.37708600000001</v>
+        <v>69.19953</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>41.331512, 69.377086</t>
+          <t>41.211644, 69.199530</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Карасу-4</t>
+          <t>Сергели-9А</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2854,30 +2854,30 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5737</v>
+        <v>19654</v>
       </c>
       <c r="M26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="O26" t="n">
         <v>12</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q26" t="n">
         <v>0.5</v>
@@ -2889,13 +2889,13 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>141</v>
+        <v>122.7</v>
       </c>
       <c r="U26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V26" t="n">
-        <v>10</v>
+        <v>450</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.331512,69.377086</t>
+          <t>https://www.google.com/maps?q=41.211644,69.199530</t>
         </is>
       </c>
     </row>
@@ -2923,22 +2923,22 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>41.252524</v>
+        <v>41.250058</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>69.20859299999999</v>
+        <v>69.342911</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>41.252524, 69.208593</t>
+          <t>41.250058, 69.342911</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ЖК "Домбрабад Тауерс"</t>
+          <t>Аханграбо (Панельный)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2947,49 +2947,47 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2199</v>
+        <v>4446</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N27" t="n">
         <v>16</v>
       </c>
       <c r="O27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q27" t="n">
         <v>0.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>28.3</v>
+        <v>141</v>
       </c>
       <c r="U27" t="n">
-        <v>9</v>
-      </c>
-      <c r="V27" t="n">
-        <v>350</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3002,7 +3000,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.252524,69.208593</t>
+          <t>https://www.google.com/maps?q=41.250058,69.342911</t>
         </is>
       </c>
     </row>
@@ -3019,19 +3017,19 @@
         <v>81</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>41.211644</v>
+        <v>41.323641</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>69.19953</v>
+        <v>69.341219</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>41.211644, 69.199530</t>
+          <t>41.323641, 69.341219</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Сергели-9А</t>
+          <t>Катта Алтынтепа махалля</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3040,30 +3038,30 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>19654</v>
+        <v>6442</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N28" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O28" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q28" t="n">
         <v>0.5</v>
@@ -3075,13 +3073,13 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>122.7</v>
+        <v>98.2</v>
       </c>
       <c r="U28" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="V28" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3095,7 +3093,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.211644,69.199530</t>
+          <t>https://www.google.com/maps?q=41.323641,69.341219</t>
         </is>
       </c>
     </row>
@@ -3112,19 +3110,19 @@
         <v>81</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>41.250058</v>
+        <v>41.346824</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>69.342911</v>
+        <v>69.38152599999999</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>41.250058, 69.342911</t>
+          <t>41.346824, 69.381526</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Аханграбо (Панельный)</t>
+          <t>Ахмада Югнаки (Солнечный)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3133,30 +3131,30 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4446</v>
+        <v>10881</v>
       </c>
       <c r="M29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N29" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="O29" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q29" t="n">
         <v>0.5</v>
@@ -3168,12 +3166,14 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>141</v>
+        <v>98.2</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="V29" t="n">
+        <v>10</v>
+      </c>
       <c r="W29" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.250058,69.342911</t>
+          <t>https://www.google.com/maps?q=41.346824,69.381526</t>
         </is>
       </c>
     </row>
@@ -3200,22 +3200,22 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>41.346824</v>
+        <v>41.278439</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>69.38152599999999</v>
+        <v>69.379378</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>41.346824, 69.381526</t>
+          <t>41.278439, 69.379378</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ахмада Югнаки (Солнечный)</t>
+          <t>Нурмухаммедов</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3224,30 +3224,30 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>10881</v>
+        <v>5429</v>
       </c>
       <c r="M30" t="n">
+        <v>7</v>
+      </c>
+      <c r="N30" t="n">
+        <v>9</v>
+      </c>
+      <c r="O30" t="n">
         <v>5</v>
       </c>
-      <c r="N30" t="n">
-        <v>24</v>
-      </c>
-      <c r="O30" t="n">
-        <v>12</v>
-      </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q30" t="n">
         <v>0.5</v>
@@ -3259,13 +3259,13 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>98.2</v>
+        <v>141</v>
       </c>
       <c r="U30" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>10</v>
+        <v>1500</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.346824,69.381526</t>
+          <t>https://www.google.com/maps?q=41.278439,69.379378</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
         <v>8</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Q31" t="n">
         <v>0.5</v>
@@ -3358,7 +3358,7 @@
         <v>8</v>
       </c>
       <c r="V31" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>15</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Q32" t="n">
         <v>0.5</v>
@@ -3482,19 +3482,19 @@
         <v>80</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>41.278439</v>
+        <v>41.348912</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>69.379378</v>
+        <v>69.361794</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>41.278439, 69.379378</t>
+          <t>41.348912, 69.361794</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Нурмухаммедов</t>
+          <t>Феруза-2</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3503,30 +3503,30 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5429</v>
+        <v>6046</v>
       </c>
       <c r="M33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N33" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="O33" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q33" t="n">
         <v>0.5</v>
@@ -3538,13 +3538,13 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>141</v>
+        <v>98.2</v>
       </c>
       <c r="U33" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="V33" t="n">
-        <v>1500</v>
+        <v>10</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.278439,69.379378</t>
+          <t>https://www.google.com/maps?q=41.348912,69.361794</t>
         </is>
       </c>
     </row>
@@ -3572,22 +3572,22 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>41.348912</v>
+        <v>41.376688</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>69.361794</v>
+        <v>69.24778499999999</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>41.348912, 69.361794</t>
+          <t>41.376688, 69.247785</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Феруза-2</t>
+          <t>Ибрагим-Ата махалля</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3596,30 +3596,30 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>6046</v>
+        <v>2816</v>
       </c>
       <c r="M34" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N34" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="O34" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="P34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q34" t="n">
         <v>0.5</v>
@@ -3631,13 +3631,13 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>98.2</v>
+        <v>139.7</v>
       </c>
       <c r="U34" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="V34" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.348912,69.361794</t>
+          <t>https://www.google.com/maps?q=41.376688,69.247785</t>
         </is>
       </c>
     </row>
@@ -3668,51 +3668,51 @@
         <v>79</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>41.376688</v>
+        <v>41.330879</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>69.24778499999999</v>
+        <v>69.22666</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>41.376688, 69.247785</t>
+          <t>41.330879, 69.226660</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ибрагим-Ата махалля</t>
+          <t>Старый Город</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>район города</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2816</v>
+        <v>11177</v>
       </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N35" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="O35" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Q35" t="n">
         <v>0.5</v>
@@ -3724,13 +3724,13 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>139.7</v>
+        <v>59.2</v>
       </c>
       <c r="U35" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="V35" t="n">
-        <v>1120</v>
+        <v>250</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.376688,69.247785</t>
+          <t>https://www.google.com/maps?q=41.330879,69.226660</t>
         </is>
       </c>
     </row>
@@ -3758,54 +3758,54 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>41.330879</v>
+        <v>41.286991</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>69.22666</v>
+        <v>69.19375700000001</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>41.330879, 69.226660</t>
+          <t>41.286991, 69.193757</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Старый Город</t>
+          <t>Чиланзар Г 9А</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>район города</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>11177</v>
+        <v>16603</v>
       </c>
       <c r="M36" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N36" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="O36" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="Q36" t="n">
         <v>0.5</v>
@@ -3817,13 +3817,13 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>59.2</v>
+        <v>47.6</v>
       </c>
       <c r="U36" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="V36" t="n">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.330879,69.226660</t>
+          <t>https://www.google.com/maps?q=41.286991,69.193757</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>41.401782</v>
@@ -3942,54 +3942,54 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>41.29219</v>
+        <v>41.390081</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>69.189949</v>
+        <v>69.26402400000001</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>41.292190, 69.189949</t>
+          <t>41.390081, 69.264024</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Чиланзар-14</t>
+          <t>Дустамабад</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>22515</v>
+        <v>2632</v>
       </c>
       <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="n">
         <v>8</v>
       </c>
-      <c r="N38" t="n">
-        <v>57</v>
-      </c>
       <c r="O38" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q38" t="n">
         <v>0.5</v>
@@ -4001,13 +4001,13 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>47.6</v>
+        <v>139.7</v>
       </c>
       <c r="U38" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="V38" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.292190,69.189949</t>
+          <t>https://www.google.com/maps?q=41.390081,69.264024</t>
         </is>
       </c>
     </row>
@@ -4035,22 +4035,22 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>41.265528</v>
+        <v>41.20054</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>69.149665</v>
+        <v>69.246605</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>41.265528, 69.149665</t>
+          <t>41.200540, 69.246605</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Чиланзар-31</t>
+          <t>Дарьябуйи махалля</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4059,30 +4059,30 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>10778</v>
+        <v>2723</v>
       </c>
       <c r="M39" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="N39" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="O39" t="n">
+        <v>8</v>
+      </c>
+      <c r="P39" t="n">
         <v>10</v>
-      </c>
-      <c r="P39" t="n">
-        <v>11</v>
       </c>
       <c r="Q39" t="n">
         <v>0.5</v>
@@ -4094,13 +4094,13 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>47.6</v>
+        <v>122.7</v>
       </c>
       <c r="U39" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V39" t="n">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.265528,69.149665</t>
+          <t>https://www.google.com/maps?q=41.200540,69.246605</t>
         </is>
       </c>
     </row>
@@ -4131,51 +4131,51 @@
         <v>75</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>41.390081</v>
+        <v>41.265528</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>69.26402400000001</v>
+        <v>69.149665</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>41.390081, 69.264024</t>
+          <t>41.265528, 69.149665</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Дустамабад</t>
+          <t>Чиланзар-31</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2632</v>
+        <v>10778</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="N40" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="O40" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Q40" t="n">
         <v>0.5</v>
@@ -4187,13 +4187,13 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>139.7</v>
+        <v>47.6</v>
       </c>
       <c r="U40" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V40" t="n">
-        <v>1120</v>
+        <v>2</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.390081,69.264024</t>
+          <t>https://www.google.com/maps?q=41.265528,69.149665</t>
         </is>
       </c>
     </row>
@@ -4221,22 +4221,22 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>41.20054</v>
+        <v>41.283644</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>69.246605</v>
+        <v>69.28462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>41.200540, 69.246605</t>
+          <t>41.283644, 69.284620</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Дарьябуйи махалля</t>
+          <t>Сарыкулька</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4245,30 +4245,30 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Мирабадский район</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2723</v>
+        <v>5986</v>
       </c>
       <c r="M41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N41" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="O41" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="Q41" t="n">
         <v>0.5</v>
@@ -4280,13 +4280,13 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>122.7</v>
+        <v>48.5</v>
       </c>
       <c r="U41" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="V41" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.200540,69.246605</t>
+          <t>https://www.google.com/maps?q=41.283644,69.284620</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4361,7 @@
         <v>17</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Q42" t="n">
         <v>0.5</v>
@@ -4376,7 +4376,7 @@
         <v>28.3</v>
       </c>
       <c r="U42" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="V42" t="n">
         <v>500</v>
@@ -4407,7 +4407,7 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>41.249607</v>
@@ -4454,7 +4454,7 @@
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q43" t="n">
         <v>0.5</v>
@@ -4500,22 +4500,22 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>41.28528</v>
+        <v>41.301173</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>69.288624</v>
+        <v>69.26140599999999</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>41.285280, 69.288624</t>
+          <t>41.301173, 69.261406</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Истиклолабад махалля</t>
+          <t>Юнус Раджаби махалля</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4524,30 +4524,30 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Мирабадский район</t>
+          <t>Яккасарайский район</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>5502</v>
+        <v>7043</v>
       </c>
       <c r="M44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N44" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="O44" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="Q44" t="n">
         <v>0.5</v>
@@ -4559,10 +4559,10 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>48.5</v>
+        <v>31.8</v>
       </c>
       <c r="U44" t="n">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="V44" t="n">
         <v>500</v>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.285280,69.288624</t>
+          <t>https://www.google.com/maps?q=41.301173,69.261406</t>
         </is>
       </c>
     </row>
@@ -4596,51 +4596,51 @@
         <v>73</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>41.301173</v>
+        <v>41.221225</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>69.26140599999999</v>
+        <v>69.330173</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>41.301173, 69.261406</t>
+          <t>41.221225, 69.330173</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Юнус Раджаби махалля</t>
+          <t>Бектемир</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>район города</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Яккасарайский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>7043</v>
+        <v>3591</v>
       </c>
       <c r="M45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N45" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="O45" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q45" t="n">
         <v>0.5</v>
@@ -4652,14 +4652,12 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>31.8</v>
+        <v>60.2</v>
       </c>
       <c r="U45" t="n">
-        <v>80</v>
-      </c>
-      <c r="V45" t="n">
-        <v>950</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4672,7 +4670,7 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.301173,69.261406</t>
+          <t>https://www.google.com/maps?q=41.221225,69.330173</t>
         </is>
       </c>
     </row>
@@ -4689,19 +4687,19 @@
         <v>73</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>41.272896</v>
+        <v>41.250505</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>69.217082</v>
+        <v>69.319208</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>41.272896, 69.217082</t>
+          <t>41.250505, 69.319208</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Катта Казирабад махалля</t>
+          <t>Билимдан махалля</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4710,30 +4708,30 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Мирабадский район</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>7975</v>
+        <v>7433</v>
       </c>
       <c r="M46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N46" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="O46" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q46" t="n">
         <v>0.5</v>
@@ -4745,13 +4743,13 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>28.3</v>
+        <v>48.5</v>
       </c>
       <c r="U46" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="V46" t="n">
-        <v>500</v>
+        <v>8000</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -4765,7 +4763,7 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.272896,69.217082</t>
+          <t>https://www.google.com/maps?q=41.250505,69.319208</t>
         </is>
       </c>
     </row>
@@ -4782,51 +4780,51 @@
         <v>73</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>41.221225</v>
+        <v>41.272896</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>69.330173</v>
+        <v>69.217082</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>41.221225, 69.330173</t>
+          <t>41.272896, 69.217082</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Бектемир</t>
+          <t>Катта Казирабад махалля</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>район города</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3591</v>
+        <v>7975</v>
       </c>
       <c r="M47" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N47" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="O47" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="Q47" t="n">
         <v>0.5</v>
@@ -4838,12 +4836,14 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>60.2</v>
+        <v>28.3</v>
       </c>
       <c r="U47" t="n">
-        <v>1</v>
-      </c>
-      <c r="V47" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="V47" t="n">
+        <v>500</v>
+      </c>
       <c r="W47" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.221225,69.330173</t>
+          <t>https://www.google.com/maps?q=41.272896,69.217082</t>
         </is>
       </c>
     </row>
@@ -4870,22 +4870,22 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>41.250505</v>
+        <v>41.368494</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>69.319208</v>
+        <v>69.227745</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>41.250505, 69.319208</t>
+          <t>41.368494, 69.227745</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Билимдан махалля</t>
+          <t>Янги Ташкент махалля</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4901,23 +4901,23 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Мирабадский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>7433</v>
+        <v>2965</v>
       </c>
       <c r="M48" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N48" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="O48" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q48" t="n">
         <v>0.5</v>
@@ -4929,13 +4929,13 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>48.5</v>
+        <v>59.2</v>
       </c>
       <c r="U48" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V48" t="n">
-        <v>8000</v>
+        <v>200</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.250505,69.319208</t>
+          <t>https://www.google.com/maps?q=41.368494,69.227745</t>
         </is>
       </c>
     </row>
@@ -4963,22 +4963,22 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>41.368494</v>
+        <v>41.270832</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>69.227745</v>
+        <v>69.23679199999999</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>41.368494, 69.227745</t>
+          <t>41.270832, 69.236792</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Янги Ташкент махалля</t>
+          <t>Дилбулак махалля</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4994,23 +4994,23 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Яккасарайский район</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2965</v>
+        <v>11138</v>
       </c>
       <c r="M49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N49" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="O49" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="Q49" t="n">
         <v>0.5</v>
@@ -5022,13 +5022,13 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>59.2</v>
+        <v>31.8</v>
       </c>
       <c r="U49" t="n">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="V49" t="n">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.368494,69.227745</t>
+          <t>https://www.google.com/maps?q=41.270832,69.236792</t>
         </is>
       </c>
     </row>
@@ -5059,70 +5059,68 @@
         <v>72</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>41.379175</v>
+        <v>41.236084</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>69.20428699999999</v>
+        <v>69.35829</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>41.379175, 69.204287</t>
+          <t>41.236084, 69.358290</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Нихол махалля</t>
+          <t>Бузаучи</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3783</v>
+        <v>1236</v>
       </c>
       <c r="M50" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N50" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="Q50" t="n">
         <v>0.5</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="T50" t="n">
-        <v>59.2</v>
+        <v>60.2</v>
       </c>
       <c r="U50" t="n">
-        <v>3</v>
-      </c>
-      <c r="V50" t="n">
-        <v>840</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5135,7 +5133,7 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.379175,69.204287</t>
+          <t>https://www.google.com/maps?q=41.236084,69.358290</t>
         </is>
       </c>
     </row>
@@ -5152,68 +5150,70 @@
         <v>72</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>41.236084</v>
+        <v>41.277832</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>69.35829</v>
+        <v>69.130234</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>41.236084, 69.358290</t>
+          <t>41.277832, 69.130234</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Бузаучи</t>
+          <t>Дамачи</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1236</v>
+        <v>1699</v>
       </c>
       <c r="M51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N51" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="O51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q51" t="n">
         <v>0.5</v>
       </c>
       <c r="R51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>60.2</v>
+        <v>184.9</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="V51" t="n">
+        <v>2</v>
+      </c>
       <c r="W51" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.236084,69.358290</t>
+          <t>https://www.google.com/maps?q=41.277832,69.130234</t>
         </is>
       </c>
     </row>
@@ -5240,22 +5240,22 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>41.270832</v>
+        <v>41.379175</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>69.23679199999999</v>
+        <v>69.20428699999999</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>41.270832, 69.236792</t>
+          <t>41.379175, 69.204287</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Дилбулак махалля</t>
+          <t>Нихол махалля</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5264,30 +5264,30 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Яккасарайский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>11138</v>
+        <v>3783</v>
       </c>
       <c r="M52" t="n">
+        <v>3</v>
+      </c>
+      <c r="N52" t="n">
+        <v>11</v>
+      </c>
+      <c r="O52" t="n">
         <v>5</v>
       </c>
-      <c r="N52" t="n">
-        <v>33</v>
-      </c>
-      <c r="O52" t="n">
-        <v>12</v>
-      </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q52" t="n">
         <v>0.5</v>
@@ -5299,13 +5299,13 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>31.8</v>
+        <v>59.2</v>
       </c>
       <c r="U52" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="V52" t="n">
-        <v>500</v>
+        <v>840</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.270832,69.236792</t>
+          <t>https://www.google.com/maps?q=41.379175,69.204287</t>
         </is>
       </c>
     </row>
@@ -5333,54 +5333,54 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>41.277832</v>
+        <v>41.382173</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>69.130234</v>
+        <v>69.228139</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>41.277832, 69.130234</t>
+          <t>41.382173, 69.228139</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Дамачи</t>
+          <t>Ахил махалля</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1699</v>
+        <v>2891</v>
       </c>
       <c r="M53" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N53" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P53" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q53" t="n">
         <v>0.5</v>
@@ -5392,14 +5392,12 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>184.9</v>
+        <v>59.2</v>
       </c>
       <c r="U53" t="n">
-        <v>3</v>
-      </c>
-      <c r="V53" t="n">
         <v>2</v>
       </c>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5412,7 +5410,7 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.277832,69.130234</t>
+          <t>https://www.google.com/maps?q=41.382173,69.228139</t>
         </is>
       </c>
     </row>
@@ -5426,27 +5424,27 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>41.382173</v>
+        <v>41.339372</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>69.228139</v>
+        <v>69.412963</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>41.382173, 69.228139</t>
+          <t>41.339372, 69.412963</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ахил махалля</t>
+          <t>Заковат</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -5457,17 +5455,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2891</v>
+        <v>1782</v>
       </c>
       <c r="M54" t="n">
         <v>3</v>
       </c>
       <c r="N54" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O54" t="n">
         <v>5</v>
@@ -5485,12 +5483,14 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>59.2</v>
+        <v>141</v>
       </c>
       <c r="U54" t="n">
-        <v>2</v>
-      </c>
-      <c r="V54" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V54" t="n">
+        <v>8000</v>
+      </c>
       <c r="W54" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.382173,69.228139</t>
+          <t>https://www.google.com/maps?q=41.339372,69.412963</t>
         </is>
       </c>
     </row>
@@ -5520,28 +5520,28 @@
         <v>70</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>41.339372</v>
+        <v>41.261799</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>69.412963</v>
+        <v>69.35513400000001</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>41.339372, 69.412963</t>
+          <t>41.261799, 69.355134</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Заковат</t>
+          <t>Янгикурган махалля</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5552,19 +5552,19 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1782</v>
+        <v>1603</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N55" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="O55" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q55" t="n">
         <v>0.5</v>
@@ -5579,10 +5579,10 @@
         <v>141</v>
       </c>
       <c r="U55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V55" t="n">
-        <v>8000</v>
+        <v>1000</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.339372,69.412963</t>
+          <t>https://www.google.com/maps?q=41.261799,69.355134</t>
         </is>
       </c>
     </row>
@@ -5610,22 +5610,22 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>41.261799</v>
+        <v>41.187154</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>69.35513400000001</v>
+        <v>69.230422</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>41.261799, 69.355134</t>
+          <t>41.187154, 69.230422</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Янгикурган махалля</t>
+          <t>Чартак махалля</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5634,30 +5634,30 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1603</v>
+        <v>1947</v>
       </c>
       <c r="M56" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N56" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O56" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q56" t="n">
         <v>0.5</v>
@@ -5669,13 +5669,13 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>141</v>
+        <v>122.7</v>
       </c>
       <c r="U56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V56" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.261799,69.355134</t>
+          <t>https://www.google.com/maps?q=41.187154,69.230422</t>
         </is>
       </c>
     </row>
@@ -5703,22 +5703,22 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>41.187154</v>
+        <v>41.244099</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>69.230422</v>
+        <v>69.386206</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>41.187154, 69.230422</t>
+          <t>41.244099, 69.386206</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Чартак махалля</t>
+          <t>Мажнунтол махалля</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5727,30 +5727,30 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1947</v>
+        <v>2672</v>
       </c>
       <c r="M57" t="n">
+        <v>3</v>
+      </c>
+      <c r="N57" t="n">
+        <v>4</v>
+      </c>
+      <c r="O57" t="n">
         <v>2</v>
       </c>
-      <c r="N57" t="n">
-        <v>5</v>
-      </c>
-      <c r="O57" t="n">
-        <v>4</v>
-      </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q57" t="n">
         <v>0.5</v>
@@ -5762,14 +5762,12 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>122.7</v>
+        <v>60.2</v>
       </c>
       <c r="U57" t="n">
-        <v>6</v>
-      </c>
-      <c r="V57" t="n">
-        <v>150</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5782,7 +5780,7 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.187154,69.230422</t>
+          <t>https://www.google.com/maps?q=41.244099,69.386206</t>
         </is>
       </c>
     </row>
@@ -5799,19 +5797,19 @@
         <v>67</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>41.244099</v>
+        <v>41.236831</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>69.386206</v>
+        <v>69.318793</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>41.244099, 69.386206</t>
+          <t>41.236831, 69.318793</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Мажнунтол махалля</t>
+          <t>Эшанбулак махалля</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5820,7 +5818,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5831,19 +5829,19 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2672</v>
+        <v>1806</v>
       </c>
       <c r="M58" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N58" t="n">
+        <v>13</v>
+      </c>
+      <c r="O58" t="n">
         <v>4</v>
       </c>
-      <c r="O58" t="n">
-        <v>2</v>
-      </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q58" t="n">
         <v>0.5</v>
@@ -5873,7 +5871,7 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.244099,69.386206</t>
+          <t>https://www.google.com/maps?q=41.236831,69.318793</t>
         </is>
       </c>
     </row>
@@ -6025,7 +6023,7 @@
         <v>5</v>
       </c>
       <c r="P60" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Q60" t="n">
         <v>0.5</v>
@@ -6043,7 +6041,7 @@
         <v>4</v>
       </c>
       <c r="V60" t="n">
-        <v>350</v>
+        <v>600</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -6071,51 +6069,51 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>41.236831</v>
+        <v>41.171844</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>69.318793</v>
+        <v>69.226033</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>41.236831, 69.318793</t>
+          <t>41.171844, 69.226033</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Эшанбулак махалля</t>
+          <t>Чартак</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1806</v>
+        <v>1842</v>
       </c>
       <c r="M61" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
@@ -6130,12 +6128,14 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>60.2</v>
+        <v>122.7</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V61" t="n">
+        <v>4000</v>
+      </c>
       <c r="W61" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6143,12 +6143,12 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.236831,69.318793</t>
+          <t>https://www.google.com/maps?q=41.171844,69.226033</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
         <v>8</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q62" t="n">
         <v>5</v>
@@ -6302,7 +6302,7 @@
         <v>9</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Q63" t="n">
         <v>5</v>
@@ -6345,7 +6345,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C64" t="n">
         <v>87</v>
@@ -6395,7 +6395,7 @@
         <v>9</v>
       </c>
       <c r="P64" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="Q64" t="n">
         <v>5</v>
@@ -6410,7 +6410,7 @@
         <v>184.9</v>
       </c>
       <c r="U64" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V64" t="n">
         <v>200</v>
@@ -6488,7 +6488,7 @@
         <v>6</v>
       </c>
       <c r="P65" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q65" t="n">
         <v>5</v>
@@ -6531,10 +6531,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C66" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D66" s="2" t="n">
         <v>41.36099</v>
@@ -6624,7 +6624,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C67" t="n">
         <v>85</v>
@@ -6674,7 +6674,7 @@
         <v>7</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q67" t="n">
         <v>5</v>
@@ -6767,7 +6767,7 @@
         <v>4</v>
       </c>
       <c r="P68" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Q68" t="n">
         <v>5</v>
@@ -6782,7 +6782,7 @@
         <v>184.9</v>
       </c>
       <c r="U68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V68" t="n">
         <v>600</v>
@@ -6860,7 +6860,7 @@
         <v>6</v>
       </c>
       <c r="P69" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q69" t="n">
         <v>5</v>
@@ -6906,7 +6906,7 @@
         <v>7</v>
       </c>
       <c r="C70" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D70" s="2" t="n">
         <v>41.387795</v>
@@ -6953,7 +6953,7 @@
         <v>4</v>
       </c>
       <c r="P70" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q70" t="n">
         <v>5</v>
@@ -6968,7 +6968,7 @@
         <v>270.6</v>
       </c>
       <c r="U70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V70" t="n">
         <v>840</v>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C71" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D71" s="2" t="n">
         <v>41.296704</v>
@@ -7046,7 +7046,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q71" t="n">
         <v>5</v>
@@ -7087,76 +7087,74 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C72" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>41.372547</v>
+        <v>41.324284</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>69.378373</v>
+        <v>69.483728</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>41.372547, 69.378373</t>
+          <t>41.324284, 69.483728</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>ТТЗ-4</t>
+          <t>Китай-Тепа</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="J72" t="n">
         <v>1.1</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Юкоричирчикский район</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1956</v>
+        <v>1851</v>
       </c>
       <c r="M72" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
         <v>5</v>
       </c>
       <c r="R72" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S72" t="n">
-        <v>2911</v>
+        <v>1673</v>
       </c>
       <c r="T72" t="n">
-        <v>213.9</v>
+        <v>151.7</v>
       </c>
       <c r="U72" t="n">
-        <v>3</v>
-      </c>
-      <c r="V72" t="n">
-        <v>500</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7164,12 +7162,12 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.372547,69.378373</t>
+          <t>https://www.google.com/maps?q=41.324284,69.483728</t>
         </is>
       </c>
     </row>
@@ -7180,74 +7178,76 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C73" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>41.324284</v>
+        <v>41.402834</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>69.483728</v>
+        <v>69.220811</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>41.324284, 69.483728</t>
+          <t>41.402834, 69.220811</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Китай-Тепа</t>
+          <t>Абдурахманов</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Юкоричирчикский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1851</v>
+        <v>2527</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q73" t="n">
         <v>5</v>
       </c>
       <c r="R73" t="n">
+        <v>5</v>
+      </c>
+      <c r="S73" t="n">
+        <v>2480</v>
+      </c>
+      <c r="T73" t="n">
+        <v>270.6</v>
+      </c>
+      <c r="U73" t="n">
         <v>3</v>
       </c>
-      <c r="S73" t="n">
-        <v>1673</v>
-      </c>
-      <c r="T73" t="n">
-        <v>151.7</v>
-      </c>
-      <c r="U73" t="n">
-        <v>0</v>
-      </c>
-      <c r="V73" t="inlineStr"/>
+      <c r="V73" t="n">
+        <v>840</v>
+      </c>
       <c r="W73" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7255,12 +7255,12 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.324284,69.483728</t>
+          <t>https://www.google.com/maps?q=41.402834,69.220811</t>
         </is>
       </c>
     </row>
@@ -7271,25 +7271,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="C74" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>41.402834</v>
+        <v>41.401834</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>69.220811</v>
+        <v>69.276258</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>41.402834, 69.220811</t>
+          <t>41.401834, 69.276258</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Абдурахманов</t>
+          <t>Дустамабад</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7298,7 +7298,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J74" t="n">
         <v>1.2</v>
@@ -7309,38 +7309,36 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2527</v>
+        <v>2226</v>
       </c>
       <c r="M74" t="n">
+        <v>1</v>
+      </c>
+      <c r="N74" t="n">
         <v>2</v>
-      </c>
-      <c r="N74" t="n">
-        <v>3</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
       </c>
       <c r="P74" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q74" t="n">
         <v>5</v>
       </c>
       <c r="R74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S74" t="n">
-        <v>2480</v>
+        <v>12149</v>
       </c>
       <c r="T74" t="n">
         <v>270.6</v>
       </c>
       <c r="U74" t="n">
-        <v>3</v>
-      </c>
-      <c r="V74" t="n">
-        <v>840</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7353,7 +7351,7 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.402834,69.220811</t>
+          <t>https://www.google.com/maps?q=41.401834,69.276258</t>
         </is>
       </c>
     </row>
@@ -7364,72 +7362,72 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C75" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>41.401834</v>
+        <v>41.276459</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>69.276258</v>
+        <v>69.110428</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>41.401834, 69.276258</t>
+          <t>41.276459, 69.110428</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Дустамабад</t>
+          <t>Мевазар</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2226</v>
+        <v>2345</v>
       </c>
       <c r="M75" t="n">
+        <v>4</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
         <v>1</v>
-      </c>
-      <c r="N75" t="n">
-        <v>2</v>
-      </c>
-      <c r="O75" t="n">
-        <v>1</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
       </c>
       <c r="R75" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="S75" t="n">
-        <v>12149</v>
+        <v>4564</v>
       </c>
       <c r="T75" t="n">
-        <v>270.6</v>
+        <v>184.9</v>
       </c>
       <c r="U75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr">
@@ -7444,7 +7442,7 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.401834,69.276258</t>
+          <t>https://www.google.com/maps?q=41.276459,69.110428</t>
         </is>
       </c>
     </row>
@@ -7455,74 +7453,76 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C76" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>41.316805</v>
+        <v>41.375967</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>69.51514299999999</v>
+        <v>69.37848099999999</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>41.316805, 69.515143</t>
+          <t>41.375967, 69.378481</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Янгибазар</t>
+          <t>Ялангач</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Юкоричирчикский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2621</v>
+        <v>2081</v>
       </c>
       <c r="M76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N76" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q76" t="n">
         <v>5</v>
       </c>
       <c r="R76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S76" t="n">
-        <v>1373</v>
+        <v>2347</v>
       </c>
       <c r="T76" t="n">
-        <v>151.7</v>
+        <v>213.9</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
-      </c>
-      <c r="V76" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V76" t="n">
+        <v>1400</v>
+      </c>
       <c r="W76" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.316805,69.515143</t>
+          <t>https://www.google.com/maps?q=41.375967,69.378481</t>
         </is>
       </c>
     </row>
@@ -7546,69 +7546,69 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C77" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>41.276459</v>
+        <v>41.392995</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>69.110428</v>
+        <v>69.470157</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>41.276459, 69.110428</t>
+          <t>41.392995, 69.470157</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Мевазар</t>
+          <t>Кибрай</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2345</v>
+        <v>2507</v>
       </c>
       <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
         <v>4</v>
       </c>
-      <c r="N77" t="n">
-        <v>0</v>
-      </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P77" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q77" t="n">
         <v>5</v>
       </c>
       <c r="R77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S77" t="n">
-        <v>4564</v>
+        <v>439</v>
       </c>
       <c r="T77" t="n">
-        <v>184.9</v>
+        <v>213.9</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.276459,69.110428</t>
+          <t>https://www.google.com/maps?q=41.392995,69.470157</t>
         </is>
       </c>
     </row>
@@ -7637,74 +7637,76 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C78" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>41.392995</v>
+        <v>41.352783</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>69.470157</v>
+        <v>69.14811</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>41.392995, 69.470157</t>
+          <t>41.352783, 69.148110</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Кибрай</t>
+          <t>Куксарай</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2507</v>
+        <v>1467</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N78" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O78" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P78" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
         <v>5</v>
       </c>
       <c r="R78" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="S78" t="n">
-        <v>439</v>
+        <v>3190</v>
       </c>
       <c r="T78" t="n">
-        <v>213.9</v>
+        <v>270.6</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
-      </c>
-      <c r="V78" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V78" t="n">
+        <v>250</v>
+      </c>
       <c r="W78" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7717,7 +7719,7 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.392995,69.470157</t>
+          <t>https://www.google.com/maps?q=41.352783,69.148110</t>
         </is>
       </c>
     </row>
@@ -7728,75 +7730,75 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="C79" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>41.352783</v>
+        <v>41.207141</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>69.14811</v>
+        <v>69.163858</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>41.352783, 69.148110</t>
+          <t>41.207141, 69.163858</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Куксарай</t>
+          <t>Зангиата</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I79" t="n">
         <v>0.6</v>
       </c>
       <c r="J79" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1467</v>
+        <v>1847</v>
       </c>
       <c r="M79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N79" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O79" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q79" t="n">
         <v>5</v>
       </c>
       <c r="R79" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="S79" t="n">
-        <v>3190</v>
+        <v>24505</v>
       </c>
       <c r="T79" t="n">
-        <v>270.6</v>
+        <v>184.9</v>
       </c>
       <c r="U79" t="n">
         <v>1</v>
       </c>
       <c r="V79" t="n">
-        <v>250</v>
+        <v>2600</v>
       </c>
       <c r="W79" t="inlineStr">
         <is>
@@ -7810,7 +7812,7 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.352783,69.148110</t>
+          <t>https://www.google.com/maps?q=41.207141,69.163858</t>
         </is>
       </c>
     </row>
@@ -7821,57 +7823,57 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C80" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>41.207141</v>
+        <v>41.399761</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>69.163858</v>
+        <v>69.29601</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>41.207141, 69.163858</t>
+          <t>41.399761, 69.296010</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Зангиата</t>
+          <t>Хавасар</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1847</v>
+        <v>2533</v>
       </c>
       <c r="M80" t="n">
         <v>1</v>
       </c>
       <c r="N80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O80" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P80" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q80" t="n">
         <v>5</v>
@@ -7880,16 +7882,16 @@
         <v>14</v>
       </c>
       <c r="S80" t="n">
-        <v>24505</v>
+        <v>16114</v>
       </c>
       <c r="T80" t="n">
-        <v>184.9</v>
+        <v>213.9</v>
       </c>
       <c r="U80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V80" t="n">
-        <v>2600</v>
+        <v>1000</v>
       </c>
       <c r="W80" t="inlineStr">
         <is>
@@ -7903,7 +7905,7 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.207141,69.163858</t>
+          <t>https://www.google.com/maps?q=41.399761,69.296010</t>
         </is>
       </c>
     </row>
@@ -7914,76 +7916,74 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C81" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>41.399761</v>
+        <v>41.33418</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>69.29601</v>
+        <v>69.13572499999999</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>41.399761, 69.296010</t>
+          <t>41.334180, 69.135725</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Хавасар</t>
+          <t>Ункурган</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J81" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2533</v>
+        <v>1727</v>
       </c>
       <c r="M81" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N81" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O81" t="n">
+        <v>4</v>
+      </c>
+      <c r="P81" t="n">
         <v>2</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
       </c>
       <c r="Q81" t="n">
         <v>5</v>
       </c>
       <c r="R81" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="S81" t="n">
-        <v>16114</v>
+        <v>6530</v>
       </c>
       <c r="T81" t="n">
-        <v>213.9</v>
+        <v>184.9</v>
       </c>
       <c r="U81" t="n">
-        <v>4</v>
-      </c>
-      <c r="V81" t="n">
-        <v>1000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.399761,69.296010</t>
+          <t>https://www.google.com/maps?q=41.334180,69.135725</t>
         </is>
       </c>
     </row>
@@ -8007,25 +8007,25 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C82" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>41.33418</v>
+        <v>41.399172</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>69.13572499999999</v>
+        <v>69.327693</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>41.334180, 69.135725</t>
+          <t>41.399172, 69.327693</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ункурган</t>
+          <t>Гульзар</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8034,47 +8034,49 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1727</v>
+        <v>2403</v>
       </c>
       <c r="M82" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N82" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q82" t="n">
         <v>5</v>
       </c>
       <c r="R82" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S82" t="n">
-        <v>6530</v>
+        <v>10876</v>
       </c>
       <c r="T82" t="n">
-        <v>184.9</v>
+        <v>213.9</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
-      </c>
-      <c r="V82" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="V82" t="n">
+        <v>1000</v>
+      </c>
       <c r="W82" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8087,7 +8089,7 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.334180,69.135725</t>
+          <t>https://www.google.com/maps?q=41.399172,69.327693</t>
         </is>
       </c>
     </row>
@@ -8098,37 +8100,37 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="C83" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>41.399172</v>
+        <v>41.378205</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>69.327693</v>
+        <v>69.350821</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>41.399172, 69.327693</t>
+          <t>41.378205, 69.350821</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Гульзар</t>
+          <t>Салар</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J83" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -8136,37 +8138,37 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2403</v>
+        <v>4623</v>
       </c>
       <c r="M83" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N83" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P83" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q83" t="n">
         <v>5</v>
       </c>
       <c r="R83" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S83" t="n">
-        <v>10876</v>
+        <v>14705</v>
       </c>
       <c r="T83" t="n">
         <v>213.9</v>
       </c>
       <c r="U83" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V83" t="n">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="W83" t="inlineStr">
         <is>
@@ -8180,7 +8182,7 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.399172,69.327693</t>
+          <t>https://www.google.com/maps?q=41.378205,69.350821</t>
         </is>
       </c>
     </row>
@@ -8191,75 +8193,75 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C84" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>41.378205</v>
+        <v>41.241734</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>69.350821</v>
+        <v>69.141108</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>41.378205, 69.350821</t>
+          <t>41.241734, 69.141108</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Салар</t>
+          <t>Далигузар</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J84" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>4623</v>
+        <v>2089</v>
       </c>
       <c r="M84" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N84" t="n">
         <v>11</v>
       </c>
       <c r="O84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="Q84" t="n">
         <v>5</v>
       </c>
       <c r="R84" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S84" t="n">
-        <v>14705</v>
+        <v>7256</v>
       </c>
       <c r="T84" t="n">
-        <v>213.9</v>
+        <v>184.9</v>
       </c>
       <c r="U84" t="n">
         <v>2</v>
       </c>
       <c r="V84" t="n">
-        <v>1100</v>
+        <v>1840</v>
       </c>
       <c r="W84" t="inlineStr">
         <is>
@@ -8273,7 +8275,7 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.378205,69.350821</t>
+          <t>https://www.google.com/maps?q=41.241734,69.141108</t>
         </is>
       </c>
     </row>
@@ -8284,75 +8286,75 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C85" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>41.241734</v>
+        <v>41.403254</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>69.141108</v>
+        <v>69.197048</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>41.241734, 69.141108</t>
+          <t>41.403254, 69.197048</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Далигузар</t>
+          <t>Келес</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="J85" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2089</v>
+        <v>9032</v>
       </c>
       <c r="M85" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N85" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="O85" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P85" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Q85" t="n">
         <v>5</v>
       </c>
       <c r="R85" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="S85" t="n">
-        <v>7256</v>
+        <v>2140</v>
       </c>
       <c r="T85" t="n">
-        <v>184.9</v>
+        <v>270.6</v>
       </c>
       <c r="U85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V85" t="n">
-        <v>1840</v>
+        <v>840</v>
       </c>
       <c r="W85" t="inlineStr">
         <is>
@@ -8366,7 +8368,7 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.241734,69.141108</t>
+          <t>https://www.google.com/maps?q=41.403254,69.197048</t>
         </is>
       </c>
     </row>
@@ -8377,37 +8379,37 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C86" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>41.403254</v>
+        <v>41.417442</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>69.197048</v>
+        <v>69.264831</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>41.403254, 69.197048</t>
+          <t>41.417442, 69.264831</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Келес</t>
+          <t>Хасанбай</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J86" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -8415,37 +8417,37 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>9032</v>
+        <v>1653</v>
       </c>
       <c r="M86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>5</v>
       </c>
       <c r="R86" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S86" t="n">
-        <v>2140</v>
+        <v>9304</v>
       </c>
       <c r="T86" t="n">
         <v>270.6</v>
       </c>
       <c r="U86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V86" t="n">
-        <v>840</v>
+        <v>600</v>
       </c>
       <c r="W86" t="inlineStr">
         <is>
@@ -8454,12 +8456,12 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.403254,69.197048</t>
+          <t>https://www.google.com/maps?q=41.417442,69.264831</t>
         </is>
       </c>
     </row>
@@ -8470,25 +8472,25 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C87" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>41.417442</v>
+        <v>41.392035</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>69.264831</v>
+        <v>69.343324</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>41.417442, 69.264831</t>
+          <t>41.392035, 69.343324</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Хасанбай</t>
+          <t>Ункурган</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -8497,48 +8499,48 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>2.3</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1653</v>
+        <v>2163</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q87" t="n">
         <v>5</v>
       </c>
       <c r="R87" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="S87" t="n">
-        <v>9304</v>
+        <v>11098</v>
       </c>
       <c r="T87" t="n">
-        <v>270.6</v>
+        <v>213.9</v>
       </c>
       <c r="U87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V87" t="n">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="W87" t="inlineStr">
         <is>
@@ -8547,12 +8549,12 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.417442,69.264831</t>
+          <t>https://www.google.com/maps?q=41.392035,69.343324</t>
         </is>
       </c>
     </row>
@@ -8563,25 +8565,25 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="C88" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>41.392035</v>
+        <v>41.308872</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>69.343324</v>
+        <v>69.115255</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>41.392035, 69.343324</t>
+          <t>41.308872, 69.115255</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ункурган</t>
+          <t>Харакат</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -8590,49 +8592,47 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2163</v>
+        <v>2845</v>
       </c>
       <c r="M88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O88" t="n">
         <v>1</v>
       </c>
       <c r="P88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q88" t="n">
         <v>5</v>
       </c>
       <c r="R88" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="S88" t="n">
-        <v>11098</v>
+        <v>3688</v>
       </c>
       <c r="T88" t="n">
-        <v>213.9</v>
+        <v>184.9</v>
       </c>
       <c r="U88" t="n">
-        <v>3</v>
-      </c>
-      <c r="V88" t="n">
-        <v>1100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.392035,69.343324</t>
+          <t>https://www.google.com/maps?q=41.308872,69.115255</t>
         </is>
       </c>
     </row>
@@ -8656,57 +8656,57 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C89" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>41.308872</v>
+        <v>41.377685</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>69.115255</v>
+        <v>69.46569100000001</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>41.308872, 69.115255</t>
+          <t>41.377685, 69.465691</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Харакат</t>
+          <t>Кибрай</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>2.7</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2845</v>
+        <v>3583</v>
       </c>
       <c r="M89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P89" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q89" t="n">
         <v>5</v>
@@ -8715,10 +8715,10 @@
         <v>2</v>
       </c>
       <c r="S89" t="n">
-        <v>3688</v>
+        <v>439</v>
       </c>
       <c r="T89" t="n">
-        <v>184.9</v>
+        <v>213.9</v>
       </c>
       <c r="U89" t="n">
         <v>0</v>
@@ -8736,7 +8736,7 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.308872,69.115255</t>
+          <t>https://www.google.com/maps?q=41.377685,69.465691</t>
         </is>
       </c>
     </row>
@@ -8747,34 +8747,34 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="C90" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>41.377685</v>
+        <v>41.44656</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>69.46569100000001</v>
+        <v>69.444159</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>41.377685, 69.465691</t>
+          <t>41.446560, 69.444159</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Кибрай</t>
+          <t>Ходжакурган</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>2.7</v>
@@ -8785,28 +8785,28 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>3583</v>
+        <v>2215</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
         <v>5</v>
       </c>
       <c r="R90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S90" t="n">
-        <v>439</v>
+        <v>129</v>
       </c>
       <c r="T90" t="n">
         <v>213.9</v>
@@ -8822,12 +8822,12 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.377685,69.465691</t>
+          <t>https://www.google.com/maps?q=41.446560,69.444159</t>
         </is>
       </c>
     </row>
@@ -8838,25 +8838,25 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C91" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>41.44656</v>
+        <v>41.380099</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>69.444159</v>
+        <v>69.43011300000001</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>41.446560, 69.444159</t>
+          <t>41.380099, 69.430113</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ходжакурган</t>
+          <t>Аргин</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8865,10 +8865,10 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J91" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -8876,36 +8876,38 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2215</v>
+        <v>2439</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q91" t="n">
         <v>5</v>
       </c>
       <c r="R91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S91" t="n">
-        <v>129</v>
+        <v>1510</v>
       </c>
       <c r="T91" t="n">
         <v>213.9</v>
       </c>
       <c r="U91" t="n">
-        <v>0</v>
-      </c>
-      <c r="V91" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V91" t="n">
+        <v>1200</v>
+      </c>
       <c r="W91" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8913,12 +8915,12 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.446560,69.444159</t>
+          <t>https://www.google.com/maps?q=41.380099,69.430113</t>
         </is>
       </c>
     </row>
@@ -8929,76 +8931,74 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C92" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>41.380099</v>
+        <v>41.378499</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>69.43011300000001</v>
+        <v>69.144857</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>41.380099, 69.430113</t>
+          <t>41.378499, 69.144857</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Аргин</t>
+          <t>Илгар</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2439</v>
+        <v>2210</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P92" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
         <v>5</v>
       </c>
       <c r="R92" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S92" t="n">
-        <v>1510</v>
+        <v>2397</v>
       </c>
       <c r="T92" t="n">
-        <v>213.9</v>
+        <v>270.6</v>
       </c>
       <c r="U92" t="n">
-        <v>1</v>
-      </c>
-      <c r="V92" t="n">
-        <v>1200</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V92" t="inlineStr"/>
       <c r="W92" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -9011,7 +9011,7 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.380099,69.430113</t>
+          <t>https://www.google.com/maps?q=41.378499,69.144857</t>
         </is>
       </c>
     </row>
@@ -9028,48 +9028,48 @@
         <v>77</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>41.378499</v>
+        <v>41.445931</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>69.144857</v>
+        <v>69.475869</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>41.378499, 69.144857</t>
+          <t>41.445931, 69.475869</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Илгар</t>
+          <t>Сасбага</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>3.1</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2210</v>
+        <v>2143</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P93" t="n">
         <v>0</v>
@@ -9078,13 +9078,13 @@
         <v>5</v>
       </c>
       <c r="R93" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S93" t="n">
-        <v>2397</v>
+        <v>129</v>
       </c>
       <c r="T93" t="n">
-        <v>270.6</v>
+        <v>213.9</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
@@ -9097,12 +9097,12 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.378499,69.144857</t>
+          <t>https://www.google.com/maps?q=41.445931,69.475869</t>
         </is>
       </c>
     </row>
@@ -9113,25 +9113,25 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="C94" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>41.445931</v>
+        <v>41.160793</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>69.475869</v>
+        <v>69.174412</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>41.445931, 69.475869</t>
+          <t>41.160793, 69.174412</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Сасбага</t>
+          <t>Боборахим</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -9140,18 +9140,18 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J94" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Янгиюльский район</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2143</v>
+        <v>1726</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
@@ -9169,13 +9169,13 @@
         <v>5</v>
       </c>
       <c r="R94" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S94" t="n">
-        <v>129</v>
+        <v>17092</v>
       </c>
       <c r="T94" t="n">
-        <v>213.9</v>
+        <v>129.6</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.445931,69.475869</t>
+          <t>https://www.google.com/maps?q=41.160793,69.174412</t>
         </is>
       </c>
     </row>
@@ -9204,54 +9204,54 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="C95" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>41.160793</v>
+        <v>41.343065</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>69.174412</v>
+        <v>69.11617699999999</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>41.160793, 69.174412</t>
+          <t>41.343065, 69.116177</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Боборахим</t>
+          <t>Илгар</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J95" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Янгиюльский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1726</v>
+        <v>2595</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P95" t="n">
         <v>0</v>
@@ -9260,13 +9260,13 @@
         <v>5</v>
       </c>
       <c r="R95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S95" t="n">
-        <v>17092</v>
+        <v>1141</v>
       </c>
       <c r="T95" t="n">
-        <v>129.6</v>
+        <v>184.9</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.160793,69.174412</t>
+          <t>https://www.google.com/maps?q=41.343065,69.116177</t>
         </is>
       </c>
     </row>
@@ -9295,69 +9295,69 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C96" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>41.343065</v>
+        <v>41.418715</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>69.11617699999999</v>
+        <v>69.193523</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>41.343065, 69.116177</t>
+          <t>41.418715, 69.193523</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Илгар</t>
+          <t>Куктерак</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J96" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2595</v>
+        <v>2247</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N96" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q96" t="n">
         <v>5</v>
       </c>
       <c r="R96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S96" t="n">
-        <v>1141</v>
+        <v>1267</v>
       </c>
       <c r="T96" t="n">
-        <v>184.9</v>
+        <v>270.6</v>
       </c>
       <c r="U96" t="n">
         <v>0</v>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.343065,69.116177</t>
+          <t>https://www.google.com/maps?q=41.418715,69.193523</t>
         </is>
       </c>
     </row>
@@ -9386,20 +9386,20 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C97" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>41.418715</v>
+        <v>41.425276</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>69.193523</v>
+        <v>69.209565</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>41.418715, 69.193523</t>
+          <t>41.425276, 69.209565</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>3.8</v>
@@ -9424,13 +9424,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2247</v>
+        <v>2734</v>
       </c>
       <c r="M97" t="n">
         <v>2</v>
       </c>
       <c r="N97" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O97" t="n">
         <v>1</v>
@@ -9442,10 +9442,10 @@
         <v>5</v>
       </c>
       <c r="R97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S97" t="n">
-        <v>1267</v>
+        <v>187</v>
       </c>
       <c r="T97" t="n">
         <v>270.6</v>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.418715,69.193523</t>
+          <t>https://www.google.com/maps?q=41.425276,69.209565</t>
         </is>
       </c>
     </row>
@@ -9477,25 +9477,25 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="C98" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>41.425276</v>
+        <v>41.358385</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>69.209565</v>
+        <v>69.120549</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>41.425276, 69.209565</t>
+          <t>41.358385, 69.120549</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Куктерак</t>
+          <t>Шамсиабад</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -9504,10 +9504,10 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -9515,28 +9515,28 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2734</v>
+        <v>3620</v>
       </c>
       <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>4</v>
+      </c>
+      <c r="O98" t="n">
         <v>2</v>
       </c>
-      <c r="N98" t="n">
-        <v>3</v>
-      </c>
-      <c r="O98" t="n">
-        <v>1</v>
-      </c>
       <c r="P98" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
         <v>5</v>
       </c>
       <c r="R98" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S98" t="n">
-        <v>187</v>
+        <v>1701</v>
       </c>
       <c r="T98" t="n">
         <v>270.6</v>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.425276,69.209565</t>
+          <t>https://www.google.com/maps?q=41.358385,69.120549</t>
         </is>
       </c>
     </row>
@@ -9568,25 +9568,25 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C99" t="n">
         <v>82</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>41.358385</v>
+        <v>41.412151</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>69.120549</v>
+        <v>69.177485</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>41.358385, 69.120549</t>
+          <t>41.412151, 69.177485</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Шамсиабад</t>
+          <t>Сагбан</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -9595,10 +9595,10 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J99" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -9606,28 +9606,28 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3620</v>
+        <v>2486</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N99" t="n">
         <v>4</v>
       </c>
       <c r="O99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q99" t="n">
         <v>5</v>
       </c>
       <c r="R99" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S99" t="n">
-        <v>1701</v>
+        <v>1519</v>
       </c>
       <c r="T99" t="n">
         <v>270.6</v>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.358385,69.120549</t>
+          <t>https://www.google.com/maps?q=41.412151,69.177485</t>
         </is>
       </c>
     </row>
@@ -9659,25 +9659,25 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C100" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>41.412151</v>
+        <v>41.404809</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>69.177485</v>
+        <v>69.391277</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>41.412151, 69.177485</t>
+          <t>41.404809, 69.391277</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Сагбан</t>
+          <t>Уткир</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -9693,35 +9693,35 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2486</v>
+        <v>1919</v>
       </c>
       <c r="M100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
         <v>5</v>
       </c>
       <c r="R100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S100" t="n">
-        <v>1519</v>
+        <v>1398</v>
       </c>
       <c r="T100" t="n">
-        <v>270.6</v>
+        <v>213.9</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
@@ -9734,12 +9734,12 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.412151,69.177485</t>
+          <t>https://www.google.com/maps?q=41.404809,69.391277</t>
         </is>
       </c>
     </row>
@@ -9750,25 +9750,25 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="C101" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>41.404809</v>
+        <v>41.173507</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>69.391277</v>
+        <v>69.131349</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>41.404809, 69.391277</t>
+          <t>41.173507, 69.131349</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Уткир</t>
+          <t>Ханкурган</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -9777,18 +9777,18 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J101" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1919</v>
+        <v>2231</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
@@ -9809,10 +9809,10 @@
         <v>2</v>
       </c>
       <c r="S101" t="n">
-        <v>1398</v>
+        <v>2842</v>
       </c>
       <c r="T101" t="n">
-        <v>213.9</v>
+        <v>184.9</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.404809,69.391277</t>
+          <t>https://www.google.com/maps?q=41.173507,69.131349</t>
         </is>
       </c>
     </row>
@@ -9841,45 +9841,45 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C102" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>41.173507</v>
+        <v>41.445091</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>69.131349</v>
+        <v>69.249785</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>41.173507, 69.131349</t>
+          <t>41.445091, 69.249785</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ханкурган</t>
+          <t>Чувалачи</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J102" t="n">
         <v>5.3</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2231</v>
+        <v>2773</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
@@ -9897,13 +9897,13 @@
         <v>5</v>
       </c>
       <c r="R102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>2842</v>
+        <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>184.9</v>
+        <v>270.6</v>
       </c>
       <c r="U102" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.173507,69.131349</t>
+          <t>https://www.google.com/maps?q=41.445091,69.249785</t>
         </is>
       </c>
     </row>
@@ -9932,34 +9932,34 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C103" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>41.445091</v>
+        <v>41.445517</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>69.249785</v>
+        <v>69.226005</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>41.445091, 69.249785</t>
+          <t>41.445517, 69.226005</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Чувалачи</t>
+          <t>Алишер Навои</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J103" t="n">
         <v>5.3</v>
@@ -9970,7 +9970,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2773</v>
+        <v>2065</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
@@ -9988,10 +9988,10 @@
         <v>5</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S103" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="T103" t="n">
         <v>270.6</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.445091,69.249785</t>
+          <t>https://www.google.com/maps?q=41.445517,69.226005</t>
         </is>
       </c>
     </row>
@@ -10023,25 +10023,25 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C104" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>41.445517</v>
+        <v>41.273963</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>69.226005</v>
+        <v>69.055013</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>41.445517, 69.226005</t>
+          <t>41.273963, 69.055013</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Алишер Навои</t>
+          <t>Тукимачи</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -10050,18 +10050,18 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J104" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2065</v>
+        <v>2760</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
@@ -10079,13 +10079,13 @@
         <v>5</v>
       </c>
       <c r="R104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="T104" t="n">
-        <v>270.6</v>
+        <v>184.9</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
@@ -10103,7 +10103,7 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.445517,69.226005</t>
+          <t>https://www.google.com/maps?q=41.273963,69.055013</t>
         </is>
       </c>
     </row>
@@ -10114,25 +10114,25 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C105" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>41.273963</v>
+        <v>41.287638</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>69.055013</v>
+        <v>69.055368</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>41.273963, 69.055013</t>
+          <t>41.287638, 69.055368</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Тукимачи</t>
+          <t>Янарык</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -10141,10 +10141,10 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="J105" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2760</v>
+        <v>2340</v>
       </c>
       <c r="M105" t="n">
         <v>0</v>
@@ -10194,7 +10194,7 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.273963,69.055013</t>
+          <t>https://www.google.com/maps?q=41.287638,69.055368</t>
         </is>
       </c>
     </row>
@@ -10387,7 +10387,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C108" t="n">
         <v>83</v>
@@ -10478,7 +10478,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C109" t="n">
         <v>81</v>
@@ -10569,7 +10569,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C110" t="n">
         <v>84</v>
@@ -10634,7 +10634,7 @@
         <v>40.8</v>
       </c>
       <c r="U110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V110" t="n">
         <v>4068</v>
@@ -10662,7 +10662,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C111" t="n">
         <v>76</v>
@@ -10818,10 +10818,10 @@
         <v>40.8</v>
       </c>
       <c r="U112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V112" t="n">
-        <v>2000</v>
+        <v>4068</v>
       </c>
       <c r="W112" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C113" t="n">
         <v>84</v>
@@ -10937,7 +10937,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C114" t="n">
         <v>78</v>
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C115" t="n">
         <v>83</v>
@@ -11119,7 +11119,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C116" t="n">
         <v>78</v>
@@ -11169,7 +11169,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q116" t="n">
         <v>5</v>
@@ -11392,7 +11392,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C119" t="n">
         <v>83</v>
@@ -11442,7 +11442,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q119" t="n">
         <v>5</v>
@@ -11483,7 +11483,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C120" t="n">
         <v>78</v>
@@ -11574,7 +11574,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C121" t="n">
         <v>78</v>
@@ -11624,7 +11624,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q121" t="n">
         <v>5</v>
@@ -11941,7 +11941,7 @@
         <v>2</v>
       </c>
       <c r="C125" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D125" s="2" t="n">
         <v>41.56088</v>
@@ -11988,7 +11988,7 @@
         <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q125" t="n">
         <v>5</v>
@@ -12211,7 +12211,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C128" t="n">
         <v>60</v>
@@ -12305,7 +12305,7 @@
         <v>3</v>
       </c>
       <c r="C129" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D129" s="2" t="n">
         <v>41.572586</v>
@@ -12352,7 +12352,7 @@
         <v>0</v>
       </c>
       <c r="P129" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q129" t="n">
         <v>5</v>
@@ -13121,7 +13121,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C138" t="n">
         <v>55</v>
@@ -13305,7 +13305,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C140" t="n">
         <v>60</v>
@@ -13855,7 +13855,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C146" t="n">
         <v>55</v>
@@ -15859,7 +15859,7 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C168" t="n">
         <v>60</v>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,10 +660,10 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V2" t="n">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="V3" t="n">
         <v>500</v>
@@ -846,10 +846,10 @@
         <v>48.5</v>
       </c>
       <c r="U4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V4" t="n">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         <v>48.5</v>
       </c>
       <c r="U5" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="V5" t="n">
-        <v>700</v>
+        <v>918</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -973,19 +973,19 @@
         <v>91</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>41.329729</v>
+        <v>41.332561</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>69.289952</v>
+        <v>69.321702</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41.329729, 69.289952</t>
+          <t>41.332561, 69.321702</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Буюк Туран махалля</t>
+          <t>Буюк Ипак Йули махалля</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -994,48 +994,48 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>10538</v>
+        <v>4166</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="O6" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="P6" t="n">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="Q6" t="n">
         <v>0.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>399</v>
+        <v>1970</v>
       </c>
       <c r="T6" t="n">
-        <v>139.7</v>
+        <v>98.2</v>
       </c>
       <c r="U6" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="V6" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.329729,69.289952</t>
+          <t>https://www.google.com/maps?q=41.332561,69.321702</t>
         </is>
       </c>
     </row>
@@ -1066,19 +1066,19 @@
         <v>91</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>41.332561</v>
+        <v>41.329729</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>69.321702</v>
+        <v>69.289952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>41.332561, 69.321702</t>
+          <t>41.329729, 69.289952</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Буюк Ипак Йули махалля</t>
+          <t>Буюк Туран махалля</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1087,48 +1087,48 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4166</v>
+        <v>10538</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="O7" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="P7" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="Q7" t="n">
         <v>0.5</v>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>1970</v>
+        <v>399</v>
       </c>
       <c r="T7" t="n">
-        <v>98.2</v>
+        <v>139.7</v>
       </c>
       <c r="U7" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="V7" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.332561,69.321702</t>
+          <t>https://www.google.com/maps?q=41.329729,69.289952</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
         <v>139.7</v>
       </c>
       <c r="U8" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="V8" t="n">
         <v>700</v>
@@ -1311,7 +1311,7 @@
         <v>98.2</v>
       </c>
       <c r="U9" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="V9" t="n">
         <v>650</v>
@@ -1404,7 +1404,7 @@
         <v>98.2</v>
       </c>
       <c r="U10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="V10" t="n">
         <v>500</v>
@@ -1590,10 +1590,10 @@
         <v>59.2</v>
       </c>
       <c r="U12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V12" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         <v>141</v>
       </c>
       <c r="U13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V13" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>141</v>
       </c>
       <c r="U14" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="V14" t="n">
         <v>500</v>
@@ -1869,7 +1869,7 @@
         <v>31.8</v>
       </c>
       <c r="U15" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="V15" t="n">
         <v>500</v>
@@ -2055,10 +2055,10 @@
         <v>122.7</v>
       </c>
       <c r="U17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="V17" t="n">
-        <v>1400</v>
+        <v>350</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>139.7</v>
       </c>
       <c r="U18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V18" t="n">
         <v>700</v>
@@ -2241,10 +2241,10 @@
         <v>139.7</v>
       </c>
       <c r="U19" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="V19" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>41.351883</v>
@@ -2334,7 +2334,7 @@
         <v>139.7</v>
       </c>
       <c r="U20" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="V20" t="n">
         <v>350</v>
@@ -2427,7 +2427,7 @@
         <v>139.7</v>
       </c>
       <c r="U21" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="V21" t="n">
         <v>300</v>
@@ -2520,7 +2520,7 @@
         <v>59.2</v>
       </c>
       <c r="U22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V22" t="n">
         <v>200</v>
@@ -2613,10 +2613,10 @@
         <v>139.7</v>
       </c>
       <c r="U23" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V23" t="n">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -2706,10 +2706,10 @@
         <v>28.3</v>
       </c>
       <c r="U24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V24" t="n">
-        <v>1500</v>
+        <v>350</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>4</v>
       </c>
       <c r="V25" t="n">
-        <v>10</v>
+        <v>600</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>122.7</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V26" t="n">
         <v>450</v>
@@ -3076,7 +3076,7 @@
         <v>98.2</v>
       </c>
       <c r="U28" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="V28" t="n">
         <v>500</v>
@@ -3172,7 +3172,7 @@
         <v>7</v>
       </c>
       <c r="V29" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>139.7</v>
       </c>
       <c r="U31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V31" t="n">
         <v>800</v>
@@ -3448,10 +3448,10 @@
         <v>98.2</v>
       </c>
       <c r="U32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V32" t="n">
-        <v>10</v>
+        <v>600</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -3541,10 +3541,10 @@
         <v>98.2</v>
       </c>
       <c r="U33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V33" t="n">
-        <v>10</v>
+        <v>600</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -3634,10 +3634,10 @@
         <v>139.7</v>
       </c>
       <c r="U34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V34" t="n">
-        <v>500</v>
+        <v>1120</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -3727,10 +3727,10 @@
         <v>59.2</v>
       </c>
       <c r="U35" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="V35" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -3820,10 +3820,10 @@
         <v>47.6</v>
       </c>
       <c r="U36" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="V36" t="n">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -4004,10 +4004,10 @@
         <v>139.7</v>
       </c>
       <c r="U38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V38" t="n">
-        <v>500</v>
+        <v>1120</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>47.6</v>
       </c>
       <c r="U40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V40" t="n">
         <v>2</v>
@@ -4283,7 +4283,7 @@
         <v>48.5</v>
       </c>
       <c r="U41" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="V41" t="n">
         <v>500</v>
@@ -4376,7 +4376,7 @@
         <v>28.3</v>
       </c>
       <c r="U42" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="V42" t="n">
         <v>500</v>
@@ -4562,7 +4562,7 @@
         <v>31.8</v>
       </c>
       <c r="U44" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="V44" t="n">
         <v>500</v>
@@ -4746,11 +4746,9 @@
         <v>48.5</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
-      </c>
-      <c r="V46" t="n">
-        <v>8000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4839,7 +4837,7 @@
         <v>28.3</v>
       </c>
       <c r="U47" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V47" t="n">
         <v>500</v>
@@ -5025,7 +5023,7 @@
         <v>31.8</v>
       </c>
       <c r="U49" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="V49" t="n">
         <v>500</v>
@@ -5209,7 +5207,7 @@
         <v>184.9</v>
       </c>
       <c r="U51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V51" t="n">
         <v>2</v>
@@ -5240,7 +5238,7 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D52" s="2" t="n">
         <v>41.379175</v>
@@ -5302,7 +5300,7 @@
         <v>59.2</v>
       </c>
       <c r="U52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V52" t="n">
         <v>840</v>
@@ -5486,7 +5484,7 @@
         <v>141</v>
       </c>
       <c r="U54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V54" t="n">
         <v>8000</v>
@@ -5672,7 +5670,7 @@
         <v>122.7</v>
       </c>
       <c r="U56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V56" t="n">
         <v>150</v>
@@ -6038,10 +6036,10 @@
         <v>28.3</v>
       </c>
       <c r="U60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V60" t="n">
-        <v>600</v>
+        <v>350</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -6345,7 +6343,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C64" t="n">
         <v>87</v>
@@ -6410,7 +6408,7 @@
         <v>184.9</v>
       </c>
       <c r="U64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V64" t="n">
         <v>200</v>
@@ -6506,7 +6504,7 @@
         <v>8</v>
       </c>
       <c r="V65" t="n">
-        <v>250</v>
+        <v>800</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -6596,11 +6594,9 @@
         <v>184.9</v>
       </c>
       <c r="U66" t="n">
-        <v>1</v>
-      </c>
-      <c r="V66" t="n">
-        <v>250</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6875,7 +6871,7 @@
         <v>270.6</v>
       </c>
       <c r="U69" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V69" t="n">
         <v>300</v>
@@ -6968,7 +6964,7 @@
         <v>270.6</v>
       </c>
       <c r="U70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V70" t="n">
         <v>840</v>
@@ -7336,7 +7332,7 @@
         <v>270.6</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr">
@@ -7702,11 +7698,9 @@
         <v>270.6</v>
       </c>
       <c r="U78" t="n">
-        <v>1</v>
-      </c>
-      <c r="V78" t="n">
-        <v>250</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7795,11 +7789,9 @@
         <v>184.9</v>
       </c>
       <c r="U79" t="n">
-        <v>1</v>
-      </c>
-      <c r="V79" t="n">
-        <v>2600</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V79" t="inlineStr"/>
       <c r="W79" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7888,7 +7880,7 @@
         <v>213.9</v>
       </c>
       <c r="U80" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V80" t="n">
         <v>1000</v>
@@ -8007,7 +7999,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C82" t="n">
         <v>78</v>
@@ -8072,7 +8064,7 @@
         <v>213.9</v>
       </c>
       <c r="U82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V82" t="n">
         <v>1000</v>
@@ -8193,7 +8185,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C84" t="n">
         <v>87</v>
@@ -8351,7 +8343,7 @@
         <v>270.6</v>
       </c>
       <c r="U85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V85" t="n">
         <v>840</v>
@@ -8537,7 +8529,7 @@
         <v>213.9</v>
       </c>
       <c r="U87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V87" t="n">
         <v>1100</v>
@@ -9932,7 +9924,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C103" t="n">
         <v>78</v>
@@ -10818,10 +10810,10 @@
         <v>40.8</v>
       </c>
       <c r="U112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V112" t="n">
-        <v>4068</v>
+        <v>2000</v>
       </c>
       <c r="W112" t="inlineStr">
         <is>
@@ -12578,7 +12570,7 @@
         <v>15</v>
       </c>
       <c r="C132" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D132" s="2" t="n">
         <v>41.587894</v>
@@ -12666,7 +12658,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C133" t="n">
         <v>54</v>
@@ -13030,7 +13022,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C137" t="n">
         <v>54</v>
@@ -13121,7 +13113,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C138" t="n">
         <v>55</v>
@@ -13277,11 +13269,9 @@
         <v>37.9</v>
       </c>
       <c r="U139" t="n">
-        <v>1</v>
-      </c>
-      <c r="V139" t="n">
-        <v>1800</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V139" t="inlineStr"/>
       <c r="W139" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -13370,11 +13360,9 @@
         <v>37.9</v>
       </c>
       <c r="U140" t="n">
-        <v>1</v>
-      </c>
-      <c r="V140" t="n">
-        <v>1800</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V140" t="inlineStr"/>
       <c r="W140" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -13645,11 +13633,9 @@
         <v>37.9</v>
       </c>
       <c r="U143" t="n">
-        <v>1</v>
-      </c>
-      <c r="V143" t="n">
-        <v>1800</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V143" t="inlineStr"/>
       <c r="W143" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -13855,25 +13841,25 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="C146" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>40.805776</v>
+        <v>40.856143</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>69.246951</v>
+        <v>69.001069</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>40.805776, 69.246951</t>
+          <t>40.856143, 69.001069</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ачмайли</t>
+          <t>Навои</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -13882,18 +13868,18 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J146" t="n">
-        <v>39.9</v>
+        <v>39.5</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Букинский район</t>
+          <t>Аккурганский район</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>2059</v>
+        <v>1522</v>
       </c>
       <c r="M146" t="n">
         <v>0</v>
@@ -13917,7 +13903,7 @@
         <v>0</v>
       </c>
       <c r="T146" t="n">
-        <v>39.6</v>
+        <v>40.3</v>
       </c>
       <c r="U146" t="n">
         <v>0</v>
@@ -13935,7 +13921,7 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.805776,69.246951</t>
+          <t>https://www.google.com/maps?q=40.856143,69.001069</t>
         </is>
       </c>
     </row>
@@ -13946,25 +13932,25 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="C147" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>41.601553</v>
+        <v>40.805776</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>69.87878000000001</v>
+        <v>69.246951</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>41.601553, 69.878780</t>
+          <t>40.805776, 69.246951</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Каранккуль</t>
+          <t>Ачмайли</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -13973,18 +13959,18 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J147" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Бостанлыкский район</t>
+          <t>Букинский район</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>1524</v>
+        <v>2059</v>
       </c>
       <c r="M147" t="n">
         <v>0</v>
@@ -14008,7 +13994,7 @@
         <v>0</v>
       </c>
       <c r="T147" t="n">
-        <v>147.5</v>
+        <v>39.6</v>
       </c>
       <c r="U147" t="n">
         <v>0</v>
@@ -14026,7 +14012,7 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.601553,69.878780</t>
+          <t>https://www.google.com/maps?q=40.805776,69.246951</t>
         </is>
       </c>
     </row>
@@ -14037,25 +14023,25 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="C148" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>40.964208</v>
+        <v>41.601553</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>68.862195</v>
+        <v>69.87878000000001</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>40.964208, 68.862195</t>
+          <t>41.601553, 69.878780</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Алмазар</t>
+          <t>Каранккуль</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -14064,18 +14050,18 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="J148" t="n">
         <v>40</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Чиназский район</t>
+          <t>Бостанлыкский район</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>3416</v>
+        <v>1524</v>
       </c>
       <c r="M148" t="n">
         <v>0</v>
@@ -14087,7 +14073,7 @@
         <v>0</v>
       </c>
       <c r="P148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q148" t="n">
         <v>5</v>
@@ -14099,7 +14085,7 @@
         <v>0</v>
       </c>
       <c r="T148" t="n">
-        <v>59.7</v>
+        <v>147.5</v>
       </c>
       <c r="U148" t="n">
         <v>0</v>
@@ -14112,12 +14098,12 @@
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.964208,68.862195</t>
+          <t>https://www.google.com/maps?q=41.601553,69.878780</t>
         </is>
       </c>
     </row>
@@ -14128,57 +14114,57 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C149" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>40.806913</v>
+        <v>40.964208</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>69.184213</v>
+        <v>68.862195</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>40.806913, 69.184213</t>
+          <t>40.964208, 68.862195</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмазар</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J149" t="n">
-        <v>40.2</v>
+        <v>40</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Букинский район</t>
+          <t>Чиназский район</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>4987</v>
+        <v>3416</v>
       </c>
       <c r="M149" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" t="n">
         <v>1</v>
-      </c>
-      <c r="N149" t="n">
-        <v>0</v>
-      </c>
-      <c r="O149" t="n">
-        <v>0</v>
-      </c>
-      <c r="P149" t="n">
-        <v>5</v>
       </c>
       <c r="Q149" t="n">
         <v>5</v>
@@ -14190,7 +14176,7 @@
         <v>0</v>
       </c>
       <c r="T149" t="n">
-        <v>39.6</v>
+        <v>59.7</v>
       </c>
       <c r="U149" t="n">
         <v>0</v>
@@ -14208,7 +14194,7 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.806913,69.184213</t>
+          <t>https://www.google.com/maps?q=40.964208,68.862195</t>
         </is>
       </c>
     </row>
@@ -14219,25 +14205,25 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C150" t="n">
         <v>59</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>40.862328</v>
+        <v>40.806913</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>68.934483</v>
+        <v>69.184213</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>40.862328, 68.934483</t>
+          <t>40.806913, 69.184213</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Дустабад (Солдатский)</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -14246,18 +14232,18 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J150" t="n">
-        <v>41.7</v>
+        <v>40.2</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Куйичирчикский район</t>
+          <t>Букинский район</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>2450</v>
+        <v>4987</v>
       </c>
       <c r="M150" t="n">
         <v>1</v>
@@ -14269,7 +14255,7 @@
         <v>0</v>
       </c>
       <c r="P150" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q150" t="n">
         <v>5</v>
@@ -14281,7 +14267,7 @@
         <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>63.5</v>
+        <v>39.6</v>
       </c>
       <c r="U150" t="n">
         <v>0</v>
@@ -14299,7 +14285,7 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.862328,68.934483</t>
+          <t>https://www.google.com/maps?q=40.806913,69.184213</t>
         </is>
       </c>
     </row>
@@ -14310,20 +14296,20 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C151" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>40.85233</v>
+        <v>40.862328</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>68.91854499999999</v>
+        <v>68.934483</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>40.852330, 68.918545</t>
+          <t>40.862328, 68.934483</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -14337,10 +14323,10 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J151" t="n">
-        <v>43.4</v>
+        <v>41.7</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
@@ -14348,7 +14334,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>3338</v>
+        <v>2450</v>
       </c>
       <c r="M151" t="n">
         <v>1</v>
@@ -14390,7 +14376,7 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.852330,68.918545</t>
+          <t>https://www.google.com/maps?q=40.862328,68.934483</t>
         </is>
       </c>
     </row>
@@ -14401,48 +14387,48 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="C152" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>40.811633</v>
+        <v>40.85233</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>69.007808</v>
+        <v>68.91854499999999</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>40.811633, 69.007808</t>
+          <t>40.852330, 68.918545</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Зафар</t>
+          <t>Дустабад (Солдатский)</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J152" t="n">
-        <v>43.7</v>
+        <v>43.4</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Аккурганский район</t>
+          <t>Куйичирчикский район</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>1613</v>
+        <v>3338</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N152" t="n">
         <v>0</v>
@@ -14451,7 +14437,7 @@
         <v>0</v>
       </c>
       <c r="P152" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q152" t="n">
         <v>5</v>
@@ -14463,7 +14449,7 @@
         <v>0</v>
       </c>
       <c r="T152" t="n">
-        <v>40.3</v>
+        <v>63.5</v>
       </c>
       <c r="U152" t="n">
         <v>0</v>
@@ -14476,12 +14462,12 @@
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.811633,69.007808</t>
+          <t>https://www.google.com/maps?q=40.852330,68.918545</t>
         </is>
       </c>
     </row>
@@ -14492,25 +14478,25 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C153" t="n">
         <v>48</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>40.913564</v>
+        <v>40.811633</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>68.821765</v>
+        <v>69.007808</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>40.913564, 68.821765</t>
+          <t>40.811633, 69.007808</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Кушек</t>
+          <t>Зафар</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -14519,18 +14505,18 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J153" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Куйичирчикский район</t>
+          <t>Аккурганский район</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>1342</v>
+        <v>1613</v>
       </c>
       <c r="M153" t="n">
         <v>0</v>
@@ -14554,7 +14540,7 @@
         <v>0</v>
       </c>
       <c r="T153" t="n">
-        <v>63.5</v>
+        <v>40.3</v>
       </c>
       <c r="U153" t="n">
         <v>0</v>
@@ -14572,7 +14558,7 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.913564,68.821765</t>
+          <t>https://www.google.com/maps?q=40.811633,69.007808</t>
         </is>
       </c>
     </row>
@@ -14583,25 +14569,25 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C154" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>40.951358</v>
+        <v>40.913564</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>68.80686900000001</v>
+        <v>68.821765</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>40.951358, 68.806869</t>
+          <t>40.913564, 68.821765</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Янги хаёт</t>
+          <t>Кушек</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -14613,15 +14599,15 @@
         <v>0.2</v>
       </c>
       <c r="J154" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Чиназский район</t>
+          <t>Куйичирчикский район</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>2189</v>
+        <v>1342</v>
       </c>
       <c r="M154" t="n">
         <v>0</v>
@@ -14645,7 +14631,7 @@
         <v>0</v>
       </c>
       <c r="T154" t="n">
-        <v>59.7</v>
+        <v>63.5</v>
       </c>
       <c r="U154" t="n">
         <v>0</v>
@@ -14663,7 +14649,7 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.951358,68.806869</t>
+          <t>https://www.google.com/maps?q=40.913564,68.821765</t>
         </is>
       </c>
     </row>
@@ -14674,25 +14660,25 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="C155" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>40.957099</v>
+        <v>40.951358</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>68.763749</v>
+        <v>68.80686900000001</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>40.957099, 68.763749</t>
+          <t>40.951358, 68.806869</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Гульзарабад</t>
+          <t>Янги хаёт</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -14701,10 +14687,10 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J155" t="n">
-        <v>45.6</v>
+        <v>43.9</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -14712,10 +14698,10 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>1420</v>
+        <v>2189</v>
       </c>
       <c r="M155" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N155" t="n">
         <v>0</v>
@@ -14724,7 +14710,7 @@
         <v>0</v>
       </c>
       <c r="P155" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q155" t="n">
         <v>5</v>
@@ -14749,12 +14735,12 @@
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.957099,68.763749</t>
+          <t>https://www.google.com/maps?q=40.951358,68.806869</t>
         </is>
       </c>
     </row>
@@ -14765,25 +14751,25 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C156" t="n">
         <v>52</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>41.622198</v>
+        <v>40.957099</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>69.947261</v>
+        <v>68.763749</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>41.622198, 69.947261</t>
+          <t>40.957099, 68.763749</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Чинаркент</t>
+          <t>Гульзарабад</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -14792,49 +14778,47 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>46.1</v>
+        <v>45.6</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Бостанлыкский район</t>
+          <t>Чиназский район</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>837</v>
+        <v>1420</v>
       </c>
       <c r="M156" t="n">
         <v>3</v>
       </c>
       <c r="N156" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" t="n">
         <v>5</v>
-      </c>
-      <c r="O156" t="n">
-        <v>3</v>
-      </c>
-      <c r="P156" t="n">
-        <v>0</v>
       </c>
       <c r="Q156" t="n">
         <v>5</v>
       </c>
       <c r="R156" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S156" t="n">
-        <v>937</v>
+        <v>0</v>
       </c>
       <c r="T156" t="n">
-        <v>147.5</v>
+        <v>59.7</v>
       </c>
       <c r="U156" t="n">
-        <v>1</v>
-      </c>
-      <c r="V156" t="n">
-        <v>140</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V156" t="inlineStr"/>
       <c r="W156" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -14847,7 +14831,7 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.622198,69.947261</t>
+          <t>https://www.google.com/maps?q=40.957099,68.763749</t>
         </is>
       </c>
     </row>
@@ -14858,25 +14842,25 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C157" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>40.971436</v>
+        <v>41.622198</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>69.968012</v>
+        <v>69.947261</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>40.971436, 69.968012</t>
+          <t>41.622198, 69.947261</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Увак</t>
+          <t>Чинаркент</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -14888,24 +14872,24 @@
         <v>0.2</v>
       </c>
       <c r="J157" t="n">
-        <v>47</v>
+        <v>46.1</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Ахангаранский район</t>
+          <t>Бостанлыкский район</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>1534</v>
+        <v>837</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O157" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P157" t="n">
         <v>0</v>
@@ -14914,18 +14898,20 @@
         <v>5</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S157" t="n">
-        <v>0</v>
+        <v>937</v>
       </c>
       <c r="T157" t="n">
-        <v>55.2</v>
+        <v>147.5</v>
       </c>
       <c r="U157" t="n">
-        <v>0</v>
-      </c>
-      <c r="V157" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V157" t="n">
+        <v>140</v>
+      </c>
       <c r="W157" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -14933,12 +14919,12 @@
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.971436,69.968012</t>
+          <t>https://www.google.com/maps?q=41.622198,69.947261</t>
         </is>
       </c>
     </row>
@@ -14949,25 +14935,25 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C158" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>40.830681</v>
+        <v>40.971436</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>68.88272600000001</v>
+        <v>69.968012</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>40.830681, 68.882726</t>
+          <t>40.971436, 69.968012</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Дустлик</t>
+          <t>Увак</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -14979,15 +14965,15 @@
         <v>0.2</v>
       </c>
       <c r="J158" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Куйичирчикский район</t>
+          <t>Ахангаранский район</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1279</v>
+        <v>1534</v>
       </c>
       <c r="M158" t="n">
         <v>0</v>
@@ -15011,7 +14997,7 @@
         <v>0</v>
       </c>
       <c r="T158" t="n">
-        <v>63.5</v>
+        <v>55.2</v>
       </c>
       <c r="U158" t="n">
         <v>0</v>
@@ -15029,7 +15015,7 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.830681,68.882726</t>
+          <t>https://www.google.com/maps?q=40.971436,69.968012</t>
         </is>
       </c>
     </row>
@@ -15040,25 +15026,25 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="C159" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>40.954123</v>
+        <v>40.830681</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>68.73223900000001</v>
+        <v>68.88272600000001</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>40.954123, 68.732239</t>
+          <t>40.830681, 68.882726</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Яллама</t>
+          <t>Дустлик</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -15067,18 +15053,18 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J159" t="n">
-        <v>47.7</v>
+        <v>47.1</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Чиназский район</t>
+          <t>Куйичирчикский район</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1716</v>
+        <v>1279</v>
       </c>
       <c r="M159" t="n">
         <v>0</v>
@@ -15090,7 +15076,7 @@
         <v>0</v>
       </c>
       <c r="P159" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q159" t="n">
         <v>5</v>
@@ -15102,7 +15088,7 @@
         <v>0</v>
       </c>
       <c r="T159" t="n">
-        <v>59.7</v>
+        <v>63.5</v>
       </c>
       <c r="U159" t="n">
         <v>0</v>
@@ -15115,12 +15101,12 @@
       </c>
       <c r="X159" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.954123,68.732239</t>
+          <t>https://www.google.com/maps?q=40.830681,68.882726</t>
         </is>
       </c>
     </row>
@@ -15131,25 +15117,25 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="C160" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>40.908954</v>
+        <v>40.954123</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>68.78631</v>
+        <v>68.73223900000001</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>40.908954, 68.786310</t>
+          <t>40.954123, 68.732239</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Курганча</t>
+          <t>Яллама</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -15158,18 +15144,18 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J160" t="n">
-        <v>48.7</v>
+        <v>47.7</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Куйичирчикский район</t>
+          <t>Чиназский район</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1815</v>
+        <v>1716</v>
       </c>
       <c r="M160" t="n">
         <v>0</v>
@@ -15181,7 +15167,7 @@
         <v>0</v>
       </c>
       <c r="P160" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q160" t="n">
         <v>5</v>
@@ -15193,7 +15179,7 @@
         <v>0</v>
       </c>
       <c r="T160" t="n">
-        <v>63.5</v>
+        <v>59.7</v>
       </c>
       <c r="U160" t="n">
         <v>0</v>
@@ -15206,12 +15192,12 @@
       </c>
       <c r="X160" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.908954,68.786310</t>
+          <t>https://www.google.com/maps?q=40.954123,68.732239</t>
         </is>
       </c>
     </row>
@@ -15222,25 +15208,25 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C161" t="n">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>41.669921</v>
+        <v>40.908954</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>69.95719</v>
+        <v>68.78631</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>41.669921, 69.957190</t>
+          <t>40.908954, 68.786310</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Хумсан</t>
+          <t>Курганча</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -15249,18 +15235,18 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J161" t="n">
-        <v>49.6</v>
+        <v>48.7</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Бостанлыкский район</t>
+          <t>Куйичирчикский район</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>2001</v>
+        <v>1815</v>
       </c>
       <c r="M161" t="n">
         <v>0</v>
@@ -15278,13 +15264,13 @@
         <v>5</v>
       </c>
       <c r="R161" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S161" t="n">
-        <v>1260</v>
+        <v>0</v>
       </c>
       <c r="T161" t="n">
-        <v>147.5</v>
+        <v>63.5</v>
       </c>
       <c r="U161" t="n">
         <v>0</v>
@@ -15302,7 +15288,7 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.669921,69.957190</t>
+          <t>https://www.google.com/maps?q=40.908954,68.786310</t>
         </is>
       </c>
     </row>
@@ -15313,25 +15299,25 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="C162" t="n">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>41.022527</v>
+        <v>41.669921</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>70.044977</v>
+        <v>69.95719</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>41.022527, 70.044977</t>
+          <t>41.669921, 69.957190</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Самарчук</t>
+          <t>Хумсан</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -15340,24 +15326,24 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="J162" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Ахангаранский район</t>
+          <t>Бостанлыкский район</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>1841</v>
+        <v>2001</v>
       </c>
       <c r="M162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -15369,13 +15355,13 @@
         <v>5</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S162" t="n">
-        <v>0</v>
+        <v>1260</v>
       </c>
       <c r="T162" t="n">
-        <v>55.2</v>
+        <v>147.5</v>
       </c>
       <c r="U162" t="n">
         <v>0</v>
@@ -15388,12 +15374,12 @@
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.022527,70.044977</t>
+          <t>https://www.google.com/maps?q=41.669921,69.957190</t>
         </is>
       </c>
     </row>
@@ -15404,25 +15390,25 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C163" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>40.768015</v>
+        <v>41.022527</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>68.959682</v>
+        <v>70.044977</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>40.768015, 68.959682</t>
+          <t>41.022527, 70.044977</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Хамзаабад</t>
+          <t>Самарчук</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -15431,24 +15417,24 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J163" t="n">
         <v>49.8</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Аккурганский район</t>
+          <t>Ахангаранский район</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>1752</v>
+        <v>1841</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -15466,7 +15452,7 @@
         <v>0</v>
       </c>
       <c r="T163" t="n">
-        <v>40.3</v>
+        <v>55.2</v>
       </c>
       <c r="U163" t="n">
         <v>0</v>
@@ -15479,12 +15465,12 @@
       </c>
       <c r="X163" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.768015,68.959682</t>
+          <t>https://www.google.com/maps?q=41.022527,70.044977</t>
         </is>
       </c>
     </row>
@@ -15495,25 +15481,25 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C164" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>41.00906</v>
+        <v>40.768015</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>70.03652700000001</v>
+        <v>68.959682</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>41.009060, 70.036527</t>
+          <t>40.768015, 68.959682</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Саглам</t>
+          <t>Хамзаабад</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -15525,27 +15511,27 @@
         <v>0.2</v>
       </c>
       <c r="J164" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Ахангаранский район</t>
+          <t>Аккурганский район</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>1664</v>
+        <v>1752</v>
       </c>
       <c r="M164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
       </c>
       <c r="P164" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q164" t="n">
         <v>5</v>
@@ -15557,7 +15543,7 @@
         <v>0</v>
       </c>
       <c r="T164" t="n">
-        <v>55.2</v>
+        <v>40.3</v>
       </c>
       <c r="U164" t="n">
         <v>0</v>
@@ -15570,12 +15556,12 @@
       </c>
       <c r="X164" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.009060,70.036527</t>
+          <t>https://www.google.com/maps?q=40.768015,68.959682</t>
         </is>
       </c>
     </row>
@@ -15586,25 +15572,25 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="C165" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>40.918102</v>
+        <v>41.00906</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>68.74329</v>
+        <v>70.03652700000001</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>40.918102, 68.743290</t>
+          <t>41.009060, 70.036527</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Янги Чиназ</t>
+          <t>Саглам</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -15613,30 +15599,30 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J165" t="n">
-        <v>50.1</v>
+        <v>49.9</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Чиназский район</t>
+          <t>Ахангаранский район</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>1784</v>
+        <v>1664</v>
       </c>
       <c r="M165" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
       </c>
       <c r="P165" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q165" t="n">
         <v>5</v>
@@ -15648,7 +15634,7 @@
         <v>0</v>
       </c>
       <c r="T165" t="n">
-        <v>59.7</v>
+        <v>55.2</v>
       </c>
       <c r="U165" t="n">
         <v>0</v>
@@ -15666,7 +15652,7 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.918102,68.743290</t>
+          <t>https://www.google.com/maps?q=41.009060,70.036527</t>
         </is>
       </c>
     </row>
@@ -15677,48 +15663,48 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="C166" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>41.56229</v>
+        <v>40.918102</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>70.016367</v>
+        <v>68.74329</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>41.562290, 70.016367</t>
+          <t>40.918102, 68.743290</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Чимган</t>
+          <t>Янги Чиназ</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J166" t="n">
         <v>50.1</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Бостанлыкский район</t>
+          <t>Чиназский район</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>1135</v>
+        <v>1784</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N166" t="n">
         <v>0</v>
@@ -15727,7 +15713,7 @@
         <v>0</v>
       </c>
       <c r="P166" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q166" t="n">
         <v>5</v>
@@ -15739,7 +15725,7 @@
         <v>0</v>
       </c>
       <c r="T166" t="n">
-        <v>147.5</v>
+        <v>59.7</v>
       </c>
       <c r="U166" t="n">
         <v>0</v>
@@ -15752,12 +15738,12 @@
       </c>
       <c r="X166" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.562290,70.016367</t>
+          <t>https://www.google.com/maps?q=40.918102,68.743290</t>
         </is>
       </c>
     </row>
@@ -15768,45 +15754,45 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C167" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D167" s="2" t="n">
-        <v>40.940787</v>
+        <v>41.56229</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>68.708387</v>
+        <v>70.016367</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>40.940787, 68.708387</t>
+          <t>41.562290, 70.016367</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Эркин</t>
+          <t>Чимган</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J167" t="n">
         <v>50.1</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Чиназский район</t>
+          <t>Бостанлыкский район</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>1357</v>
+        <v>1135</v>
       </c>
       <c r="M167" t="n">
         <v>0</v>
@@ -15830,7 +15816,7 @@
         <v>0</v>
       </c>
       <c r="T167" t="n">
-        <v>59.7</v>
+        <v>147.5</v>
       </c>
       <c r="U167" t="n">
         <v>0</v>
@@ -15848,7 +15834,7 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.940787,68.708387</t>
+          <t>https://www.google.com/maps?q=41.562290,70.016367</t>
         </is>
       </c>
     </row>
@@ -15859,25 +15845,25 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="C168" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>40.98193</v>
+        <v>40.940787</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>70.027506</v>
+        <v>68.708387</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>40.981930, 70.027506</t>
+          <t>40.940787, 68.708387</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Гульбог</t>
+          <t>Эркин</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -15886,18 +15872,18 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J168" t="n">
-        <v>50.6</v>
+        <v>50.1</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Ахангаранский район</t>
+          <t>Чиназский район</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>2111</v>
+        <v>1357</v>
       </c>
       <c r="M168" t="n">
         <v>0</v>
@@ -15921,7 +15907,7 @@
         <v>0</v>
       </c>
       <c r="T168" t="n">
-        <v>55.2</v>
+        <v>59.7</v>
       </c>
       <c r="U168" t="n">
         <v>0</v>
@@ -15939,7 +15925,7 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.981930,70.027506</t>
+          <t>https://www.google.com/maps?q=40.940787,68.708387</t>
         </is>
       </c>
     </row>
@@ -15950,25 +15936,25 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C169" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>40.854323</v>
+        <v>40.98193</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>68.78514800000001</v>
+        <v>70.027506</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>40.854323, 68.785148</t>
+          <t>40.981930, 70.027506</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Гул</t>
+          <t>Гульбог</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -15977,18 +15963,18 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J169" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Куйичирчикский район</t>
+          <t>Ахангаранский район</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>1430</v>
+        <v>2111</v>
       </c>
       <c r="M169" t="n">
         <v>0</v>
@@ -16012,7 +15998,7 @@
         <v>0</v>
       </c>
       <c r="T169" t="n">
-        <v>63.5</v>
+        <v>55.2</v>
       </c>
       <c r="U169" t="n">
         <v>0</v>
@@ -16030,7 +16016,7 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.854323,68.785148</t>
+          <t>https://www.google.com/maps?q=40.981930,70.027506</t>
         </is>
       </c>
     </row>
@@ -16041,45 +16027,45 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="C170" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D170" s="2" t="n">
-        <v>41.120414</v>
+        <v>40.854323</v>
       </c>
       <c r="E170" s="2" t="n">
-        <v>70.096497</v>
+        <v>68.78514800000001</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>41.120414, 70.096497</t>
+          <t>40.854323, 68.785148</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Янгиабад</t>
+          <t>Гул</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J170" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Ахангаранский район</t>
+          <t>Куйичирчикский район</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>2298</v>
+        <v>1430</v>
       </c>
       <c r="M170" t="n">
         <v>0</v>
@@ -16103,7 +16089,7 @@
         <v>0</v>
       </c>
       <c r="T170" t="n">
-        <v>55.2</v>
+        <v>63.5</v>
       </c>
       <c r="U170" t="n">
         <v>0</v>
@@ -16121,7 +16107,7 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.120414,70.096497</t>
+          <t>https://www.google.com/maps?q=40.854323,68.785148</t>
         </is>
       </c>
     </row>
@@ -16132,37 +16118,37 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C171" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>41.059111</v>
+        <v>41.120414</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>70.08595699999999</v>
+        <v>70.096497</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>41.059111, 70.085957</t>
+          <t>41.120414, 70.096497</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Янгиабад-2</t>
+          <t>Янгиабад</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>район города</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J171" t="n">
-        <v>51.5</v>
+        <v>51</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -16170,7 +16156,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>2043</v>
+        <v>2298</v>
       </c>
       <c r="M171" t="n">
         <v>0</v>
@@ -16212,7 +16198,7 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.059111,70.085957</t>
+          <t>https://www.google.com/maps?q=41.120414,70.096497</t>
         </is>
       </c>
     </row>
@@ -16223,37 +16209,37 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C172" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>41.04022</v>
+        <v>41.059111</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>70.089085</v>
+        <v>70.08595699999999</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>41.040220, 70.089085</t>
+          <t>41.059111, 70.085957</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>14 квартал</t>
+          <t>Янгиабад-2</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>район города</t>
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J172" t="n">
-        <v>52.5</v>
+        <v>51.5</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -16261,19 +16247,19 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>6421</v>
+        <v>2043</v>
       </c>
       <c r="M172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P172" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q172" t="n">
         <v>5</v>
@@ -16298,12 +16284,12 @@
       </c>
       <c r="X172" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.040220,70.089085</t>
+          <t>https://www.google.com/maps?q=41.059111,70.085957</t>
         </is>
       </c>
     </row>
@@ -16314,37 +16300,37 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C173" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>40.976114</v>
+        <v>41.04022</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>70.054822</v>
+        <v>70.089085</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>40.976114, 70.054822</t>
+          <t>41.040220, 70.089085</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Аблык курган</t>
+          <t>14 квартал</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I173" t="n">
         <v>0.4</v>
       </c>
       <c r="J173" t="n">
-        <v>52.9</v>
+        <v>52.5</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -16352,19 +16338,19 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>2688</v>
+        <v>6421</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N173" t="n">
+        <v>3</v>
+      </c>
+      <c r="O173" t="n">
         <v>1</v>
       </c>
-      <c r="O173" t="n">
-        <v>0</v>
-      </c>
       <c r="P173" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q173" t="n">
         <v>5</v>
@@ -16394,7 +16380,7 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.976114,70.054822</t>
+          <t>https://www.google.com/maps?q=41.040220,70.089085</t>
         </is>
       </c>
     </row>
@@ -16405,57 +16391,57 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="C174" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>41.603156</v>
+        <v>40.976114</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>70.02605200000001</v>
+        <v>70.054822</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>41.603156, 70.026052</t>
+          <t>40.976114, 70.054822</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Юбилейный</t>
+          <t>Аблык курган</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J174" t="n">
-        <v>53.4</v>
+        <v>52.9</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Бостанлыкский район</t>
+          <t>Ахангаранский район</t>
         </is>
       </c>
       <c r="L174" t="n">
-        <v>1070</v>
+        <v>2688</v>
       </c>
       <c r="M174" t="n">
         <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
       </c>
       <c r="P174" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q174" t="n">
         <v>5</v>
@@ -16467,7 +16453,7 @@
         <v>0</v>
       </c>
       <c r="T174" t="n">
-        <v>147.5</v>
+        <v>55.2</v>
       </c>
       <c r="U174" t="n">
         <v>0</v>
@@ -16480,12 +16466,12 @@
       </c>
       <c r="X174" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.603156,70.026052</t>
+          <t>https://www.google.com/maps?q=40.976114,70.054822</t>
         </is>
       </c>
     </row>
@@ -16769,7 +16755,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C178" t="n">
         <v>59</v>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,10 +660,10 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V2" t="n">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="V3" t="n">
         <v>500</v>
@@ -846,7 +846,7 @@
         <v>48.5</v>
       </c>
       <c r="U4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V4" t="n">
         <v>1400</v>
@@ -939,7 +939,7 @@
         <v>48.5</v>
       </c>
       <c r="U5" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="V5" t="n">
         <v>918</v>
@@ -1032,7 +1032,7 @@
         <v>98.2</v>
       </c>
       <c r="U6" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="V6" t="n">
         <v>500</v>
@@ -1125,10 +1125,10 @@
         <v>139.7</v>
       </c>
       <c r="U7" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="V7" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>139.7</v>
       </c>
       <c r="U8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V8" t="n">
         <v>700</v>
@@ -1311,7 +1311,7 @@
         <v>98.2</v>
       </c>
       <c r="U9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V9" t="n">
         <v>650</v>
@@ -1590,10 +1590,10 @@
         <v>59.2</v>
       </c>
       <c r="U12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="V12" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         <v>141</v>
       </c>
       <c r="U13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="V13" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>141</v>
       </c>
       <c r="U14" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V14" t="n">
         <v>500</v>
@@ -1869,7 +1869,7 @@
         <v>31.8</v>
       </c>
       <c r="U15" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="V15" t="n">
         <v>500</v>
@@ -1962,10 +1962,10 @@
         <v>59.2</v>
       </c>
       <c r="U16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V16" t="n">
-        <v>200</v>
+        <v>570</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>122.7</v>
       </c>
       <c r="U17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V17" t="n">
         <v>350</v>
@@ -2241,7 +2241,7 @@
         <v>139.7</v>
       </c>
       <c r="U19" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="V19" t="n">
         <v>600</v>
@@ -2334,10 +2334,10 @@
         <v>139.7</v>
       </c>
       <c r="U20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V20" t="n">
-        <v>350</v>
+        <v>600</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2427,10 +2427,10 @@
         <v>139.7</v>
       </c>
       <c r="U21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V21" t="n">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
         <v>59.2</v>
       </c>
       <c r="U22" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V22" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>7</v>
       </c>
       <c r="V23" t="n">
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>28.3</v>
       </c>
       <c r="U24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V24" t="n">
         <v>350</v>
@@ -2892,7 +2892,7 @@
         <v>122.7</v>
       </c>
       <c r="U26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V26" t="n">
         <v>450</v>
@@ -3076,7 +3076,7 @@
         <v>98.2</v>
       </c>
       <c r="U28" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="V28" t="n">
         <v>500</v>
@@ -3169,10 +3169,10 @@
         <v>98.2</v>
       </c>
       <c r="U29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V29" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>141</v>
       </c>
       <c r="U30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V30" t="n">
         <v>1500</v>
@@ -3448,7 +3448,7 @@
         <v>98.2</v>
       </c>
       <c r="U32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V32" t="n">
         <v>600</v>
@@ -3544,7 +3544,7 @@
         <v>10</v>
       </c>
       <c r="V33" t="n">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -3634,10 +3634,10 @@
         <v>139.7</v>
       </c>
       <c r="U34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V34" t="n">
-        <v>1120</v>
+        <v>500</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -3820,10 +3820,10 @@
         <v>47.6</v>
       </c>
       <c r="U36" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="V36" t="n">
-        <v>700</v>
+        <v>70</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -4004,10 +4004,10 @@
         <v>139.7</v>
       </c>
       <c r="U38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V38" t="n">
-        <v>1120</v>
+        <v>500</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>122.7</v>
       </c>
       <c r="U39" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V39" t="n">
         <v>150</v>
@@ -4190,7 +4190,7 @@
         <v>47.6</v>
       </c>
       <c r="U40" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V40" t="n">
         <v>2</v>
@@ -4283,7 +4283,7 @@
         <v>48.5</v>
       </c>
       <c r="U41" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="V41" t="n">
         <v>500</v>
@@ -4376,10 +4376,10 @@
         <v>28.3</v>
       </c>
       <c r="U42" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="V42" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>31.8</v>
       </c>
       <c r="U44" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V44" t="n">
         <v>500</v>
@@ -4837,10 +4837,10 @@
         <v>28.3</v>
       </c>
       <c r="U47" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="V47" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -4930,10 +4930,10 @@
         <v>59.2</v>
       </c>
       <c r="U48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V48" t="n">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -5023,10 +5023,10 @@
         <v>31.8</v>
       </c>
       <c r="U49" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="V49" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>59.2</v>
       </c>
       <c r="U52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V52" t="n">
         <v>840</v>
@@ -5393,7 +5393,7 @@
         <v>59.2</v>
       </c>
       <c r="U53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
@@ -5577,7 +5577,7 @@
         <v>141</v>
       </c>
       <c r="U55" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V55" t="n">
         <v>1000</v>
@@ -5670,7 +5670,7 @@
         <v>122.7</v>
       </c>
       <c r="U56" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V56" t="n">
         <v>150</v>
@@ -5945,7 +5945,7 @@
         <v>122.7</v>
       </c>
       <c r="U59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr">
@@ -6315,10 +6315,10 @@
         <v>270.6</v>
       </c>
       <c r="U63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V63" t="n">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>184.9</v>
       </c>
       <c r="U64" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V64" t="n">
         <v>200</v>
@@ -6504,7 +6504,7 @@
         <v>8</v>
       </c>
       <c r="V65" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>1</v>
       </c>
       <c r="V67" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
@@ -6871,10 +6871,10 @@
         <v>270.6</v>
       </c>
       <c r="U69" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V69" t="n">
-        <v>300</v>
+        <v>1300</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>213.9</v>
       </c>
       <c r="U80" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V80" t="n">
         <v>1000</v>
@@ -8064,7 +8064,7 @@
         <v>213.9</v>
       </c>
       <c r="U82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V82" t="n">
         <v>1000</v>
@@ -8250,7 +8250,7 @@
         <v>184.9</v>
       </c>
       <c r="U84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V84" t="n">
         <v>1840</v>
@@ -8898,7 +8898,7 @@
         <v>1</v>
       </c>
       <c r="V91" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="W91" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>40.8</v>
       </c>
       <c r="U110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V110" t="n">
         <v>4068</v>
@@ -13269,9 +13269,11 @@
         <v>37.9</v>
       </c>
       <c r="U139" t="n">
-        <v>0</v>
-      </c>
-      <c r="V139" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V139" t="n">
+        <v>1800</v>
+      </c>
       <c r="W139" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -13360,9 +13362,11 @@
         <v>37.9</v>
       </c>
       <c r="U140" t="n">
-        <v>0</v>
-      </c>
-      <c r="V140" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V140" t="n">
+        <v>1800</v>
+      </c>
       <c r="W140" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -13633,9 +13637,11 @@
         <v>37.9</v>
       </c>
       <c r="U143" t="n">
-        <v>0</v>
-      </c>
-      <c r="V143" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V143" t="n">
+        <v>1800</v>
+      </c>
       <c r="W143" t="inlineStr">
         <is>
           <t>рекомендуемая</t>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,7 +660,7 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="V2" t="n">
         <v>70</v>
@@ -753,7 +753,7 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="V3" t="n">
         <v>500</v>
@@ -846,7 +846,7 @@
         <v>48.5</v>
       </c>
       <c r="U4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V4" t="n">
         <v>1400</v>
@@ -939,10 +939,10 @@
         <v>48.5</v>
       </c>
       <c r="U5" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="V5" t="n">
-        <v>918</v>
+        <v>1000</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -973,19 +973,19 @@
         <v>91</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>41.332561</v>
+        <v>41.329729</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>69.321702</v>
+        <v>69.289952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41.332561, 69.321702</t>
+          <t>41.329729, 69.289952</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Буюк Ипак Йули махалля</t>
+          <t>Буюк Туран махалля</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -994,48 +994,48 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4166</v>
+        <v>10538</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="O6" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="P6" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="Q6" t="n">
         <v>0.5</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>1970</v>
+        <v>399</v>
       </c>
       <c r="T6" t="n">
-        <v>98.2</v>
+        <v>139.7</v>
       </c>
       <c r="U6" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="V6" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.332561,69.321702</t>
+          <t>https://www.google.com/maps?q=41.329729,69.289952</t>
         </is>
       </c>
     </row>
@@ -1066,19 +1066,19 @@
         <v>91</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>41.329729</v>
+        <v>41.332561</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>69.289952</v>
+        <v>69.321702</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>41.329729, 69.289952</t>
+          <t>41.332561, 69.321702</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Буюк Туран махалля</t>
+          <t>Буюк Ипак Йули махалля</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1087,48 +1087,48 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>10538</v>
+        <v>4166</v>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="O7" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="P7" t="n">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="Q7" t="n">
         <v>0.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>399</v>
+        <v>1970</v>
       </c>
       <c r="T7" t="n">
-        <v>139.7</v>
+        <v>98.2</v>
       </c>
       <c r="U7" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.329729,69.289952</t>
+          <t>https://www.google.com/maps?q=41.332561,69.321702</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
         <v>139.7</v>
       </c>
       <c r="U8" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V8" t="n">
         <v>700</v>
@@ -1311,7 +1311,7 @@
         <v>98.2</v>
       </c>
       <c r="U9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="V9" t="n">
         <v>650</v>
@@ -1404,7 +1404,7 @@
         <v>98.2</v>
       </c>
       <c r="U10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="V10" t="n">
         <v>500</v>
@@ -1590,7 +1590,7 @@
         <v>59.2</v>
       </c>
       <c r="U12" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="V12" t="n">
         <v>400</v>
@@ -1683,7 +1683,7 @@
         <v>141</v>
       </c>
       <c r="U13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V13" t="n">
         <v>500</v>
@@ -1776,7 +1776,7 @@
         <v>141</v>
       </c>
       <c r="U14" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="V14" t="n">
         <v>500</v>
@@ -1869,7 +1869,7 @@
         <v>31.8</v>
       </c>
       <c r="U15" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="V15" t="n">
         <v>500</v>
@@ -1962,10 +1962,10 @@
         <v>59.2</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V16" t="n">
-        <v>570</v>
+        <v>200</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>139.7</v>
       </c>
       <c r="U19" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="V19" t="n">
         <v>600</v>
@@ -2334,10 +2334,10 @@
         <v>139.7</v>
       </c>
       <c r="U20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="V20" t="n">
-        <v>600</v>
+        <v>350</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2427,10 +2427,10 @@
         <v>139.7</v>
       </c>
       <c r="U21" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="V21" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2520,10 +2520,10 @@
         <v>59.2</v>
       </c>
       <c r="U22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V22" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>139.7</v>
       </c>
       <c r="U23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V23" t="n">
         <v>700</v>
@@ -2706,7 +2706,7 @@
         <v>28.3</v>
       </c>
       <c r="U24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V24" t="n">
         <v>350</v>
@@ -2799,10 +2799,10 @@
         <v>141</v>
       </c>
       <c r="U25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V25" t="n">
-        <v>600</v>
+        <v>10</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>122.7</v>
       </c>
       <c r="U26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V26" t="n">
         <v>450</v>
@@ -3076,7 +3076,7 @@
         <v>98.2</v>
       </c>
       <c r="U28" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="V28" t="n">
         <v>500</v>
@@ -3169,10 +3169,10 @@
         <v>98.2</v>
       </c>
       <c r="U29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V29" t="n">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>139.7</v>
       </c>
       <c r="U31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V31" t="n">
         <v>800</v>
@@ -3448,10 +3448,10 @@
         <v>98.2</v>
       </c>
       <c r="U32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V32" t="n">
-        <v>600</v>
+        <v>10</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -3541,10 +3541,10 @@
         <v>98.2</v>
       </c>
       <c r="U33" t="n">
+        <v>11</v>
+      </c>
+      <c r="V33" t="n">
         <v>10</v>
-      </c>
-      <c r="V33" t="n">
-        <v>250</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>59.2</v>
       </c>
       <c r="U35" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="V35" t="n">
         <v>200</v>
@@ -3820,7 +3820,7 @@
         <v>47.6</v>
       </c>
       <c r="U36" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="V36" t="n">
         <v>70</v>
@@ -4097,10 +4097,10 @@
         <v>122.7</v>
       </c>
       <c r="U39" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V39" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>47.6</v>
       </c>
       <c r="U40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V40" t="n">
         <v>2</v>
@@ -4283,7 +4283,7 @@
         <v>48.5</v>
       </c>
       <c r="U41" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="V41" t="n">
         <v>500</v>
@@ -4376,10 +4376,10 @@
         <v>28.3</v>
       </c>
       <c r="U42" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V42" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -4562,10 +4562,10 @@
         <v>31.8</v>
       </c>
       <c r="U44" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="V44" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -4746,9 +4746,11 @@
         <v>48.5</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V46" t="n">
+        <v>8000</v>
+      </c>
       <c r="W46" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4837,10 +4839,10 @@
         <v>28.3</v>
       </c>
       <c r="U47" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V47" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -4930,10 +4932,10 @@
         <v>59.2</v>
       </c>
       <c r="U48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V48" t="n">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -5023,10 +5025,10 @@
         <v>31.8</v>
       </c>
       <c r="U49" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="V49" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -5238,7 +5240,7 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D52" s="2" t="n">
         <v>41.379175</v>
@@ -5300,10 +5302,10 @@
         <v>59.2</v>
       </c>
       <c r="U52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V52" t="n">
-        <v>840</v>
+        <v>1860</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -5484,7 +5486,7 @@
         <v>141</v>
       </c>
       <c r="U54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V54" t="n">
         <v>8000</v>
@@ -5670,10 +5672,10 @@
         <v>122.7</v>
       </c>
       <c r="U56" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V56" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -5945,7 +5947,7 @@
         <v>122.7</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr">
@@ -6036,7 +6038,7 @@
         <v>28.3</v>
       </c>
       <c r="U60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V60" t="n">
         <v>350</v>
@@ -6129,7 +6131,7 @@
         <v>122.7</v>
       </c>
       <c r="U61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V61" t="n">
         <v>4000</v>
@@ -6315,10 +6317,10 @@
         <v>270.6</v>
       </c>
       <c r="U63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V63" t="n">
-        <v>800</v>
+        <v>750</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -6408,7 +6410,7 @@
         <v>184.9</v>
       </c>
       <c r="U64" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V64" t="n">
         <v>200</v>
@@ -6501,10 +6503,10 @@
         <v>213.9</v>
       </c>
       <c r="U65" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V65" t="n">
-        <v>250</v>
+        <v>800</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -6594,9 +6596,11 @@
         <v>184.9</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V66" t="n">
+        <v>250</v>
+      </c>
       <c r="W66" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6778,11 +6782,9 @@
         <v>184.9</v>
       </c>
       <c r="U68" t="n">
-        <v>2</v>
-      </c>
-      <c r="V68" t="n">
-        <v>600</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6871,10 +6873,10 @@
         <v>270.6</v>
       </c>
       <c r="U69" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V69" t="n">
-        <v>1300</v>
+        <v>300</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
@@ -6964,10 +6966,10 @@
         <v>270.6</v>
       </c>
       <c r="U70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V70" t="n">
-        <v>840</v>
+        <v>1860</v>
       </c>
       <c r="W70" t="inlineStr">
         <is>
@@ -7239,10 +7241,10 @@
         <v>270.6</v>
       </c>
       <c r="U73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V73" t="n">
-        <v>840</v>
+        <v>1860</v>
       </c>
       <c r="W73" t="inlineStr">
         <is>
@@ -7698,9 +7700,11 @@
         <v>270.6</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
-      </c>
-      <c r="V78" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V78" t="n">
+        <v>250</v>
+      </c>
       <c r="W78" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7880,7 +7884,7 @@
         <v>213.9</v>
       </c>
       <c r="U80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V80" t="n">
         <v>1000</v>
@@ -8064,7 +8068,7 @@
         <v>213.9</v>
       </c>
       <c r="U82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V82" t="n">
         <v>1000</v>
@@ -8250,7 +8254,7 @@
         <v>184.9</v>
       </c>
       <c r="U84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V84" t="n">
         <v>1840</v>
@@ -8343,10 +8347,10 @@
         <v>270.6</v>
       </c>
       <c r="U85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V85" t="n">
-        <v>840</v>
+        <v>1860</v>
       </c>
       <c r="W85" t="inlineStr">
         <is>
@@ -8436,11 +8440,9 @@
         <v>270.6</v>
       </c>
       <c r="U86" t="n">
-        <v>1</v>
-      </c>
-      <c r="V86" t="n">
-        <v>600</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -10626,7 +10628,7 @@
         <v>40.8</v>
       </c>
       <c r="U110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V110" t="n">
         <v>4068</v>
@@ -10841,7 +10843,7 @@
         <v>22</v>
       </c>
       <c r="C113" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D113" s="2" t="n">
         <v>41.463685</v>
@@ -12570,7 +12572,7 @@
         <v>15</v>
       </c>
       <c r="C132" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D132" s="2" t="n">
         <v>41.587894</v>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,7 +660,7 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V2" t="n">
         <v>70</v>
@@ -753,10 +753,10 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="V3" t="n">
-        <v>500</v>
+        <v>1265</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>41.302521</v>
@@ -939,7 +939,7 @@
         <v>48.5</v>
       </c>
       <c r="U5" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="V5" t="n">
         <v>1000</v>
@@ -973,19 +973,19 @@
         <v>91</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>41.329729</v>
+        <v>41.332561</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>69.289952</v>
+        <v>69.321702</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41.329729, 69.289952</t>
+          <t>41.332561, 69.321702</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Буюк Туран махалля</t>
+          <t>Буюк Ипак Йули махалля</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -994,48 +994,48 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>10538</v>
+        <v>4166</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="O6" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="P6" t="n">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="Q6" t="n">
         <v>0.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>399</v>
+        <v>1970</v>
       </c>
       <c r="T6" t="n">
-        <v>139.7</v>
+        <v>98.2</v>
       </c>
       <c r="U6" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.329729,69.289952</t>
+          <t>https://www.google.com/maps?q=41.332561,69.321702</t>
         </is>
       </c>
     </row>
@@ -1066,19 +1066,19 @@
         <v>91</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>41.332561</v>
+        <v>41.329729</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>69.321702</v>
+        <v>69.289952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>41.332561, 69.321702</t>
+          <t>41.329729, 69.289952</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Буюк Ипак Йули махалля</t>
+          <t>Буюк Туран махалля</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1087,48 +1087,48 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4166</v>
+        <v>10538</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="O7" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="P7" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="Q7" t="n">
         <v>0.5</v>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>1970</v>
+        <v>399</v>
       </c>
       <c r="T7" t="n">
-        <v>98.2</v>
+        <v>139.7</v>
       </c>
       <c r="U7" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="V7" t="n">
-        <v>650</v>
+        <v>350</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.332561,69.321702</t>
+          <t>https://www.google.com/maps?q=41.329729,69.289952</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
         <v>139.7</v>
       </c>
       <c r="U8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V8" t="n">
         <v>700</v>
@@ -1311,7 +1311,7 @@
         <v>98.2</v>
       </c>
       <c r="U9" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="V9" t="n">
         <v>650</v>
@@ -1404,7 +1404,7 @@
         <v>98.2</v>
       </c>
       <c r="U10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="V10" t="n">
         <v>500</v>
@@ -1497,11 +1497,9 @@
         <v>213.9</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
-      </c>
-      <c r="V11" t="n">
-        <v>500</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -1683,10 +1681,10 @@
         <v>141</v>
       </c>
       <c r="U13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V13" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1776,7 +1774,7 @@
         <v>141</v>
       </c>
       <c r="U14" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="V14" t="n">
         <v>500</v>
@@ -1962,7 +1960,7 @@
         <v>59.2</v>
       </c>
       <c r="U16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V16" t="n">
         <v>200</v>
@@ -2055,7 +2053,7 @@
         <v>122.7</v>
       </c>
       <c r="U17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V17" t="n">
         <v>350</v>
@@ -2148,7 +2146,7 @@
         <v>139.7</v>
       </c>
       <c r="U18" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="V18" t="n">
         <v>700</v>
@@ -2241,7 +2239,7 @@
         <v>139.7</v>
       </c>
       <c r="U19" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="V19" t="n">
         <v>600</v>
@@ -2272,7 +2270,7 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>41.351883</v>
@@ -2427,10 +2425,10 @@
         <v>139.7</v>
       </c>
       <c r="U21" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="V21" t="n">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2613,7 +2611,7 @@
         <v>139.7</v>
       </c>
       <c r="U23" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V23" t="n">
         <v>700</v>
@@ -2706,7 +2704,7 @@
         <v>28.3</v>
       </c>
       <c r="U24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V24" t="n">
         <v>350</v>
@@ -2892,10 +2890,10 @@
         <v>122.7</v>
       </c>
       <c r="U26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V26" t="n">
-        <v>450</v>
+        <v>850</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3076,7 +3074,7 @@
         <v>98.2</v>
       </c>
       <c r="U28" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="V28" t="n">
         <v>500</v>
@@ -3200,7 +3198,7 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>41.278439</v>
@@ -3262,10 +3260,10 @@
         <v>141</v>
       </c>
       <c r="U30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>1500</v>
+        <v>1716</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3355,7 +3353,7 @@
         <v>139.7</v>
       </c>
       <c r="U31" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V31" t="n">
         <v>800</v>
@@ -3541,7 +3539,7 @@
         <v>98.2</v>
       </c>
       <c r="U33" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V33" t="n">
         <v>10</v>
@@ -3634,7 +3632,7 @@
         <v>139.7</v>
       </c>
       <c r="U34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V34" t="n">
         <v>500</v>
@@ -3727,7 +3725,7 @@
         <v>59.2</v>
       </c>
       <c r="U35" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="V35" t="n">
         <v>200</v>
@@ -3820,7 +3818,7 @@
         <v>47.6</v>
       </c>
       <c r="U36" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V36" t="n">
         <v>70</v>
@@ -4004,7 +4002,7 @@
         <v>139.7</v>
       </c>
       <c r="U38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V38" t="n">
         <v>500</v>
@@ -4097,10 +4095,10 @@
         <v>122.7</v>
       </c>
       <c r="U39" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V39" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -4193,7 +4191,7 @@
         <v>8</v>
       </c>
       <c r="V40" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -4283,10 +4281,10 @@
         <v>48.5</v>
       </c>
       <c r="U41" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="V41" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -4376,7 +4374,7 @@
         <v>28.3</v>
       </c>
       <c r="U42" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="V42" t="n">
         <v>500</v>
@@ -4562,7 +4560,7 @@
         <v>31.8</v>
       </c>
       <c r="U44" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V44" t="n">
         <v>950</v>
@@ -4839,7 +4837,7 @@
         <v>28.3</v>
       </c>
       <c r="U47" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="V47" t="n">
         <v>500</v>
@@ -5025,7 +5023,7 @@
         <v>31.8</v>
       </c>
       <c r="U49" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="V49" t="n">
         <v>500</v>
@@ -5209,10 +5207,10 @@
         <v>184.9</v>
       </c>
       <c r="U51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V51" t="n">
-        <v>2</v>
+        <v>450</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -5240,7 +5238,7 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D52" s="2" t="n">
         <v>41.379175</v>
@@ -5302,10 +5300,10 @@
         <v>59.2</v>
       </c>
       <c r="U52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V52" t="n">
-        <v>1860</v>
+        <v>840</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -5395,7 +5393,7 @@
         <v>59.2</v>
       </c>
       <c r="U53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
@@ -5486,7 +5484,7 @@
         <v>141</v>
       </c>
       <c r="U54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V54" t="n">
         <v>8000</v>
@@ -5579,10 +5577,10 @@
         <v>141</v>
       </c>
       <c r="U55" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V55" t="n">
-        <v>1000</v>
+        <v>1716</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -5672,10 +5670,10 @@
         <v>122.7</v>
       </c>
       <c r="U56" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V56" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -6038,7 +6036,7 @@
         <v>28.3</v>
       </c>
       <c r="U60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V60" t="n">
         <v>350</v>
@@ -6224,11 +6222,9 @@
         <v>213.9</v>
       </c>
       <c r="U62" t="n">
-        <v>2</v>
-      </c>
-      <c r="V62" t="n">
-        <v>500</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6317,10 +6313,10 @@
         <v>270.6</v>
       </c>
       <c r="U63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V63" t="n">
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -6410,7 +6406,7 @@
         <v>184.9</v>
       </c>
       <c r="U64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V64" t="n">
         <v>200</v>
@@ -6503,7 +6499,7 @@
         <v>213.9</v>
       </c>
       <c r="U65" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V65" t="n">
         <v>800</v>
@@ -6782,9 +6778,11 @@
         <v>184.9</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V68" t="n">
+        <v>2400</v>
+      </c>
       <c r="W68" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6873,10 +6871,10 @@
         <v>270.6</v>
       </c>
       <c r="U69" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V69" t="n">
-        <v>300</v>
+        <v>1300</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
@@ -6966,10 +6964,10 @@
         <v>270.6</v>
       </c>
       <c r="U70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V70" t="n">
-        <v>1860</v>
+        <v>840</v>
       </c>
       <c r="W70" t="inlineStr">
         <is>
@@ -7241,10 +7239,10 @@
         <v>270.6</v>
       </c>
       <c r="U73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V73" t="n">
-        <v>1860</v>
+        <v>840</v>
       </c>
       <c r="W73" t="inlineStr">
         <is>
@@ -7516,11 +7514,9 @@
         <v>213.9</v>
       </c>
       <c r="U76" t="n">
-        <v>1</v>
-      </c>
-      <c r="V76" t="n">
-        <v>1400</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V76" t="inlineStr"/>
       <c r="W76" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8068,7 +8064,7 @@
         <v>213.9</v>
       </c>
       <c r="U82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V82" t="n">
         <v>1000</v>
@@ -8347,10 +8343,10 @@
         <v>270.6</v>
       </c>
       <c r="U85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V85" t="n">
-        <v>1860</v>
+        <v>840</v>
       </c>
       <c r="W85" t="inlineStr">
         <is>
@@ -8531,7 +8527,7 @@
         <v>213.9</v>
       </c>
       <c r="U87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V87" t="n">
         <v>1100</v>
@@ -10843,7 +10839,7 @@
         <v>22</v>
       </c>
       <c r="C113" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D113" s="2" t="n">
         <v>41.463685</v>
@@ -11750,25 +11746,25 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C123" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>41.613627</v>
+        <v>40.914676</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>69.724091</v>
+        <v>69.611769</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>41.613627, 69.724091</t>
+          <t>40.914676, 69.611769</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Хандайлык</t>
+          <t>Нугайкурган</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -11777,42 +11773,42 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J123" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Бостанлыкский район</t>
+          <t>Ахангаранский район</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1637</v>
+        <v>2293</v>
       </c>
       <c r="M123" t="n">
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q123" t="n">
         <v>5</v>
       </c>
       <c r="R123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="T123" t="n">
-        <v>147.5</v>
+        <v>55.2</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
@@ -11825,12 +11821,12 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.613627,69.724091</t>
+          <t>https://www.google.com/maps?q=40.914676,69.611769</t>
         </is>
       </c>
     </row>
@@ -11841,69 +11837,69 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C124" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>40.91613</v>
+        <v>41.613627</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>69.623615</v>
+        <v>69.724091</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>40.916130, 69.623615</t>
+          <t>41.613627, 69.724091</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>4-й микрорайон</t>
+          <t>Хандайлык</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I124" t="n">
         <v>0.4</v>
       </c>
       <c r="J124" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Ахангаранский район</t>
+          <t>Бостанлыкский район</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>16463</v>
+        <v>1637</v>
       </c>
       <c r="M124" t="n">
         <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
       </c>
       <c r="P124" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
         <v>5</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S124" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T124" t="n">
-        <v>55.2</v>
+        <v>147.5</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
@@ -11916,12 +11912,12 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.916130,69.623615</t>
+          <t>https://www.google.com/maps?q=41.613627,69.724091</t>
         </is>
       </c>
     </row>
@@ -12114,7 +12110,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C127" t="n">
         <v>64</v>
@@ -12205,7 +12201,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C128" t="n">
         <v>60</v>
@@ -12569,10 +12565,10 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C132" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D132" s="2" t="n">
         <v>41.587894</v>
@@ -12933,7 +12929,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C136" t="n">
         <v>59</v>
@@ -13299,7 +13295,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C140" t="n">
         <v>60</v>
@@ -14031,7 +14027,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C148" t="n">
         <v>61</v>
@@ -14213,7 +14209,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C150" t="n">
         <v>59</v>
@@ -14304,7 +14300,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C151" t="n">
         <v>59</v>
@@ -14395,7 +14391,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C152" t="n">
         <v>61</v>
@@ -14668,7 +14664,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C155" t="n">
         <v>63</v>
@@ -15216,7 +15212,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C161" t="n">
         <v>60</v>
@@ -15671,7 +15667,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C166" t="n">
         <v>58</v>
@@ -15944,7 +15940,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C169" t="n">
         <v>60</v>
@@ -16126,7 +16122,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C171" t="n">
         <v>61</v>
@@ -16217,7 +16213,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C172" t="n">
         <v>59</v>
@@ -16854,7 +16850,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C179" t="n">
         <v>64</v>
@@ -17036,7 +17032,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C181" t="n">
         <v>62</v>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,7 +660,7 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V2" t="n">
         <v>70</v>
@@ -753,10 +753,10 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="V3" t="n">
-        <v>1265</v>
+        <v>500</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -846,10 +846,10 @@
         <v>48.5</v>
       </c>
       <c r="U4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V4" t="n">
-        <v>1400</v>
+        <v>4500</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -880,19 +880,19 @@
         <v>92</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>41.302521</v>
+        <v>41.332561</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>69.281226</v>
+        <v>69.321702</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>41.302521, 69.281226</t>
+          <t>41.332561, 69.321702</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Айбек</t>
+          <t>Буюк Ипак Йули махалля</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -901,48 +901,48 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Мирабадский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>6299</v>
+        <v>4166</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="O5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P5" t="n">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="Q5" t="n">
         <v>0.5</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>610</v>
+        <v>1970</v>
       </c>
       <c r="T5" t="n">
-        <v>48.5</v>
+        <v>98.2</v>
       </c>
       <c r="U5" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="V5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.302521,69.281226</t>
+          <t>https://www.google.com/maps?q=41.332561,69.321702</t>
         </is>
       </c>
     </row>
@@ -970,22 +970,22 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>41.332561</v>
+        <v>41.302521</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>69.321702</v>
+        <v>69.281226</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41.332561, 69.321702</t>
+          <t>41.302521, 69.281226</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Буюк Ипак Йули махалля</t>
+          <t>Айбек</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -994,48 +994,48 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Мирабадский район</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4166</v>
+        <v>6299</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="O6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P6" t="n">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="Q6" t="n">
         <v>0.5</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>1970</v>
+        <v>610</v>
       </c>
       <c r="T6" t="n">
-        <v>98.2</v>
+        <v>48.5</v>
       </c>
       <c r="U6" t="n">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="V6" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.332561,69.321702</t>
+          <t>https://www.google.com/maps?q=41.302521,69.281226</t>
         </is>
       </c>
     </row>
@@ -1066,19 +1066,19 @@
         <v>91</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>41.329729</v>
+        <v>41.367635</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>69.289952</v>
+        <v>69.275244</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>41.329729, 69.289952</t>
+          <t>41.367635, 69.275244</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Буюк Туран махалля</t>
+          <t>Туркистан махалля</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1098,19 +1098,19 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>10538</v>
+        <v>15593</v>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N7" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="O7" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="P7" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="Q7" t="n">
         <v>0.5</v>
@@ -1119,16 +1119,16 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>399</v>
+        <v>438</v>
       </c>
       <c r="T7" t="n">
         <v>139.7</v>
       </c>
       <c r="U7" t="n">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="V7" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.329729,69.289952</t>
+          <t>https://www.google.com/maps?q=41.367635,69.275244</t>
         </is>
       </c>
     </row>
@@ -1159,19 +1159,19 @@
         <v>91</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>41.367635</v>
+        <v>41.347726</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>69.275244</v>
+        <v>69.334041</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>41.367635, 69.275244</t>
+          <t>41.347726, 69.334041</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Туркистан махалля</t>
+          <t>Навнихол махалля</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1180,48 +1180,48 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>15593</v>
+        <v>8650</v>
       </c>
       <c r="M8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N8" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="O8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="P8" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="Q8" t="n">
         <v>0.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>438</v>
+        <v>1122</v>
       </c>
       <c r="T8" t="n">
-        <v>139.7</v>
+        <v>98.2</v>
       </c>
       <c r="U8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="V8" t="n">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.367635,69.275244</t>
+          <t>https://www.google.com/maps?q=41.347726,69.334041</t>
         </is>
       </c>
     </row>
@@ -1252,19 +1252,19 @@
         <v>91</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>41.347726</v>
+        <v>41.309964</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>69.334041</v>
+        <v>69.34079800000001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>41.347726, 69.334041</t>
+          <t>41.309964, 69.340798</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Навнихол махалля</t>
+          <t>Авайхан махалля</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1284,37 +1284,37 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>8650</v>
+        <v>9976</v>
       </c>
       <c r="M9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N9" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="O9" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="P9" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="Q9" t="n">
         <v>0.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>1122</v>
+        <v>500</v>
       </c>
       <c r="T9" t="n">
         <v>98.2</v>
       </c>
       <c r="U9" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="V9" t="n">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.347726,69.334041</t>
+          <t>https://www.google.com/maps?q=41.309964,69.340798</t>
         </is>
       </c>
     </row>
@@ -1345,19 +1345,19 @@
         <v>90</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>41.309964</v>
+        <v>41.365403</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>69.34079800000001</v>
+        <v>69.393992</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>41.309964, 69.340798</t>
+          <t>41.365403, 69.393992</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Авайхан махалля</t>
+          <t>ТТЗ-4</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1366,30 +1366,30 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>9976</v>
+        <v>13404</v>
       </c>
       <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>16</v>
+      </c>
+      <c r="O10" t="n">
         <v>8</v>
       </c>
-      <c r="N10" t="n">
-        <v>31</v>
-      </c>
-      <c r="O10" t="n">
-        <v>16</v>
-      </c>
       <c r="P10" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
         <v>0.5</v>
@@ -1398,16 +1398,16 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="T10" t="n">
-        <v>98.2</v>
+        <v>213.9</v>
       </c>
       <c r="U10" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>500</v>
+        <v>1400</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.309964,69.340798</t>
+          <t>https://www.google.com/maps?q=41.365403,69.393992</t>
         </is>
       </c>
     </row>
@@ -1438,19 +1438,19 @@
         <v>90</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>41.365403</v>
+        <v>41.345911</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>69.393992</v>
+        <v>69.246887</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>41.365403, 69.393992</t>
+          <t>41.345911, 69.246887</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ТТЗ-4</t>
+          <t>Карасарай махалля</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1459,30 +1459,30 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>13404</v>
+        <v>14912</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="N11" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="O11" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="Q11" t="n">
         <v>0.5</v>
@@ -1491,15 +1491,17 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>1200</v>
+        <v>252</v>
       </c>
       <c r="T11" t="n">
-        <v>213.9</v>
+        <v>59.2</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="V11" t="n">
+        <v>400</v>
+      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -1512,7 +1514,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.365403,69.393992</t>
+          <t>https://www.google.com/maps?q=41.345911,69.246887</t>
         </is>
       </c>
     </row>
@@ -1529,19 +1531,19 @@
         <v>90</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>41.345911</v>
+        <v>41.293314</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>69.246887</v>
+        <v>69.316553</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>41.345911, 69.246887</t>
+          <t>41.293314, 69.316553</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Карасарай махалля</t>
+          <t>Ширинабад махалля</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1557,41 +1559,41 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>14912</v>
+        <v>6723</v>
       </c>
       <c r="M12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="O12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="P12" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="Q12" t="n">
         <v>0.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>252</v>
+        <v>664</v>
       </c>
       <c r="T12" t="n">
-        <v>59.2</v>
+        <v>141</v>
       </c>
       <c r="U12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V12" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1605,7 +1607,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.345911,69.246887</t>
+          <t>https://www.google.com/maps?q=41.293314,69.316553</t>
         </is>
       </c>
     </row>
@@ -1622,19 +1624,19 @@
         <v>90</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>41.293314</v>
+        <v>41.308774</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>69.316553</v>
+        <v>69.31306499999999</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>41.293314, 69.316553</t>
+          <t>41.308774, 69.313065</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ширинабад махалля</t>
+          <t>Машинасозлар (Ташсельмаш)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1643,7 +1645,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1654,37 +1656,37 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6723</v>
+        <v>6677</v>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="O13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P13" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="Q13" t="n">
         <v>0.5</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>664</v>
+        <v>446</v>
       </c>
       <c r="T13" t="n">
         <v>141</v>
       </c>
       <c r="U13" t="n">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="V13" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1698,7 +1700,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.293314,69.316553</t>
+          <t>https://www.google.com/maps?q=41.308774,69.313065</t>
         </is>
       </c>
     </row>
@@ -1715,19 +1717,19 @@
         <v>90</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>41.308774</v>
+        <v>41.284507</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>69.31306499999999</v>
+        <v>69.237188</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>41.308774, 69.313065</t>
+          <t>41.284507, 69.237188</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Машинасозлар (Ташсельмаш)</t>
+          <t>Ракат махалля</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1743,23 +1745,23 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Яккасарайский район</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6677</v>
+        <v>7882</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N14" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="O14" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="P14" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="Q14" t="n">
         <v>0.5</v>
@@ -1768,13 +1770,13 @@
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>446</v>
+        <v>312</v>
       </c>
       <c r="T14" t="n">
-        <v>141</v>
+        <v>31.8</v>
       </c>
       <c r="U14" t="n">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="V14" t="n">
         <v>500</v>
@@ -1791,7 +1793,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.308774,69.313065</t>
+          <t>https://www.google.com/maps?q=41.284507,69.237188</t>
         </is>
       </c>
     </row>
@@ -1808,19 +1810,19 @@
         <v>89</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>41.284507</v>
+        <v>41.333149</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>69.237188</v>
+        <v>69.290054</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41.284507, 69.237188</t>
+          <t>41.333149, 69.290054</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ракат махалля</t>
+          <t>Минор (Ц-6)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1829,30 +1831,30 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Яккасарайский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>7882</v>
+        <v>5182</v>
       </c>
       <c r="M15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P15" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="Q15" t="n">
         <v>0.5</v>
@@ -1861,16 +1863,16 @@
         <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>312</v>
+        <v>399</v>
       </c>
       <c r="T15" t="n">
-        <v>31.8</v>
+        <v>139.7</v>
       </c>
       <c r="U15" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="V15" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -1884,7 +1886,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.284507,69.237188</t>
+          <t>https://www.google.com/maps?q=41.333149,69.290054</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2055,7 @@
         <v>122.7</v>
       </c>
       <c r="U17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V17" t="n">
         <v>350</v>
@@ -2146,7 +2148,7 @@
         <v>139.7</v>
       </c>
       <c r="U18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V18" t="n">
         <v>700</v>
@@ -2239,7 +2241,7 @@
         <v>139.7</v>
       </c>
       <c r="U19" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="V19" t="n">
         <v>600</v>
@@ -2332,7 +2334,7 @@
         <v>139.7</v>
       </c>
       <c r="U20" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="V20" t="n">
         <v>350</v>
@@ -2363,7 +2365,7 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>41.370618</v>
@@ -2425,10 +2427,10 @@
         <v>139.7</v>
       </c>
       <c r="U21" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="V21" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2518,7 +2520,7 @@
         <v>59.2</v>
       </c>
       <c r="U22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V22" t="n">
         <v>200</v>
@@ -2611,10 +2613,10 @@
         <v>139.7</v>
       </c>
       <c r="U23" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="V23" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -2704,7 +2706,7 @@
         <v>28.3</v>
       </c>
       <c r="U24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V24" t="n">
         <v>350</v>
@@ -2828,7 +2830,7 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>41.211644</v>
@@ -2890,10 +2892,10 @@
         <v>122.7</v>
       </c>
       <c r="U26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V26" t="n">
-        <v>850</v>
+        <v>450</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3074,7 +3076,7 @@
         <v>98.2</v>
       </c>
       <c r="U28" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="V28" t="n">
         <v>500</v>
@@ -3167,7 +3169,7 @@
         <v>98.2</v>
       </c>
       <c r="U29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V29" t="n">
         <v>10</v>
@@ -3353,10 +3355,10 @@
         <v>139.7</v>
       </c>
       <c r="U31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V31" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3539,7 +3541,7 @@
         <v>98.2</v>
       </c>
       <c r="U33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V33" t="n">
         <v>10</v>
@@ -3632,7 +3634,7 @@
         <v>139.7</v>
       </c>
       <c r="U34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V34" t="n">
         <v>500</v>
@@ -3725,7 +3727,7 @@
         <v>59.2</v>
       </c>
       <c r="U35" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="V35" t="n">
         <v>200</v>
@@ -3756,54 +3758,54 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>41.286991</v>
+        <v>41.401782</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>69.19375700000001</v>
+        <v>69.458556</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>41.286991, 69.193757</t>
+          <t>41.401782, 69.458556</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Чиланзар Г 9А</t>
+          <t>Улугбек</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>16603</v>
+        <v>3473</v>
       </c>
       <c r="M36" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="O36" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="Q36" t="n">
         <v>0.5</v>
@@ -3815,14 +3817,12 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>47.6</v>
+        <v>213.9</v>
       </c>
       <c r="U36" t="n">
-        <v>23</v>
-      </c>
-      <c r="V36" t="n">
-        <v>70</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.286991,69.193757</t>
+          <t>https://www.google.com/maps?q=41.401782,69.458556</t>
         </is>
       </c>
     </row>
@@ -3852,51 +3852,51 @@
         <v>77</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>41.401782</v>
+        <v>41.286991</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>69.458556</v>
+        <v>69.19375700000001</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>41.401782, 69.458556</t>
+          <t>41.286991, 69.193757</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Улугбек</t>
+          <t>Чиланзар Г 9А</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3473</v>
+        <v>16603</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N37" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="O37" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="P37" t="n">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="Q37" t="n">
         <v>0.5</v>
@@ -3908,12 +3908,14 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>213.9</v>
+        <v>47.6</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="V37" t="n">
+        <v>70</v>
+      </c>
       <c r="W37" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3926,7 +3928,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.401782,69.458556</t>
+          <t>https://www.google.com/maps?q=41.286991,69.193757</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4004,7 @@
         <v>139.7</v>
       </c>
       <c r="U38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V38" t="n">
         <v>500</v>
@@ -4095,7 +4097,7 @@
         <v>122.7</v>
       </c>
       <c r="U39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V39" t="n">
         <v>150</v>
@@ -4188,10 +4190,10 @@
         <v>47.6</v>
       </c>
       <c r="U40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V40" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -4281,10 +4283,10 @@
         <v>48.5</v>
       </c>
       <c r="U41" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="V41" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -4374,7 +4376,7 @@
         <v>28.3</v>
       </c>
       <c r="U42" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="V42" t="n">
         <v>500</v>
@@ -4467,11 +4469,9 @@
         <v>60.2</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1800</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4560,10 +4560,10 @@
         <v>31.8</v>
       </c>
       <c r="U44" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="V44" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>41.221225</v>
@@ -4837,7 +4837,7 @@
         <v>28.3</v>
       </c>
       <c r="U47" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="V47" t="n">
         <v>500</v>
@@ -5023,7 +5023,7 @@
         <v>31.8</v>
       </c>
       <c r="U49" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="V49" t="n">
         <v>500</v>
@@ -5207,10 +5207,10 @@
         <v>184.9</v>
       </c>
       <c r="U51" t="n">
+        <v>3</v>
+      </c>
+      <c r="V51" t="n">
         <v>2</v>
-      </c>
-      <c r="V51" t="n">
-        <v>450</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D53" s="2" t="n">
         <v>41.382173</v>
@@ -5580,7 +5580,7 @@
         <v>3</v>
       </c>
       <c r="V55" t="n">
-        <v>1716</v>
+        <v>1000</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>122.7</v>
       </c>
       <c r="U56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V56" t="n">
         <v>150</v>
@@ -6036,7 +6036,7 @@
         <v>28.3</v>
       </c>
       <c r="U60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V60" t="n">
         <v>350</v>
@@ -6222,9 +6222,11 @@
         <v>213.9</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1400</v>
+      </c>
       <c r="W62" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6313,7 +6315,7 @@
         <v>270.6</v>
       </c>
       <c r="U63" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V63" t="n">
         <v>700</v>
@@ -6406,7 +6408,7 @@
         <v>184.9</v>
       </c>
       <c r="U64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V64" t="n">
         <v>200</v>
@@ -6499,10 +6501,10 @@
         <v>213.9</v>
       </c>
       <c r="U65" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V65" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -6778,10 +6780,10 @@
         <v>184.9</v>
       </c>
       <c r="U68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V68" t="n">
-        <v>2400</v>
+        <v>600</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
@@ -6871,7 +6873,7 @@
         <v>270.6</v>
       </c>
       <c r="U69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V69" t="n">
         <v>1300</v>
@@ -7177,7 +7179,7 @@
         <v>27</v>
       </c>
       <c r="C73" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D73" s="2" t="n">
         <v>41.402834</v>
@@ -7332,9 +7334,11 @@
         <v>270.6</v>
       </c>
       <c r="U74" t="n">
-        <v>2</v>
-      </c>
-      <c r="V74" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="V74" t="n">
+        <v>6000</v>
+      </c>
       <c r="W74" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7514,9 +7518,11 @@
         <v>213.9</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
-      </c>
-      <c r="V76" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V76" t="n">
+        <v>1400</v>
+      </c>
       <c r="W76" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7631,7 +7637,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C78" t="n">
         <v>76</v>
@@ -7880,7 +7886,7 @@
         <v>213.9</v>
       </c>
       <c r="U80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V80" t="n">
         <v>1000</v>
@@ -8436,9 +8442,11 @@
         <v>270.6</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
-      </c>
-      <c r="V86" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V86" t="n">
+        <v>600</v>
+      </c>
       <c r="W86" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8924,7 +8932,7 @@
         <v>55</v>
       </c>
       <c r="C92" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D92" s="2" t="n">
         <v>41.378499</v>
@@ -10652,7 +10660,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C111" t="n">
         <v>76</v>
@@ -11385,7 +11393,7 @@
         <v>23</v>
       </c>
       <c r="C119" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D119" s="2" t="n">
         <v>41.02079</v>
@@ -11567,7 +11575,7 @@
         <v>46</v>
       </c>
       <c r="C121" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D121" s="2" t="n">
         <v>41.570059</v>
@@ -12113,7 +12121,7 @@
         <v>12</v>
       </c>
       <c r="C127" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D127" s="2" t="n">
         <v>40.913997</v>
@@ -13845,25 +13853,25 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C146" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>40.856143</v>
+        <v>40.805776</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>69.001069</v>
+        <v>69.246951</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>40.856143, 69.001069</t>
+          <t>40.805776, 69.246951</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Навои</t>
+          <t>Ачмайли</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -13872,18 +13880,18 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J146" t="n">
-        <v>39.5</v>
+        <v>39.9</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Аккурганский район</t>
+          <t>Букинский район</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1522</v>
+        <v>2059</v>
       </c>
       <c r="M146" t="n">
         <v>0</v>
@@ -13907,7 +13915,7 @@
         <v>0</v>
       </c>
       <c r="T146" t="n">
-        <v>40.3</v>
+        <v>39.6</v>
       </c>
       <c r="U146" t="n">
         <v>0</v>
@@ -13925,7 +13933,7 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.856143,69.001069</t>
+          <t>https://www.google.com/maps?q=40.805776,69.246951</t>
         </is>
       </c>
     </row>
@@ -13936,25 +13944,25 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C147" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>40.805776</v>
+        <v>41.601553</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>69.246951</v>
+        <v>69.87878000000001</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>40.805776, 69.246951</t>
+          <t>41.601553, 69.878780</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ачмайли</t>
+          <t>Каранккуль</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -13963,18 +13971,18 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J147" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Букинский район</t>
+          <t>Бостанлыкский район</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>2059</v>
+        <v>1524</v>
       </c>
       <c r="M147" t="n">
         <v>0</v>
@@ -13998,7 +14006,7 @@
         <v>0</v>
       </c>
       <c r="T147" t="n">
-        <v>39.6</v>
+        <v>147.5</v>
       </c>
       <c r="U147" t="n">
         <v>0</v>
@@ -14016,7 +14024,7 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.805776,69.246951</t>
+          <t>https://www.google.com/maps?q=41.601553,69.878780</t>
         </is>
       </c>
     </row>
@@ -14027,25 +14035,25 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="C148" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>41.601553</v>
+        <v>40.964208</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>69.87878000000001</v>
+        <v>68.862195</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>41.601553, 69.878780</t>
+          <t>40.964208, 68.862195</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Каранккуль</t>
+          <t>Алмазар</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -14054,18 +14062,18 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="J148" t="n">
         <v>40</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Бостанлыкский район</t>
+          <t>Чиназский район</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>1524</v>
+        <v>3416</v>
       </c>
       <c r="M148" t="n">
         <v>0</v>
@@ -14077,7 +14085,7 @@
         <v>0</v>
       </c>
       <c r="P148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q148" t="n">
         <v>5</v>
@@ -14089,7 +14097,7 @@
         <v>0</v>
       </c>
       <c r="T148" t="n">
-        <v>147.5</v>
+        <v>59.7</v>
       </c>
       <c r="U148" t="n">
         <v>0</v>
@@ -14102,12 +14110,12 @@
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.601553,69.878780</t>
+          <t>https://www.google.com/maps?q=40.964208,68.862195</t>
         </is>
       </c>
     </row>
@@ -14118,48 +14126,48 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C149" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>40.964208</v>
+        <v>40.806913</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>68.862195</v>
+        <v>69.184213</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>40.964208, 68.862195</t>
+          <t>40.806913, 69.184213</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Алмазар</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J149" t="n">
-        <v>40</v>
+        <v>40.2</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Чиназский район</t>
+          <t>Букинский район</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>3416</v>
+        <v>4987</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N149" t="n">
         <v>0</v>
@@ -14168,7 +14176,7 @@
         <v>0</v>
       </c>
       <c r="P149" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q149" t="n">
         <v>5</v>
@@ -14180,7 +14188,7 @@
         <v>0</v>
       </c>
       <c r="T149" t="n">
-        <v>59.7</v>
+        <v>39.6</v>
       </c>
       <c r="U149" t="n">
         <v>0</v>
@@ -14198,7 +14206,7 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.964208,68.862195</t>
+          <t>https://www.google.com/maps?q=40.806913,69.184213</t>
         </is>
       </c>
     </row>
@@ -14209,25 +14217,25 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C150" t="n">
         <v>59</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>40.806913</v>
+        <v>40.862328</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>69.184213</v>
+        <v>68.934483</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>40.806913, 69.184213</t>
+          <t>40.862328, 68.934483</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Дустабад (Солдатский)</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -14236,18 +14244,18 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J150" t="n">
-        <v>40.2</v>
+        <v>41.7</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Букинский район</t>
+          <t>Куйичирчикский район</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>4987</v>
+        <v>2450</v>
       </c>
       <c r="M150" t="n">
         <v>1</v>
@@ -14259,7 +14267,7 @@
         <v>0</v>
       </c>
       <c r="P150" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q150" t="n">
         <v>5</v>
@@ -14271,7 +14279,7 @@
         <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>39.6</v>
+        <v>63.5</v>
       </c>
       <c r="U150" t="n">
         <v>0</v>
@@ -14289,7 +14297,7 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.806913,69.184213</t>
+          <t>https://www.google.com/maps?q=40.862328,68.934483</t>
         </is>
       </c>
     </row>
@@ -14300,20 +14308,20 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C151" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>40.862328</v>
+        <v>40.85233</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>68.934483</v>
+        <v>68.91854499999999</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>40.862328, 68.934483</t>
+          <t>40.852330, 68.918545</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -14327,10 +14335,10 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J151" t="n">
-        <v>41.7</v>
+        <v>43.4</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
@@ -14338,7 +14346,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>2450</v>
+        <v>3338</v>
       </c>
       <c r="M151" t="n">
         <v>1</v>
@@ -14380,7 +14388,7 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.862328,68.934483</t>
+          <t>https://www.google.com/maps?q=40.852330,68.918545</t>
         </is>
       </c>
     </row>
@@ -14391,48 +14399,48 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="C152" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>40.85233</v>
+        <v>40.811633</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>68.91854499999999</v>
+        <v>69.007808</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>40.852330, 68.918545</t>
+          <t>40.811633, 69.007808</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Дустабад (Солдатский)</t>
+          <t>Зафар</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J152" t="n">
-        <v>43.4</v>
+        <v>43.7</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Куйичирчикский район</t>
+          <t>Аккурганский район</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>3338</v>
+        <v>1613</v>
       </c>
       <c r="M152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
         <v>0</v>
@@ -14441,7 +14449,7 @@
         <v>0</v>
       </c>
       <c r="P152" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q152" t="n">
         <v>5</v>
@@ -14453,7 +14461,7 @@
         <v>0</v>
       </c>
       <c r="T152" t="n">
-        <v>63.5</v>
+        <v>40.3</v>
       </c>
       <c r="U152" t="n">
         <v>0</v>
@@ -14466,12 +14474,12 @@
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.852330,68.918545</t>
+          <t>https://www.google.com/maps?q=40.811633,69.007808</t>
         </is>
       </c>
     </row>
@@ -14482,25 +14490,25 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C153" t="n">
         <v>48</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>40.811633</v>
+        <v>40.913564</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>69.007808</v>
+        <v>68.821765</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>40.811633, 69.007808</t>
+          <t>40.913564, 68.821765</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Зафар</t>
+          <t>Кушек</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -14509,18 +14517,18 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J153" t="n">
-        <v>43.7</v>
+        <v>43.8</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Аккурганский район</t>
+          <t>Куйичирчикский район</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>1613</v>
+        <v>1342</v>
       </c>
       <c r="M153" t="n">
         <v>0</v>
@@ -14544,7 +14552,7 @@
         <v>0</v>
       </c>
       <c r="T153" t="n">
-        <v>40.3</v>
+        <v>63.5</v>
       </c>
       <c r="U153" t="n">
         <v>0</v>
@@ -14562,7 +14570,7 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.811633,69.007808</t>
+          <t>https://www.google.com/maps?q=40.913564,68.821765</t>
         </is>
       </c>
     </row>
@@ -14573,25 +14581,25 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="C154" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>40.913564</v>
+        <v>40.951358</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>68.821765</v>
+        <v>68.80686900000001</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>40.913564, 68.821765</t>
+          <t>40.951358, 68.806869</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Кушек</t>
+          <t>Янги хаёт</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -14603,15 +14611,15 @@
         <v>0.2</v>
       </c>
       <c r="J154" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Куйичирчикский район</t>
+          <t>Чиназский район</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>1342</v>
+        <v>2189</v>
       </c>
       <c r="M154" t="n">
         <v>0</v>
@@ -14635,7 +14643,7 @@
         <v>0</v>
       </c>
       <c r="T154" t="n">
-        <v>63.5</v>
+        <v>59.7</v>
       </c>
       <c r="U154" t="n">
         <v>0</v>
@@ -14653,7 +14661,7 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.913564,68.821765</t>
+          <t>https://www.google.com/maps?q=40.951358,68.806869</t>
         </is>
       </c>
     </row>
@@ -14664,25 +14672,25 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="C155" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>40.951358</v>
+        <v>40.957099</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>68.80686900000001</v>
+        <v>68.763749</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>40.951358, 68.806869</t>
+          <t>40.957099, 68.763749</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Янги хаёт</t>
+          <t>Гульзарабад</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -14691,10 +14699,10 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>43.9</v>
+        <v>45.6</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -14702,10 +14710,10 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>2189</v>
+        <v>1420</v>
       </c>
       <c r="M155" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N155" t="n">
         <v>0</v>
@@ -14714,7 +14722,7 @@
         <v>0</v>
       </c>
       <c r="P155" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q155" t="n">
         <v>5</v>
@@ -14739,12 +14747,12 @@
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.951358,68.806869</t>
+          <t>https://www.google.com/maps?q=40.957099,68.763749</t>
         </is>
       </c>
     </row>
@@ -14755,25 +14763,25 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C156" t="n">
         <v>52</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>40.957099</v>
+        <v>41.622198</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>68.763749</v>
+        <v>69.947261</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>40.957099, 68.763749</t>
+          <t>41.622198, 69.947261</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Гульзарабад</t>
+          <t>Чинаркент</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -14782,47 +14790,49 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J156" t="n">
-        <v>45.6</v>
+        <v>46.1</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Чиназский район</t>
+          <t>Бостанлыкский район</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>1420</v>
+        <v>837</v>
       </c>
       <c r="M156" t="n">
         <v>3</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O156" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P156" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q156" t="n">
         <v>5</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S156" t="n">
-        <v>0</v>
+        <v>937</v>
       </c>
       <c r="T156" t="n">
-        <v>59.7</v>
+        <v>147.5</v>
       </c>
       <c r="U156" t="n">
-        <v>0</v>
-      </c>
-      <c r="V156" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V156" t="n">
+        <v>140</v>
+      </c>
       <c r="W156" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -14835,7 +14845,7 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.957099,68.763749</t>
+          <t>https://www.google.com/maps?q=41.622198,69.947261</t>
         </is>
       </c>
     </row>
@@ -14846,25 +14856,25 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C157" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>41.622198</v>
+        <v>40.971436</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>69.947261</v>
+        <v>69.968012</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>41.622198, 69.947261</t>
+          <t>40.971436, 69.968012</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Чинаркент</t>
+          <t>Увак</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -14876,24 +14886,24 @@
         <v>0.2</v>
       </c>
       <c r="J157" t="n">
-        <v>46.1</v>
+        <v>47</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Бостанлыкский район</t>
+          <t>Ахангаранский район</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>837</v>
+        <v>1534</v>
       </c>
       <c r="M157" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P157" t="n">
         <v>0</v>
@@ -14902,20 +14912,18 @@
         <v>5</v>
       </c>
       <c r="R157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
-        <v>937</v>
+        <v>0</v>
       </c>
       <c r="T157" t="n">
-        <v>147.5</v>
+        <v>55.2</v>
       </c>
       <c r="U157" t="n">
-        <v>1</v>
-      </c>
-      <c r="V157" t="n">
-        <v>140</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V157" t="inlineStr"/>
       <c r="W157" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -14923,12 +14931,12 @@
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.622198,69.947261</t>
+          <t>https://www.google.com/maps?q=40.971436,69.968012</t>
         </is>
       </c>
     </row>
@@ -14939,25 +14947,25 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C158" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>40.971436</v>
+        <v>40.830681</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>69.968012</v>
+        <v>68.88272600000001</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>40.971436, 69.968012</t>
+          <t>40.830681, 68.882726</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Увак</t>
+          <t>Дустлик</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -14969,15 +14977,15 @@
         <v>0.2</v>
       </c>
       <c r="J158" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Ахангаранский район</t>
+          <t>Куйичирчикский район</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1534</v>
+        <v>1279</v>
       </c>
       <c r="M158" t="n">
         <v>0</v>
@@ -15001,7 +15009,7 @@
         <v>0</v>
       </c>
       <c r="T158" t="n">
-        <v>55.2</v>
+        <v>63.5</v>
       </c>
       <c r="U158" t="n">
         <v>0</v>
@@ -15019,7 +15027,7 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.971436,69.968012</t>
+          <t>https://www.google.com/maps?q=40.830681,68.882726</t>
         </is>
       </c>
     </row>
@@ -15030,25 +15038,25 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C159" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>40.830681</v>
+        <v>40.954123</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>68.88272600000001</v>
+        <v>68.73223900000001</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>40.830681, 68.882726</t>
+          <t>40.954123, 68.732239</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Дустлик</t>
+          <t>Яллама</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -15057,18 +15065,18 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J159" t="n">
-        <v>47.1</v>
+        <v>47.7</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Куйичирчикский район</t>
+          <t>Чиназский район</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1279</v>
+        <v>1716</v>
       </c>
       <c r="M159" t="n">
         <v>0</v>
@@ -15080,7 +15088,7 @@
         <v>0</v>
       </c>
       <c r="P159" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q159" t="n">
         <v>5</v>
@@ -15092,7 +15100,7 @@
         <v>0</v>
       </c>
       <c r="T159" t="n">
-        <v>63.5</v>
+        <v>59.7</v>
       </c>
       <c r="U159" t="n">
         <v>0</v>
@@ -15105,12 +15113,12 @@
       </c>
       <c r="X159" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.830681,68.882726</t>
+          <t>https://www.google.com/maps?q=40.954123,68.732239</t>
         </is>
       </c>
     </row>
@@ -15121,25 +15129,25 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="C160" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>40.954123</v>
+        <v>40.908954</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>68.73223900000001</v>
+        <v>68.78631</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>40.954123, 68.732239</t>
+          <t>40.908954, 68.786310</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Яллама</t>
+          <t>Курганча</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -15148,18 +15156,18 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J160" t="n">
-        <v>47.7</v>
+        <v>48.7</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Чиназский район</t>
+          <t>Куйичирчикский район</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1716</v>
+        <v>1815</v>
       </c>
       <c r="M160" t="n">
         <v>0</v>
@@ -15171,7 +15179,7 @@
         <v>0</v>
       </c>
       <c r="P160" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q160" t="n">
         <v>5</v>
@@ -15183,7 +15191,7 @@
         <v>0</v>
       </c>
       <c r="T160" t="n">
-        <v>59.7</v>
+        <v>63.5</v>
       </c>
       <c r="U160" t="n">
         <v>0</v>
@@ -15196,12 +15204,12 @@
       </c>
       <c r="X160" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.954123,68.732239</t>
+          <t>https://www.google.com/maps?q=40.908954,68.786310</t>
         </is>
       </c>
     </row>
@@ -15212,25 +15220,25 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C161" t="n">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>40.908954</v>
+        <v>41.669921</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>68.78631</v>
+        <v>69.95719</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>40.908954, 68.786310</t>
+          <t>41.669921, 69.957190</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Курганча</t>
+          <t>Хумсан</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -15239,18 +15247,18 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J161" t="n">
-        <v>48.7</v>
+        <v>49.6</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Куйичирчикский район</t>
+          <t>Бостанлыкский район</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>1815</v>
+        <v>2001</v>
       </c>
       <c r="M161" t="n">
         <v>0</v>
@@ -15268,13 +15276,13 @@
         <v>5</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S161" t="n">
-        <v>0</v>
+        <v>1260</v>
       </c>
       <c r="T161" t="n">
-        <v>63.5</v>
+        <v>147.5</v>
       </c>
       <c r="U161" t="n">
         <v>0</v>
@@ -15292,7 +15300,7 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.908954,68.786310</t>
+          <t>https://www.google.com/maps?q=41.669921,69.957190</t>
         </is>
       </c>
     </row>
@@ -15303,51 +15311,51 @@
         </is>
       </c>
       <c r="B162" t="n">
+        <v>41</v>
+      </c>
+      <c r="C162" t="n">
+        <v>52</v>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>41.022527</v>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>70.044977</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>41.022527, 70.044977</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Самарчук</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>село</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J162" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Ахангаранский район</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
+        <v>1841</v>
+      </c>
+      <c r="M162" t="n">
+        <v>2</v>
+      </c>
+      <c r="N162" t="n">
         <v>1</v>
-      </c>
-      <c r="C162" t="n">
-        <v>81</v>
-      </c>
-      <c r="D162" s="2" t="n">
-        <v>41.669921</v>
-      </c>
-      <c r="E162" s="2" t="n">
-        <v>69.95719</v>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>41.669921, 69.957190</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>Хумсан</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>село</t>
-        </is>
-      </c>
-      <c r="I162" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J162" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>Бостанлыкский район</t>
-        </is>
-      </c>
-      <c r="L162" t="n">
-        <v>2001</v>
-      </c>
-      <c r="M162" t="n">
-        <v>0</v>
-      </c>
-      <c r="N162" t="n">
-        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -15359,13 +15367,13 @@
         <v>5</v>
       </c>
       <c r="R162" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S162" t="n">
-        <v>1260</v>
+        <v>0</v>
       </c>
       <c r="T162" t="n">
-        <v>147.5</v>
+        <v>55.2</v>
       </c>
       <c r="U162" t="n">
         <v>0</v>
@@ -15378,12 +15386,12 @@
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.669921,69.957190</t>
+          <t>https://www.google.com/maps?q=41.022527,70.044977</t>
         </is>
       </c>
     </row>
@@ -15394,25 +15402,25 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C163" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>41.022527</v>
+        <v>40.768015</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>70.044977</v>
+        <v>68.959682</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>41.022527, 70.044977</t>
+          <t>40.768015, 68.959682</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Самарчук</t>
+          <t>Хамзаабад</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -15421,24 +15429,24 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J163" t="n">
         <v>49.8</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Ахангаранский район</t>
+          <t>Аккурганский район</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>1841</v>
+        <v>1752</v>
       </c>
       <c r="M163" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -15456,7 +15464,7 @@
         <v>0</v>
       </c>
       <c r="T163" t="n">
-        <v>55.2</v>
+        <v>40.3</v>
       </c>
       <c r="U163" t="n">
         <v>0</v>
@@ -15469,12 +15477,12 @@
       </c>
       <c r="X163" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.022527,70.044977</t>
+          <t>https://www.google.com/maps?q=40.768015,68.959682</t>
         </is>
       </c>
     </row>
@@ -15485,25 +15493,25 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C164" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>40.768015</v>
+        <v>41.00906</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>68.959682</v>
+        <v>70.03652700000001</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>40.768015, 68.959682</t>
+          <t>41.009060, 70.036527</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Хамзаабад</t>
+          <t>Саглам</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -15515,27 +15523,27 @@
         <v>0.2</v>
       </c>
       <c r="J164" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Аккурганский район</t>
+          <t>Ахангаранский район</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>1752</v>
+        <v>1664</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
       </c>
       <c r="P164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q164" t="n">
         <v>5</v>
@@ -15547,7 +15555,7 @@
         <v>0</v>
       </c>
       <c r="T164" t="n">
-        <v>40.3</v>
+        <v>55.2</v>
       </c>
       <c r="U164" t="n">
         <v>0</v>
@@ -15560,12 +15568,12 @@
       </c>
       <c r="X164" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.768015,68.959682</t>
+          <t>https://www.google.com/maps?q=41.009060,70.036527</t>
         </is>
       </c>
     </row>
@@ -15576,25 +15584,25 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="C165" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>41.00906</v>
+        <v>40.918102</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>70.03652700000001</v>
+        <v>68.74329</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>41.009060, 70.036527</t>
+          <t>40.918102, 68.743290</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Саглам</t>
+          <t>Янги Чиназ</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -15603,30 +15611,30 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J165" t="n">
-        <v>49.9</v>
+        <v>50.1</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Ахангаранский район</t>
+          <t>Чиназский район</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>1664</v>
+        <v>1784</v>
       </c>
       <c r="M165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
       </c>
       <c r="P165" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q165" t="n">
         <v>5</v>
@@ -15638,7 +15646,7 @@
         <v>0</v>
       </c>
       <c r="T165" t="n">
-        <v>55.2</v>
+        <v>59.7</v>
       </c>
       <c r="U165" t="n">
         <v>0</v>
@@ -15656,7 +15664,7 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.009060,70.036527</t>
+          <t>https://www.google.com/maps?q=40.918102,68.743290</t>
         </is>
       </c>
     </row>
@@ -15667,48 +15675,48 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="C166" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>40.918102</v>
+        <v>41.56229</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>68.74329</v>
+        <v>70.016367</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>40.918102, 68.743290</t>
+          <t>41.562290, 70.016367</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Янги Чиназ</t>
+          <t>Чимган</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="J166" t="n">
         <v>50.1</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Чиназский район</t>
+          <t>Бостанлыкский район</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>1784</v>
+        <v>1135</v>
       </c>
       <c r="M166" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
         <v>0</v>
@@ -15717,7 +15725,7 @@
         <v>0</v>
       </c>
       <c r="P166" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q166" t="n">
         <v>5</v>
@@ -15729,7 +15737,7 @@
         <v>0</v>
       </c>
       <c r="T166" t="n">
-        <v>59.7</v>
+        <v>147.5</v>
       </c>
       <c r="U166" t="n">
         <v>0</v>
@@ -15742,12 +15750,12 @@
       </c>
       <c r="X166" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.918102,68.743290</t>
+          <t>https://www.google.com/maps?q=41.562290,70.016367</t>
         </is>
       </c>
     </row>
@@ -15758,45 +15766,45 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C167" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D167" s="2" t="n">
-        <v>41.56229</v>
+        <v>40.940787</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>70.016367</v>
+        <v>68.708387</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>41.562290, 70.016367</t>
+          <t>40.940787, 68.708387</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Чимган</t>
+          <t>Эркин</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J167" t="n">
         <v>50.1</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Бостанлыкский район</t>
+          <t>Чиназский район</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>1135</v>
+        <v>1357</v>
       </c>
       <c r="M167" t="n">
         <v>0</v>
@@ -15820,7 +15828,7 @@
         <v>0</v>
       </c>
       <c r="T167" t="n">
-        <v>147.5</v>
+        <v>59.7</v>
       </c>
       <c r="U167" t="n">
         <v>0</v>
@@ -15838,7 +15846,7 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.562290,70.016367</t>
+          <t>https://www.google.com/maps?q=40.940787,68.708387</t>
         </is>
       </c>
     </row>
@@ -15849,25 +15857,25 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="C168" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>40.940787</v>
+        <v>40.98193</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>68.708387</v>
+        <v>70.027506</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>40.940787, 68.708387</t>
+          <t>40.981930, 70.027506</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Эркин</t>
+          <t>Гульбог</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -15876,18 +15884,18 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J168" t="n">
-        <v>50.1</v>
+        <v>50.6</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Чиназский район</t>
+          <t>Ахангаранский район</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>1357</v>
+        <v>2111</v>
       </c>
       <c r="M168" t="n">
         <v>0</v>
@@ -15911,7 +15919,7 @@
         <v>0</v>
       </c>
       <c r="T168" t="n">
-        <v>59.7</v>
+        <v>55.2</v>
       </c>
       <c r="U168" t="n">
         <v>0</v>
@@ -15929,7 +15937,7 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.940787,68.708387</t>
+          <t>https://www.google.com/maps?q=40.981930,70.027506</t>
         </is>
       </c>
     </row>
@@ -15940,25 +15948,25 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="C169" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>40.98193</v>
+        <v>40.854323</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>70.027506</v>
+        <v>68.78514800000001</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>40.981930, 70.027506</t>
+          <t>40.854323, 68.785148</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Гульбог</t>
+          <t>Гул</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -15967,18 +15975,18 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J169" t="n">
-        <v>50.6</v>
+        <v>50.8</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Ахангаранский район</t>
+          <t>Куйичирчикский район</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>2111</v>
+        <v>1430</v>
       </c>
       <c r="M169" t="n">
         <v>0</v>
@@ -16002,7 +16010,7 @@
         <v>0</v>
       </c>
       <c r="T169" t="n">
-        <v>55.2</v>
+        <v>63.5</v>
       </c>
       <c r="U169" t="n">
         <v>0</v>
@@ -16020,7 +16028,7 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.981930,70.027506</t>
+          <t>https://www.google.com/maps?q=40.854323,68.785148</t>
         </is>
       </c>
     </row>
@@ -16031,45 +16039,45 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="C170" t="n">
+        <v>61</v>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>41.120414</v>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>70.096497</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>41.120414, 70.096497</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Янгиабад</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>город</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J170" t="n">
         <v>51</v>
       </c>
-      <c r="D170" s="2" t="n">
-        <v>40.854323</v>
-      </c>
-      <c r="E170" s="2" t="n">
-        <v>68.78514800000001</v>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>40.854323, 68.785148</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>Гул</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>село</t>
-        </is>
-      </c>
-      <c r="I170" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J170" t="n">
-        <v>50.8</v>
-      </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Куйичирчикский район</t>
+          <t>Ахангаранский район</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1430</v>
+        <v>2298</v>
       </c>
       <c r="M170" t="n">
         <v>0</v>
@@ -16093,7 +16101,7 @@
         <v>0</v>
       </c>
       <c r="T170" t="n">
-        <v>63.5</v>
+        <v>55.2</v>
       </c>
       <c r="U170" t="n">
         <v>0</v>
@@ -16111,7 +16119,7 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.854323,68.785148</t>
+          <t>https://www.google.com/maps?q=41.120414,70.096497</t>
         </is>
       </c>
     </row>
@@ -16122,37 +16130,37 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C171" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>41.120414</v>
+        <v>41.059111</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>70.096497</v>
+        <v>70.08595699999999</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>41.120414, 70.096497</t>
+          <t>41.059111, 70.085957</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Янгиабад</t>
+          <t>Янгиабад-2</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>район города</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J171" t="n">
-        <v>51</v>
+        <v>51.5</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -16160,7 +16168,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>2298</v>
+        <v>2043</v>
       </c>
       <c r="M171" t="n">
         <v>0</v>
@@ -16202,7 +16210,7 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.120414,70.096497</t>
+          <t>https://www.google.com/maps?q=41.059111,70.085957</t>
         </is>
       </c>
     </row>
@@ -16213,37 +16221,37 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C172" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>41.059111</v>
+        <v>41.04022</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>70.08595699999999</v>
+        <v>70.089085</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>41.059111, 70.085957</t>
+          <t>41.040220, 70.089085</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Янгиабад-2</t>
+          <t>14 квартал</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>район города</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J172" t="n">
-        <v>51.5</v>
+        <v>52.5</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -16251,19 +16259,19 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>2043</v>
+        <v>6421</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P172" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q172" t="n">
         <v>5</v>
@@ -16288,12 +16296,12 @@
       </c>
       <c r="X172" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.059111,70.085957</t>
+          <t>https://www.google.com/maps?q=41.040220,70.089085</t>
         </is>
       </c>
     </row>
@@ -16304,37 +16312,37 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C173" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>41.04022</v>
+        <v>40.976114</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>70.089085</v>
+        <v>70.054822</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>41.040220, 70.089085</t>
+          <t>40.976114, 70.054822</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>14 квартал</t>
+          <t>Аблык курган</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I173" t="n">
         <v>0.4</v>
       </c>
       <c r="J173" t="n">
-        <v>52.5</v>
+        <v>52.9</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -16342,19 +16350,19 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>6421</v>
+        <v>2688</v>
       </c>
       <c r="M173" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
+        <v>1</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" t="n">
         <v>3</v>
-      </c>
-      <c r="O173" t="n">
-        <v>1</v>
-      </c>
-      <c r="P173" t="n">
-        <v>4</v>
       </c>
       <c r="Q173" t="n">
         <v>5</v>
@@ -16384,7 +16392,7 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.040220,70.089085</t>
+          <t>https://www.google.com/maps?q=40.976114,70.054822</t>
         </is>
       </c>
     </row>
@@ -16395,57 +16403,57 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="C174" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>40.976114</v>
+        <v>41.603156</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>70.054822</v>
+        <v>70.02605200000001</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>40.976114, 70.054822</t>
+          <t>41.603156, 70.026052</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Аблык курган</t>
+          <t>Юбилейный</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J174" t="n">
-        <v>52.9</v>
+        <v>53.4</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Ахангаранский район</t>
+          <t>Бостанлыкский район</t>
         </is>
       </c>
       <c r="L174" t="n">
-        <v>2688</v>
+        <v>1070</v>
       </c>
       <c r="M174" t="n">
         <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
       </c>
       <c r="P174" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q174" t="n">
         <v>5</v>
@@ -16457,7 +16465,7 @@
         <v>0</v>
       </c>
       <c r="T174" t="n">
-        <v>55.2</v>
+        <v>147.5</v>
       </c>
       <c r="U174" t="n">
         <v>0</v>
@@ -16470,12 +16478,12 @@
       </c>
       <c r="X174" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.976114,70.054822</t>
+          <t>https://www.google.com/maps?q=41.603156,70.026052</t>
         </is>
       </c>
     </row>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,7 +660,7 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V2" t="n">
         <v>70</v>
@@ -753,7 +753,7 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="V3" t="n">
         <v>500</v>
@@ -846,10 +846,10 @@
         <v>48.5</v>
       </c>
       <c r="U4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V4" t="n">
-        <v>4500</v>
+        <v>2500</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -880,19 +880,19 @@
         <v>92</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>41.332561</v>
+        <v>41.302521</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>69.321702</v>
+        <v>69.281226</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>41.332561, 69.321702</t>
+          <t>41.302521, 69.281226</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Буюк Ипак Йули махалля</t>
+          <t>Айбек</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -901,48 +901,48 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Мирабадский район</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4166</v>
+        <v>6299</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P5" t="n">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="Q5" t="n">
         <v>0.5</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>1970</v>
+        <v>610</v>
       </c>
       <c r="T5" t="n">
-        <v>98.2</v>
+        <v>48.5</v>
       </c>
       <c r="U5" t="n">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="V5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.332561,69.321702</t>
+          <t>https://www.google.com/maps?q=41.302521,69.281226</t>
         </is>
       </c>
     </row>
@@ -973,19 +973,19 @@
         <v>92</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>41.302521</v>
+        <v>41.332561</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>69.281226</v>
+        <v>69.321702</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41.302521, 69.281226</t>
+          <t>41.332561, 69.321702</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Айбек</t>
+          <t>Буюк Ипак Йули махалля</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -994,48 +994,48 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Мирабадский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6299</v>
+        <v>4166</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="O6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P6" t="n">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="Q6" t="n">
         <v>0.5</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>610</v>
+        <v>1970</v>
       </c>
       <c r="T6" t="n">
-        <v>48.5</v>
+        <v>98.2</v>
       </c>
       <c r="U6" t="n">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="V6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.302521,69.281226</t>
+          <t>https://www.google.com/maps?q=41.332561,69.321702</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
         <v>139.7</v>
       </c>
       <c r="U7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V7" t="n">
         <v>500</v>
@@ -1249,7 +1249,7 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>41.309964</v>
@@ -1311,7 +1311,7 @@
         <v>98.2</v>
       </c>
       <c r="U9" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="V9" t="n">
         <v>500</v>
@@ -1497,7 +1497,7 @@
         <v>59.2</v>
       </c>
       <c r="U11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="V11" t="n">
         <v>400</v>
@@ -1531,19 +1531,19 @@
         <v>90</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>41.293314</v>
+        <v>41.308774</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>69.316553</v>
+        <v>69.31306499999999</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>41.293314, 69.316553</t>
+          <t>41.308774, 69.313065</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ширинабад махалля</t>
+          <t>Машинасозлар (Ташсельмаш)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1563,37 +1563,37 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6723</v>
+        <v>6677</v>
       </c>
       <c r="M12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="O12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P12" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="Q12" t="n">
         <v>0.5</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>664</v>
+        <v>446</v>
       </c>
       <c r="T12" t="n">
         <v>141</v>
       </c>
       <c r="U12" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="V12" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.293314,69.316553</t>
+          <t>https://www.google.com/maps?q=41.308774,69.313065</t>
         </is>
       </c>
     </row>
@@ -1624,19 +1624,19 @@
         <v>90</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>41.308774</v>
+        <v>41.293314</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>69.31306499999999</v>
+        <v>69.316553</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>41.308774, 69.313065</t>
+          <t>41.293314, 69.316553</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Машинасозлар (Ташсельмаш)</t>
+          <t>Ширинабад махалля</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1656,34 +1656,34 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6677</v>
+        <v>6723</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="O13" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P13" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="Q13" t="n">
         <v>0.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>446</v>
+        <v>664</v>
       </c>
       <c r="T13" t="n">
         <v>141</v>
       </c>
       <c r="U13" t="n">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="V13" t="n">
         <v>500</v>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.308774,69.313065</t>
+          <t>https://www.google.com/maps?q=41.293314,69.316553</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
         <v>31.8</v>
       </c>
       <c r="U14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V14" t="n">
         <v>500</v>
@@ -1869,7 +1869,7 @@
         <v>139.7</v>
       </c>
       <c r="U15" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="V15" t="n">
         <v>350</v>
@@ -2241,7 +2241,7 @@
         <v>139.7</v>
       </c>
       <c r="U19" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="V19" t="n">
         <v>600</v>
@@ -2334,7 +2334,7 @@
         <v>139.7</v>
       </c>
       <c r="U20" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="V20" t="n">
         <v>350</v>
@@ -2365,7 +2365,7 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>41.370618</v>
@@ -2427,7 +2427,7 @@
         <v>139.7</v>
       </c>
       <c r="U21" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="V21" t="n">
         <v>500</v>
@@ -2520,7 +2520,7 @@
         <v>59.2</v>
       </c>
       <c r="U22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V22" t="n">
         <v>200</v>
@@ -2613,7 +2613,7 @@
         <v>139.7</v>
       </c>
       <c r="U23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V23" t="n">
         <v>500</v>
@@ -2830,7 +2830,7 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>41.211644</v>
@@ -3076,7 +3076,7 @@
         <v>98.2</v>
       </c>
       <c r="U28" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="V28" t="n">
         <v>500</v>
@@ -3727,7 +3727,7 @@
         <v>59.2</v>
       </c>
       <c r="U35" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="V35" t="n">
         <v>200</v>
@@ -3758,54 +3758,54 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>41.401782</v>
+        <v>41.286991</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>69.458556</v>
+        <v>69.19375700000001</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>41.401782, 69.458556</t>
+          <t>41.286991, 69.193757</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Улугбек</t>
+          <t>Чиланзар Г 9А</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3473</v>
+        <v>16603</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N36" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="O36" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="P36" t="n">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="Q36" t="n">
         <v>0.5</v>
@@ -3817,12 +3817,14 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>213.9</v>
+        <v>47.6</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="V36" t="n">
+        <v>70</v>
+      </c>
       <c r="W36" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3835,7 +3837,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.401782,69.458556</t>
+          <t>https://www.google.com/maps?q=41.286991,69.193757</t>
         </is>
       </c>
     </row>
@@ -3852,51 +3854,51 @@
         <v>77</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>41.286991</v>
+        <v>41.401782</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>69.19375700000001</v>
+        <v>69.458556</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>41.286991, 69.193757</t>
+          <t>41.401782, 69.458556</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Чиланзар Г 9А</t>
+          <t>Улугбек</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>16603</v>
+        <v>3473</v>
       </c>
       <c r="M37" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="O37" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="P37" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="Q37" t="n">
         <v>0.5</v>
@@ -3908,14 +3910,12 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>47.6</v>
+        <v>213.9</v>
       </c>
       <c r="U37" t="n">
-        <v>24</v>
-      </c>
-      <c r="V37" t="n">
-        <v>70</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.286991,69.193757</t>
+          <t>https://www.google.com/maps?q=41.401782,69.458556</t>
         </is>
       </c>
     </row>
@@ -4097,10 +4097,10 @@
         <v>122.7</v>
       </c>
       <c r="U39" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V39" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>38</v>
       </c>
       <c r="V42" t="n">
-        <v>500</v>
+        <v>999</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>41.221225</v>
@@ -4653,7 +4653,7 @@
         <v>60.2</v>
       </c>
       <c r="U45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
@@ -4840,7 +4840,7 @@
         <v>39</v>
       </c>
       <c r="V47" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -5023,10 +5023,10 @@
         <v>31.8</v>
       </c>
       <c r="U49" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="V49" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D53" s="2" t="n">
         <v>41.382173</v>
@@ -5577,10 +5577,10 @@
         <v>141</v>
       </c>
       <c r="U55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V55" t="n">
-        <v>1000</v>
+        <v>1716</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -5670,10 +5670,10 @@
         <v>122.7</v>
       </c>
       <c r="U56" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V56" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>60.2</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr">
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C67" t="n">
         <v>85</v>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C72" t="n">
         <v>81</v>
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C73" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D73" s="2" t="n">
         <v>41.402834</v>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C74" t="n">
         <v>79</v>
@@ -7362,7 +7362,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C75" t="n">
         <v>79</v>
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C76" t="n">
         <v>84</v>
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C77" t="n">
         <v>78</v>
@@ -7637,76 +7637,74 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="C78" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>41.352783</v>
+        <v>41.207141</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>69.14811</v>
+        <v>69.163858</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>41.352783, 69.148110</t>
+          <t>41.207141, 69.163858</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Куксарай</t>
+          <t>Зангиата</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I78" t="n">
         <v>0.6</v>
       </c>
       <c r="J78" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1467</v>
+        <v>1847</v>
       </c>
       <c r="M78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N78" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O78" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q78" t="n">
         <v>5</v>
       </c>
       <c r="R78" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="S78" t="n">
-        <v>3190</v>
+        <v>24505</v>
       </c>
       <c r="T78" t="n">
-        <v>270.6</v>
+        <v>184.9</v>
       </c>
       <c r="U78" t="n">
-        <v>1</v>
-      </c>
-      <c r="V78" t="n">
-        <v>250</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7719,7 +7717,7 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.352783,69.148110</t>
+          <t>https://www.google.com/maps?q=41.207141,69.163858</t>
         </is>
       </c>
     </row>
@@ -7730,57 +7728,57 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="C79" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>41.207141</v>
+        <v>41.399761</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>69.163858</v>
+        <v>69.29601</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>41.207141, 69.163858</t>
+          <t>41.399761, 69.296010</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Зангиата</t>
+          <t>Хавасар</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J79" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1847</v>
+        <v>2533</v>
       </c>
       <c r="M79" t="n">
         <v>1</v>
       </c>
       <c r="N79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O79" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P79" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q79" t="n">
         <v>5</v>
@@ -7789,15 +7787,17 @@
         <v>14</v>
       </c>
       <c r="S79" t="n">
-        <v>24505</v>
+        <v>16114</v>
       </c>
       <c r="T79" t="n">
-        <v>184.9</v>
+        <v>213.9</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
-      </c>
-      <c r="V79" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="V79" t="n">
+        <v>1000</v>
+      </c>
       <c r="W79" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.207141,69.163858</t>
+          <t>https://www.google.com/maps?q=41.399761,69.296010</t>
         </is>
       </c>
     </row>
@@ -7821,76 +7821,74 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C80" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>41.399761</v>
+        <v>41.33418</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>69.29601</v>
+        <v>69.13572499999999</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>41.399761, 69.296010</t>
+          <t>41.334180, 69.135725</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Хавасар</t>
+          <t>Ункурган</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J80" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2533</v>
+        <v>1727</v>
       </c>
       <c r="M80" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N80" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O80" t="n">
+        <v>4</v>
+      </c>
+      <c r="P80" t="n">
         <v>2</v>
-      </c>
-      <c r="P80" t="n">
-        <v>5</v>
       </c>
       <c r="Q80" t="n">
         <v>5</v>
       </c>
       <c r="R80" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="S80" t="n">
-        <v>16114</v>
+        <v>6530</v>
       </c>
       <c r="T80" t="n">
-        <v>213.9</v>
+        <v>184.9</v>
       </c>
       <c r="U80" t="n">
-        <v>4</v>
-      </c>
-      <c r="V80" t="n">
-        <v>1000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V80" t="inlineStr"/>
       <c r="W80" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7903,7 +7901,7 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.399761,69.296010</t>
+          <t>https://www.google.com/maps?q=41.334180,69.135725</t>
         </is>
       </c>
     </row>
@@ -7914,25 +7912,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="C81" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>41.33418</v>
+        <v>41.399172</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>69.13572499999999</v>
+        <v>69.327693</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>41.334180, 69.135725</t>
+          <t>41.399172, 69.327693</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ункурган</t>
+          <t>Гульзар</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7941,47 +7939,49 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1727</v>
+        <v>2403</v>
       </c>
       <c r="M81" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N81" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O81" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q81" t="n">
         <v>5</v>
       </c>
       <c r="R81" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S81" t="n">
-        <v>6530</v>
+        <v>10876</v>
       </c>
       <c r="T81" t="n">
-        <v>184.9</v>
+        <v>213.9</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
-      </c>
-      <c r="V81" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="V81" t="n">
+        <v>1000</v>
+      </c>
       <c r="W81" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.334180,69.135725</t>
+          <t>https://www.google.com/maps?q=41.399172,69.327693</t>
         </is>
       </c>
     </row>
@@ -8005,37 +8005,37 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="C82" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>41.399172</v>
+        <v>41.378205</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>69.327693</v>
+        <v>69.350821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>41.399172, 69.327693</t>
+          <t>41.378205, 69.350821</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Гульзар</t>
+          <t>Салар</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J82" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -8043,37 +8043,37 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2403</v>
+        <v>4623</v>
       </c>
       <c r="M82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N82" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q82" t="n">
         <v>5</v>
       </c>
       <c r="R82" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S82" t="n">
-        <v>10876</v>
+        <v>14705</v>
       </c>
       <c r="T82" t="n">
         <v>213.9</v>
       </c>
       <c r="U82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V82" t="n">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="W82" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.399172,69.327693</t>
+          <t>https://www.google.com/maps?q=41.378205,69.350821</t>
         </is>
       </c>
     </row>
@@ -8098,75 +8098,75 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C83" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>41.378205</v>
+        <v>41.241734</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>69.350821</v>
+        <v>69.141108</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>41.378205, 69.350821</t>
+          <t>41.241734, 69.141108</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Салар</t>
+          <t>Далигузар</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J83" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>4623</v>
+        <v>2089</v>
       </c>
       <c r="M83" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N83" t="n">
         <v>11</v>
       </c>
       <c r="O83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P83" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="Q83" t="n">
         <v>5</v>
       </c>
       <c r="R83" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S83" t="n">
-        <v>14705</v>
+        <v>7256</v>
       </c>
       <c r="T83" t="n">
-        <v>213.9</v>
+        <v>184.9</v>
       </c>
       <c r="U83" t="n">
         <v>2</v>
       </c>
       <c r="V83" t="n">
-        <v>1100</v>
+        <v>1840</v>
       </c>
       <c r="W83" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.378205,69.350821</t>
+          <t>https://www.google.com/maps?q=41.241734,69.141108</t>
         </is>
       </c>
     </row>
@@ -8191,75 +8191,75 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C84" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>41.241734</v>
+        <v>41.403254</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>69.141108</v>
+        <v>69.197048</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>41.241734, 69.141108</t>
+          <t>41.403254, 69.197048</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Далигузар</t>
+          <t>Келес</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="J84" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2089</v>
+        <v>9032</v>
       </c>
       <c r="M84" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N84" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="O84" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P84" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="Q84" t="n">
         <v>5</v>
       </c>
       <c r="R84" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="S84" t="n">
-        <v>7256</v>
+        <v>2140</v>
       </c>
       <c r="T84" t="n">
-        <v>184.9</v>
+        <v>270.6</v>
       </c>
       <c r="U84" t="n">
         <v>2</v>
       </c>
       <c r="V84" t="n">
-        <v>1840</v>
+        <v>840</v>
       </c>
       <c r="W84" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.241734,69.141108</t>
+          <t>https://www.google.com/maps?q=41.403254,69.197048</t>
         </is>
       </c>
     </row>
@@ -8284,37 +8284,37 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C85" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>41.403254</v>
+        <v>41.417442</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>69.197048</v>
+        <v>69.264831</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>41.403254, 69.197048</t>
+          <t>41.417442, 69.264831</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Келес</t>
+          <t>Хасанбай</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -8322,37 +8322,37 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>9032</v>
+        <v>1653</v>
       </c>
       <c r="M85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
         <v>5</v>
       </c>
       <c r="R85" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S85" t="n">
-        <v>2140</v>
+        <v>9304</v>
       </c>
       <c r="T85" t="n">
         <v>270.6</v>
       </c>
       <c r="U85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V85" t="n">
-        <v>840</v>
+        <v>600</v>
       </c>
       <c r="W85" t="inlineStr">
         <is>
@@ -8361,12 +8361,12 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.403254,69.197048</t>
+          <t>https://www.google.com/maps?q=41.417442,69.264831</t>
         </is>
       </c>
     </row>
@@ -8377,25 +8377,25 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C86" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>41.417442</v>
+        <v>41.392035</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>69.264831</v>
+        <v>69.343324</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>41.417442, 69.264831</t>
+          <t>41.392035, 69.343324</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Хасанбай</t>
+          <t>Ункурган</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8404,48 +8404,48 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J86" t="n">
         <v>2.3</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1653</v>
+        <v>2163</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q86" t="n">
         <v>5</v>
       </c>
       <c r="R86" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="S86" t="n">
-        <v>9304</v>
+        <v>11098</v>
       </c>
       <c r="T86" t="n">
-        <v>270.6</v>
+        <v>213.9</v>
       </c>
       <c r="U86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V86" t="n">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="W86" t="inlineStr">
         <is>
@@ -8454,12 +8454,12 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.417442,69.264831</t>
+          <t>https://www.google.com/maps?q=41.392035,69.343324</t>
         </is>
       </c>
     </row>
@@ -8470,25 +8470,25 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C87" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>41.392035</v>
+        <v>41.308872</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>69.343324</v>
+        <v>69.115255</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>41.392035, 69.343324</t>
+          <t>41.308872, 69.115255</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ункурган</t>
+          <t>Харакат</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -8497,49 +8497,47 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2163</v>
+        <v>2845</v>
       </c>
       <c r="M87" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O87" t="n">
         <v>1</v>
       </c>
       <c r="P87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q87" t="n">
         <v>5</v>
       </c>
       <c r="R87" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="S87" t="n">
-        <v>11098</v>
+        <v>3688</v>
       </c>
       <c r="T87" t="n">
-        <v>213.9</v>
+        <v>184.9</v>
       </c>
       <c r="U87" t="n">
-        <v>2</v>
-      </c>
-      <c r="V87" t="n">
-        <v>1100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8552,7 +8550,7 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.392035,69.343324</t>
+          <t>https://www.google.com/maps?q=41.308872,69.115255</t>
         </is>
       </c>
     </row>
@@ -8563,57 +8561,57 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="C88" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>41.308872</v>
+        <v>41.377685</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>69.115255</v>
+        <v>69.46569100000001</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>41.308872, 69.115255</t>
+          <t>41.377685, 69.465691</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Харакат</t>
+          <t>Кибрай</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J88" t="n">
         <v>2.7</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2845</v>
+        <v>3583</v>
       </c>
       <c r="M88" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P88" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q88" t="n">
         <v>5</v>
@@ -8622,10 +8620,10 @@
         <v>2</v>
       </c>
       <c r="S88" t="n">
-        <v>3688</v>
+        <v>439</v>
       </c>
       <c r="T88" t="n">
-        <v>184.9</v>
+        <v>213.9</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
@@ -8643,7 +8641,7 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.308872,69.115255</t>
+          <t>https://www.google.com/maps?q=41.377685,69.465691</t>
         </is>
       </c>
     </row>
@@ -8654,34 +8652,34 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C89" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>41.377685</v>
+        <v>41.44656</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>69.46569100000001</v>
+        <v>69.444159</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>41.377685, 69.465691</t>
+          <t>41.446560, 69.444159</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Кибрай</t>
+          <t>Ходжакурган</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>2.7</v>
@@ -8692,28 +8690,28 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>3583</v>
+        <v>2215</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
         <v>5</v>
       </c>
       <c r="R89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S89" t="n">
-        <v>439</v>
+        <v>129</v>
       </c>
       <c r="T89" t="n">
         <v>213.9</v>
@@ -8729,12 +8727,12 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.377685,69.465691</t>
+          <t>https://www.google.com/maps?q=41.446560,69.444159</t>
         </is>
       </c>
     </row>
@@ -8745,25 +8743,25 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C90" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>41.44656</v>
+        <v>41.380099</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>69.444159</v>
+        <v>69.43011300000001</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>41.446560, 69.444159</t>
+          <t>41.380099, 69.430113</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ходжакурган</t>
+          <t>Аргин</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -8772,10 +8770,10 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J90" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -8783,36 +8781,38 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2215</v>
+        <v>2439</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q90" t="n">
         <v>5</v>
       </c>
       <c r="R90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S90" t="n">
-        <v>129</v>
+        <v>1510</v>
       </c>
       <c r="T90" t="n">
         <v>213.9</v>
       </c>
       <c r="U90" t="n">
-        <v>0</v>
-      </c>
-      <c r="V90" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V90" t="n">
+        <v>900</v>
+      </c>
       <c r="W90" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.446560,69.444159</t>
+          <t>https://www.google.com/maps?q=41.380099,69.430113</t>
         </is>
       </c>
     </row>
@@ -8836,76 +8836,74 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C91" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>41.380099</v>
+        <v>41.378499</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>69.43011300000001</v>
+        <v>69.144857</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>41.380099, 69.430113</t>
+          <t>41.378499, 69.144857</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Аргин</t>
+          <t>Илгар</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2439</v>
+        <v>2210</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P91" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>5</v>
       </c>
       <c r="R91" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S91" t="n">
-        <v>1510</v>
+        <v>2397</v>
       </c>
       <c r="T91" t="n">
-        <v>213.9</v>
+        <v>270.6</v>
       </c>
       <c r="U91" t="n">
-        <v>1</v>
-      </c>
-      <c r="V91" t="n">
-        <v>900</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V91" t="inlineStr"/>
       <c r="W91" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8918,7 +8916,7 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.380099,69.430113</t>
+          <t>https://www.google.com/maps?q=41.378499,69.144857</t>
         </is>
       </c>
     </row>
@@ -8929,54 +8927,54 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C92" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>41.378499</v>
+        <v>41.445931</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>69.144857</v>
+        <v>69.475869</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>41.378499, 69.144857</t>
+          <t>41.445931, 69.475869</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Илгар</t>
+          <t>Сасбага</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J92" t="n">
         <v>3.1</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2210</v>
+        <v>2143</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
         <v>0</v>
@@ -8985,13 +8983,13 @@
         <v>5</v>
       </c>
       <c r="R92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S92" t="n">
-        <v>2397</v>
+        <v>129</v>
       </c>
       <c r="T92" t="n">
-        <v>270.6</v>
+        <v>213.9</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -9004,12 +9002,12 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.378499,69.144857</t>
+          <t>https://www.google.com/maps?q=41.445931,69.475869</t>
         </is>
       </c>
     </row>
@@ -9020,25 +9018,25 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="C93" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>41.445931</v>
+        <v>41.160793</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>69.475869</v>
+        <v>69.174412</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>41.445931, 69.475869</t>
+          <t>41.160793, 69.174412</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Сасбага</t>
+          <t>Боборахим</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9047,18 +9045,18 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J93" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Янгиюльский район</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2143</v>
+        <v>1726</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
@@ -9076,13 +9074,13 @@
         <v>5</v>
       </c>
       <c r="R93" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S93" t="n">
-        <v>129</v>
+        <v>17092</v>
       </c>
       <c r="T93" t="n">
-        <v>213.9</v>
+        <v>129.6</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
@@ -9100,7 +9098,7 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.445931,69.475869</t>
+          <t>https://www.google.com/maps?q=41.160793,69.174412</t>
         </is>
       </c>
     </row>
@@ -9111,54 +9109,54 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="C94" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>41.160793</v>
+        <v>41.343065</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>69.174412</v>
+        <v>69.11617699999999</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>41.160793, 69.174412</t>
+          <t>41.343065, 69.116177</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Боборахим</t>
+          <t>Илгар</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J94" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Янгиюльский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1726</v>
+        <v>2595</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P94" t="n">
         <v>0</v>
@@ -9167,13 +9165,13 @@
         <v>5</v>
       </c>
       <c r="R94" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S94" t="n">
-        <v>17092</v>
+        <v>1141</v>
       </c>
       <c r="T94" t="n">
-        <v>129.6</v>
+        <v>184.9</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -9186,12 +9184,12 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.160793,69.174412</t>
+          <t>https://www.google.com/maps?q=41.343065,69.116177</t>
         </is>
       </c>
     </row>
@@ -9202,69 +9200,69 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="C95" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>41.343065</v>
+        <v>41.418715</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>69.11617699999999</v>
+        <v>69.193523</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>41.343065, 69.116177</t>
+          <t>41.418715, 69.193523</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Илгар</t>
+          <t>Куктерак</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J95" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2595</v>
+        <v>2247</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N95" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q95" t="n">
         <v>5</v>
       </c>
       <c r="R95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S95" t="n">
-        <v>1141</v>
+        <v>1267</v>
       </c>
       <c r="T95" t="n">
-        <v>184.9</v>
+        <v>270.6</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
@@ -9282,7 +9280,7 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.343065,69.116177</t>
+          <t>https://www.google.com/maps?q=41.418715,69.193523</t>
         </is>
       </c>
     </row>
@@ -9293,20 +9291,20 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="C96" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>41.418715</v>
+        <v>41.425276</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>69.193523</v>
+        <v>69.209565</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>41.418715, 69.193523</t>
+          <t>41.425276, 69.209565</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -9320,7 +9318,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J96" t="n">
         <v>3.8</v>
@@ -9331,13 +9329,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2247</v>
+        <v>2734</v>
       </c>
       <c r="M96" t="n">
         <v>2</v>
       </c>
       <c r="N96" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O96" t="n">
         <v>1</v>
@@ -9349,10 +9347,10 @@
         <v>5</v>
       </c>
       <c r="R96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S96" t="n">
-        <v>1267</v>
+        <v>187</v>
       </c>
       <c r="T96" t="n">
         <v>270.6</v>
@@ -9373,7 +9371,7 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.418715,69.193523</t>
+          <t>https://www.google.com/maps?q=41.425276,69.209565</t>
         </is>
       </c>
     </row>
@@ -9384,25 +9382,25 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="C97" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>41.425276</v>
+        <v>41.358385</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>69.209565</v>
+        <v>69.120549</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>41.425276, 69.209565</t>
+          <t>41.358385, 69.120549</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Куктерак</t>
+          <t>Шамсиабад</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9411,10 +9409,10 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -9422,28 +9420,28 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2734</v>
+        <v>3620</v>
       </c>
       <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
+        <v>4</v>
+      </c>
+      <c r="O97" t="n">
         <v>2</v>
       </c>
-      <c r="N97" t="n">
-        <v>3</v>
-      </c>
-      <c r="O97" t="n">
-        <v>1</v>
-      </c>
       <c r="P97" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
         <v>5</v>
       </c>
       <c r="R97" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S97" t="n">
-        <v>187</v>
+        <v>1701</v>
       </c>
       <c r="T97" t="n">
         <v>270.6</v>
@@ -9464,7 +9462,7 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.425276,69.209565</t>
+          <t>https://www.google.com/maps?q=41.358385,69.120549</t>
         </is>
       </c>
     </row>
@@ -9481,19 +9479,19 @@
         <v>82</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>41.358385</v>
+        <v>41.412151</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>69.120549</v>
+        <v>69.177485</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>41.358385, 69.120549</t>
+          <t>41.412151, 69.177485</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Шамсиабад</t>
+          <t>Сагбан</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -9502,10 +9500,10 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J98" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -9513,28 +9511,28 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3620</v>
+        <v>2486</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N98" t="n">
         <v>4</v>
       </c>
       <c r="O98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q98" t="n">
         <v>5</v>
       </c>
       <c r="R98" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S98" t="n">
-        <v>1701</v>
+        <v>1519</v>
       </c>
       <c r="T98" t="n">
         <v>270.6</v>
@@ -9555,7 +9553,7 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.358385,69.120549</t>
+          <t>https://www.google.com/maps?q=41.412151,69.177485</t>
         </is>
       </c>
     </row>
@@ -9566,25 +9564,25 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C99" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>41.412151</v>
+        <v>41.404809</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>69.177485</v>
+        <v>69.391277</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>41.412151, 69.177485</t>
+          <t>41.404809, 69.391277</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Сагбан</t>
+          <t>Уткир</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -9600,35 +9598,35 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2486</v>
+        <v>1919</v>
       </c>
       <c r="M99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>5</v>
       </c>
       <c r="R99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S99" t="n">
-        <v>1519</v>
+        <v>1398</v>
       </c>
       <c r="T99" t="n">
-        <v>270.6</v>
+        <v>213.9</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
@@ -9641,12 +9639,12 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.412151,69.177485</t>
+          <t>https://www.google.com/maps?q=41.404809,69.391277</t>
         </is>
       </c>
     </row>
@@ -9657,25 +9655,25 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="C100" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>41.404809</v>
+        <v>41.173507</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>69.391277</v>
+        <v>69.131349</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>41.404809, 69.391277</t>
+          <t>41.173507, 69.131349</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Уткир</t>
+          <t>Ханкурган</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -9684,18 +9682,18 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J100" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1919</v>
+        <v>2231</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
@@ -9716,10 +9714,10 @@
         <v>2</v>
       </c>
       <c r="S100" t="n">
-        <v>1398</v>
+        <v>2842</v>
       </c>
       <c r="T100" t="n">
-        <v>213.9</v>
+        <v>184.9</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
@@ -9737,7 +9735,7 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.404809,69.391277</t>
+          <t>https://www.google.com/maps?q=41.173507,69.131349</t>
         </is>
       </c>
     </row>
@@ -9748,45 +9746,45 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C101" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>41.173507</v>
+        <v>41.445091</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>69.131349</v>
+        <v>69.249785</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>41.173507, 69.131349</t>
+          <t>41.445091, 69.249785</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ханкурган</t>
+          <t>Чувалачи</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J101" t="n">
         <v>5.3</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2231</v>
+        <v>2773</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
@@ -9804,13 +9802,13 @@
         <v>5</v>
       </c>
       <c r="R101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
-        <v>2842</v>
+        <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>184.9</v>
+        <v>270.6</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
@@ -9828,7 +9826,7 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.173507,69.131349</t>
+          <t>https://www.google.com/maps?q=41.445091,69.249785</t>
         </is>
       </c>
     </row>
@@ -9839,34 +9837,34 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="C102" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>41.445091</v>
+        <v>41.445517</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>69.249785</v>
+        <v>69.226005</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>41.445091, 69.249785</t>
+          <t>41.445517, 69.226005</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Чувалачи</t>
+          <t>Алишер Навои</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J102" t="n">
         <v>5.3</v>
@@ -9877,7 +9875,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2773</v>
+        <v>2065</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
@@ -9895,10 +9893,10 @@
         <v>5</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S102" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="T102" t="n">
         <v>270.6</v>
@@ -9919,7 +9917,7 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.445091,69.249785</t>
+          <t>https://www.google.com/maps?q=41.445517,69.226005</t>
         </is>
       </c>
     </row>
@@ -9930,25 +9928,25 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C103" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>41.445517</v>
+        <v>41.273963</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>69.226005</v>
+        <v>69.055013</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>41.445517, 69.226005</t>
+          <t>41.273963, 69.055013</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Алишер Навои</t>
+          <t>Тукимачи</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -9957,18 +9955,18 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J103" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2065</v>
+        <v>2760</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
@@ -9986,13 +9984,13 @@
         <v>5</v>
       </c>
       <c r="R103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="T103" t="n">
-        <v>270.6</v>
+        <v>184.9</v>
       </c>
       <c r="U103" t="n">
         <v>0</v>
@@ -10010,7 +10008,7 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.445517,69.226005</t>
+          <t>https://www.google.com/maps?q=41.273963,69.055013</t>
         </is>
       </c>
     </row>
@@ -10021,69 +10019,69 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="C104" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>41.273963</v>
+        <v>41.434386</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>69.055013</v>
+        <v>69.538939</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>41.273963, 69.055013</t>
+          <t>41.434386, 69.538939</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Тукимачи</t>
+          <t>Вахид Хайдаров махалля</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J104" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Город Чиpчик</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2760</v>
+        <v>7155</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q104" t="n">
         <v>5</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S104" t="n">
-        <v>0</v>
+        <v>1599</v>
       </c>
       <c r="T104" t="n">
-        <v>184.9</v>
+        <v>40.8</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
@@ -10096,12 +10094,12 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.273963,69.055013</t>
+          <t>https://www.google.com/maps?q=41.434386,69.538939</t>
         </is>
       </c>
     </row>
@@ -10112,69 +10110,69 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="C105" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>41.287638</v>
+        <v>41.44823</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>69.055368</v>
+        <v>69.53147800000001</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>41.287638, 69.055368</t>
+          <t>41.448230, 69.531478</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Янарык</t>
+          <t>Нурабад махалля</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J105" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2340</v>
+        <v>4150</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q105" t="n">
         <v>5</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S105" t="n">
-        <v>0</v>
+        <v>1599</v>
       </c>
       <c r="T105" t="n">
-        <v>184.9</v>
+        <v>213.9</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
@@ -10187,12 +10185,12 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.287638,69.055368</t>
+          <t>https://www.google.com/maps?q=41.448230,69.531478</t>
         </is>
       </c>
     </row>
@@ -10203,57 +10201,57 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C106" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>41.434386</v>
+        <v>41.151495</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>69.538939</v>
+        <v>69.118915</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>41.434386, 69.538939</t>
+          <t>41.151495, 69.118915</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Вахид Хайдаров махалля</t>
+          <t>Машраб</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J106" t="n">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Город Чиpчик</t>
+          <t>Янгиюльский район</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>7155</v>
+        <v>2329</v>
       </c>
       <c r="M106" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
         <v>5</v>
@@ -10262,10 +10260,10 @@
         <v>2</v>
       </c>
       <c r="S106" t="n">
-        <v>1599</v>
+        <v>829</v>
       </c>
       <c r="T106" t="n">
-        <v>40.8</v>
+        <v>129.6</v>
       </c>
       <c r="U106" t="n">
         <v>0</v>
@@ -10278,12 +10276,12 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.434386,69.538939</t>
+          <t>https://www.google.com/maps?q=41.151495,69.118915</t>
         </is>
       </c>
     </row>
@@ -10294,69 +10292,69 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C107" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>41.44823</v>
+        <v>41.461777</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>69.53147800000001</v>
+        <v>69.36531100000001</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>41.448230, 69.531478</t>
+          <t>41.461777, 69.365311</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Нурабад махалля</t>
+          <t>Гышткуприк</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J107" t="n">
-        <v>6.5</v>
+        <v>8.1</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>4150</v>
+        <v>2850</v>
       </c>
       <c r="M107" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
         <v>5</v>
       </c>
       <c r="R107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>1599</v>
+        <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>213.9</v>
+        <v>270.6</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
@@ -10369,12 +10367,12 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.448230,69.531478</t>
+          <t>https://www.google.com/maps?q=41.461777,69.365311</t>
         </is>
       </c>
     </row>
@@ -10385,57 +10383,57 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C108" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>41.151495</v>
+        <v>41.445785</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>69.118915</v>
+        <v>69.567094</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>41.151495, 69.118915</t>
+          <t>41.445785, 69.567094</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Машраб</t>
+          <t>Умид махалля</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J108" t="n">
-        <v>7.5</v>
+        <v>8.9</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Янгиюльский район</t>
+          <t>Город Чиpчик</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2329</v>
+        <v>2606</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q108" t="n">
         <v>5</v>
@@ -10444,15 +10442,17 @@
         <v>2</v>
       </c>
       <c r="S108" t="n">
-        <v>829</v>
+        <v>1599</v>
       </c>
       <c r="T108" t="n">
-        <v>129.6</v>
+        <v>40.8</v>
       </c>
       <c r="U108" t="n">
-        <v>0</v>
-      </c>
-      <c r="V108" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="V108" t="n">
+        <v>4068</v>
+      </c>
       <c r="W108" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -10460,12 +10460,12 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.151495,69.118915</t>
+          <t>https://www.google.com/maps?q=41.445785,69.567094</t>
         </is>
       </c>
     </row>
@@ -10476,25 +10476,25 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C109" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>41.461777</v>
+        <v>41.115948</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>69.36531100000001</v>
+        <v>69.098242</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>41.461777, 69.365311</t>
+          <t>41.115948, 69.098242</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Гышткуприк</t>
+          <t>Тахтакуприк</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -10503,18 +10503,18 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J109" t="n">
-        <v>8.1</v>
+        <v>11.5</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Янгиюльский район</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2850</v>
+        <v>1767</v>
       </c>
       <c r="M109" t="n">
         <v>0</v>
@@ -10532,13 +10532,13 @@
         <v>5</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S109" t="n">
-        <v>0</v>
+        <v>909</v>
       </c>
       <c r="T109" t="n">
-        <v>270.6</v>
+        <v>129.6</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.461777,69.365311</t>
+          <t>https://www.google.com/maps?q=41.115948,69.098242</t>
         </is>
       </c>
     </row>
@@ -10567,25 +10567,25 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C110" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>41.445785</v>
+        <v>41.478034</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>69.567094</v>
+        <v>69.580118</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>41.445785, 69.567094</t>
+          <t>41.478034, 69.580118</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Умид махалля</t>
+          <t>Бахор махалля</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -10594,10 +10594,10 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J110" t="n">
-        <v>8.9</v>
+        <v>11.7</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -10605,28 +10605,28 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2606</v>
+        <v>18190</v>
       </c>
       <c r="M110" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N110" t="n">
+        <v>8</v>
+      </c>
+      <c r="O110" t="n">
         <v>4</v>
       </c>
-      <c r="O110" t="n">
-        <v>2</v>
-      </c>
       <c r="P110" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Q110" t="n">
         <v>5</v>
       </c>
       <c r="R110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S110" t="n">
-        <v>1599</v>
+        <v>1995</v>
       </c>
       <c r="T110" t="n">
         <v>40.8</v>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.445785,69.567094</t>
+          <t>https://www.google.com/maps?q=41.478034,69.580118</t>
         </is>
       </c>
     </row>
@@ -10660,25 +10660,25 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="C111" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>41.115948</v>
+        <v>41.463685</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>69.098242</v>
+        <v>69.611362</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>41.115948, 69.098242</t>
+          <t>41.463685, 69.611362</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Тахтакуприк</t>
+          <t>Карабай</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -10687,30 +10687,30 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
-        <v>11.5</v>
+        <v>13.1</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Янгиюльский район</t>
+          <t>Бостанлыкский район</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1767</v>
+        <v>2282</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q111" t="n">
         <v>5</v>
@@ -10719,10 +10719,10 @@
         <v>3</v>
       </c>
       <c r="S111" t="n">
-        <v>909</v>
+        <v>1995</v>
       </c>
       <c r="T111" t="n">
-        <v>129.6</v>
+        <v>147.5</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
@@ -10735,12 +10735,12 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.115948,69.098242</t>
+          <t>https://www.google.com/maps?q=41.463685,69.611362</t>
         </is>
       </c>
     </row>
@@ -10751,57 +10751,57 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="C112" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>41.478034</v>
+        <v>41.157616</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>69.580118</v>
+        <v>69.059894</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>41.478034, 69.580118</t>
+          <t>41.157616, 69.059894</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Бахор махалля</t>
+          <t>Конкус</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J112" t="n">
-        <v>11.7</v>
+        <v>13.1</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Город Чиpчик</t>
+          <t>Янгиюльский район</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>18190</v>
+        <v>1815</v>
       </c>
       <c r="M112" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
         <v>5</v>
@@ -10810,17 +10810,15 @@
         <v>3</v>
       </c>
       <c r="S112" t="n">
-        <v>1995</v>
+        <v>909</v>
       </c>
       <c r="T112" t="n">
-        <v>40.8</v>
+        <v>129.6</v>
       </c>
       <c r="U112" t="n">
-        <v>3</v>
-      </c>
-      <c r="V112" t="n">
-        <v>2000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V112" t="inlineStr"/>
       <c r="W112" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -10828,12 +10826,12 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.478034,69.580118</t>
+          <t>https://www.google.com/maps?q=41.157616,69.059894</t>
         </is>
       </c>
     </row>
@@ -10844,25 +10842,25 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C113" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>41.463685</v>
+        <v>41.104188</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>69.611362</v>
+        <v>69.08610299999999</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>41.463685, 69.611362</t>
+          <t>41.104188, 69.086103</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Карабай</t>
+          <t>Ниязбаш</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -10871,30 +10869,30 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J113" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Бостанлыкский район</t>
+          <t>Янгиюльский район</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2282</v>
+        <v>2547</v>
       </c>
       <c r="M113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N113" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O113" t="n">
         <v>2</v>
       </c>
       <c r="P113" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q113" t="n">
         <v>5</v>
@@ -10903,10 +10901,10 @@
         <v>3</v>
       </c>
       <c r="S113" t="n">
-        <v>1995</v>
+        <v>909</v>
       </c>
       <c r="T113" t="n">
-        <v>147.5</v>
+        <v>129.6</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
@@ -10924,7 +10922,7 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.463685,69.611362</t>
+          <t>https://www.google.com/maps?q=41.104188,69.086103</t>
         </is>
       </c>
     </row>
@@ -10935,69 +10933,69 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C114" t="n">
         <v>78</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>41.157616</v>
+        <v>41.039806</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>69.059894</v>
+        <v>69.340406</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>41.157616, 69.059894</t>
+          <t>41.039806, 69.340406</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Конкус</t>
+          <t>Нурафшан (Тойтепа)</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J114" t="n">
-        <v>13.1</v>
+        <v>13.6</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Янгиюльский район</t>
+          <t>Уртачирчикский район</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1815</v>
+        <v>1871</v>
       </c>
       <c r="M114" t="n">
         <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q114" t="n">
         <v>5</v>
       </c>
       <c r="R114" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S114" t="n">
-        <v>909</v>
+        <v>1946</v>
       </c>
       <c r="T114" t="n">
-        <v>129.6</v>
+        <v>134.2</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
@@ -11010,12 +11008,12 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.157616,69.059894</t>
+          <t>https://www.google.com/maps?q=41.039806,69.340406</t>
         </is>
       </c>
     </row>
@@ -11026,20 +11024,20 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C115" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>41.104188</v>
+        <v>41.088745</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>69.08610299999999</v>
+        <v>69.089637</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>41.104188, 69.086103</t>
+          <t>41.088745, 69.089637</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -11053,10 +11051,10 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J115" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -11064,19 +11062,19 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2547</v>
+        <v>2111</v>
       </c>
       <c r="M115" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
         <v>5</v>
@@ -11101,12 +11099,12 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.104188,69.086103</t>
+          <t>https://www.google.com/maps?q=41.088745,69.089637</t>
         </is>
       </c>
     </row>
@@ -11117,69 +11115,69 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="C116" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>41.039806</v>
+        <v>41.10839</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>69.340406</v>
+        <v>69.038905</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>41.039806, 69.340406</t>
+          <t>41.108390, 69.038905</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Нурафшан (Тойтепа)</t>
+          <t>Тонг массив</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="J116" t="n">
-        <v>13.6</v>
+        <v>15.7</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Уртачирчикский район</t>
+          <t>Янгиюльский район</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1871</v>
+        <v>4351</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N116" t="n">
+        <v>6</v>
+      </c>
+      <c r="O116" t="n">
         <v>2</v>
       </c>
-      <c r="O116" t="n">
-        <v>1</v>
-      </c>
       <c r="P116" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q116" t="n">
         <v>5</v>
       </c>
       <c r="R116" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S116" t="n">
-        <v>1946</v>
+        <v>909</v>
       </c>
       <c r="T116" t="n">
-        <v>134.2</v>
+        <v>129.6</v>
       </c>
       <c r="U116" t="n">
         <v>0</v>
@@ -11197,7 +11195,7 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.039806,69.340406</t>
+          <t>https://www.google.com/maps?q=41.108390,69.038905</t>
         </is>
       </c>
     </row>
@@ -11208,69 +11206,69 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C117" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>41.088745</v>
+        <v>41.02079</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>69.089637</v>
+        <v>69.351637</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>41.088745, 69.089637</t>
+          <t>41.020790, 69.351637</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ниязбаш</t>
+          <t>Чигирик</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J117" t="n">
-        <v>13.9</v>
+        <v>15.7</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Янгиюльский район</t>
+          <t>Уртачирчикский район</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2111</v>
+        <v>3239</v>
       </c>
       <c r="M117" t="n">
         <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q117" t="n">
         <v>5</v>
       </c>
       <c r="R117" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S117" t="n">
-        <v>909</v>
+        <v>1946</v>
       </c>
       <c r="T117" t="n">
-        <v>129.6</v>
+        <v>134.2</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -11283,12 +11281,12 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.088745,69.089637</t>
+          <t>https://www.google.com/maps?q=41.020790,69.351637</t>
         </is>
       </c>
     </row>
@@ -11299,69 +11297,69 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C118" t="n">
         <v>86</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>41.10839</v>
+        <v>41.514494</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>69.038905</v>
+        <v>69.636989</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>41.108390, 69.038905</t>
+          <t>41.514494, 69.636989</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Тонг массив</t>
+          <t>Аранчи</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J118" t="n">
-        <v>15.7</v>
+        <v>17.9</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Янгиюльский район</t>
+          <t>Город Чиpчик</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>4351</v>
+        <v>4566</v>
       </c>
       <c r="M118" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
         <v>5</v>
       </c>
       <c r="R118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S118" t="n">
-        <v>909</v>
+        <v>444</v>
       </c>
       <c r="T118" t="n">
-        <v>129.6</v>
+        <v>40.8</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
@@ -11374,12 +11372,12 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.108390,69.038905</t>
+          <t>https://www.google.com/maps?q=41.514494,69.636989</t>
         </is>
       </c>
     </row>
@@ -11390,69 +11388,69 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C119" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>41.02079</v>
+        <v>41.531601</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>69.351637</v>
+        <v>69.637602</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>41.020790, 69.351637</t>
+          <t>41.531601, 69.637602</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Чигирик</t>
+          <t>Азадбаш</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J119" t="n">
-        <v>15.7</v>
+        <v>19.2</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Уртачирчикский район</t>
+          <t>Бостанлыкский район</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>3239</v>
+        <v>2381</v>
       </c>
       <c r="M119" t="n">
         <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
         <v>5</v>
       </c>
       <c r="R119" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S119" t="n">
-        <v>1946</v>
+        <v>444</v>
       </c>
       <c r="T119" t="n">
-        <v>134.2</v>
+        <v>147.5</v>
       </c>
       <c r="U119" t="n">
         <v>0</v>
@@ -11465,12 +11463,12 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.020790,69.351637</t>
+          <t>https://www.google.com/maps?q=41.531601,69.637602</t>
         </is>
       </c>
     </row>
@@ -11481,54 +11479,54 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C120" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>41.514663</v>
+        <v>41.520827</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>69.629052</v>
+        <v>69.66104799999999</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>41.514663, 69.629052</t>
+          <t>41.520827, 69.661048</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Бахт махалля</t>
+          <t>Аранчи</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J120" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Город Чиpчик</t>
+          <t>Бостанлыкский район</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>8262</v>
+        <v>1866</v>
       </c>
       <c r="M120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P120" t="n">
         <v>0</v>
@@ -11543,7 +11541,7 @@
         <v>444</v>
       </c>
       <c r="T120" t="n">
-        <v>40.8</v>
+        <v>147.5</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
@@ -11556,12 +11554,12 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.514663,69.629052</t>
+          <t>https://www.google.com/maps?q=41.520827,69.661048</t>
         </is>
       </c>
     </row>
@@ -11572,10 +11570,10 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C121" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D121" s="2" t="n">
         <v>41.570059</v>
@@ -12121,7 +12119,7 @@
         <v>12</v>
       </c>
       <c r="C127" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D127" s="2" t="n">
         <v>40.913997</v>
@@ -12940,7 +12938,7 @@
         <v>28</v>
       </c>
       <c r="C136" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D136" s="2" t="n">
         <v>40.877498</v>
@@ -13119,7 +13117,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C138" t="n">
         <v>55</v>
@@ -13853,7 +13851,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C146" t="n">
         <v>55</v>
@@ -13944,7 +13942,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C147" t="n">
         <v>61</v>
@@ -14308,10 +14306,10 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C151" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D151" s="2" t="n">
         <v>40.85233</v>
@@ -15496,7 +15494,7 @@
         <v>52</v>
       </c>
       <c r="C164" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D164" s="2" t="n">
         <v>41.00906</v>
@@ -17225,7 +17223,7 @@
         <v>1</v>
       </c>
       <c r="C183" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D183" s="2" t="n">
         <v>40.252947</v>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,7 +660,7 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V2" t="n">
         <v>70</v>
@@ -880,19 +880,19 @@
         <v>92</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>41.302521</v>
+        <v>41.332561</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>69.281226</v>
+        <v>69.321702</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>41.302521, 69.281226</t>
+          <t>41.332561, 69.321702</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Айбек</t>
+          <t>Буюк Ипак Йули махалля</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -901,48 +901,48 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Мирабадский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>6299</v>
+        <v>4166</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="O5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P5" t="n">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="Q5" t="n">
         <v>0.5</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>610</v>
+        <v>1970</v>
       </c>
       <c r="T5" t="n">
-        <v>48.5</v>
+        <v>98.2</v>
       </c>
       <c r="U5" t="n">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="V5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.302521,69.281226</t>
+          <t>https://www.google.com/maps?q=41.332561,69.321702</t>
         </is>
       </c>
     </row>
@@ -973,19 +973,19 @@
         <v>92</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>41.332561</v>
+        <v>41.302521</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>69.321702</v>
+        <v>69.281226</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41.332561, 69.321702</t>
+          <t>41.302521, 69.281226</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Буюк Ипак Йули махалля</t>
+          <t>Айбек</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -994,48 +994,48 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Мирабадский район</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4166</v>
+        <v>6299</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="O6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P6" t="n">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="Q6" t="n">
         <v>0.5</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>1970</v>
+        <v>610</v>
       </c>
       <c r="T6" t="n">
-        <v>98.2</v>
+        <v>48.5</v>
       </c>
       <c r="U6" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="V6" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.332561,69.321702</t>
+          <t>https://www.google.com/maps?q=41.302521,69.281226</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
         <v>139.7</v>
       </c>
       <c r="U7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V7" t="n">
         <v>500</v>
@@ -1249,7 +1249,7 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>41.309964</v>
@@ -1311,7 +1311,7 @@
         <v>98.2</v>
       </c>
       <c r="U9" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="V9" t="n">
         <v>500</v>
@@ -1497,10 +1497,10 @@
         <v>59.2</v>
       </c>
       <c r="U11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V11" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1531,19 +1531,19 @@
         <v>90</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>41.308774</v>
+        <v>41.293314</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>69.31306499999999</v>
+        <v>69.316553</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>41.308774, 69.313065</t>
+          <t>41.293314, 69.316553</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Машинасозлар (Ташсельмаш)</t>
+          <t>Ширинабад махалля</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1563,34 +1563,34 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6677</v>
+        <v>6723</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N12" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="O12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P12" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="Q12" t="n">
         <v>0.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>446</v>
+        <v>664</v>
       </c>
       <c r="T12" t="n">
         <v>141</v>
       </c>
       <c r="U12" t="n">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="V12" t="n">
         <v>500</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.308774,69.313065</t>
+          <t>https://www.google.com/maps?q=41.293314,69.316553</t>
         </is>
       </c>
     </row>
@@ -1624,19 +1624,19 @@
         <v>90</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>41.293314</v>
+        <v>41.308774</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>69.316553</v>
+        <v>69.31306499999999</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>41.293314, 69.316553</t>
+          <t>41.308774, 69.313065</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ширинабад махалля</t>
+          <t>Машинасозлар (Ташсельмаш)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1656,34 +1656,34 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6723</v>
+        <v>6677</v>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="O13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P13" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="Q13" t="n">
         <v>0.5</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>664</v>
+        <v>446</v>
       </c>
       <c r="T13" t="n">
         <v>141</v>
       </c>
       <c r="U13" t="n">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="V13" t="n">
         <v>500</v>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.293314,69.316553</t>
+          <t>https://www.google.com/maps?q=41.308774,69.313065</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
         <v>31.8</v>
       </c>
       <c r="U14" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V14" t="n">
         <v>500</v>
@@ -1962,7 +1962,7 @@
         <v>59.2</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V16" t="n">
         <v>200</v>
@@ -2055,7 +2055,7 @@
         <v>122.7</v>
       </c>
       <c r="U17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V17" t="n">
         <v>350</v>
@@ -2148,10 +2148,10 @@
         <v>139.7</v>
       </c>
       <c r="U18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V18" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>139.7</v>
       </c>
       <c r="U19" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="V19" t="n">
         <v>600</v>
@@ -2334,7 +2334,7 @@
         <v>139.7</v>
       </c>
       <c r="U20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V20" t="n">
         <v>350</v>
@@ -2365,7 +2365,7 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>41.370618</v>
@@ -2520,7 +2520,7 @@
         <v>59.2</v>
       </c>
       <c r="U22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V22" t="n">
         <v>200</v>
@@ -2830,7 +2830,7 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>41.211644</v>
@@ -2892,7 +2892,7 @@
         <v>122.7</v>
       </c>
       <c r="U26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V26" t="n">
         <v>450</v>
@@ -3110,19 +3110,19 @@
         <v>81</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>41.346824</v>
+        <v>41.278439</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>69.38152599999999</v>
+        <v>69.379378</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>41.346824, 69.381526</t>
+          <t>41.278439, 69.379378</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ахмада Югнаки (Солнечный)</t>
+          <t>Нурмухаммедов</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3131,30 +3131,30 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>10881</v>
+        <v>5429</v>
       </c>
       <c r="M29" t="n">
+        <v>7</v>
+      </c>
+      <c r="N29" t="n">
+        <v>9</v>
+      </c>
+      <c r="O29" t="n">
         <v>5</v>
       </c>
-      <c r="N29" t="n">
-        <v>24</v>
-      </c>
-      <c r="O29" t="n">
-        <v>12</v>
-      </c>
       <c r="P29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q29" t="n">
         <v>0.5</v>
@@ -3166,13 +3166,13 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>98.2</v>
+        <v>141</v>
       </c>
       <c r="U29" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="V29" t="n">
-        <v>10</v>
+        <v>1716</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.346824,69.381526</t>
+          <t>https://www.google.com/maps?q=41.278439,69.379378</t>
         </is>
       </c>
     </row>
@@ -3203,19 +3203,19 @@
         <v>81</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>41.278439</v>
+        <v>41.346824</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>69.379378</v>
+        <v>69.38152599999999</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>41.278439, 69.379378</t>
+          <t>41.346824, 69.381526</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Нурмухаммедов</t>
+          <t>Ахмада Югнаки (Солнечный)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3224,30 +3224,30 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5429</v>
+        <v>10881</v>
       </c>
       <c r="M30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N30" t="n">
+        <v>24</v>
+      </c>
+      <c r="O30" t="n">
+        <v>12</v>
+      </c>
+      <c r="P30" t="n">
         <v>9</v>
-      </c>
-      <c r="O30" t="n">
-        <v>5</v>
-      </c>
-      <c r="P30" t="n">
-        <v>11</v>
       </c>
       <c r="Q30" t="n">
         <v>0.5</v>
@@ -3259,13 +3259,13 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>141</v>
+        <v>98.2</v>
       </c>
       <c r="U30" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="V30" t="n">
-        <v>1716</v>
+        <v>10</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.278439,69.379378</t>
+          <t>https://www.google.com/maps?q=41.346824,69.381526</t>
         </is>
       </c>
     </row>
@@ -3355,7 +3355,7 @@
         <v>139.7</v>
       </c>
       <c r="U31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V31" t="n">
         <v>1200</v>
@@ -3727,7 +3727,7 @@
         <v>59.2</v>
       </c>
       <c r="U35" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V35" t="n">
         <v>200</v>
@@ -3758,54 +3758,54 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>41.286991</v>
+        <v>41.401782</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>69.19375700000001</v>
+        <v>69.458556</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>41.286991, 69.193757</t>
+          <t>41.401782, 69.458556</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Чиланзар Г 9А</t>
+          <t>Улугбек</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>16603</v>
+        <v>3473</v>
       </c>
       <c r="M36" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="O36" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="Q36" t="n">
         <v>0.5</v>
@@ -3817,14 +3817,12 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>47.6</v>
+        <v>213.9</v>
       </c>
       <c r="U36" t="n">
-        <v>23</v>
-      </c>
-      <c r="V36" t="n">
-        <v>70</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3837,7 +3835,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.286991,69.193757</t>
+          <t>https://www.google.com/maps?q=41.401782,69.458556</t>
         </is>
       </c>
     </row>
@@ -3854,51 +3852,51 @@
         <v>77</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>41.401782</v>
+        <v>41.286991</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>69.458556</v>
+        <v>69.19375700000001</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>41.401782, 69.458556</t>
+          <t>41.286991, 69.193757</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Улугбек</t>
+          <t>Чиланзар Г 9А</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3473</v>
+        <v>16603</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N37" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="O37" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="P37" t="n">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="Q37" t="n">
         <v>0.5</v>
@@ -3910,12 +3908,14 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>213.9</v>
+        <v>47.6</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="V37" t="n">
+        <v>70</v>
+      </c>
       <c r="W37" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.401782,69.458556</t>
+          <t>https://www.google.com/maps?q=41.286991,69.193757</t>
         </is>
       </c>
     </row>
@@ -4283,7 +4283,7 @@
         <v>48.5</v>
       </c>
       <c r="U41" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="V41" t="n">
         <v>500</v>
@@ -4376,7 +4376,7 @@
         <v>28.3</v>
       </c>
       <c r="U42" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="V42" t="n">
         <v>999</v>
@@ -4560,7 +4560,7 @@
         <v>31.8</v>
       </c>
       <c r="U44" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="V44" t="n">
         <v>500</v>
@@ -4591,7 +4591,7 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>41.221225</v>
@@ -4930,7 +4930,7 @@
         <v>59.2</v>
       </c>
       <c r="U48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V48" t="n">
         <v>200</v>
@@ -5023,7 +5023,7 @@
         <v>31.8</v>
       </c>
       <c r="U49" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="V49" t="n">
         <v>600</v>
@@ -5331,7 +5331,7 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D53" s="2" t="n">
         <v>41.382173</v>
@@ -6501,7 +6501,7 @@
         <v>213.9</v>
       </c>
       <c r="U65" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V65" t="n">
         <v>250</v>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C67" t="n">
         <v>85</v>
@@ -6873,7 +6873,7 @@
         <v>270.6</v>
       </c>
       <c r="U69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V69" t="n">
         <v>1300</v>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C72" t="n">
         <v>81</v>
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C73" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D73" s="2" t="n">
         <v>41.402834</v>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C74" t="n">
         <v>79</v>
@@ -7362,7 +7362,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C75" t="n">
         <v>79</v>
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C76" t="n">
         <v>84</v>
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C77" t="n">
         <v>78</v>
@@ -7637,74 +7637,76 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="C78" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>41.207141</v>
+        <v>41.352783</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>69.163858</v>
+        <v>69.14811</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>41.207141, 69.163858</t>
+          <t>41.352783, 69.148110</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Зангиата</t>
+          <t>Куксарай</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I78" t="n">
         <v>0.6</v>
       </c>
       <c r="J78" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1847</v>
+        <v>1467</v>
       </c>
       <c r="M78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N78" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O78" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
         <v>5</v>
       </c>
       <c r="R78" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="S78" t="n">
-        <v>24505</v>
+        <v>3190</v>
       </c>
       <c r="T78" t="n">
-        <v>184.9</v>
+        <v>270.6</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
-      </c>
-      <c r="V78" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V78" t="n">
+        <v>250</v>
+      </c>
       <c r="W78" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7717,7 +7719,7 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.207141,69.163858</t>
+          <t>https://www.google.com/maps?q=41.352783,69.148110</t>
         </is>
       </c>
     </row>
@@ -7728,57 +7730,57 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C79" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>41.399761</v>
+        <v>41.207141</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>69.29601</v>
+        <v>69.163858</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>41.399761, 69.296010</t>
+          <t>41.207141, 69.163858</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Хавасар</t>
+          <t>Зангиата</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2533</v>
+        <v>1847</v>
       </c>
       <c r="M79" t="n">
         <v>1</v>
       </c>
       <c r="N79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O79" t="n">
+        <v>4</v>
+      </c>
+      <c r="P79" t="n">
         <v>2</v>
-      </c>
-      <c r="P79" t="n">
-        <v>5</v>
       </c>
       <c r="Q79" t="n">
         <v>5</v>
@@ -7787,17 +7789,15 @@
         <v>14</v>
       </c>
       <c r="S79" t="n">
-        <v>16114</v>
+        <v>24505</v>
       </c>
       <c r="T79" t="n">
-        <v>213.9</v>
+        <v>184.9</v>
       </c>
       <c r="U79" t="n">
-        <v>4</v>
-      </c>
-      <c r="V79" t="n">
-        <v>1000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V79" t="inlineStr"/>
       <c r="W79" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.399761,69.296010</t>
+          <t>https://www.google.com/maps?q=41.207141,69.163858</t>
         </is>
       </c>
     </row>
@@ -7821,74 +7821,76 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="C80" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>41.33418</v>
+        <v>41.399761</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>69.13572499999999</v>
+        <v>69.29601</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>41.334180, 69.135725</t>
+          <t>41.399761, 69.296010</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ункурган</t>
+          <t>Хавасар</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1727</v>
+        <v>2533</v>
       </c>
       <c r="M80" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N80" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O80" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P80" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q80" t="n">
         <v>5</v>
       </c>
       <c r="R80" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="S80" t="n">
-        <v>6530</v>
+        <v>16114</v>
       </c>
       <c r="T80" t="n">
-        <v>184.9</v>
+        <v>213.9</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
-      </c>
-      <c r="V80" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="V80" t="n">
+        <v>1000</v>
+      </c>
       <c r="W80" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7901,7 +7903,7 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.334180,69.135725</t>
+          <t>https://www.google.com/maps?q=41.399761,69.296010</t>
         </is>
       </c>
     </row>
@@ -7912,25 +7914,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="C81" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>41.399172</v>
+        <v>41.33418</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>69.327693</v>
+        <v>69.13572499999999</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>41.399172, 69.327693</t>
+          <t>41.334180, 69.135725</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Гульзар</t>
+          <t>Ункурган</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7939,49 +7941,47 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J81" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2403</v>
+        <v>1727</v>
       </c>
       <c r="M81" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N81" t="n">
+        <v>7</v>
+      </c>
+      <c r="O81" t="n">
+        <v>4</v>
+      </c>
+      <c r="P81" t="n">
         <v>2</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>1</v>
       </c>
       <c r="Q81" t="n">
         <v>5</v>
       </c>
       <c r="R81" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S81" t="n">
-        <v>10876</v>
+        <v>6530</v>
       </c>
       <c r="T81" t="n">
-        <v>213.9</v>
+        <v>184.9</v>
       </c>
       <c r="U81" t="n">
-        <v>3</v>
-      </c>
-      <c r="V81" t="n">
-        <v>1000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.399172,69.327693</t>
+          <t>https://www.google.com/maps?q=41.334180,69.135725</t>
         </is>
       </c>
     </row>
@@ -8005,75 +8005,75 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="C82" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>41.378205</v>
+        <v>41.399172</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>69.350821</v>
+        <v>69.327693</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>41.378205, 69.350821</t>
+          <t>41.399172, 69.327693</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Салар</t>
+          <t>Гульзар</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Кибрайский район</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>2403</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1</v>
+      </c>
+      <c r="N82" t="n">
         <v>2</v>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Кибрайский район</t>
-        </is>
-      </c>
-      <c r="L82" t="n">
-        <v>4623</v>
-      </c>
-      <c r="M82" t="n">
-        <v>4</v>
-      </c>
-      <c r="N82" t="n">
-        <v>11</v>
-      </c>
       <c r="O82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q82" t="n">
         <v>5</v>
       </c>
       <c r="R82" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S82" t="n">
-        <v>14705</v>
+        <v>10876</v>
       </c>
       <c r="T82" t="n">
         <v>213.9</v>
       </c>
       <c r="U82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V82" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="W82" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.378205,69.350821</t>
+          <t>https://www.google.com/maps?q=41.399172,69.327693</t>
         </is>
       </c>
     </row>
@@ -8098,75 +8098,75 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C83" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>41.241734</v>
+        <v>41.378205</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>69.141108</v>
+        <v>69.350821</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>41.241734, 69.141108</t>
+          <t>41.378205, 69.350821</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Далигузар</t>
+          <t>Салар</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J83" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2089</v>
+        <v>4623</v>
       </c>
       <c r="M83" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N83" t="n">
         <v>11</v>
       </c>
       <c r="O83" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P83" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="Q83" t="n">
         <v>5</v>
       </c>
       <c r="R83" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S83" t="n">
-        <v>7256</v>
+        <v>14705</v>
       </c>
       <c r="T83" t="n">
-        <v>184.9</v>
+        <v>213.9</v>
       </c>
       <c r="U83" t="n">
         <v>2</v>
       </c>
       <c r="V83" t="n">
-        <v>1840</v>
+        <v>1100</v>
       </c>
       <c r="W83" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.241734,69.141108</t>
+          <t>https://www.google.com/maps?q=41.378205,69.350821</t>
         </is>
       </c>
     </row>
@@ -8191,75 +8191,75 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C84" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>41.403254</v>
+        <v>41.241734</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>69.197048</v>
+        <v>69.141108</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>41.403254, 69.197048</t>
+          <t>41.241734, 69.141108</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Келес</t>
+          <t>Далигузар</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="J84" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>9032</v>
+        <v>2089</v>
       </c>
       <c r="M84" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N84" t="n">
+        <v>11</v>
+      </c>
+      <c r="O84" t="n">
         <v>5</v>
       </c>
-      <c r="O84" t="n">
-        <v>1</v>
-      </c>
       <c r="P84" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="Q84" t="n">
         <v>5</v>
       </c>
       <c r="R84" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="S84" t="n">
-        <v>2140</v>
+        <v>7256</v>
       </c>
       <c r="T84" t="n">
-        <v>270.6</v>
+        <v>184.9</v>
       </c>
       <c r="U84" t="n">
         <v>2</v>
       </c>
       <c r="V84" t="n">
-        <v>840</v>
+        <v>1840</v>
       </c>
       <c r="W84" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.403254,69.197048</t>
+          <t>https://www.google.com/maps?q=41.241734,69.141108</t>
         </is>
       </c>
     </row>
@@ -8284,37 +8284,37 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C85" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>41.417442</v>
+        <v>41.403254</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>69.264831</v>
+        <v>69.197048</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>41.417442, 69.264831</t>
+          <t>41.403254, 69.197048</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Хасанбай</t>
+          <t>Келес</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J85" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -8322,37 +8322,37 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1653</v>
+        <v>9032</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q85" t="n">
         <v>5</v>
       </c>
       <c r="R85" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S85" t="n">
-        <v>9304</v>
+        <v>2140</v>
       </c>
       <c r="T85" t="n">
         <v>270.6</v>
       </c>
       <c r="U85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V85" t="n">
-        <v>600</v>
+        <v>840</v>
       </c>
       <c r="W85" t="inlineStr">
         <is>
@@ -8361,12 +8361,12 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.417442,69.264831</t>
+          <t>https://www.google.com/maps?q=41.403254,69.197048</t>
         </is>
       </c>
     </row>
@@ -8377,25 +8377,25 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C86" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>41.392035</v>
+        <v>41.417442</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>69.343324</v>
+        <v>69.264831</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>41.392035, 69.343324</t>
+          <t>41.417442, 69.264831</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ункурган</t>
+          <t>Хасанбай</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8404,48 +8404,48 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J86" t="n">
         <v>2.3</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2163</v>
+        <v>1653</v>
       </c>
       <c r="M86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>5</v>
       </c>
       <c r="R86" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="S86" t="n">
-        <v>11098</v>
+        <v>9304</v>
       </c>
       <c r="T86" t="n">
-        <v>213.9</v>
+        <v>270.6</v>
       </c>
       <c r="U86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V86" t="n">
-        <v>1100</v>
+        <v>600</v>
       </c>
       <c r="W86" t="inlineStr">
         <is>
@@ -8454,12 +8454,12 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.392035,69.343324</t>
+          <t>https://www.google.com/maps?q=41.417442,69.264831</t>
         </is>
       </c>
     </row>
@@ -8470,25 +8470,25 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C87" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>41.308872</v>
+        <v>41.392035</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>69.115255</v>
+        <v>69.343324</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>41.308872, 69.115255</t>
+          <t>41.392035, 69.343324</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Харакат</t>
+          <t>Ункурган</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -8497,47 +8497,49 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2845</v>
+        <v>2163</v>
       </c>
       <c r="M87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O87" t="n">
         <v>1</v>
       </c>
       <c r="P87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q87" t="n">
         <v>5</v>
       </c>
       <c r="R87" t="n">
+        <v>11</v>
+      </c>
+      <c r="S87" t="n">
+        <v>11098</v>
+      </c>
+      <c r="T87" t="n">
+        <v>213.9</v>
+      </c>
+      <c r="U87" t="n">
         <v>2</v>
       </c>
-      <c r="S87" t="n">
-        <v>3688</v>
-      </c>
-      <c r="T87" t="n">
-        <v>184.9</v>
-      </c>
-      <c r="U87" t="n">
-        <v>0</v>
-      </c>
-      <c r="V87" t="inlineStr"/>
+      <c r="V87" t="n">
+        <v>1100</v>
+      </c>
       <c r="W87" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8550,7 +8552,7 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.308872,69.115255</t>
+          <t>https://www.google.com/maps?q=41.392035,69.343324</t>
         </is>
       </c>
     </row>
@@ -8561,57 +8563,57 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C88" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>41.377685</v>
+        <v>41.308872</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>69.46569100000001</v>
+        <v>69.115255</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>41.377685, 69.465691</t>
+          <t>41.308872, 69.115255</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Кибрай</t>
+          <t>Харакат</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>2.7</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>3583</v>
+        <v>2845</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N88" t="n">
+        <v>1</v>
+      </c>
+      <c r="O88" t="n">
+        <v>1</v>
+      </c>
+      <c r="P88" t="n">
         <v>2</v>
-      </c>
-      <c r="O88" t="n">
-        <v>2</v>
-      </c>
-      <c r="P88" t="n">
-        <v>7</v>
       </c>
       <c r="Q88" t="n">
         <v>5</v>
@@ -8620,10 +8622,10 @@
         <v>2</v>
       </c>
       <c r="S88" t="n">
-        <v>439</v>
+        <v>3688</v>
       </c>
       <c r="T88" t="n">
-        <v>213.9</v>
+        <v>184.9</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
@@ -8641,7 +8643,7 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.377685,69.465691</t>
+          <t>https://www.google.com/maps?q=41.308872,69.115255</t>
         </is>
       </c>
     </row>
@@ -8652,34 +8654,34 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C89" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>41.44656</v>
+        <v>41.377685</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>69.444159</v>
+        <v>69.46569100000001</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>41.446560, 69.444159</t>
+          <t>41.377685, 69.465691</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ходжакурган</t>
+          <t>Кибрай</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>2.7</v>
@@ -8690,28 +8692,28 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2215</v>
+        <v>3583</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q89" t="n">
         <v>5</v>
       </c>
       <c r="R89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S89" t="n">
-        <v>129</v>
+        <v>439</v>
       </c>
       <c r="T89" t="n">
         <v>213.9</v>
@@ -8727,12 +8729,12 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.446560,69.444159</t>
+          <t>https://www.google.com/maps?q=41.377685,69.465691</t>
         </is>
       </c>
     </row>
@@ -8743,25 +8745,25 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C90" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>41.380099</v>
+        <v>41.44656</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>69.43011300000001</v>
+        <v>69.444159</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>41.380099, 69.430113</t>
+          <t>41.446560, 69.444159</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Аргин</t>
+          <t>Ходжакурган</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -8770,10 +8772,10 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -8781,38 +8783,36 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2439</v>
+        <v>2215</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
         <v>5</v>
       </c>
       <c r="R90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S90" t="n">
-        <v>1510</v>
+        <v>129</v>
       </c>
       <c r="T90" t="n">
         <v>213.9</v>
       </c>
       <c r="U90" t="n">
-        <v>1</v>
-      </c>
-      <c r="V90" t="n">
-        <v>900</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.380099,69.430113</t>
+          <t>https://www.google.com/maps?q=41.446560,69.444159</t>
         </is>
       </c>
     </row>
@@ -8836,74 +8836,76 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="C91" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>41.378499</v>
+        <v>41.380099</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>69.144857</v>
+        <v>69.43011300000001</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>41.378499, 69.144857</t>
+          <t>41.380099, 69.430113</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Илгар</t>
+          <t>Аргин</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J91" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2210</v>
+        <v>2439</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q91" t="n">
         <v>5</v>
       </c>
       <c r="R91" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S91" t="n">
-        <v>2397</v>
+        <v>1510</v>
       </c>
       <c r="T91" t="n">
-        <v>270.6</v>
+        <v>213.9</v>
       </c>
       <c r="U91" t="n">
-        <v>0</v>
-      </c>
-      <c r="V91" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V91" t="n">
+        <v>900</v>
+      </c>
       <c r="W91" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8916,7 +8918,7 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.378499,69.144857</t>
+          <t>https://www.google.com/maps?q=41.380099,69.430113</t>
         </is>
       </c>
     </row>
@@ -8927,54 +8929,54 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C92" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>41.445931</v>
+        <v>41.378499</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>69.475869</v>
+        <v>69.144857</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>41.445931, 69.475869</t>
+          <t>41.378499, 69.144857</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Сасбага</t>
+          <t>Илгар</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>3.1</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2143</v>
+        <v>2210</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P92" t="n">
         <v>0</v>
@@ -8983,13 +8985,13 @@
         <v>5</v>
       </c>
       <c r="R92" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S92" t="n">
-        <v>129</v>
+        <v>2397</v>
       </c>
       <c r="T92" t="n">
-        <v>213.9</v>
+        <v>270.6</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -9002,12 +9004,12 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.445931,69.475869</t>
+          <t>https://www.google.com/maps?q=41.378499,69.144857</t>
         </is>
       </c>
     </row>
@@ -9018,25 +9020,25 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="C93" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>41.160793</v>
+        <v>41.445931</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>69.174412</v>
+        <v>69.475869</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>41.160793, 69.174412</t>
+          <t>41.445931, 69.475869</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Боборахим</t>
+          <t>Сасбага</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9045,18 +9047,18 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Янгиюльский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1726</v>
+        <v>2143</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
@@ -9074,13 +9076,13 @@
         <v>5</v>
       </c>
       <c r="R93" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S93" t="n">
-        <v>17092</v>
+        <v>129</v>
       </c>
       <c r="T93" t="n">
-        <v>129.6</v>
+        <v>213.9</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
@@ -9098,7 +9100,7 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.160793,69.174412</t>
+          <t>https://www.google.com/maps?q=41.445931,69.475869</t>
         </is>
       </c>
     </row>
@@ -9109,54 +9111,54 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="C94" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>41.343065</v>
+        <v>41.160793</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>69.11617699999999</v>
+        <v>69.174412</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>41.343065, 69.116177</t>
+          <t>41.160793, 69.174412</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Илгар</t>
+          <t>Боборахим</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J94" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Янгиюльский район</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2595</v>
+        <v>1726</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
         <v>0</v>
@@ -9165,13 +9167,13 @@
         <v>5</v>
       </c>
       <c r="R94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S94" t="n">
-        <v>1141</v>
+        <v>17092</v>
       </c>
       <c r="T94" t="n">
-        <v>184.9</v>
+        <v>129.6</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -9184,12 +9186,12 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.343065,69.116177</t>
+          <t>https://www.google.com/maps?q=41.160793,69.174412</t>
         </is>
       </c>
     </row>
@@ -9200,69 +9202,69 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="C95" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>41.418715</v>
+        <v>41.343065</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>69.193523</v>
+        <v>69.11617699999999</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>41.418715, 69.193523</t>
+          <t>41.343065, 69.116177</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Куктерак</t>
+          <t>Илгар</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J95" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2247</v>
+        <v>2595</v>
       </c>
       <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
         <v>2</v>
       </c>
-      <c r="N95" t="n">
-        <v>4</v>
-      </c>
       <c r="O95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P95" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
         <v>5</v>
       </c>
       <c r="R95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S95" t="n">
-        <v>1267</v>
+        <v>1141</v>
       </c>
       <c r="T95" t="n">
-        <v>270.6</v>
+        <v>184.9</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
@@ -9280,7 +9282,7 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.418715,69.193523</t>
+          <t>https://www.google.com/maps?q=41.343065,69.116177</t>
         </is>
       </c>
     </row>
@@ -9291,20 +9293,20 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="C96" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>41.425276</v>
+        <v>41.418715</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>69.209565</v>
+        <v>69.193523</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>41.425276, 69.209565</t>
+          <t>41.418715, 69.193523</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -9318,7 +9320,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J96" t="n">
         <v>3.8</v>
@@ -9329,13 +9331,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2734</v>
+        <v>2247</v>
       </c>
       <c r="M96" t="n">
         <v>2</v>
       </c>
       <c r="N96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O96" t="n">
         <v>1</v>
@@ -9347,10 +9349,10 @@
         <v>5</v>
       </c>
       <c r="R96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S96" t="n">
-        <v>187</v>
+        <v>1267</v>
       </c>
       <c r="T96" t="n">
         <v>270.6</v>
@@ -9371,7 +9373,7 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.425276,69.209565</t>
+          <t>https://www.google.com/maps?q=41.418715,69.193523</t>
         </is>
       </c>
     </row>
@@ -9382,25 +9384,25 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C97" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>41.358385</v>
+        <v>41.425276</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>69.120549</v>
+        <v>69.209565</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>41.358385, 69.120549</t>
+          <t>41.425276, 69.209565</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Шамсиабад</t>
+          <t>Куктерак</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9409,10 +9411,10 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -9420,28 +9422,28 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3620</v>
+        <v>2734</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N97" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q97" t="n">
         <v>5</v>
       </c>
       <c r="R97" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S97" t="n">
-        <v>1701</v>
+        <v>187</v>
       </c>
       <c r="T97" t="n">
         <v>270.6</v>
@@ -9462,7 +9464,7 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.358385,69.120549</t>
+          <t>https://www.google.com/maps?q=41.425276,69.209565</t>
         </is>
       </c>
     </row>
@@ -9479,19 +9481,19 @@
         <v>82</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>41.412151</v>
+        <v>41.358385</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>69.177485</v>
+        <v>69.120549</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>41.412151, 69.177485</t>
+          <t>41.358385, 69.120549</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Сагбан</t>
+          <t>Шамсиабад</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -9500,10 +9502,10 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -9511,28 +9513,28 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2486</v>
+        <v>3620</v>
       </c>
       <c r="M98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
         <v>4</v>
       </c>
       <c r="O98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P98" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
         <v>5</v>
       </c>
       <c r="R98" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S98" t="n">
-        <v>1519</v>
+        <v>1701</v>
       </c>
       <c r="T98" t="n">
         <v>270.6</v>
@@ -9553,7 +9555,7 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.412151,69.177485</t>
+          <t>https://www.google.com/maps?q=41.358385,69.120549</t>
         </is>
       </c>
     </row>
@@ -9564,25 +9566,25 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C99" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>41.404809</v>
+        <v>41.412151</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>69.391277</v>
+        <v>69.177485</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>41.404809, 69.391277</t>
+          <t>41.412151, 69.177485</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Уткир</t>
+          <t>Сагбан</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -9598,35 +9600,35 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1919</v>
+        <v>2486</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q99" t="n">
         <v>5</v>
       </c>
       <c r="R99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S99" t="n">
-        <v>1398</v>
+        <v>1519</v>
       </c>
       <c r="T99" t="n">
-        <v>213.9</v>
+        <v>270.6</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
@@ -9639,12 +9641,12 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.404809,69.391277</t>
+          <t>https://www.google.com/maps?q=41.412151,69.177485</t>
         </is>
       </c>
     </row>
@@ -9655,25 +9657,25 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C100" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>41.173507</v>
+        <v>41.404809</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>69.131349</v>
+        <v>69.391277</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>41.173507, 69.131349</t>
+          <t>41.404809, 69.391277</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ханкурган</t>
+          <t>Уткир</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -9682,18 +9684,18 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J100" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2231</v>
+        <v>1919</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
@@ -9714,10 +9716,10 @@
         <v>2</v>
       </c>
       <c r="S100" t="n">
-        <v>2842</v>
+        <v>1398</v>
       </c>
       <c r="T100" t="n">
-        <v>184.9</v>
+        <v>213.9</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
@@ -9735,7 +9737,7 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.173507,69.131349</t>
+          <t>https://www.google.com/maps?q=41.404809,69.391277</t>
         </is>
       </c>
     </row>
@@ -9746,45 +9748,45 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C101" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>41.445091</v>
+        <v>41.173507</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>69.249785</v>
+        <v>69.131349</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>41.445091, 69.249785</t>
+          <t>41.173507, 69.131349</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Чувалачи</t>
+          <t>Ханкурган</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="J101" t="n">
         <v>5.3</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2773</v>
+        <v>2231</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
@@ -9802,13 +9804,13 @@
         <v>5</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S101" t="n">
-        <v>0</v>
+        <v>2842</v>
       </c>
       <c r="T101" t="n">
-        <v>270.6</v>
+        <v>184.9</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
@@ -9826,7 +9828,7 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.445091,69.249785</t>
+          <t>https://www.google.com/maps?q=41.173507,69.131349</t>
         </is>
       </c>
     </row>
@@ -9837,34 +9839,34 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="C102" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>41.445517</v>
+        <v>41.445091</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>69.226005</v>
+        <v>69.249785</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>41.445517, 69.226005</t>
+          <t>41.445091, 69.249785</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Алишер Навои</t>
+          <t>Чувалачи</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J102" t="n">
         <v>5.3</v>
@@ -9875,7 +9877,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2065</v>
+        <v>2773</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
@@ -9893,10 +9895,10 @@
         <v>5</v>
       </c>
       <c r="R102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="T102" t="n">
         <v>270.6</v>
@@ -9917,7 +9919,7 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.445517,69.226005</t>
+          <t>https://www.google.com/maps?q=41.445091,69.249785</t>
         </is>
       </c>
     </row>
@@ -9928,25 +9930,25 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C103" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>41.273963</v>
+        <v>41.445517</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>69.055013</v>
+        <v>69.226005</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>41.273963, 69.055013</t>
+          <t>41.445517, 69.226005</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Тукимачи</t>
+          <t>Алишер Навои</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -9955,18 +9957,18 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J103" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2760</v>
+        <v>2065</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
@@ -9984,13 +9986,13 @@
         <v>5</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S103" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="T103" t="n">
-        <v>184.9</v>
+        <v>270.6</v>
       </c>
       <c r="U103" t="n">
         <v>0</v>
@@ -10008,7 +10010,7 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.273963,69.055013</t>
+          <t>https://www.google.com/maps?q=41.445517,69.226005</t>
         </is>
       </c>
     </row>
@@ -10019,69 +10021,69 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="C104" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>41.434386</v>
+        <v>41.273963</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>69.538939</v>
+        <v>69.055013</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>41.434386, 69.538939</t>
+          <t>41.273963, 69.055013</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Вахид Хайдаров махалля</t>
+          <t>Тукимачи</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J104" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Город Чиpчик</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>7155</v>
+        <v>2760</v>
       </c>
       <c r="M104" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
         <v>5</v>
       </c>
       <c r="R104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
-        <v>1599</v>
+        <v>0</v>
       </c>
       <c r="T104" t="n">
-        <v>40.8</v>
+        <v>184.9</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
@@ -10094,12 +10096,12 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.434386,69.538939</t>
+          <t>https://www.google.com/maps?q=41.273963,69.055013</t>
         </is>
       </c>
     </row>
@@ -10110,69 +10112,69 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="C105" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>41.44823</v>
+        <v>41.287638</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>69.53147800000001</v>
+        <v>69.055368</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>41.448230, 69.531478</t>
+          <t>41.287638, 69.055368</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Нурабад махалля</t>
+          <t>Янарык</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J105" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>4150</v>
+        <v>2340</v>
       </c>
       <c r="M105" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
         <v>5</v>
       </c>
       <c r="R105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
-        <v>1599</v>
+        <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>213.9</v>
+        <v>184.9</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
@@ -10185,12 +10187,12 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.448230,69.531478</t>
+          <t>https://www.google.com/maps?q=41.287638,69.055368</t>
         </is>
       </c>
     </row>
@@ -10201,57 +10203,57 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C106" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>41.151495</v>
+        <v>41.434386</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>69.118915</v>
+        <v>69.538939</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>41.151495, 69.118915</t>
+          <t>41.434386, 69.538939</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Машраб</t>
+          <t>Вахид Хайдаров махалля</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J106" t="n">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Янгиюльский район</t>
+          <t>Город Чиpчик</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2329</v>
+        <v>7155</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q106" t="n">
         <v>5</v>
@@ -10260,10 +10262,10 @@
         <v>2</v>
       </c>
       <c r="S106" t="n">
-        <v>829</v>
+        <v>1599</v>
       </c>
       <c r="T106" t="n">
-        <v>129.6</v>
+        <v>40.8</v>
       </c>
       <c r="U106" t="n">
         <v>0</v>
@@ -10276,12 +10278,12 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.151495,69.118915</t>
+          <t>https://www.google.com/maps?q=41.434386,69.538939</t>
         </is>
       </c>
     </row>
@@ -10292,69 +10294,69 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C107" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>41.461777</v>
+        <v>41.44823</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>69.36531100000001</v>
+        <v>69.53147800000001</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>41.461777, 69.365311</t>
+          <t>41.448230, 69.531478</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Гышткуприк</t>
+          <t>Нурабад махалля</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J107" t="n">
-        <v>8.1</v>
+        <v>6.5</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2850</v>
+        <v>4150</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q107" t="n">
         <v>5</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S107" t="n">
-        <v>0</v>
+        <v>1599</v>
       </c>
       <c r="T107" t="n">
-        <v>270.6</v>
+        <v>213.9</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
@@ -10367,12 +10369,12 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.461777,69.365311</t>
+          <t>https://www.google.com/maps?q=41.448230,69.531478</t>
         </is>
       </c>
     </row>
@@ -10383,57 +10385,57 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C108" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>41.445785</v>
+        <v>41.151495</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>69.567094</v>
+        <v>69.118915</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>41.445785, 69.567094</t>
+          <t>41.151495, 69.118915</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Умид махалля</t>
+          <t>Машраб</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J108" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Город Чиpчик</t>
+          <t>Янгиюльский район</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2606</v>
+        <v>2329</v>
       </c>
       <c r="M108" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
         <v>5</v>
@@ -10442,17 +10444,15 @@
         <v>2</v>
       </c>
       <c r="S108" t="n">
-        <v>1599</v>
+        <v>829</v>
       </c>
       <c r="T108" t="n">
-        <v>40.8</v>
+        <v>129.6</v>
       </c>
       <c r="U108" t="n">
-        <v>2</v>
-      </c>
-      <c r="V108" t="n">
-        <v>4068</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V108" t="inlineStr"/>
       <c r="W108" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -10460,12 +10460,12 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.445785,69.567094</t>
+          <t>https://www.google.com/maps?q=41.151495,69.118915</t>
         </is>
       </c>
     </row>
@@ -10476,25 +10476,25 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="C109" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>41.115948</v>
+        <v>41.461777</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>69.098242</v>
+        <v>69.36531100000001</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>41.115948, 69.098242</t>
+          <t>41.461777, 69.365311</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Тахтакуприк</t>
+          <t>Гышткуприк</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -10503,18 +10503,18 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J109" t="n">
-        <v>11.5</v>
+        <v>8.1</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Янгиюльский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1767</v>
+        <v>2850</v>
       </c>
       <c r="M109" t="n">
         <v>0</v>
@@ -10532,13 +10532,13 @@
         <v>5</v>
       </c>
       <c r="R109" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
-        <v>909</v>
+        <v>0</v>
       </c>
       <c r="T109" t="n">
-        <v>129.6</v>
+        <v>270.6</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.115948,69.098242</t>
+          <t>https://www.google.com/maps?q=41.461777,69.365311</t>
         </is>
       </c>
     </row>
@@ -10567,66 +10567,66 @@
         </is>
       </c>
       <c r="B110" t="n">
+        <v>21</v>
+      </c>
+      <c r="C110" t="n">
+        <v>84</v>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>41.445785</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>69.567094</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>41.445785, 69.567094</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Умид махалля</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>махалля</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J110" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Город Чиpчик</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>2606</v>
+      </c>
+      <c r="M110" t="n">
+        <v>5</v>
+      </c>
+      <c r="N110" t="n">
         <v>4</v>
       </c>
-      <c r="C110" t="n">
-        <v>91</v>
-      </c>
-      <c r="D110" s="2" t="n">
-        <v>41.478034</v>
-      </c>
-      <c r="E110" s="2" t="n">
-        <v>69.580118</v>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>41.478034, 69.580118</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Бахор махалля</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>махалля</t>
-        </is>
-      </c>
-      <c r="I110" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J110" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>Город Чиpчик</t>
-        </is>
-      </c>
-      <c r="L110" t="n">
-        <v>18190</v>
-      </c>
-      <c r="M110" t="n">
+      <c r="O110" t="n">
         <v>2</v>
       </c>
-      <c r="N110" t="n">
-        <v>8</v>
-      </c>
-      <c r="O110" t="n">
-        <v>4</v>
-      </c>
       <c r="P110" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Q110" t="n">
         <v>5</v>
       </c>
       <c r="R110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S110" t="n">
-        <v>1995</v>
+        <v>1599</v>
       </c>
       <c r="T110" t="n">
         <v>40.8</v>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.478034,69.580118</t>
+          <t>https://www.google.com/maps?q=41.445785,69.567094</t>
         </is>
       </c>
     </row>
@@ -10660,25 +10660,25 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="C111" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>41.463685</v>
+        <v>41.115948</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>69.611362</v>
+        <v>69.098242</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>41.463685, 69.611362</t>
+          <t>41.115948, 69.098242</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Карабай</t>
+          <t>Тахтакуприк</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -10687,30 +10687,30 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J111" t="n">
-        <v>13.1</v>
+        <v>11.5</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Бостанлыкский район</t>
+          <t>Янгиюльский район</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2282</v>
+        <v>1767</v>
       </c>
       <c r="M111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P111" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
         <v>5</v>
@@ -10719,10 +10719,10 @@
         <v>3</v>
       </c>
       <c r="S111" t="n">
-        <v>1995</v>
+        <v>909</v>
       </c>
       <c r="T111" t="n">
-        <v>147.5</v>
+        <v>129.6</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
@@ -10735,12 +10735,12 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.463685,69.611362</t>
+          <t>https://www.google.com/maps?q=41.115948,69.098242</t>
         </is>
       </c>
     </row>
@@ -10751,57 +10751,57 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="C112" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>41.157616</v>
+        <v>41.478034</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>69.059894</v>
+        <v>69.580118</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>41.157616, 69.059894</t>
+          <t>41.478034, 69.580118</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Конкус</t>
+          <t>Бахор махалля</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J112" t="n">
-        <v>13.1</v>
+        <v>11.7</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Янгиюльский район</t>
+          <t>Город Чиpчик</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1815</v>
+        <v>18190</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q112" t="n">
         <v>5</v>
@@ -10810,15 +10810,17 @@
         <v>3</v>
       </c>
       <c r="S112" t="n">
-        <v>909</v>
+        <v>1995</v>
       </c>
       <c r="T112" t="n">
-        <v>129.6</v>
+        <v>40.8</v>
       </c>
       <c r="U112" t="n">
-        <v>0</v>
-      </c>
-      <c r="V112" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="V112" t="n">
+        <v>4068</v>
+      </c>
       <c r="W112" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -10826,12 +10828,12 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.157616,69.059894</t>
+          <t>https://www.google.com/maps?q=41.478034,69.580118</t>
         </is>
       </c>
     </row>
@@ -10842,25 +10844,25 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C113" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>41.104188</v>
+        <v>41.463685</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>69.08610299999999</v>
+        <v>69.611362</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>41.104188, 69.086103</t>
+          <t>41.463685, 69.611362</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ниязбаш</t>
+          <t>Карабай</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -10869,30 +10871,30 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J113" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Янгиюльский район</t>
+          <t>Бостанлыкский район</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2547</v>
+        <v>2282</v>
       </c>
       <c r="M113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N113" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O113" t="n">
         <v>2</v>
       </c>
       <c r="P113" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q113" t="n">
         <v>5</v>
@@ -10901,10 +10903,10 @@
         <v>3</v>
       </c>
       <c r="S113" t="n">
-        <v>909</v>
+        <v>1995</v>
       </c>
       <c r="T113" t="n">
-        <v>129.6</v>
+        <v>147.5</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
@@ -10922,7 +10924,7 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.104188,69.086103</t>
+          <t>https://www.google.com/maps?q=41.463685,69.611362</t>
         </is>
       </c>
     </row>
@@ -10933,69 +10935,69 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C114" t="n">
         <v>78</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>41.039806</v>
+        <v>41.157616</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>69.340406</v>
+        <v>69.059894</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>41.039806, 69.340406</t>
+          <t>41.157616, 69.059894</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Нурафшан (Тойтепа)</t>
+          <t>Конкус</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J114" t="n">
-        <v>13.6</v>
+        <v>13.1</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Уртачирчикский район</t>
+          <t>Янгиюльский район</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1871</v>
+        <v>1815</v>
       </c>
       <c r="M114" t="n">
         <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
         <v>5</v>
       </c>
       <c r="R114" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S114" t="n">
-        <v>1946</v>
+        <v>909</v>
       </c>
       <c r="T114" t="n">
-        <v>134.2</v>
+        <v>129.6</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
@@ -11008,12 +11010,12 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.039806,69.340406</t>
+          <t>https://www.google.com/maps?q=41.157616,69.059894</t>
         </is>
       </c>
     </row>
@@ -11024,20 +11026,20 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C115" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>41.088745</v>
+        <v>41.104188</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>69.089637</v>
+        <v>69.08610299999999</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>41.088745, 69.089637</t>
+          <t>41.104188, 69.086103</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -11051,10 +11053,10 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J115" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -11062,19 +11064,19 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2111</v>
+        <v>2547</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q115" t="n">
         <v>5</v>
@@ -11099,12 +11101,12 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.088745,69.089637</t>
+          <t>https://www.google.com/maps?q=41.104188,69.086103</t>
         </is>
       </c>
     </row>
@@ -11115,69 +11117,69 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="C116" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>41.10839</v>
+        <v>41.039806</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>69.038905</v>
+        <v>69.340406</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>41.108390, 69.038905</t>
+          <t>41.039806, 69.340406</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Тонг массив</t>
+          <t>Нурафшан (Тойтепа)</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="J116" t="n">
-        <v>15.7</v>
+        <v>13.6</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Янгиюльский район</t>
+          <t>Уртачирчикский район</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>4351</v>
+        <v>1871</v>
       </c>
       <c r="M116" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P116" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q116" t="n">
         <v>5</v>
       </c>
       <c r="R116" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S116" t="n">
-        <v>909</v>
+        <v>1946</v>
       </c>
       <c r="T116" t="n">
-        <v>129.6</v>
+        <v>134.2</v>
       </c>
       <c r="U116" t="n">
         <v>0</v>
@@ -11195,7 +11197,7 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.108390,69.038905</t>
+          <t>https://www.google.com/maps?q=41.039806,69.340406</t>
         </is>
       </c>
     </row>
@@ -11206,69 +11208,69 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C117" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>41.02079</v>
+        <v>41.088745</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>69.351637</v>
+        <v>69.089637</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>41.020790, 69.351637</t>
+          <t>41.088745, 69.089637</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Чигирик</t>
+          <t>Ниязбаш</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J117" t="n">
-        <v>15.7</v>
+        <v>13.9</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Уртачирчикский район</t>
+          <t>Янгиюльский район</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>3239</v>
+        <v>2111</v>
       </c>
       <c r="M117" t="n">
         <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P117" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
         <v>5</v>
       </c>
       <c r="R117" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S117" t="n">
-        <v>1946</v>
+        <v>909</v>
       </c>
       <c r="T117" t="n">
-        <v>134.2</v>
+        <v>129.6</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -11281,12 +11283,12 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.020790,69.351637</t>
+          <t>https://www.google.com/maps?q=41.088745,69.089637</t>
         </is>
       </c>
     </row>
@@ -11297,69 +11299,69 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C118" t="n">
         <v>86</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>41.514494</v>
+        <v>41.10839</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>69.636989</v>
+        <v>69.038905</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>41.514494, 69.636989</t>
+          <t>41.108390, 69.038905</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Аранчи</t>
+          <t>Тонг массив</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J118" t="n">
-        <v>17.9</v>
+        <v>15.7</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Город Чиpчик</t>
+          <t>Янгиюльский район</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>4566</v>
+        <v>4351</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O118" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q118" t="n">
         <v>5</v>
       </c>
       <c r="R118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S118" t="n">
-        <v>444</v>
+        <v>909</v>
       </c>
       <c r="T118" t="n">
-        <v>40.8</v>
+        <v>129.6</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
@@ -11372,12 +11374,12 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.514494,69.636989</t>
+          <t>https://www.google.com/maps?q=41.108390,69.038905</t>
         </is>
       </c>
     </row>
@@ -11388,69 +11390,69 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C119" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>41.531601</v>
+        <v>41.02079</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>69.637602</v>
+        <v>69.351637</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>41.531601, 69.637602</t>
+          <t>41.020790, 69.351637</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Азадбаш</t>
+          <t>Чигирик</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J119" t="n">
-        <v>19.2</v>
+        <v>15.7</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Бостанлыкский район</t>
+          <t>Уртачирчикский район</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2381</v>
+        <v>3239</v>
       </c>
       <c r="M119" t="n">
         <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q119" t="n">
         <v>5</v>
       </c>
       <c r="R119" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S119" t="n">
-        <v>444</v>
+        <v>1946</v>
       </c>
       <c r="T119" t="n">
-        <v>147.5</v>
+        <v>134.2</v>
       </c>
       <c r="U119" t="n">
         <v>0</v>
@@ -11463,12 +11465,12 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.531601,69.637602</t>
+          <t>https://www.google.com/maps?q=41.020790,69.351637</t>
         </is>
       </c>
     </row>
@@ -11479,54 +11481,54 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C120" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>41.520827</v>
+        <v>41.514663</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>69.66104799999999</v>
+        <v>69.629052</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>41.520827, 69.661048</t>
+          <t>41.514663, 69.629052</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Аранчи</t>
+          <t>Бахт махалля</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J120" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Бостанлыкский район</t>
+          <t>Город Чиpчик</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1866</v>
+        <v>8262</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P120" t="n">
         <v>0</v>
@@ -11541,7 +11543,7 @@
         <v>444</v>
       </c>
       <c r="T120" t="n">
-        <v>147.5</v>
+        <v>40.8</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
@@ -11554,12 +11556,12 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.520827,69.661048</t>
+          <t>https://www.google.com/maps?q=41.514663,69.629052</t>
         </is>
       </c>
     </row>
@@ -11570,10 +11572,10 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C121" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D121" s="2" t="n">
         <v>41.570059</v>
@@ -12119,7 +12121,7 @@
         <v>12</v>
       </c>
       <c r="C127" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D127" s="2" t="n">
         <v>40.913997</v>
@@ -12938,7 +12940,7 @@
         <v>28</v>
       </c>
       <c r="C136" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D136" s="2" t="n">
         <v>40.877498</v>
@@ -13117,7 +13119,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C138" t="n">
         <v>55</v>
@@ -13851,7 +13853,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C146" t="n">
         <v>55</v>
@@ -13942,7 +13944,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C147" t="n">
         <v>61</v>
@@ -14306,10 +14308,10 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C151" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D151" s="2" t="n">
         <v>40.85233</v>
@@ -15494,7 +15496,7 @@
         <v>52</v>
       </c>
       <c r="C164" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D164" s="2" t="n">
         <v>41.00906</v>
@@ -17223,7 +17225,7 @@
         <v>1</v>
       </c>
       <c r="C183" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D183" s="2" t="n">
         <v>40.252947</v>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,7 +660,7 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V2" t="n">
         <v>70</v>
@@ -738,7 +738,7 @@
         <v>12</v>
       </c>
       <c r="P3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q3" t="n">
         <v>0.5</v>
@@ -753,7 +753,7 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V3" t="n">
         <v>900</v>
@@ -831,7 +831,7 @@
         <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q4" t="n">
         <v>0.5</v>
@@ -939,7 +939,7 @@
         <v>48.5</v>
       </c>
       <c r="U5" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="V5" t="n">
         <v>918</v>
@@ -1032,7 +1032,7 @@
         <v>139.7</v>
       </c>
       <c r="U6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V6" t="n">
         <v>500</v>
@@ -1125,7 +1125,7 @@
         <v>59.2</v>
       </c>
       <c r="U7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V7" t="n">
         <v>500</v>
@@ -1218,7 +1218,7 @@
         <v>98.2</v>
       </c>
       <c r="U8" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="V8" t="n">
         <v>500</v>
@@ -1311,10 +1311,10 @@
         <v>98.2</v>
       </c>
       <c r="U9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V9" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>41.284507</v>
@@ -1389,7 +1389,7 @@
         <v>21</v>
       </c>
       <c r="P10" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q10" t="n">
         <v>0.5</v>
@@ -1404,7 +1404,7 @@
         <v>31.8</v>
       </c>
       <c r="U10" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V10" t="n">
         <v>800</v>
@@ -1497,7 +1497,7 @@
         <v>98.2</v>
       </c>
       <c r="U11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V11" t="n">
         <v>1200</v>
@@ -1575,7 +1575,7 @@
         <v>18</v>
       </c>
       <c r="P12" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q12" t="n">
         <v>0.5</v>
@@ -1590,7 +1590,7 @@
         <v>141</v>
       </c>
       <c r="U12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V12" t="n">
         <v>600</v>
@@ -1668,7 +1668,7 @@
         <v>10</v>
       </c>
       <c r="P13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q13" t="n">
         <v>0.5</v>
@@ -1776,7 +1776,7 @@
         <v>139.7</v>
       </c>
       <c r="U14" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="V14" t="n">
         <v>350</v>
@@ -1947,7 +1947,7 @@
         <v>15</v>
       </c>
       <c r="P16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q16" t="n">
         <v>0.5</v>
@@ -1962,7 +1962,7 @@
         <v>141</v>
       </c>
       <c r="U16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V16" t="n">
         <v>500</v>
@@ -2055,7 +2055,7 @@
         <v>139.7</v>
       </c>
       <c r="U17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V17" t="n">
         <v>350</v>
@@ -2319,7 +2319,7 @@
         <v>26</v>
       </c>
       <c r="P20" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q20" t="n">
         <v>0.5</v>
@@ -2334,7 +2334,7 @@
         <v>139.7</v>
       </c>
       <c r="U20" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="V20" t="n">
         <v>600</v>
@@ -2520,7 +2520,7 @@
         <v>139.7</v>
       </c>
       <c r="U22" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="V22" t="n">
         <v>300</v>
@@ -2551,7 +2551,7 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>41.348398</v>
@@ -2613,7 +2613,7 @@
         <v>59.2</v>
       </c>
       <c r="U23" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="V23" t="n">
         <v>200</v>
@@ -2802,7 +2802,7 @@
         <v>38</v>
       </c>
       <c r="V25" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -2833,24 +2833,24 @@
         <v>80</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>41.328395</v>
+        <v>41.336868</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>69.361155</v>
+        <v>69.36537800000001</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>41.328395, 69.361155</t>
+          <t>41.336868, 69.365378</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Карасу</t>
+          <t>Шуртепа махалля</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>район города</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -2865,19 +2865,19 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>10284</v>
+        <v>8847</v>
       </c>
       <c r="M26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N26" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O26" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="P26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q26" t="n">
         <v>0.5</v>
@@ -2892,7 +2892,7 @@
         <v>98.2</v>
       </c>
       <c r="U26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V26" t="n">
         <v>10</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.328395,69.361155</t>
+          <t>https://www.google.com/maps?q=41.336868,69.365378</t>
         </is>
       </c>
     </row>
@@ -3019,19 +3019,19 @@
         <v>79</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>41.279342</v>
+        <v>41.32319</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>69.331948</v>
+        <v>69.364951</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>41.279342, 69.331948</t>
+          <t>41.323190, 69.364951</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Асалабад-2 (Слонима)</t>
+          <t>Карасу-5</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3040,30 +3040,30 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3595</v>
+        <v>10568</v>
       </c>
       <c r="M28" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N28" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O28" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P28" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="Q28" t="n">
         <v>0.5</v>
@@ -3075,13 +3075,13 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>141</v>
+        <v>98.2</v>
       </c>
       <c r="U28" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="V28" t="n">
-        <v>500</v>
+        <v>1100</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.279342,69.331948</t>
+          <t>https://www.google.com/maps?q=41.323190,69.364951</t>
         </is>
       </c>
     </row>
@@ -3112,19 +3112,19 @@
         <v>79</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>41.343858</v>
+        <v>41.279342</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>69.357677</v>
+        <v>69.331948</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>41.343858, 69.357677</t>
+          <t>41.279342, 69.331948</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Буз-2 (Черданцева)</t>
+          <t>Асалабад-2 (Слонима)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3133,30 +3133,30 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5378</v>
+        <v>3595</v>
       </c>
       <c r="M29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N29" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="O29" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="P29" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="Q29" t="n">
         <v>0.5</v>
@@ -3168,13 +3168,13 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>98.2</v>
+        <v>141</v>
       </c>
       <c r="U29" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="V29" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.343858,69.357677</t>
+          <t>https://www.google.com/maps?q=41.279342,69.331948</t>
         </is>
       </c>
     </row>
@@ -3355,7 +3355,7 @@
         <v>59.2</v>
       </c>
       <c r="U31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V31" t="n">
         <v>200</v>
@@ -3448,7 +3448,7 @@
         <v>139.7</v>
       </c>
       <c r="U32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V32" t="n">
         <v>1200</v>
@@ -3634,7 +3634,7 @@
         <v>47.6</v>
       </c>
       <c r="U34" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="V34" t="n">
         <v>70</v>
@@ -4004,7 +4004,7 @@
         <v>59.2</v>
       </c>
       <c r="U38" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="V38" t="n">
         <v>200</v>
@@ -4097,7 +4097,7 @@
         <v>139.7</v>
       </c>
       <c r="U39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V39" t="n">
         <v>500</v>
@@ -4190,7 +4190,7 @@
         <v>28.3</v>
       </c>
       <c r="U40" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="V40" t="n">
         <v>800</v>
@@ -4283,7 +4283,7 @@
         <v>47.6</v>
       </c>
       <c r="U41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V41" t="n">
         <v>2</v>
@@ -4361,7 +4361,7 @@
         <v>22</v>
       </c>
       <c r="P42" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q42" t="n">
         <v>0.5</v>
@@ -4376,7 +4376,7 @@
         <v>31.8</v>
       </c>
       <c r="U42" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V42" t="n">
         <v>900</v>
@@ -4469,7 +4469,7 @@
         <v>48.5</v>
       </c>
       <c r="U43" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="V43" t="n">
         <v>1600</v>
@@ -4655,7 +4655,7 @@
         <v>28.3</v>
       </c>
       <c r="U45" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V45" t="n">
         <v>600</v>
@@ -5008,7 +5008,7 @@
         <v>3</v>
       </c>
       <c r="P49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q49" t="n">
         <v>0.5</v>
@@ -6493,10 +6493,10 @@
         <v>184.9</v>
       </c>
       <c r="U65" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V65" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>213.9</v>
       </c>
       <c r="U80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V80" t="n">
         <v>1000</v>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,7 +660,7 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V2" t="n">
         <v>70</v>
@@ -753,7 +753,7 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="V3" t="n">
         <v>900</v>
@@ -784,7 +784,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>41.273095</v>
@@ -939,7 +939,7 @@
         <v>48.5</v>
       </c>
       <c r="U5" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="V5" t="n">
         <v>918</v>
@@ -1032,7 +1032,7 @@
         <v>59.2</v>
       </c>
       <c r="U6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V6" t="n">
         <v>500</v>
@@ -1125,7 +1125,7 @@
         <v>139.7</v>
       </c>
       <c r="U7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V7" t="n">
         <v>500</v>
@@ -1342,22 +1342,22 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>41.31234</v>
+        <v>41.332561</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>69.30525900000001</v>
+        <v>69.321702</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>41.312340, 69.305259</t>
+          <t>41.332561, 69.321702</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Машинасозлар (Ташсельмаш)</t>
+          <t>Буюк Ипак Йули махалля</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1366,48 +1366,48 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>7574</v>
+        <v>4166</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="O10" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P10" t="n">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="Q10" t="n">
         <v>0.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>220</v>
+        <v>1970</v>
       </c>
       <c r="T10" t="n">
-        <v>141</v>
+        <v>98.2</v>
       </c>
       <c r="U10" t="n">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="V10" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.312340,69.305259</t>
+          <t>https://www.google.com/maps?q=41.332561,69.321702</t>
         </is>
       </c>
     </row>
@@ -1438,19 +1438,19 @@
         <v>85</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>41.332561</v>
+        <v>41.31234</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>69.321702</v>
+        <v>69.30525900000001</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>41.332561, 69.321702</t>
+          <t>41.312340, 69.305259</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Буюк Ипак Йули махалля</t>
+          <t>Машинасозлар (Ташсельмаш)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1459,48 +1459,48 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4166</v>
+        <v>7574</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="O11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P11" t="n">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="Q11" t="n">
         <v>0.5</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>1970</v>
+        <v>220</v>
       </c>
       <c r="T11" t="n">
-        <v>98.2</v>
+        <v>141</v>
       </c>
       <c r="U11" t="n">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="V11" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.332561,69.321702</t>
+          <t>https://www.google.com/maps?q=41.312340,69.305259</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
         <v>139.7</v>
       </c>
       <c r="U12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="V12" t="n">
         <v>350</v>
@@ -1683,7 +1683,7 @@
         <v>98.2</v>
       </c>
       <c r="U13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V13" t="n">
         <v>1200</v>
@@ -1869,7 +1869,7 @@
         <v>139.7</v>
       </c>
       <c r="U15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V15" t="n">
         <v>500</v>
@@ -2055,7 +2055,7 @@
         <v>139.7</v>
       </c>
       <c r="U17" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="V17" t="n">
         <v>600</v>
@@ -2241,7 +2241,7 @@
         <v>139.7</v>
       </c>
       <c r="U19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V19" t="n">
         <v>300</v>
@@ -2613,7 +2613,7 @@
         <v>47.6</v>
       </c>
       <c r="U23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V23" t="n">
         <v>70</v>
@@ -2799,7 +2799,7 @@
         <v>98.2</v>
       </c>
       <c r="U25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V25" t="n">
         <v>10</v>
@@ -3264,7 +3264,7 @@
         <v>139.7</v>
       </c>
       <c r="U30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V30" t="n">
         <v>650</v>
@@ -3450,7 +3450,7 @@
         <v>28.3</v>
       </c>
       <c r="U32" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="V32" t="n">
         <v>800</v>
@@ -3543,7 +3543,7 @@
         <v>31.8</v>
       </c>
       <c r="U33" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V33" t="n">
         <v>900</v>
@@ -3636,10 +3636,10 @@
         <v>139.7</v>
       </c>
       <c r="U34" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V34" t="n">
-        <v>500</v>
+        <v>16500</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>28.3</v>
       </c>
       <c r="U36" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="V36" t="n">
         <v>350</v>
@@ -3915,7 +3915,7 @@
         <v>48.5</v>
       </c>
       <c r="U37" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="V37" t="n">
         <v>1600</v>
@@ -3949,19 +3949,19 @@
         <v>70</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>41.270832</v>
+        <v>41.251241</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>69.23679199999999</v>
+        <v>69.370619</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>41.270832, 69.236792</t>
+          <t>41.251241, 69.370619</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Дилбулак махалля</t>
+          <t>Чашма махалля</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3970,30 +3970,30 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Яккасарайский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>11138</v>
+        <v>8604</v>
       </c>
       <c r="M38" t="n">
+        <v>6</v>
+      </c>
+      <c r="N38" t="n">
+        <v>9</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3</v>
+      </c>
+      <c r="P38" t="n">
         <v>5</v>
-      </c>
-      <c r="N38" t="n">
-        <v>33</v>
-      </c>
-      <c r="O38" t="n">
-        <v>12</v>
-      </c>
-      <c r="P38" t="n">
-        <v>41</v>
       </c>
       <c r="Q38" t="n">
         <v>0.5</v>
@@ -4005,14 +4005,12 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>31.8</v>
+        <v>60.2</v>
       </c>
       <c r="U38" t="n">
-        <v>72</v>
-      </c>
-      <c r="V38" t="n">
-        <v>350</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4025,7 +4023,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.270832,69.236792</t>
+          <t>https://www.google.com/maps?q=41.251241,69.370619</t>
         </is>
       </c>
     </row>
@@ -4039,22 +4037,22 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>41.20054</v>
+        <v>41.270832</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>69.246605</v>
+        <v>69.23679199999999</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>41.200540, 69.246605</t>
+          <t>41.270832, 69.236792</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Дарьябуйи махалля</t>
+          <t>Дилбулак махалля</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4063,30 +4061,30 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Яккасарайский район</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2723</v>
+        <v>11138</v>
       </c>
       <c r="M39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N39" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="O39" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P39" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="Q39" t="n">
         <v>0.5</v>
@@ -4098,13 +4096,13 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>122.7</v>
+        <v>31.8</v>
       </c>
       <c r="U39" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="V39" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -4118,7 +4116,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.200540,69.246605</t>
+          <t>https://www.google.com/maps?q=41.270832,69.236792</t>
         </is>
       </c>
     </row>
@@ -4135,19 +4133,19 @@
         <v>68</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>41.257926</v>
+        <v>41.20054</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>69.37873399999999</v>
+        <v>69.246605</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>41.257926, 69.378734</t>
+          <t>41.200540, 69.246605</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Сувсоз-2 (Водник)</t>
+          <t>Дарьябуйи махалля</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4156,30 +4154,30 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>6724</v>
+        <v>2723</v>
       </c>
       <c r="M40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N40" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O40" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q40" t="n">
         <v>0.5</v>
@@ -4191,12 +4189,14 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>60.2</v>
+        <v>122.7</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="V40" t="n">
+        <v>200</v>
+      </c>
       <c r="W40" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.257926,69.378734</t>
+          <t>https://www.google.com/maps?q=41.200540,69.246605</t>
         </is>
       </c>
     </row>
@@ -4317,51 +4317,51 @@
         <v>66</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>41.221225</v>
+        <v>41.391863</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>69.330173</v>
+        <v>69.260114</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>41.221225, 69.330173</t>
+          <t>41.391863, 69.260114</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Бектемир</t>
+          <t>Дустамабад</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>район города</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3591</v>
+        <v>2522</v>
       </c>
       <c r="M42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P42" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="n">
         <v>0.5</v>
@@ -4373,12 +4373,14 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>60.2</v>
+        <v>139.7</v>
       </c>
       <c r="U42" t="n">
-        <v>2</v>
-      </c>
-      <c r="V42" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="V42" t="n">
+        <v>6000</v>
+      </c>
       <c r="W42" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4391,7 +4393,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.221225,69.330173</t>
+          <t>https://www.google.com/maps?q=41.391863,69.260114</t>
         </is>
       </c>
     </row>
@@ -4405,54 +4407,54 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>41.391863</v>
+        <v>41.368494</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>69.260114</v>
+        <v>69.227745</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>41.391863, 69.260114</t>
+          <t>41.368494, 69.227745</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Дустамабад</t>
+          <t>Янги Ташкент махалля</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2522</v>
+        <v>2965</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N43" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="O43" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="P43" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q43" t="n">
         <v>0.5</v>
@@ -4464,13 +4466,13 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>139.7</v>
+        <v>59.2</v>
       </c>
       <c r="U43" t="n">
         <v>5</v>
       </c>
       <c r="V43" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -4484,7 +4486,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.391863,69.260114</t>
+          <t>https://www.google.com/maps?q=41.368494,69.227745</t>
         </is>
       </c>
     </row>
@@ -4498,51 +4500,51 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>41.368494</v>
+        <v>41.277832</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>69.227745</v>
+        <v>69.130234</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>41.368494, 69.227745</t>
+          <t>41.277832, 69.130234</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Янги Ташкент махалля</t>
+          <t>Дамачи</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2965</v>
+        <v>1699</v>
       </c>
       <c r="M44" t="n">
+        <v>6</v>
+      </c>
+      <c r="N44" t="n">
         <v>7</v>
       </c>
-      <c r="N44" t="n">
-        <v>20</v>
-      </c>
       <c r="O44" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="P44" t="n">
         <v>8</v>
@@ -4557,13 +4559,13 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>59.2</v>
+        <v>184.9</v>
       </c>
       <c r="U44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V44" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -4577,7 +4579,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.368494,69.227745</t>
+          <t>https://www.google.com/maps?q=41.277832,69.130234</t>
         </is>
       </c>
     </row>
@@ -4591,54 +4593,54 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>41.277832</v>
+        <v>41.244099</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>69.130234</v>
+        <v>69.386206</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>41.277832, 69.130234</t>
+          <t>41.244099, 69.386206</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Дамачи</t>
+          <t>Мажнунтол махалля</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1699</v>
+        <v>2672</v>
       </c>
       <c r="M45" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N45" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P45" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Q45" t="n">
         <v>0.5</v>
@@ -4650,14 +4652,12 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>184.9</v>
+        <v>60.2</v>
       </c>
       <c r="U45" t="n">
-        <v>3</v>
-      </c>
-      <c r="V45" t="n">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.277832,69.130234</t>
+          <t>https://www.google.com/maps?q=41.244099,69.386206</t>
         </is>
       </c>
     </row>
@@ -4684,22 +4684,22 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>41.244099</v>
+        <v>41.261799</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>69.386206</v>
+        <v>69.35513400000001</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>41.244099, 69.386206</t>
+          <t>41.261799, 69.355134</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Мажнунтол махалля</t>
+          <t>Янгикурган махалля</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4708,30 +4708,30 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2672</v>
+        <v>1603</v>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N46" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="O46" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P46" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Q46" t="n">
         <v>0.5</v>
@@ -4743,12 +4743,14 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>60.2</v>
+        <v>141</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1716</v>
+      </c>
       <c r="W46" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4761,7 +4763,7 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.244099,69.386206</t>
+          <t>https://www.google.com/maps?q=41.261799,69.355134</t>
         </is>
       </c>
     </row>
@@ -4778,19 +4780,19 @@
         <v>60</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>41.261799</v>
+        <v>41.187154</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>69.35513400000001</v>
+        <v>69.230422</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>41.261799, 69.355134</t>
+          <t>41.187154, 69.230422</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Янгикурган махалля</t>
+          <t>Чартак махалля</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4799,30 +4801,30 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1603</v>
+        <v>1947</v>
       </c>
       <c r="M47" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N47" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O47" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="Q47" t="n">
         <v>0.5</v>
@@ -4834,13 +4836,13 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>141</v>
+        <v>122.7</v>
       </c>
       <c r="U47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V47" t="n">
-        <v>1716</v>
+        <v>200</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -4854,7 +4856,7 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.261799,69.355134</t>
+          <t>https://www.google.com/maps?q=41.187154,69.230422</t>
         </is>
       </c>
     </row>
@@ -4868,31 +4870,31 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>41.187154</v>
+        <v>41.174834</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>69.230422</v>
+        <v>69.249804</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>41.187154, 69.230422</t>
+          <t>41.174834, 69.249804</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Чартак махалля</t>
+          <t>Бинокор</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4903,19 +4905,19 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1947</v>
+        <v>2032</v>
       </c>
       <c r="M48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0.5</v>
@@ -4930,11 +4932,9 @@
         <v>122.7</v>
       </c>
       <c r="U48" t="n">
-        <v>3</v>
-      </c>
-      <c r="V48" t="n">
-        <v>200</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4942,12 +4942,12 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.187154,69.230422</t>
+          <t>https://www.google.com/maps?q=41.174834,69.249804</t>
         </is>
       </c>
     </row>
@@ -4961,54 +4961,54 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>41.174834</v>
+        <v>41.236831</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>69.249804</v>
+        <v>69.318793</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>41.174834, 69.249804</t>
+          <t>41.236831, 69.318793</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Бинокор</t>
+          <t>Эшанбулак махалля</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2032</v>
+        <v>1806</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q49" t="n">
         <v>0.5</v>
@@ -5020,10 +5020,10 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>122.7</v>
+        <v>60.2</v>
       </c>
       <c r="U49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.174834,69.249804</t>
+          <t>https://www.google.com/maps?q=41.236831,69.318793</t>
         </is>
       </c>
     </row>
@@ -5052,31 +5052,31 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>41.236831</v>
+        <v>41.217508</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>69.318793</v>
+        <v>69.345862</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>41.236831, 69.318793</t>
+          <t>41.217508, 69.345862</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Эшанбулак махалля</t>
+          <t>Забардаст</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5087,19 +5087,19 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1806</v>
+        <v>1799</v>
       </c>
       <c r="M50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N50" t="n">
+        <v>11</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1</v>
+      </c>
+      <c r="P50" t="n">
         <v>13</v>
-      </c>
-      <c r="O50" t="n">
-        <v>4</v>
-      </c>
-      <c r="P50" t="n">
-        <v>22</v>
       </c>
       <c r="Q50" t="n">
         <v>0.5</v>
@@ -5114,9 +5114,11 @@
         <v>60.2</v>
       </c>
       <c r="U50" t="n">
-        <v>1</v>
-      </c>
-      <c r="V50" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="V50" t="n">
+        <v>100</v>
+      </c>
       <c r="W50" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5129,7 +5131,7 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.236831,69.318793</t>
+          <t>https://www.google.com/maps?q=41.217508,69.345862</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5393,7 @@
         <v>60.2</v>
       </c>
       <c r="U53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
@@ -5482,7 +5484,7 @@
         <v>28.3</v>
       </c>
       <c r="U54" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="V54" t="n">
         <v>550</v>
@@ -5604,22 +5606,22 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>41.21409</v>
+        <v>41.214537</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>69.34575700000001</v>
+        <v>69.322068</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>41.214090, 69.345757</t>
+          <t>41.214537, 69.322068</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Забардаст</t>
+          <t>Кипчак</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5628,7 +5630,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5639,19 +5641,19 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1409</v>
+        <v>1338</v>
       </c>
       <c r="M56" t="n">
         <v>5</v>
       </c>
       <c r="N56" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q56" t="n">
         <v>0.5</v>
@@ -5666,7 +5668,7 @@
         <v>60.2</v>
       </c>
       <c r="U56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V56" t="n">
         <v>100</v>
@@ -5683,7 +5685,7 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.214090,69.345757</t>
+          <t>https://www.google.com/maps?q=41.214537,69.322068</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6153,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C62" t="n">
         <v>65</v>
@@ -6309,7 +6311,7 @@
         <v>213.9</v>
       </c>
       <c r="U63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V63" t="n">
         <v>1500</v>
@@ -6402,7 +6404,7 @@
         <v>270.6</v>
       </c>
       <c r="U64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V64" t="n">
         <v>650</v>
@@ -6430,7 +6432,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C65" t="n">
         <v>69</v>
@@ -6521,7 +6523,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C66" t="n">
         <v>67</v>
@@ -6772,9 +6774,11 @@
         <v>213.9</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V68" t="n">
+        <v>600</v>
+      </c>
       <c r="W68" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6798,7 +6802,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C69" t="n">
         <v>64</v>
@@ -6863,10 +6867,10 @@
         <v>270.6</v>
       </c>
       <c r="U69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V69" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
@@ -7075,25 +7079,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="C72" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>41.161874</v>
+        <v>41.416088</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>69.20996</v>
+        <v>69.427311</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>41.161874, 69.209960</t>
+          <t>41.416088, 69.427311</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Чартак</t>
+          <t>Чинабад</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7102,24 +7106,24 @@
         </is>
       </c>
       <c r="I72" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J72" t="n">
         <v>1.2</v>
       </c>
-      <c r="J72" t="n">
-        <v>1.3</v>
-      </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Янгиюльский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1254</v>
+        <v>2829</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -7131,20 +7135,18 @@
         <v>5</v>
       </c>
       <c r="R72" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S72" t="n">
-        <v>19602</v>
+        <v>439</v>
       </c>
       <c r="T72" t="n">
-        <v>129.6</v>
+        <v>213.9</v>
       </c>
       <c r="U72" t="n">
-        <v>1</v>
-      </c>
-      <c r="V72" t="n">
-        <v>4000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7152,12 +7154,12 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.161874,69.209960</t>
+          <t>https://www.google.com/maps?q=41.416088,69.427311</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7445,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C76" t="n">
         <v>69</v>
@@ -7601,7 +7603,7 @@
         <v>213.9</v>
       </c>
       <c r="U77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V77" t="n">
         <v>1100</v>
@@ -7904,7 +7906,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C81" t="n">
         <v>66</v>
@@ -7997,7 +7999,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C82" t="n">
         <v>62</v>
@@ -8062,10 +8064,10 @@
         <v>213.9</v>
       </c>
       <c r="U82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V82" t="n">
-        <v>1400</v>
+        <v>600</v>
       </c>
       <c r="W82" t="inlineStr">
         <is>
@@ -8093,7 +8095,7 @@
         <v>17</v>
       </c>
       <c r="C83" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D83" s="2" t="n">
         <v>41.417442</v>
@@ -8183,7 +8185,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C84" t="n">
         <v>66</v>
@@ -8274,7 +8276,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C85" t="n">
         <v>65</v>
@@ -8339,9 +8341,11 @@
         <v>213.9</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
-      </c>
-      <c r="V85" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V85" t="n">
+        <v>600</v>
+      </c>
       <c r="W85" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8430,9 +8434,11 @@
         <v>213.9</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
-      </c>
-      <c r="V86" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V86" t="n">
+        <v>600</v>
+      </c>
       <c r="W86" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8456,7 +8462,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C87" t="n">
         <v>70</v>
@@ -8638,7 +8644,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C89" t="n">
         <v>67</v>
@@ -8731,7 +8737,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C90" t="n">
         <v>66</v>
@@ -8796,7 +8802,7 @@
         <v>184.9</v>
       </c>
       <c r="U90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V90" t="n">
         <v>3</v>
@@ -8918,7 +8924,7 @@
         <v>37</v>
       </c>
       <c r="C92" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D92" s="2" t="n">
         <v>41.343065</v>
@@ -9097,7 +9103,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C94" t="n">
         <v>69</v>
@@ -9188,25 +9194,25 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C95" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>41.420136</v>
+        <v>41.412151</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>69.30455000000001</v>
+        <v>69.177485</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>41.420136, 69.304550</t>
+          <t>41.412151, 69.177485</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Шурб</t>
+          <t>Сагбан</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -9218,36 +9224,36 @@
         <v>0.4</v>
       </c>
       <c r="J95" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Ташкентский район</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>2486</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
         <v>4</v>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>Ташкентский район</t>
-        </is>
-      </c>
-      <c r="L95" t="n">
-        <v>1966</v>
-      </c>
-      <c r="M95" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" t="n">
+      <c r="O95" t="n">
         <v>1</v>
       </c>
-      <c r="O95" t="n">
-        <v>0</v>
-      </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q95" t="n">
         <v>5</v>
       </c>
       <c r="R95" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S95" t="n">
-        <v>6140</v>
+        <v>1519</v>
       </c>
       <c r="T95" t="n">
         <v>270.6</v>
@@ -9268,7 +9274,7 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.420136,69.304550</t>
+          <t>https://www.google.com/maps?q=41.412151,69.177485</t>
         </is>
       </c>
     </row>
@@ -9279,25 +9285,25 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C96" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>41.412151</v>
+        <v>41.404809</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>69.177485</v>
+        <v>69.391277</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>41.412151, 69.177485</t>
+          <t>41.404809, 69.391277</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Сагбан</t>
+          <t>Уткир</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -9313,35 +9319,35 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2486</v>
+        <v>1919</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
         <v>5</v>
       </c>
       <c r="R96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S96" t="n">
-        <v>1519</v>
+        <v>1398</v>
       </c>
       <c r="T96" t="n">
-        <v>270.6</v>
+        <v>213.9</v>
       </c>
       <c r="U96" t="n">
         <v>0</v>
@@ -9354,12 +9360,12 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.412151,69.177485</t>
+          <t>https://www.google.com/maps?q=41.404809,69.391277</t>
         </is>
       </c>
     </row>
@@ -9370,25 +9376,25 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="C97" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>41.404809</v>
+        <v>41.168041</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>69.391277</v>
+        <v>69.15093400000001</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>41.404809, 69.391277</t>
+          <t>41.168041, 69.150934</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Уткир</t>
+          <t>Багзар</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9397,18 +9403,18 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J97" t="n">
         <v>4.3</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1919</v>
+        <v>1409</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -9429,10 +9435,10 @@
         <v>2</v>
       </c>
       <c r="S97" t="n">
-        <v>1398</v>
+        <v>2842</v>
       </c>
       <c r="T97" t="n">
-        <v>213.9</v>
+        <v>184.9</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
@@ -9450,7 +9456,7 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.404809,69.391277</t>
+          <t>https://www.google.com/maps?q=41.168041,69.150934</t>
         </is>
       </c>
     </row>
@@ -9461,25 +9467,25 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C98" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>41.168041</v>
+        <v>41.266003</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>69.15093400000001</v>
+        <v>69.572754</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>41.168041, 69.150934</t>
+          <t>41.266003, 69.572754</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Багзар</t>
+          <t>Навбахор</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -9488,18 +9494,18 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J98" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Паркентский район</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1409</v>
+        <v>3713</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
@@ -9517,13 +9523,13 @@
         <v>5</v>
       </c>
       <c r="R98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>2842</v>
+        <v>0</v>
       </c>
       <c r="T98" t="n">
-        <v>184.9</v>
+        <v>94.3</v>
       </c>
       <c r="U98" t="n">
         <v>0</v>
@@ -9541,7 +9547,7 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.168041,69.150934</t>
+          <t>https://www.google.com/maps?q=41.266003,69.572754</t>
         </is>
       </c>
     </row>
@@ -9552,25 +9558,25 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C99" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>41.266003</v>
+        <v>41.4457</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>69.572754</v>
+        <v>69.400503</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>41.266003, 69.572754</t>
+          <t>41.445700, 69.400503</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Навбахор</t>
+          <t>Бирлик</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -9579,18 +9585,18 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J99" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Паркентский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3713</v>
+        <v>1876</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
@@ -9614,7 +9620,7 @@
         <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>94.3</v>
+        <v>213.9</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
@@ -9632,7 +9638,7 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.266003,69.572754</t>
+          <t>https://www.google.com/maps?q=41.445700,69.400503</t>
         </is>
       </c>
     </row>
@@ -9643,25 +9649,25 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C100" t="n">
         <v>64</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>41.4457</v>
+        <v>41.463034</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>69.400503</v>
+        <v>69.476435</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>41.445700, 69.400503</t>
+          <t>41.463034, 69.476435</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Бирлик</t>
+          <t>Майский</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -9670,10 +9676,10 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J100" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -9681,7 +9687,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1876</v>
+        <v>1883</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
@@ -9708,9 +9714,11 @@
         <v>213.9</v>
       </c>
       <c r="U100" t="n">
-        <v>0</v>
-      </c>
-      <c r="V100" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V100" t="n">
+        <v>2000</v>
+      </c>
       <c r="W100" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -9723,7 +9731,7 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.445700,69.400503</t>
+          <t>https://www.google.com/maps?q=41.463034,69.476435</t>
         </is>
       </c>
     </row>
@@ -9734,25 +9742,25 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C101" t="n">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>41.463034</v>
+        <v>41.173507</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>69.476435</v>
+        <v>69.131349</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>41.463034, 69.476435</t>
+          <t>41.173507, 69.131349</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Майский</t>
+          <t>Ханкурган</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -9761,18 +9769,18 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J101" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1883</v>
+        <v>2231</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
@@ -9790,20 +9798,18 @@
         <v>5</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S101" t="n">
-        <v>0</v>
+        <v>2842</v>
       </c>
       <c r="T101" t="n">
-        <v>213.9</v>
+        <v>184.9</v>
       </c>
       <c r="U101" t="n">
-        <v>1</v>
-      </c>
-      <c r="V101" t="n">
-        <v>2000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V101" t="inlineStr"/>
       <c r="W101" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -9816,7 +9822,7 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.463034,69.476435</t>
+          <t>https://www.google.com/maps?q=41.173507,69.131349</t>
         </is>
       </c>
     </row>
@@ -9827,45 +9833,45 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C102" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>41.173507</v>
+        <v>41.445091</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>69.131349</v>
+        <v>69.249785</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>41.173507, 69.131349</t>
+          <t>41.445091, 69.249785</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ханкурган</t>
+          <t>Чувалачи</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J102" t="n">
         <v>5.3</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2231</v>
+        <v>2773</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
@@ -9883,13 +9889,13 @@
         <v>5</v>
       </c>
       <c r="R102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>2842</v>
+        <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>184.9</v>
+        <v>270.6</v>
       </c>
       <c r="U102" t="n">
         <v>0</v>
@@ -9907,7 +9913,7 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.173507,69.131349</t>
+          <t>https://www.google.com/maps?q=41.445091,69.249785</t>
         </is>
       </c>
     </row>
@@ -9918,34 +9924,34 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C103" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>41.445091</v>
+        <v>41.445517</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>69.249785</v>
+        <v>69.226005</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>41.445091, 69.249785</t>
+          <t>41.445517, 69.226005</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Чувалачи</t>
+          <t>Алишер Навои</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J103" t="n">
         <v>5.3</v>
@@ -9956,7 +9962,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2773</v>
+        <v>2065</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
@@ -9974,10 +9980,10 @@
         <v>5</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S103" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="T103" t="n">
         <v>270.6</v>
@@ -9998,7 +10004,7 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.445091,69.249785</t>
+          <t>https://www.google.com/maps?q=41.445517,69.226005</t>
         </is>
       </c>
     </row>
@@ -10009,25 +10015,25 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C104" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>41.445517</v>
+        <v>41.431739</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>69.226005</v>
+        <v>69.324724</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>41.445517, 69.226005</t>
+          <t>41.431739, 69.324724</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Алишер Навои</t>
+          <t>Кашкарлик</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -10036,7 +10042,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>5.3</v>
@@ -10047,13 +10053,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2065</v>
+        <v>2008</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -10065,10 +10071,10 @@
         <v>5</v>
       </c>
       <c r="R104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S104" t="n">
-        <v>187</v>
+        <v>2507</v>
       </c>
       <c r="T104" t="n">
         <v>270.6</v>
@@ -10084,12 +10090,12 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.445517,69.226005</t>
+          <t>https://www.google.com/maps?q=41.431739,69.324724</t>
         </is>
       </c>
     </row>
@@ -10103,7 +10109,7 @@
         <v>9</v>
       </c>
       <c r="C105" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D105" s="2" t="n">
         <v>41.437457</v>
@@ -10191,7 +10197,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C106" t="n">
         <v>73</v>
@@ -10646,10 +10652,10 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C111" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D111" s="2" t="n">
         <v>41.426559</v>
@@ -10921,7 +10927,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C114" t="n">
         <v>69</v>
@@ -11012,7 +11018,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C115" t="n">
         <v>63</v>
@@ -11288,7 +11294,7 @@
         <v>25</v>
       </c>
       <c r="C118" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D118" s="2" t="n">
         <v>41.514832</v>
@@ -11376,7 +11382,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C119" t="n">
         <v>63</v>
@@ -11558,7 +11564,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C121" t="n">
         <v>70</v>
@@ -11834,7 +11840,7 @@
         <v>5</v>
       </c>
       <c r="C124" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D124" s="2" t="n">
         <v>41.613627</v>
@@ -12016,7 +12022,7 @@
         <v>17</v>
       </c>
       <c r="C126" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D126" s="2" t="n">
         <v>41.604632</v>
@@ -12471,7 +12477,7 @@
         <v>31</v>
       </c>
       <c r="C131" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D131" s="2" t="n">
         <v>40.947575</v>
@@ -12559,10 +12565,10 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C132" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D132" s="2" t="n">
         <v>41.007896</v>
@@ -12653,7 +12659,7 @@
         <v>51</v>
       </c>
       <c r="C133" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D133" s="2" t="n">
         <v>40.850739</v>
@@ -12741,7 +12747,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C134" t="n">
         <v>28</v>
@@ -13017,7 +13023,7 @@
         <v>55</v>
       </c>
       <c r="C137" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D137" s="2" t="n">
         <v>40.897682</v>
@@ -13287,7 +13293,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C140" t="n">
         <v>28</v>
@@ -13469,7 +13475,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C142" t="n">
         <v>28</v>
@@ -13560,7 +13566,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C143" t="n">
         <v>52</v>
@@ -13653,7 +13659,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C144" t="n">
         <v>28</v>
@@ -14017,10 +14023,10 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C148" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D148" s="2" t="n">
         <v>40.838298</v>
@@ -14111,7 +14117,7 @@
         <v>40</v>
       </c>
       <c r="C149" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D149" s="2" t="n">
         <v>40.974689</v>
@@ -14202,7 +14208,7 @@
         <v>12</v>
       </c>
       <c r="C150" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D150" s="2" t="n">
         <v>41.601553</v>
@@ -14384,7 +14390,7 @@
         <v>41</v>
       </c>
       <c r="C152" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D152" s="2" t="n">
         <v>40.861957</v>
@@ -14657,7 +14663,7 @@
         <v>38</v>
       </c>
       <c r="C155" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D155" s="2" t="n">
         <v>40.985851</v>
@@ -14745,7 +14751,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C156" t="n">
         <v>28</v>
@@ -15021,7 +15027,7 @@
         <v>6</v>
       </c>
       <c r="C159" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D159" s="2" t="n">
         <v>40.951358</v>
@@ -15200,7 +15206,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C161" t="n">
         <v>40</v>
@@ -15660,7 +15666,7 @@
         <v>25</v>
       </c>
       <c r="C166" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D166" s="2" t="n">
         <v>40.771428</v>
@@ -15842,7 +15848,7 @@
         <v>39</v>
       </c>
       <c r="C168" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D168" s="2" t="n">
         <v>40.937372</v>
@@ -16112,7 +16118,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C171" t="n">
         <v>55</v>
@@ -16385,10 +16391,10 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C174" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D174" s="2" t="n">
         <v>40.947577</v>
@@ -16476,7 +16482,7 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C175" t="n">
         <v>36</v>
@@ -16570,7 +16576,7 @@
         <v>18</v>
       </c>
       <c r="C176" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D176" s="2" t="n">
         <v>41.022127</v>
@@ -16658,7 +16664,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C177" t="n">
         <v>52</v>
@@ -16749,7 +16755,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C178" t="n">
         <v>55</v>
@@ -16843,7 +16849,7 @@
         <v>54</v>
       </c>
       <c r="C179" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D179" s="2" t="n">
         <v>40.644161</v>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -753,7 +753,7 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V3" t="n">
         <v>900</v>
@@ -846,7 +846,7 @@
         <v>48.5</v>
       </c>
       <c r="U4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V4" t="n">
         <v>2500</v>
@@ -939,7 +939,7 @@
         <v>48.5</v>
       </c>
       <c r="U5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V5" t="n">
         <v>918</v>
@@ -1063,7 +1063,7 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>41.367635</v>
@@ -1218,7 +1218,7 @@
         <v>98.2</v>
       </c>
       <c r="U8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="V8" t="n">
         <v>600</v>
@@ -1311,7 +1311,7 @@
         <v>31.8</v>
       </c>
       <c r="U9" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="V9" t="n">
         <v>350</v>
@@ -1404,7 +1404,7 @@
         <v>98.2</v>
       </c>
       <c r="U10" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V10" t="n">
         <v>500</v>
@@ -1438,19 +1438,19 @@
         <v>86</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>41.365403</v>
+        <v>41.31234</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>69.393992</v>
+        <v>69.30525900000001</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>41.365403, 69.393992</t>
+          <t>41.312340, 69.305259</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ТТЗ-4</t>
+          <t>Машинасозлар (Ташсельмаш)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1459,30 +1459,30 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>13404</v>
+        <v>7574</v>
       </c>
       <c r="M11" t="n">
         <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="O11" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="Q11" t="n">
         <v>0.5</v>
@@ -1491,16 +1491,16 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>1200</v>
+        <v>220</v>
       </c>
       <c r="T11" t="n">
-        <v>213.9</v>
+        <v>141</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="V11" t="n">
-        <v>1400</v>
+        <v>600</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.365403,69.393992</t>
+          <t>https://www.google.com/maps?q=41.312340,69.305259</t>
         </is>
       </c>
     </row>
@@ -1531,19 +1531,19 @@
         <v>86</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>41.308774</v>
+        <v>41.365403</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>69.31306499999999</v>
+        <v>69.393992</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>41.308774, 69.313065</t>
+          <t>41.365403, 69.393992</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Машинасозлар (Ташсельмаш)</t>
+          <t>ТТЗ-4</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1552,30 +1552,30 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6677</v>
+        <v>13404</v>
       </c>
       <c r="M12" t="n">
         <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="O12" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="Q12" t="n">
         <v>0.5</v>
@@ -1584,16 +1584,16 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>446</v>
+        <v>1200</v>
       </c>
       <c r="T12" t="n">
-        <v>141</v>
+        <v>213.9</v>
       </c>
       <c r="U12" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="V12" t="n">
-        <v>600</v>
+        <v>1400</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.308774,69.313065</t>
+          <t>https://www.google.com/maps?q=41.365403,69.393992</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
         <v>139.7</v>
       </c>
       <c r="U15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V15" t="n">
         <v>350</v>
@@ -2179,22 +2179,22 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>41.370618</v>
+        <v>41.296436</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>69.29909600000001</v>
+        <v>69.332471</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>41.370618, 69.299096</t>
+          <t>41.296436, 69.332471</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Юнусабад 13-й квартал</t>
+          <t>Куксарай махалля</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2203,48 +2203,48 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>22705</v>
+        <v>4067</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N19" t="n">
+        <v>25</v>
+      </c>
+      <c r="O19" t="n">
+        <v>14</v>
+      </c>
+      <c r="P19" t="n">
         <v>33</v>
-      </c>
-      <c r="O19" t="n">
-        <v>13</v>
-      </c>
-      <c r="P19" t="n">
-        <v>31</v>
       </c>
       <c r="Q19" t="n">
         <v>0.5</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>488</v>
       </c>
       <c r="T19" t="n">
-        <v>139.7</v>
+        <v>141</v>
       </c>
       <c r="U19" t="n">
         <v>25</v>
       </c>
       <c r="V19" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.370618,69.299096</t>
+          <t>https://www.google.com/maps?q=41.296436,69.332471</t>
         </is>
       </c>
     </row>
@@ -2272,22 +2272,22 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>41.291531</v>
+        <v>41.370618</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>69.320454</v>
+        <v>69.29909600000001</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>41.291531, 69.320454</t>
+          <t>41.370618, 69.299096</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ширинабад махалля</t>
+          <t>Юнусабад 13-й квартал</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2296,48 +2296,48 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>5303</v>
+        <v>22705</v>
       </c>
       <c r="M20" t="n">
         <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="O20" t="n">
         <v>13</v>
       </c>
       <c r="P20" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="Q20" t="n">
         <v>0.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>141</v>
+        <v>139.7</v>
       </c>
       <c r="U20" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="V20" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.291531,69.320454</t>
+          <t>https://www.google.com/maps?q=41.370618,69.299096</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>59.2</v>
       </c>
       <c r="U24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V24" t="n">
         <v>200</v>
@@ -2985,10 +2985,10 @@
         <v>98.2</v>
       </c>
       <c r="U27" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V27" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>41.346824</v>
@@ -3202,7 +3202,7 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>41.343858</v>
@@ -3264,7 +3264,7 @@
         <v>98.2</v>
       </c>
       <c r="U30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V30" t="n">
         <v>10</v>
@@ -3295,7 +3295,7 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>41.381315</v>
@@ -3388,7 +3388,7 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>41.276071</v>
@@ -3729,10 +3729,10 @@
         <v>139.7</v>
       </c>
       <c r="U35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V35" t="n">
-        <v>16500</v>
+        <v>500</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>41.346337</v>
@@ -3915,7 +3915,7 @@
         <v>28.3</v>
       </c>
       <c r="U37" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V37" t="n">
         <v>350</v>
@@ -3946,7 +3946,7 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>41.283644</v>
@@ -4008,7 +4008,7 @@
         <v>48.5</v>
       </c>
       <c r="U38" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="V38" t="n">
         <v>1300</v>
@@ -4194,7 +4194,7 @@
         <v>31.8</v>
       </c>
       <c r="U40" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="V40" t="n">
         <v>350</v>
@@ -4225,7 +4225,7 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>41.366713</v>
@@ -4380,10 +4380,10 @@
         <v>139.7</v>
       </c>
       <c r="U42" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V42" t="n">
-        <v>3500</v>
+        <v>500</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -4502,54 +4502,54 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>41.261799</v>
+        <v>41.217956</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>69.35513400000001</v>
+        <v>69.322171</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>41.261799, 69.355134</t>
+          <t>41.217956, 69.322171</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Янгикурган махалля</t>
+          <t>Кипчак</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1603</v>
+        <v>2115</v>
       </c>
       <c r="M44" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N44" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="O44" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P44" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q44" t="n">
         <v>0.5</v>
@@ -4561,14 +4561,12 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>141</v>
+        <v>60.2</v>
       </c>
       <c r="U44" t="n">
-        <v>3</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1270</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4581,7 +4579,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.261799,69.355134</t>
+          <t>https://www.google.com/maps?q=41.217956,69.322171</t>
         </is>
       </c>
     </row>
@@ -4595,22 +4593,22 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>41.187154</v>
+        <v>41.261799</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>69.230422</v>
+        <v>69.35513400000001</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>41.187154, 69.230422</t>
+          <t>41.261799, 69.355134</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Чартак махалля</t>
+          <t>Янгикурган махалля</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4619,30 +4617,30 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1947</v>
+        <v>1603</v>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N45" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="O45" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P45" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="Q45" t="n">
         <v>0.5</v>
@@ -4654,13 +4652,13 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>122.7</v>
+        <v>141</v>
       </c>
       <c r="U45" t="n">
         <v>3</v>
       </c>
       <c r="V45" t="n">
-        <v>200</v>
+        <v>1270</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -4674,7 +4672,7 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.187154,69.230422</t>
+          <t>https://www.google.com/maps?q=41.261799,69.355134</t>
         </is>
       </c>
     </row>
@@ -4691,19 +4689,19 @@
         <v>61</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>41.244099</v>
+        <v>41.187154</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>69.386206</v>
+        <v>69.230422</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>41.244099, 69.386206</t>
+          <t>41.187154, 69.230422</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Мажнунтол махалля</t>
+          <t>Чартак махалля</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4712,30 +4710,30 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2672</v>
+        <v>1947</v>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N46" t="n">
+        <v>5</v>
+      </c>
+      <c r="O46" t="n">
         <v>4</v>
       </c>
-      <c r="O46" t="n">
-        <v>2</v>
-      </c>
       <c r="P46" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q46" t="n">
         <v>0.5</v>
@@ -4747,12 +4745,14 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>60.2</v>
+        <v>122.7</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="V46" t="n">
+        <v>200</v>
+      </c>
       <c r="W46" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.244099,69.386206</t>
+          <t>https://www.google.com/maps?q=41.187154,69.230422</t>
         </is>
       </c>
     </row>
@@ -4779,27 +4779,27 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>41.174834</v>
+        <v>41.244099</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>69.249804</v>
+        <v>69.386206</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>41.174834, 69.249804</t>
+          <t>41.244099, 69.386206</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Бинокор</t>
+          <t>Мажнунтол махалля</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -4810,23 +4810,23 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2032</v>
+        <v>2672</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q47" t="n">
         <v>0.5</v>
@@ -4838,10 +4838,10 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>122.7</v>
+        <v>60.2</v>
       </c>
       <c r="U47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
@@ -4851,12 +4851,12 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.174834,69.249804</t>
+          <t>https://www.google.com/maps?q=41.244099,69.386206</t>
         </is>
       </c>
     </row>
@@ -4870,54 +4870,54 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>41.236831</v>
+        <v>41.174834</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>69.318793</v>
+        <v>69.249804</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>41.236831, 69.318793</t>
+          <t>41.174834, 69.249804</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Эшанбулак махалля</t>
+          <t>Бинокор</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1806</v>
+        <v>2032</v>
       </c>
       <c r="M48" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0.5</v>
@@ -4929,14 +4929,12 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>60.2</v>
+        <v>122.7</v>
       </c>
       <c r="U48" t="n">
-        <v>1</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1950</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4944,12 +4942,12 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.236831,69.318793</t>
+          <t>https://www.google.com/maps?q=41.174834,69.249804</t>
         </is>
       </c>
     </row>
@@ -4963,31 +4961,31 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>41.217508</v>
+        <v>41.236831</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>69.345862</v>
+        <v>69.318793</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>41.217508, 69.345862</t>
+          <t>41.236831, 69.318793</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Забардаст</t>
+          <t>Эшанбулак махалля</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4998,19 +4996,19 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1799</v>
+        <v>1806</v>
       </c>
       <c r="M49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N49" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P49" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="Q49" t="n">
         <v>0.5</v>
@@ -5025,10 +5023,10 @@
         <v>60.2</v>
       </c>
       <c r="U49" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V49" t="n">
-        <v>100</v>
+        <v>1950</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -5042,7 +5040,7 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.217508,69.345862</t>
+          <t>https://www.google.com/maps?q=41.236831,69.318793</t>
         </is>
       </c>
     </row>
@@ -5056,22 +5054,22 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>41.171844</v>
+        <v>41.217508</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>69.226033</v>
+        <v>69.345862</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>41.171844, 69.226033</t>
+          <t>41.217508, 69.345862</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Чартак</t>
+          <t>Забардаст</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5080,30 +5078,30 @@
         </is>
       </c>
       <c r="I50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Бектемирский район</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>1799</v>
+      </c>
+      <c r="M50" t="n">
+        <v>6</v>
+      </c>
+      <c r="N50" t="n">
+        <v>11</v>
+      </c>
+      <c r="O50" t="n">
         <v>1</v>
       </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Янгихаётский район</t>
-        </is>
-      </c>
-      <c r="L50" t="n">
-        <v>1842</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q50" t="n">
         <v>0.5</v>
@@ -5115,13 +5113,13 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>122.7</v>
+        <v>60.2</v>
       </c>
       <c r="U50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V50" t="n">
-        <v>4000</v>
+        <v>100</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -5130,12 +5128,12 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.171844,69.226033</t>
+          <t>https://www.google.com/maps?q=41.217508,69.345862</t>
         </is>
       </c>
     </row>
@@ -5149,31 +5147,31 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>41.197122</v>
+        <v>41.171844</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>69.246505</v>
+        <v>69.226033</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>41.197122, 69.246505</t>
+          <t>41.171844, 69.226033</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Янги Кипчак махалля</t>
+          <t>Чартак</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5184,19 +5182,19 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1526</v>
+        <v>1842</v>
       </c>
       <c r="M51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0.5</v>
@@ -5211,10 +5209,10 @@
         <v>122.7</v>
       </c>
       <c r="U51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V51" t="n">
-        <v>200</v>
+        <v>4000</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -5223,12 +5221,12 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.197122,69.246505</t>
+          <t>https://www.google.com/maps?q=41.171844,69.226033</t>
         </is>
       </c>
     </row>
@@ -5242,54 +5240,54 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>41.229152</v>
+        <v>41.197122</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>69.17632</v>
+        <v>69.246505</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>41.229152, 69.176320</t>
+          <t>41.197122, 69.246505</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Эркин</t>
+          <t>Янги Кипчак махалля</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1935</v>
+        <v>1526</v>
       </c>
       <c r="M52" t="n">
+        <v>3</v>
+      </c>
+      <c r="N52" t="n">
         <v>7</v>
       </c>
-      <c r="N52" t="n">
-        <v>8</v>
-      </c>
       <c r="O52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P52" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q52" t="n">
         <v>0.5</v>
@@ -5301,13 +5299,13 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>28.3</v>
+        <v>122.7</v>
       </c>
       <c r="U52" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V52" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -5321,7 +5319,7 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.229152,69.176320</t>
+          <t>https://www.google.com/maps?q=41.197122,69.246505</t>
         </is>
       </c>
     </row>
@@ -5335,54 +5333,54 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>41.21498</v>
+        <v>41.229152</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>69.298378</v>
+        <v>69.17632</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>41.214980, 69.298378</t>
+          <t>41.229152, 69.176320</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Автомобилчи гузар</t>
+          <t>Эркин</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1713</v>
+        <v>1935</v>
       </c>
       <c r="M53" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N53" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P53" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Q53" t="n">
         <v>0.5</v>
@@ -5394,12 +5392,14 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>60.2</v>
+        <v>28.3</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="V53" t="n">
+        <v>350</v>
+      </c>
       <c r="W53" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.214980,69.298378</t>
+          <t>https://www.google.com/maps?q=41.229152,69.176320</t>
         </is>
       </c>
     </row>
@@ -5426,22 +5426,22 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>41.314971</v>
+        <v>41.21498</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>69.435928</v>
+        <v>69.298378</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>41.314971, 69.435928</t>
+          <t>41.214980, 69.298378</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Жарбаши</t>
+          <t>Автомобилчи гузар</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5450,30 +5450,30 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1459</v>
+        <v>1713</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
         <v>0.5</v>
@@ -5485,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>141</v>
+        <v>60.2</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -5498,12 +5498,12 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.314971,69.435928</t>
+          <t>https://www.google.com/maps?q=41.214980,69.298378</t>
         </is>
       </c>
     </row>
@@ -5517,54 +5517,54 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>41.214537</v>
+        <v>41.298183</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>69.322068</v>
+        <v>69.237584</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>41.214537, 69.322068</t>
+          <t>41.298183, 69.237584</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Кипчак</t>
+          <t>Чарх Камалан-1 махалля</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1338</v>
+        <v>1408</v>
       </c>
       <c r="M55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N55" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P55" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="Q55" t="n">
         <v>0.5</v>
@@ -5576,13 +5576,13 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>60.2</v>
+        <v>28.3</v>
       </c>
       <c r="U55" t="n">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="V55" t="n">
-        <v>100</v>
+        <v>550</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.214537,69.322068</t>
+          <t>https://www.google.com/maps?q=41.298183,69.237584</t>
         </is>
       </c>
     </row>
@@ -5610,22 +5610,22 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>41.227311</v>
+        <v>41.314971</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>69.369872</v>
+        <v>69.435928</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>41.227311, 69.369872</t>
+          <t>41.314971, 69.435928</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Йик-Ата</t>
+          <t>Жарбаши</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5634,30 +5634,30 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1354</v>
+        <v>1459</v>
       </c>
       <c r="M56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
         <v>0.5</v>
@@ -5669,7 +5669,7 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>60.2</v>
+        <v>141</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -5682,12 +5682,12 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.227311,69.369872</t>
+          <t>https://www.google.com/maps?q=41.314971,69.435928</t>
         </is>
       </c>
     </row>
@@ -5701,54 +5701,54 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>41.308443</v>
+        <v>41.383812</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>69.419889</v>
+        <v>69.232148</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>41.308443, 69.419889</t>
+          <t>41.383812, 69.232148</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ташисти</t>
+          <t>Ахил махалля</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1384</v>
+        <v>1495</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N57" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q57" t="n">
         <v>0.5</v>
@@ -5760,12 +5760,14 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>141</v>
+        <v>59.2</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="V57" t="n">
+        <v>500</v>
+      </c>
       <c r="W57" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5778,7 +5780,7 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.308443,69.419889</t>
+          <t>https://www.google.com/maps?q=41.383812,69.232148</t>
         </is>
       </c>
     </row>
@@ -5792,54 +5794,54 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>41.269353</v>
+        <v>41.227311</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>69.12605000000001</v>
+        <v>69.369872</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>41.269353, 69.126050</t>
+          <t>41.227311, 69.369872</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Дамачи</t>
+          <t>Йик-Ата</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>850</v>
+        <v>1354</v>
       </c>
       <c r="M58" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N58" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O58" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P58" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Q58" t="n">
         <v>0.5</v>
@@ -5851,14 +5853,12 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>47.6</v>
+        <v>60.2</v>
       </c>
       <c r="U58" t="n">
-        <v>3</v>
-      </c>
-      <c r="V58" t="n">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.269353,69.126050</t>
+          <t>https://www.google.com/maps?q=41.227311,69.369872</t>
         </is>
       </c>
     </row>
@@ -5885,71 +5885,73 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>41.189999</v>
+        <v>41.205769</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>69.262092</v>
+        <v>69.333651</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>41.189999, 69.262092</t>
+          <t>41.205769, 69.333651</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Дарьябуйи махалля</t>
+          <t>Бектемир</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>850</v>
+        <v>624</v>
       </c>
       <c r="M59" t="n">
         <v>1</v>
       </c>
       <c r="N59" t="n">
+        <v>7</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
         <v>2</v>
-      </c>
-      <c r="O59" t="n">
-        <v>2</v>
-      </c>
-      <c r="P59" t="n">
-        <v>1</v>
       </c>
       <c r="Q59" t="n">
         <v>0.5</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="T59" t="n">
-        <v>122.7</v>
+        <v>60.2</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="V59" t="n">
+        <v>100</v>
+      </c>
       <c r="W59" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5962,7 +5964,7 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.189999,69.262092</t>
+          <t>https://www.google.com/maps?q=41.205769,69.333651</t>
         </is>
       </c>
     </row>
@@ -5976,22 +5978,22 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>41.180799</v>
+        <v>41.308443</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>69.297354</v>
+        <v>69.419889</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>41.180799, 69.297354</t>
+          <t>41.308443, 69.419889</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Кокандаул</t>
+          <t>Ташисти</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6000,27 +6002,27 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>991</v>
+        <v>1384</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
@@ -6035,14 +6037,12 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>122.7</v>
+        <v>141</v>
       </c>
       <c r="U60" t="n">
-        <v>1</v>
-      </c>
-      <c r="V60" t="n">
-        <v>500</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6050,12 +6050,12 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.180799,69.297354</t>
+          <t>https://www.google.com/maps?q=41.308443,69.419889</t>
         </is>
       </c>
     </row>
@@ -6069,54 +6069,54 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>41.333386</v>
+        <v>41.269353</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>69.456318</v>
+        <v>69.12605000000001</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>41.333386, 69.456318</t>
+          <t>41.269353, 69.126050</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Чингельды</t>
+          <t>Дамачи</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1092</v>
+        <v>850</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P61" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Q61" t="n">
         <v>0.5</v>
@@ -6128,12 +6128,14 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>141</v>
+        <v>47.6</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="V61" t="n">
+        <v>2</v>
+      </c>
       <c r="W61" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6146,7 +6148,7 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.333386,69.456318</t>
+          <t>https://www.google.com/maps?q=41.269353,69.126050</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6162,7 @@
         <v>52</v>
       </c>
       <c r="C62" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D62" s="2" t="n">
         <v>41.168426</v>
@@ -6315,7 +6317,7 @@
         <v>213.9</v>
       </c>
       <c r="U63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V63" t="n">
         <v>1000</v>
@@ -6343,7 +6345,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C64" t="n">
         <v>81</v>
@@ -6436,51 +6438,51 @@
         </is>
       </c>
       <c r="B65" t="n">
+        <v>4</v>
+      </c>
+      <c r="C65" t="n">
+        <v>86</v>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>41.382072</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>69.32717100000001</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>41.382072, 69.327171</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Тутзар</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>село</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Ташкентский район</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>3068</v>
+      </c>
+      <c r="M65" t="n">
         <v>5</v>
       </c>
-      <c r="C65" t="n">
-        <v>84</v>
-      </c>
-      <c r="D65" s="2" t="n">
-        <v>41.387795</v>
-      </c>
-      <c r="E65" s="2" t="n">
-        <v>69.200571</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>41.387795, 69.200571</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Айрикуйлак</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>село</t>
-        </is>
-      </c>
-      <c r="I65" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Ташкентский район</t>
-        </is>
-      </c>
-      <c r="L65" t="n">
-        <v>4778</v>
-      </c>
-      <c r="M65" t="n">
-        <v>3</v>
-      </c>
       <c r="N65" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O65" t="n">
         <v>4</v>
@@ -6492,19 +6494,19 @@
         <v>5</v>
       </c>
       <c r="R65" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="S65" t="n">
-        <v>2236</v>
+        <v>20792</v>
       </c>
       <c r="T65" t="n">
         <v>270.6</v>
       </c>
       <c r="U65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V65" t="n">
-        <v>840</v>
+        <v>300</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -6518,7 +6520,7 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.387795,69.200571</t>
+          <t>https://www.google.com/maps?q=41.382072,69.327171</t>
         </is>
       </c>
     </row>
@@ -6529,25 +6531,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C66" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>41.361522</v>
+        <v>41.387795</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>69.417632</v>
+        <v>69.200571</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>41.361522, 69.417632</t>
+          <t>41.387795, 69.200571</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Дурмень</t>
+          <t>Айрикуйлак</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6556,30 +6558,30 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J66" t="n">
         <v>0.9</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1892</v>
+        <v>4778</v>
       </c>
       <c r="M66" t="n">
         <v>3</v>
       </c>
       <c r="N66" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P66" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q66" t="n">
         <v>5</v>
@@ -6588,16 +6590,16 @@
         <v>6</v>
       </c>
       <c r="S66" t="n">
-        <v>3237</v>
+        <v>2236</v>
       </c>
       <c r="T66" t="n">
-        <v>213.9</v>
+        <v>270.6</v>
       </c>
       <c r="U66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V66" t="n">
-        <v>600</v>
+        <v>840</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
@@ -6611,7 +6613,7 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.361522,69.417632</t>
+          <t>https://www.google.com/maps?q=41.387795,69.200571</t>
         </is>
       </c>
     </row>
@@ -6622,25 +6624,25 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="C67" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>41.405686</v>
+        <v>41.361522</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>69.252595</v>
+        <v>69.417632</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>41.405686, 69.252595</t>
+          <t>41.361522, 69.417632</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Хасанбай</t>
+          <t>Дурмень</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6649,48 +6651,48 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0.9</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2341</v>
+        <v>1892</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q67" t="n">
         <v>5</v>
       </c>
       <c r="R67" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S67" t="n">
-        <v>7207</v>
+        <v>3237</v>
       </c>
       <c r="T67" t="n">
-        <v>270.6</v>
+        <v>213.9</v>
       </c>
       <c r="U67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V67" t="n">
-        <v>3500</v>
+        <v>600</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
@@ -6704,7 +6706,7 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.405686,69.252595</t>
+          <t>https://www.google.com/maps?q=41.361522,69.417632</t>
         </is>
       </c>
     </row>
@@ -6715,25 +6717,25 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="C68" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>41.324284</v>
+        <v>41.405686</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>69.483728</v>
+        <v>69.252595</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>41.324284, 69.483728</t>
+          <t>41.405686, 69.252595</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Китай-Тепа</t>
+          <t>Хасанбай</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6742,24 +6744,24 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Юкоричирчикский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1851</v>
+        <v>2341</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -6771,18 +6773,20 @@
         <v>5</v>
       </c>
       <c r="R68" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S68" t="n">
-        <v>1673</v>
+        <v>7207</v>
       </c>
       <c r="T68" t="n">
-        <v>151.7</v>
+        <v>270.6</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="V68" t="n">
+        <v>500</v>
+      </c>
       <c r="W68" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6790,12 +6794,12 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.324284,69.483728</t>
+          <t>https://www.google.com/maps?q=41.405686,69.252595</t>
         </is>
       </c>
     </row>
@@ -6806,76 +6810,74 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C69" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>41.402834</v>
+        <v>41.324284</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>69.220811</v>
+        <v>69.483728</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>41.402834, 69.220811</t>
+          <t>41.324284, 69.483728</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Абдурахманов</t>
+          <t>Китай-Тепа</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J69" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Юкоричирчикский район</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2527</v>
+        <v>1851</v>
       </c>
       <c r="M69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>5</v>
       </c>
       <c r="R69" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S69" t="n">
-        <v>2480</v>
+        <v>1673</v>
       </c>
       <c r="T69" t="n">
-        <v>270.6</v>
+        <v>151.7</v>
       </c>
       <c r="U69" t="n">
-        <v>4</v>
-      </c>
-      <c r="V69" t="n">
-        <v>840</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6883,12 +6885,12 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.402834,69.220811</t>
+          <t>https://www.google.com/maps?q=41.324284,69.483728</t>
         </is>
       </c>
     </row>
@@ -6899,25 +6901,25 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C70" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>41.401834</v>
+        <v>41.402834</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>69.276258</v>
+        <v>69.220811</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>41.401834, 69.276258</t>
+          <t>41.402834, 69.220811</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Дустамабад</t>
+          <t>Абдурахманов</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6926,7 +6928,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>1.2</v>
@@ -6937,37 +6939,37 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2226</v>
+        <v>2527</v>
       </c>
       <c r="M70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O70" t="n">
         <v>1</v>
       </c>
       <c r="P70" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q70" t="n">
         <v>5</v>
       </c>
       <c r="R70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="S70" t="n">
-        <v>12149</v>
+        <v>2480</v>
       </c>
       <c r="T70" t="n">
         <v>270.6</v>
       </c>
       <c r="U70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V70" t="n">
-        <v>6000</v>
+        <v>840</v>
       </c>
       <c r="W70" t="inlineStr">
         <is>
@@ -6981,7 +6983,7 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.401834,69.276258</t>
+          <t>https://www.google.com/maps?q=41.402834,69.220811</t>
         </is>
       </c>
     </row>
@@ -6992,74 +6994,76 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C71" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>41.416088</v>
+        <v>41.401834</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>69.427311</v>
+        <v>69.276258</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>41.416088, 69.427311</t>
+          <t>41.401834, 69.276258</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Чинабад</t>
+          <t>Дустамабад</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>1.2</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2829</v>
+        <v>2226</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q71" t="n">
         <v>5</v>
       </c>
       <c r="R71" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="S71" t="n">
-        <v>439</v>
+        <v>12149</v>
       </c>
       <c r="T71" t="n">
-        <v>213.9</v>
+        <v>270.6</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
-      </c>
-      <c r="V71" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="V71" t="n">
+        <v>6000</v>
+      </c>
       <c r="W71" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7072,7 +7076,7 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.416088,69.427311</t>
+          <t>https://www.google.com/maps?q=41.401834,69.276258</t>
         </is>
       </c>
     </row>
@@ -7083,25 +7087,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="C72" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>41.276459</v>
+        <v>41.416088</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>69.110428</v>
+        <v>69.427311</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>41.276459, 69.110428</t>
+          <t>41.416088, 69.427311</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Мевазар</t>
+          <t>Чинабад</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7110,42 +7114,42 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J72" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2345</v>
+        <v>2829</v>
       </c>
       <c r="M72" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
         <v>5</v>
       </c>
       <c r="R72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S72" t="n">
-        <v>4564</v>
+        <v>439</v>
       </c>
       <c r="T72" t="n">
-        <v>184.9</v>
+        <v>213.9</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
@@ -7163,7 +7167,7 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.276459,69.110428</t>
+          <t>https://www.google.com/maps?q=41.416088,69.427311</t>
         </is>
       </c>
     </row>
@@ -7174,25 +7178,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C73" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>41.375967</v>
+        <v>41.276459</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>69.37848099999999</v>
+        <v>69.110428</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>41.375967, 69.378481</t>
+          <t>41.276459, 69.110428</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ялангач</t>
+          <t>Мевазар</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7201,49 +7205,47 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2081</v>
+        <v>2345</v>
       </c>
       <c r="M73" t="n">
         <v>4</v>
       </c>
       <c r="N73" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q73" t="n">
         <v>5</v>
       </c>
       <c r="R73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S73" t="n">
-        <v>2347</v>
+        <v>4564</v>
       </c>
       <c r="T73" t="n">
-        <v>213.9</v>
+        <v>184.9</v>
       </c>
       <c r="U73" t="n">
-        <v>1</v>
-      </c>
-      <c r="V73" t="n">
-        <v>1400</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V73" t="inlineStr"/>
       <c r="W73" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7256,7 +7258,7 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.375967,69.378481</t>
+          <t>https://www.google.com/maps?q=41.276459,69.110428</t>
         </is>
       </c>
     </row>
@@ -7267,25 +7269,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C74" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>41.214114</v>
+        <v>41.375967</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>69.15615099999999</v>
+        <v>69.37848099999999</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>41.214114, 69.156151</t>
+          <t>41.375967, 69.378481</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Янгибаг</t>
+          <t>Ялангач</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7294,48 +7296,48 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="J74" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1649</v>
+        <v>2081</v>
       </c>
       <c r="M74" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N74" t="n">
+        <v>11</v>
+      </c>
+      <c r="O74" t="n">
+        <v>5</v>
+      </c>
+      <c r="P74" t="n">
         <v>4</v>
-      </c>
-      <c r="O74" t="n">
-        <v>4</v>
-      </c>
-      <c r="P74" t="n">
-        <v>2</v>
       </c>
       <c r="Q74" t="n">
         <v>5</v>
       </c>
       <c r="R74" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="S74" t="n">
-        <v>22255</v>
+        <v>2347</v>
       </c>
       <c r="T74" t="n">
-        <v>184.9</v>
+        <v>213.9</v>
       </c>
       <c r="U74" t="n">
         <v>1</v>
       </c>
       <c r="V74" t="n">
-        <v>700</v>
+        <v>1400</v>
       </c>
       <c r="W74" t="inlineStr">
         <is>
@@ -7349,7 +7351,7 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.214114,69.156151</t>
+          <t>https://www.google.com/maps?q=41.375967,69.378481</t>
         </is>
       </c>
     </row>
@@ -7360,25 +7362,25 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="C75" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>41.380562</v>
+        <v>41.214114</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>69.406357</v>
+        <v>69.15615099999999</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>41.380562, 69.406357</t>
+          <t>41.214114, 69.156151</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Кадырлик</t>
+          <t>Янгибаг</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7387,48 +7389,48 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J75" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1570</v>
+        <v>1649</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N75" t="n">
         <v>4</v>
       </c>
       <c r="O75" t="n">
+        <v>4</v>
+      </c>
+      <c r="P75" t="n">
         <v>2</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
       </c>
       <c r="R75" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="S75" t="n">
-        <v>1901</v>
+        <v>22255</v>
       </c>
       <c r="T75" t="n">
-        <v>213.9</v>
+        <v>184.9</v>
       </c>
       <c r="U75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V75" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="W75" t="inlineStr">
         <is>
@@ -7442,7 +7444,7 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.380562,69.406357</t>
+          <t>https://www.google.com/maps?q=41.214114,69.156151</t>
         </is>
       </c>
     </row>
@@ -7453,7 +7455,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C76" t="n">
         <v>71</v>
@@ -7642,7 +7644,7 @@
         <v>28</v>
       </c>
       <c r="C78" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D78" s="2" t="n">
         <v>41.332538</v>
@@ -7823,7 +7825,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C80" t="n">
         <v>84</v>
@@ -7916,7 +7918,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C81" t="n">
         <v>74</v>
@@ -8007,7 +8009,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C82" t="n">
         <v>69</v>
@@ -8098,7 +8100,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C83" t="n">
         <v>67</v>
@@ -8189,7 +8191,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C84" t="n">
         <v>65</v>
@@ -8282,37 +8284,37 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C85" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>41.380099</v>
+        <v>41.377685</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>69.43011300000001</v>
+        <v>69.46569100000001</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>41.380099, 69.430113</t>
+          <t>41.377685, 69.465691</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Аргин</t>
+          <t>Кибрай</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J85" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -8320,19 +8322,19 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2439</v>
+        <v>3583</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O85" t="n">
         <v>2</v>
       </c>
       <c r="P85" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q85" t="n">
         <v>5</v>
@@ -8341,17 +8343,15 @@
         <v>2</v>
       </c>
       <c r="S85" t="n">
-        <v>1510</v>
+        <v>439</v>
       </c>
       <c r="T85" t="n">
         <v>213.9</v>
       </c>
       <c r="U85" t="n">
-        <v>1</v>
-      </c>
-      <c r="V85" t="n">
-        <v>600</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.380099,69.430113</t>
+          <t>https://www.google.com/maps?q=41.377685,69.465691</t>
         </is>
       </c>
     </row>
@@ -8375,74 +8375,76 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C86" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>41.378499</v>
+        <v>41.380099</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>69.144857</v>
+        <v>69.43011300000001</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>41.378499, 69.144857</t>
+          <t>41.380099, 69.430113</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Илгар</t>
+          <t>Аргин</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J86" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2210</v>
+        <v>2439</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q86" t="n">
         <v>5</v>
       </c>
       <c r="R86" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S86" t="n">
-        <v>2397</v>
+        <v>1510</v>
       </c>
       <c r="T86" t="n">
-        <v>270.6</v>
+        <v>213.9</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
-      </c>
-      <c r="V86" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V86" t="n">
+        <v>600</v>
+      </c>
       <c r="W86" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8455,7 +8457,7 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.378499,69.144857</t>
+          <t>https://www.google.com/maps?q=41.380099,69.430113</t>
         </is>
       </c>
     </row>
@@ -8472,19 +8474,19 @@
         <v>70</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>41.389799</v>
+        <v>41.378499</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>69.370991</v>
+        <v>69.144857</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>41.389799, 69.370991</t>
+          <t>41.378499, 69.144857</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Янгиюль</t>
+          <t>Илгар</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -8493,42 +8495,42 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>3.1</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2589</v>
+        <v>2210</v>
       </c>
       <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>4</v>
+      </c>
+      <c r="O87" t="n">
         <v>1</v>
       </c>
-      <c r="N87" t="n">
-        <v>1</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
       <c r="P87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
         <v>5</v>
       </c>
       <c r="R87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S87" t="n">
-        <v>3023</v>
+        <v>2397</v>
       </c>
       <c r="T87" t="n">
-        <v>213.9</v>
+        <v>270.6</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
@@ -8546,7 +8548,7 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.389799,69.370991</t>
+          <t>https://www.google.com/maps?q=41.378499,69.144857</t>
         </is>
       </c>
     </row>
@@ -8557,45 +8559,45 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C88" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>41.314067</v>
+        <v>41.389799</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>69.111439</v>
+        <v>69.370991</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>41.314067, 69.111439</t>
+          <t>41.389799, 69.370991</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Алимбаба</t>
+          <t>Янгиюль</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J88" t="n">
         <v>3.1</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2154</v>
+        <v>2589</v>
       </c>
       <c r="M88" t="n">
         <v>1</v>
@@ -8604,7 +8606,7 @@
         <v>1</v>
       </c>
       <c r="O88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
         <v>1</v>
@@ -8616,10 +8618,10 @@
         <v>3</v>
       </c>
       <c r="S88" t="n">
-        <v>3868</v>
+        <v>3023</v>
       </c>
       <c r="T88" t="n">
-        <v>184.9</v>
+        <v>213.9</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
@@ -8637,7 +8639,7 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.314067,69.111439</t>
+          <t>https://www.google.com/maps?q=41.389799,69.370991</t>
         </is>
       </c>
     </row>
@@ -8648,25 +8650,25 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C89" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>41.202356</v>
+        <v>41.314067</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>69.14398</v>
+        <v>69.111439</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>41.202356, 69.143980</t>
+          <t>41.314067, 69.111439</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Куёшли (Солнечный)</t>
+          <t>Алимбаба</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8675,7 +8677,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J89" t="n">
         <v>3.1</v>
@@ -8686,7 +8688,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1820</v>
+        <v>2154</v>
       </c>
       <c r="M89" t="n">
         <v>1</v>
@@ -8698,26 +8700,24 @@
         <v>1</v>
       </c>
       <c r="P89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q89" t="n">
         <v>5</v>
       </c>
       <c r="R89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S89" t="n">
-        <v>16256</v>
+        <v>3868</v>
       </c>
       <c r="T89" t="n">
         <v>184.9</v>
       </c>
       <c r="U89" t="n">
-        <v>4</v>
-      </c>
-      <c r="V89" t="n">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V89" t="inlineStr"/>
       <c r="W89" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.202356,69.143980</t>
+          <t>https://www.google.com/maps?q=41.314067,69.111439</t>
         </is>
       </c>
     </row>
@@ -8741,25 +8741,25 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="C90" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>41.160793</v>
+        <v>41.202356</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>69.174412</v>
+        <v>69.14398</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>41.160793, 69.174412</t>
+          <t>41.202356, 69.143980</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Боборахим</t>
+          <t>Куёшли (Солнечный)</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -8768,47 +8768,49 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="J90" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Янгиюльский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1726</v>
+        <v>1820</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q90" t="n">
         <v>5</v>
       </c>
       <c r="R90" t="n">
+        <v>5</v>
+      </c>
+      <c r="S90" t="n">
+        <v>16256</v>
+      </c>
+      <c r="T90" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="U90" t="n">
         <v>4</v>
       </c>
-      <c r="S90" t="n">
-        <v>17092</v>
-      </c>
-      <c r="T90" t="n">
-        <v>129.6</v>
-      </c>
-      <c r="U90" t="n">
-        <v>0</v>
-      </c>
-      <c r="V90" t="inlineStr"/>
+      <c r="V90" t="n">
+        <v>3</v>
+      </c>
       <c r="W90" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8816,12 +8818,12 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.160793,69.174412</t>
+          <t>https://www.google.com/maps?q=41.202356,69.143980</t>
         </is>
       </c>
     </row>
@@ -8832,25 +8834,25 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C91" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>41.40393</v>
+        <v>41.160793</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>69.34765400000001</v>
+        <v>69.174412</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>41.403930, 69.347654</t>
+          <t>41.160793, 69.174412</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ункурган</t>
+          <t>Боборахим</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8859,49 +8861,47 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="J91" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Янгиюльский район</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1893</v>
+        <v>1726</v>
       </c>
       <c r="M91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>5</v>
       </c>
       <c r="R91" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S91" t="n">
-        <v>6209</v>
+        <v>17092</v>
       </c>
       <c r="T91" t="n">
-        <v>213.9</v>
+        <v>129.6</v>
       </c>
       <c r="U91" t="n">
-        <v>1</v>
-      </c>
-      <c r="V91" t="n">
-        <v>3000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V91" t="inlineStr"/>
       <c r="W91" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8909,12 +8909,12 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.403930,69.347654</t>
+          <t>https://www.google.com/maps?q=41.160793,69.174412</t>
         </is>
       </c>
     </row>
@@ -8925,74 +8925,76 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="C92" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>41.343065</v>
+        <v>41.40393</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>69.11617699999999</v>
+        <v>69.34765400000001</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>41.343065, 69.116177</t>
+          <t>41.403930, 69.347654</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Илгар</t>
+          <t>Ункурган</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="J92" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2595</v>
+        <v>1893</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q92" t="n">
         <v>5</v>
       </c>
       <c r="R92" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S92" t="n">
-        <v>1141</v>
+        <v>6209</v>
       </c>
       <c r="T92" t="n">
-        <v>184.9</v>
+        <v>213.9</v>
       </c>
       <c r="U92" t="n">
-        <v>0</v>
-      </c>
-      <c r="V92" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V92" t="n">
+        <v>3000</v>
+      </c>
       <c r="W92" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -9005,7 +9007,7 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.343065,69.116177</t>
+          <t>https://www.google.com/maps?q=41.403930,69.347654</t>
         </is>
       </c>
     </row>
@@ -9016,69 +9018,69 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C93" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>41.418715</v>
+        <v>41.343065</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>69.193523</v>
+        <v>69.11617699999999</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>41.418715, 69.193523</t>
+          <t>41.343065, 69.116177</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Куктерак</t>
+          <t>Илгар</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J93" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2247</v>
+        <v>2595</v>
       </c>
       <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
         <v>2</v>
       </c>
-      <c r="N93" t="n">
-        <v>4</v>
-      </c>
       <c r="O93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P93" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
         <v>5</v>
       </c>
       <c r="R93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S93" t="n">
-        <v>1267</v>
+        <v>1141</v>
       </c>
       <c r="T93" t="n">
-        <v>270.6</v>
+        <v>184.9</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
@@ -9096,7 +9098,7 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.418715,69.193523</t>
+          <t>https://www.google.com/maps?q=41.343065,69.116177</t>
         </is>
       </c>
     </row>
@@ -9107,20 +9109,20 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C94" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>41.425276</v>
+        <v>41.418715</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>69.209565</v>
+        <v>69.193523</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>41.425276, 69.209565</t>
+          <t>41.418715, 69.193523</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -9134,7 +9136,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J94" t="n">
         <v>3.8</v>
@@ -9145,13 +9147,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2734</v>
+        <v>2247</v>
       </c>
       <c r="M94" t="n">
         <v>2</v>
       </c>
       <c r="N94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O94" t="n">
         <v>1</v>
@@ -9163,10 +9165,10 @@
         <v>5</v>
       </c>
       <c r="R94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S94" t="n">
-        <v>187</v>
+        <v>1267</v>
       </c>
       <c r="T94" t="n">
         <v>270.6</v>
@@ -9187,7 +9189,7 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.425276,69.209565</t>
+          <t>https://www.google.com/maps?q=41.418715,69.193523</t>
         </is>
       </c>
     </row>
@@ -9198,25 +9200,25 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C95" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>41.412151</v>
+        <v>41.425276</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>69.177485</v>
+        <v>69.209565</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>41.412151, 69.177485</t>
+          <t>41.425276, 69.209565</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Сагбан</t>
+          <t>Куктерак</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -9225,10 +9227,10 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J95" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -9236,13 +9238,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2486</v>
+        <v>2734</v>
       </c>
       <c r="M95" t="n">
         <v>2</v>
       </c>
       <c r="N95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O95" t="n">
         <v>1</v>
@@ -9254,10 +9256,10 @@
         <v>5</v>
       </c>
       <c r="R95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S95" t="n">
-        <v>1519</v>
+        <v>187</v>
       </c>
       <c r="T95" t="n">
         <v>270.6</v>
@@ -9278,7 +9280,7 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.412151,69.177485</t>
+          <t>https://www.google.com/maps?q=41.425276,69.209565</t>
         </is>
       </c>
     </row>
@@ -9289,25 +9291,25 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C96" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>41.404809</v>
+        <v>41.412151</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>69.391277</v>
+        <v>69.177485</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>41.404809, 69.391277</t>
+          <t>41.412151, 69.177485</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Уткир</t>
+          <t>Сагбан</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -9323,35 +9325,35 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1919</v>
+        <v>2486</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q96" t="n">
         <v>5</v>
       </c>
       <c r="R96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S96" t="n">
-        <v>1398</v>
+        <v>1519</v>
       </c>
       <c r="T96" t="n">
-        <v>213.9</v>
+        <v>270.6</v>
       </c>
       <c r="U96" t="n">
         <v>0</v>
@@ -9364,12 +9366,12 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.404809,69.391277</t>
+          <t>https://www.google.com/maps?q=41.412151,69.177485</t>
         </is>
       </c>
     </row>
@@ -9380,25 +9382,25 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="C97" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>41.168041</v>
+        <v>41.404809</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>69.15093400000001</v>
+        <v>69.391277</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>41.168041, 69.150934</t>
+          <t>41.404809, 69.391277</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Багзар</t>
+          <t>Уткир</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9407,18 +9409,18 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J97" t="n">
         <v>4.3</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1409</v>
+        <v>1919</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -9439,10 +9441,10 @@
         <v>2</v>
       </c>
       <c r="S97" t="n">
-        <v>2842</v>
+        <v>1398</v>
       </c>
       <c r="T97" t="n">
-        <v>184.9</v>
+        <v>213.9</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
@@ -9460,7 +9462,7 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.168041,69.150934</t>
+          <t>https://www.google.com/maps?q=41.404809,69.391277</t>
         </is>
       </c>
     </row>
@@ -9471,25 +9473,25 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C98" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>41.266003</v>
+        <v>41.168041</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>69.572754</v>
+        <v>69.15093400000001</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>41.266003, 69.572754</t>
+          <t>41.168041, 69.150934</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Навбахор</t>
+          <t>Багзар</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -9498,18 +9500,18 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J98" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Паркентский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3713</v>
+        <v>1409</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
@@ -9527,13 +9529,13 @@
         <v>5</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S98" t="n">
-        <v>0</v>
+        <v>2842</v>
       </c>
       <c r="T98" t="n">
-        <v>94.3</v>
+        <v>184.9</v>
       </c>
       <c r="U98" t="n">
         <v>0</v>
@@ -9551,7 +9553,7 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.266003,69.572754</t>
+          <t>https://www.google.com/maps?q=41.168041,69.150934</t>
         </is>
       </c>
     </row>
@@ -9562,25 +9564,25 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C99" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>41.4457</v>
+        <v>41.266003</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>69.400503</v>
+        <v>69.572754</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>41.445700, 69.400503</t>
+          <t>41.266003, 69.572754</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Бирлик</t>
+          <t>Навбахор</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -9589,18 +9591,18 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.2</v>
+        <v>2.9</v>
       </c>
       <c r="J99" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Паркентский район</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1876</v>
+        <v>3713</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
@@ -9624,7 +9626,7 @@
         <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>213.9</v>
+        <v>94.3</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
@@ -9642,7 +9644,7 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.445700,69.400503</t>
+          <t>https://www.google.com/maps?q=41.266003,69.572754</t>
         </is>
       </c>
     </row>
@@ -9653,25 +9655,25 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C100" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>41.463034</v>
+        <v>41.4457</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>69.476435</v>
+        <v>69.400503</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>41.463034, 69.476435</t>
+          <t>41.445700, 69.400503</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Майский</t>
+          <t>Бирлик</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -9680,10 +9682,10 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J100" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -9691,7 +9693,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1883</v>
+        <v>1876</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
@@ -9718,11 +9720,9 @@
         <v>213.9</v>
       </c>
       <c r="U100" t="n">
-        <v>1</v>
-      </c>
-      <c r="V100" t="n">
-        <v>2000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V100" t="inlineStr"/>
       <c r="W100" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -9735,7 +9735,7 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.463034,69.476435</t>
+          <t>https://www.google.com/maps?q=41.445700,69.400503</t>
         </is>
       </c>
     </row>
@@ -9746,25 +9746,25 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="C101" t="n">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>41.173507</v>
+        <v>41.463034</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>69.131349</v>
+        <v>69.476435</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>41.173507, 69.131349</t>
+          <t>41.463034, 69.476435</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ханкурган</t>
+          <t>Майский</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -9773,18 +9773,18 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J101" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2231</v>
+        <v>1883</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
@@ -9802,18 +9802,20 @@
         <v>5</v>
       </c>
       <c r="R101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
-        <v>2842</v>
+        <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>184.9</v>
+        <v>213.9</v>
       </c>
       <c r="U101" t="n">
-        <v>0</v>
-      </c>
-      <c r="V101" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V101" t="n">
+        <v>2000</v>
+      </c>
       <c r="W101" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -9826,7 +9828,7 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.173507,69.131349</t>
+          <t>https://www.google.com/maps?q=41.463034,69.476435</t>
         </is>
       </c>
     </row>
@@ -9837,45 +9839,45 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C102" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>41.445091</v>
+        <v>41.173507</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>69.249785</v>
+        <v>69.131349</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>41.445091, 69.249785</t>
+          <t>41.173507, 69.131349</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Чувалачи</t>
+          <t>Ханкурган</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="J102" t="n">
         <v>5.3</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2773</v>
+        <v>2231</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
@@ -9893,13 +9895,13 @@
         <v>5</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S102" t="n">
-        <v>0</v>
+        <v>2842</v>
       </c>
       <c r="T102" t="n">
-        <v>270.6</v>
+        <v>184.9</v>
       </c>
       <c r="U102" t="n">
         <v>0</v>
@@ -9917,7 +9919,7 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.445091,69.249785</t>
+          <t>https://www.google.com/maps?q=41.173507,69.131349</t>
         </is>
       </c>
     </row>
@@ -9928,34 +9930,34 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C103" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>41.445517</v>
+        <v>41.445091</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>69.226005</v>
+        <v>69.249785</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>41.445517, 69.226005</t>
+          <t>41.445091, 69.249785</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Алишер Навои</t>
+          <t>Чувалачи</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J103" t="n">
         <v>5.3</v>
@@ -9966,7 +9968,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2065</v>
+        <v>2773</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
@@ -9984,10 +9986,10 @@
         <v>5</v>
       </c>
       <c r="R103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="T103" t="n">
         <v>270.6</v>
@@ -10008,7 +10010,7 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.445517,69.226005</t>
+          <t>https://www.google.com/maps?q=41.445091,69.249785</t>
         </is>
       </c>
     </row>
@@ -10019,25 +10021,25 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="C104" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>41.431739</v>
+        <v>41.445517</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>69.324724</v>
+        <v>69.226005</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>41.431739, 69.324724</t>
+          <t>41.445517, 69.226005</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Кашкарлик</t>
+          <t>Алишер Навои</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -10046,7 +10048,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J104" t="n">
         <v>5.3</v>
@@ -10057,13 +10059,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2008</v>
+        <v>2065</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -10075,10 +10077,10 @@
         <v>5</v>
       </c>
       <c r="R104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S104" t="n">
-        <v>2507</v>
+        <v>187</v>
       </c>
       <c r="T104" t="n">
         <v>270.6</v>
@@ -10094,12 +10096,12 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.431739,69.324724</t>
+          <t>https://www.google.com/maps?q=41.445517,69.226005</t>
         </is>
       </c>
     </row>
@@ -10110,25 +10112,25 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="C105" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>41.273963</v>
+        <v>41.431739</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>69.055013</v>
+        <v>69.324724</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>41.273963, 69.055013</t>
+          <t>41.431739, 69.324724</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Тукимачи</t>
+          <t>Кашкарлик</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -10137,24 +10139,24 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2760</v>
+        <v>2008</v>
       </c>
       <c r="M105" t="n">
         <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -10166,13 +10168,13 @@
         <v>5</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S105" t="n">
-        <v>0</v>
+        <v>2507</v>
       </c>
       <c r="T105" t="n">
-        <v>184.9</v>
+        <v>270.6</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
@@ -10185,12 +10187,12 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.273963,69.055013</t>
+          <t>https://www.google.com/maps?q=41.431739,69.324724</t>
         </is>
       </c>
     </row>
@@ -10201,25 +10203,25 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="C106" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>41.287638</v>
+        <v>41.273963</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>69.055368</v>
+        <v>69.055013</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>41.287638, 69.055368</t>
+          <t>41.273963, 69.055013</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Янарык</t>
+          <t>Тукимачи</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -10228,10 +10230,10 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -10239,7 +10241,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2340</v>
+        <v>2760</v>
       </c>
       <c r="M106" t="n">
         <v>0</v>
@@ -10281,7 +10283,7 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.287638,69.055368</t>
+          <t>https://www.google.com/maps?q=41.273963,69.055013</t>
         </is>
       </c>
     </row>
@@ -10292,69 +10294,69 @@
         </is>
       </c>
       <c r="B107" t="n">
+        <v>37</v>
+      </c>
+      <c r="C107" t="n">
+        <v>70</v>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>41.287638</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>69.055368</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>41.287638, 69.055368</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Янарык</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>село</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J107" t="n">
         <v>6</v>
       </c>
-      <c r="C107" t="n">
-        <v>82</v>
-      </c>
-      <c r="D107" s="2" t="n">
-        <v>41.434386</v>
-      </c>
-      <c r="E107" s="2" t="n">
-        <v>69.538939</v>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>41.434386, 69.538939</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Вахид Хайдаров махалля</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>махалля</t>
-        </is>
-      </c>
-      <c r="I107" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J107" t="n">
-        <v>6.2</v>
-      </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Город Чиpчик</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>7155</v>
+        <v>2340</v>
       </c>
       <c r="M107" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
         <v>5</v>
       </c>
       <c r="R107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>1599</v>
+        <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>40.8</v>
+        <v>184.9</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
@@ -10367,12 +10369,12 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.434386,69.538939</t>
+          <t>https://www.google.com/maps?q=41.287638,69.055368</t>
         </is>
       </c>
     </row>
@@ -10383,69 +10385,69 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C108" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>41.461777</v>
+        <v>41.434386</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>69.36531100000001</v>
+        <v>69.538939</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>41.461777, 69.365311</t>
+          <t>41.434386, 69.538939</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Гышткуприк</t>
+          <t>Вахид Хайдаров махалля</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J108" t="n">
-        <v>8.1</v>
+        <v>6.2</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Город Чиpчик</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2850</v>
+        <v>7155</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q108" t="n">
         <v>5</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S108" t="n">
-        <v>0</v>
+        <v>1599</v>
       </c>
       <c r="T108" t="n">
-        <v>270.6</v>
+        <v>40.8</v>
       </c>
       <c r="U108" t="n">
         <v>0</v>
@@ -10458,12 +10460,12 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.461777,69.365311</t>
+          <t>https://www.google.com/maps?q=41.434386,69.538939</t>
         </is>
       </c>
     </row>
@@ -10474,25 +10476,25 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="C109" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>41.229781</v>
+        <v>41.461777</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>69.038067</v>
+        <v>69.36531100000001</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>41.229781, 69.038067</t>
+          <t>41.461777, 69.365311</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Гулистан</t>
+          <t>Гышткуприк</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -10501,18 +10503,18 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J109" t="n">
         <v>8.1</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2080</v>
+        <v>2850</v>
       </c>
       <c r="M109" t="n">
         <v>0</v>
@@ -10536,7 +10538,7 @@
         <v>0</v>
       </c>
       <c r="T109" t="n">
-        <v>184.9</v>
+        <v>270.6</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
@@ -10554,7 +10556,7 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.229781,69.038067</t>
+          <t>https://www.google.com/maps?q=41.461777,69.365311</t>
         </is>
       </c>
     </row>
@@ -10565,25 +10567,25 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C110" t="n">
         <v>67</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>41.426559</v>
+        <v>41.229781</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>69.586257</v>
+        <v>69.038067</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>41.426559, 69.586257</t>
+          <t>41.229781, 69.038067</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Янгикурган</t>
+          <t>Гулистан</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -10592,18 +10594,18 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J110" t="n">
-        <v>9.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Юкоричирчикский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1591</v>
+        <v>2080</v>
       </c>
       <c r="M110" t="n">
         <v>0</v>
@@ -10621,13 +10623,13 @@
         <v>5</v>
       </c>
       <c r="R110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
-        <v>1599</v>
+        <v>0</v>
       </c>
       <c r="T110" t="n">
-        <v>151.7</v>
+        <v>184.9</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
@@ -10645,7 +10647,7 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.426559,69.586257</t>
+          <t>https://www.google.com/maps?q=41.229781,69.038067</t>
         </is>
       </c>
     </row>
@@ -10656,76 +10658,74 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="C111" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>41.478034</v>
+        <v>41.426559</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>69.580118</v>
+        <v>69.586257</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>41.478034, 69.580118</t>
+          <t>41.426559, 69.586257</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Бахор махалля</t>
+          <t>Янгикурган</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I111" t="n">
         <v>0.2</v>
       </c>
       <c r="J111" t="n">
-        <v>11.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Город Чиpчик</t>
+          <t>Юкоричирчикский район</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>18190</v>
+        <v>1591</v>
       </c>
       <c r="M111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P111" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
         <v>5</v>
       </c>
       <c r="R111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S111" t="n">
-        <v>1995</v>
+        <v>1599</v>
       </c>
       <c r="T111" t="n">
-        <v>40.8</v>
+        <v>151.7</v>
       </c>
       <c r="U111" t="n">
-        <v>2</v>
-      </c>
-      <c r="V111" t="n">
-        <v>4068</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V111" t="inlineStr"/>
       <c r="W111" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -10733,12 +10733,12 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.478034,69.580118</t>
+          <t>https://www.google.com/maps?q=41.426559,69.586257</t>
         </is>
       </c>
     </row>
@@ -10749,57 +10749,57 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C112" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>41.463685</v>
+        <v>41.478034</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>69.611362</v>
+        <v>69.580118</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>41.463685, 69.611362</t>
+          <t>41.478034, 69.580118</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Карабай</t>
+          <t>Бахор махалля</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J112" t="n">
-        <v>13.1</v>
+        <v>11.7</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Бостанлыкский район</t>
+          <t>Город Чиpчик</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2282</v>
+        <v>18190</v>
       </c>
       <c r="M112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N112" t="n">
+        <v>8</v>
+      </c>
+      <c r="O112" t="n">
         <v>4</v>
       </c>
-      <c r="O112" t="n">
-        <v>2</v>
-      </c>
       <c r="P112" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q112" t="n">
         <v>5</v>
@@ -10811,12 +10811,14 @@
         <v>1995</v>
       </c>
       <c r="T112" t="n">
-        <v>147.5</v>
+        <v>40.8</v>
       </c>
       <c r="U112" t="n">
-        <v>0</v>
-      </c>
-      <c r="V112" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="V112" t="n">
+        <v>4068</v>
+      </c>
       <c r="W112" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -10829,7 +10831,7 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.463685,69.611362</t>
+          <t>https://www.google.com/maps?q=41.478034,69.580118</t>
         </is>
       </c>
     </row>
@@ -10840,25 +10842,25 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C113" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>41.157616</v>
+        <v>41.463685</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>69.059894</v>
+        <v>69.611362</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>41.157616, 69.059894</t>
+          <t>41.463685, 69.611362</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Конкус</t>
+          <t>Карабай</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -10867,30 +10869,30 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J113" t="n">
         <v>13.1</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Янгиюльский район</t>
+          <t>Бостанлыкский район</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1815</v>
+        <v>2282</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q113" t="n">
         <v>5</v>
@@ -10899,10 +10901,10 @@
         <v>3</v>
       </c>
       <c r="S113" t="n">
-        <v>909</v>
+        <v>1995</v>
       </c>
       <c r="T113" t="n">
-        <v>129.6</v>
+        <v>147.5</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
@@ -10915,12 +10917,12 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.157616,69.059894</t>
+          <t>https://www.google.com/maps?q=41.463685,69.611362</t>
         </is>
       </c>
     </row>
@@ -10931,69 +10933,69 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C114" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>41.043222</v>
+        <v>41.157616</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>69.34051100000001</v>
+        <v>69.059894</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>41.043222, 69.340511</t>
+          <t>41.157616, 69.059894</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Нурафшан (Тойтепа)</t>
+          <t>Конкус</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J114" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Уртачирчикский район</t>
+          <t>Янгиюльский район</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1601</v>
+        <v>1815</v>
       </c>
       <c r="M114" t="n">
         <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
         <v>5</v>
       </c>
       <c r="R114" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S114" t="n">
-        <v>1946</v>
+        <v>909</v>
       </c>
       <c r="T114" t="n">
-        <v>134.2</v>
+        <v>129.6</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
@@ -11006,12 +11008,12 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.043222,69.340511</t>
+          <t>https://www.google.com/maps?q=41.157616,69.059894</t>
         </is>
       </c>
     </row>
@@ -11028,63 +11030,63 @@
         <v>66</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>41.093937</v>
+        <v>41.043222</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>69.085832</v>
+        <v>69.34051100000001</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>41.093937, 69.085832</t>
+          <t>41.043222, 69.340511</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ниязбаш</t>
+          <t>Нурафшан (Тойтепа)</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J115" t="n">
-        <v>13.9</v>
+        <v>13.3</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Янгиюльский район</t>
+          <t>Уртачирчикский район</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>3151</v>
+        <v>1601</v>
       </c>
       <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="n">
+        <v>2</v>
+      </c>
+      <c r="O115" t="n">
         <v>1</v>
       </c>
-      <c r="N115" t="n">
-        <v>0</v>
-      </c>
-      <c r="O115" t="n">
-        <v>0</v>
-      </c>
       <c r="P115" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Q115" t="n">
         <v>5</v>
       </c>
       <c r="R115" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S115" t="n">
-        <v>909</v>
+        <v>1946</v>
       </c>
       <c r="T115" t="n">
-        <v>129.6</v>
+        <v>134.2</v>
       </c>
       <c r="U115" t="n">
         <v>0</v>
@@ -11102,7 +11104,7 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.093937,69.085832</t>
+          <t>https://www.google.com/maps?q=41.043222,69.340511</t>
         </is>
       </c>
     </row>
@@ -11113,25 +11115,25 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C116" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>41.475237</v>
+        <v>41.093937</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>69.631615</v>
+        <v>69.085832</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>41.475237, 69.631615</t>
+          <t>41.093937, 69.085832</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Кушкурган</t>
+          <t>Ниязбаш</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -11140,21 +11142,21 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J116" t="n">
-        <v>15.2</v>
+        <v>13.9</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Бостанлыкский район</t>
+          <t>Янгиюльский район</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1805</v>
+        <v>3151</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N116" t="n">
         <v>0</v>
@@ -11163,19 +11165,19 @@
         <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q116" t="n">
         <v>5</v>
       </c>
       <c r="R116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S116" t="n">
-        <v>396</v>
+        <v>909</v>
       </c>
       <c r="T116" t="n">
-        <v>147.5</v>
+        <v>129.6</v>
       </c>
       <c r="U116" t="n">
         <v>0</v>
@@ -11188,12 +11190,12 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.475237,69.631615</t>
+          <t>https://www.google.com/maps?q=41.093937,69.085832</t>
         </is>
       </c>
     </row>
@@ -11204,69 +11206,69 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C117" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>41.02079</v>
+        <v>41.475237</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>69.351637</v>
+        <v>69.631615</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>41.020790, 69.351637</t>
+          <t>41.475237, 69.631615</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Чигирик</t>
+          <t>Кушкурган</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
-        <v>15.7</v>
+        <v>15.2</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Уртачирчикский район</t>
+          <t>Бостанлыкский район</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>3239</v>
+        <v>1805</v>
       </c>
       <c r="M117" t="n">
         <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P117" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
         <v>5</v>
       </c>
       <c r="R117" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S117" t="n">
-        <v>1946</v>
+        <v>396</v>
       </c>
       <c r="T117" t="n">
-        <v>134.2</v>
+        <v>147.5</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -11279,12 +11281,12 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.020790,69.351637</t>
+          <t>https://www.google.com/maps?q=41.475237,69.631615</t>
         </is>
       </c>
     </row>
@@ -11295,69 +11297,69 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C118" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>41.514832</v>
+        <v>41.02079</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>69.621115</v>
+        <v>69.351637</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>41.514832, 69.621115</t>
+          <t>41.020790, 69.351637</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Верхне-чирчикский район</t>
+          <t>Чигирик</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J118" t="n">
-        <v>17</v>
+        <v>15.7</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Город Чиpчик</t>
+          <t>Уртачирчикский район</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>7842</v>
+        <v>3239</v>
       </c>
       <c r="M118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
         <v>2</v>
       </c>
       <c r="O118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q118" t="n">
         <v>5</v>
       </c>
       <c r="R118" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S118" t="n">
-        <v>444</v>
+        <v>1946</v>
       </c>
       <c r="T118" t="n">
-        <v>40.8</v>
+        <v>134.2</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
@@ -11375,7 +11377,7 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.514832,69.621115</t>
+          <t>https://www.google.com/maps?q=41.020790,69.351637</t>
         </is>
       </c>
     </row>
@@ -11386,7 +11388,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C119" t="n">
         <v>63</v>
@@ -11477,7 +11479,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C120" t="n">
         <v>68</v>
@@ -11568,10 +11570,10 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C121" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D121" s="2" t="n">
         <v>41.570059</v>
@@ -11659,45 +11661,45 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="C122" t="n">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>40.999053</v>
+        <v>41.613627</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>68.92986999999999</v>
+        <v>69.724091</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>40.999053, 68.929870</t>
+          <t>41.613627, 69.724091</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Навои</t>
+          <t>Хандайлык</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J122" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Чиназский район</t>
+          <t>Бостанлыкский район</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>983</v>
+        <v>1637</v>
       </c>
       <c r="M122" t="n">
         <v>0</v>
@@ -11715,13 +11717,13 @@
         <v>5</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S122" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T122" t="n">
-        <v>59.7</v>
+        <v>147.5</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
@@ -11739,7 +11741,7 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.999053,68.929870</t>
+          <t>https://www.google.com/maps?q=41.613627,69.724091</t>
         </is>
       </c>
     </row>
@@ -11750,37 +11752,37 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C123" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>41.613627</v>
+        <v>41.56088</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>69.724091</v>
+        <v>69.785724</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>41.613627, 69.724091</t>
+          <t>41.560880, 69.785724</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Хандайлык</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J123" t="n">
-        <v>30.8</v>
+        <v>31</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -11788,10 +11790,10 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1637</v>
+        <v>11955</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N123" t="n">
         <v>0</v>
@@ -11800,7 +11802,7 @@
         <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q123" t="n">
         <v>5</v>
@@ -11809,7 +11811,7 @@
         <v>1</v>
       </c>
       <c r="S123" t="n">
-        <v>200</v>
+        <v>767</v>
       </c>
       <c r="T123" t="n">
         <v>147.5</v>
@@ -11825,12 +11827,12 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.613627,69.724091</t>
+          <t>https://www.google.com/maps?q=41.560880,69.785724</t>
         </is>
       </c>
     </row>
@@ -11841,37 +11843,37 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C124" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>41.56088</v>
+        <v>41.606431</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>69.785724</v>
+        <v>69.739734</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>41.560880, 69.785724</t>
+          <t>41.606431, 69.739734</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Хандайлык</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J124" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -11879,10 +11881,10 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>11955</v>
+        <v>1704</v>
       </c>
       <c r="M124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
         <v>0</v>
@@ -11891,7 +11893,7 @@
         <v>0</v>
       </c>
       <c r="P124" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
         <v>5</v>
@@ -11900,7 +11902,7 @@
         <v>1</v>
       </c>
       <c r="S124" t="n">
-        <v>767</v>
+        <v>200</v>
       </c>
       <c r="T124" t="n">
         <v>147.5</v>
@@ -11916,12 +11918,12 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.560880,69.785724</t>
+          <t>https://www.google.com/maps?q=41.606431,69.739734</t>
         </is>
       </c>
     </row>
@@ -11932,25 +11934,25 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="C125" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>41.604632</v>
+        <v>40.902515</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>69.743645</v>
+        <v>69.088656</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>41.604632, 69.743645</t>
+          <t>40.902515, 69.088656</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Хандайлык</t>
+          <t>Талаул</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -11959,18 +11961,18 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="J125" t="n">
-        <v>31.2</v>
+        <v>31.9</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Бостанлыкский район</t>
+          <t>Аккурганский район</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1268</v>
+        <v>1357</v>
       </c>
       <c r="M125" t="n">
         <v>0</v>
@@ -11988,13 +11990,13 @@
         <v>5</v>
       </c>
       <c r="R125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="T125" t="n">
-        <v>147.5</v>
+        <v>40.3</v>
       </c>
       <c r="U125" t="n">
         <v>0</v>
@@ -12012,7 +12014,7 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.604632,69.743645</t>
+          <t>https://www.google.com/maps?q=40.902515,69.088656</t>
         </is>
       </c>
     </row>
@@ -12023,45 +12025,45 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C126" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>40.902515</v>
+        <v>40.994233</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>69.088656</v>
+        <v>68.910084</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>40.902515, 69.088656</t>
+          <t>40.994233, 68.910084</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Талаул</t>
+          <t>Навои</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="J126" t="n">
-        <v>31.9</v>
+        <v>32.3</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Аккурганский район</t>
+          <t>Чиназский район</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1357</v>
+        <v>1217</v>
       </c>
       <c r="M126" t="n">
         <v>0</v>
@@ -12085,7 +12087,7 @@
         <v>0</v>
       </c>
       <c r="T126" t="n">
-        <v>40.3</v>
+        <v>59.7</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
@@ -12103,7 +12105,7 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.902515,69.088656</t>
+          <t>https://www.google.com/maps?q=40.994233,68.910084</t>
         </is>
       </c>
     </row>
@@ -12114,48 +12116,48 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="C127" t="n">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>40.994233</v>
+        <v>41.572586</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>68.910084</v>
+        <v>69.798101</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>40.994233, 68.910084</t>
+          <t>41.572586, 69.798101</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Навои</t>
+          <t>Чимбайлык</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J127" t="n">
-        <v>32.3</v>
+        <v>32.6</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Чиназский район</t>
+          <t>Бостанлыкский район</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1217</v>
+        <v>2565</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N127" t="n">
         <v>0</v>
@@ -12164,19 +12166,19 @@
         <v>0</v>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q127" t="n">
         <v>5</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S127" t="n">
-        <v>0</v>
+        <v>767</v>
       </c>
       <c r="T127" t="n">
-        <v>59.7</v>
+        <v>147.5</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
@@ -12189,12 +12191,12 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.994233,68.910084</t>
+          <t>https://www.google.com/maps?q=41.572586,69.798101</t>
         </is>
       </c>
     </row>
@@ -12205,25 +12207,25 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C128" t="n">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>41.572586</v>
+        <v>40.866402</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>69.798101</v>
+        <v>69.468656</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>41.572586, 69.798101</t>
+          <t>40.866402, 69.468656</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Чимбайлык</t>
+          <t>Сагана</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -12232,21 +12234,21 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J128" t="n">
         <v>32.6</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Бостанлыкский район</t>
+          <t>Пскентский район</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2565</v>
+        <v>1184</v>
       </c>
       <c r="M128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
         <v>0</v>
@@ -12255,19 +12257,19 @@
         <v>0</v>
       </c>
       <c r="P128" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
         <v>5</v>
       </c>
       <c r="R128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
-        <v>767</v>
+        <v>0</v>
       </c>
       <c r="T128" t="n">
-        <v>147.5</v>
+        <v>37.9</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
@@ -12280,12 +12282,12 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.572586,69.798101</t>
+          <t>https://www.google.com/maps?q=40.866402,69.468656</t>
         </is>
       </c>
     </row>
@@ -12296,25 +12298,25 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="C129" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>40.866402</v>
+        <v>40.926335</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>69.468656</v>
+        <v>68.99102600000001</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>40.866402, 69.468656</t>
+          <t>40.926335, 68.991026</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Сагана</t>
+          <t>Гулистан</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -12326,15 +12328,15 @@
         <v>0.2</v>
       </c>
       <c r="J129" t="n">
-        <v>32.6</v>
+        <v>33.2</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Пскентский район</t>
+          <t>Куйичирчикский район</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1184</v>
+        <v>1476</v>
       </c>
       <c r="M129" t="n">
         <v>0</v>
@@ -12358,7 +12360,7 @@
         <v>0</v>
       </c>
       <c r="T129" t="n">
-        <v>37.9</v>
+        <v>63.5</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -12376,7 +12378,7 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.866402,69.468656</t>
+          <t>https://www.google.com/maps?q=40.926335,68.991026</t>
         </is>
       </c>
     </row>
@@ -12387,25 +12389,25 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="C130" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>40.926335</v>
+        <v>40.95099</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>68.99102600000001</v>
+        <v>68.944456</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>40.926335, 68.991026</t>
+          <t>40.950990, 68.944456</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Гулистан</t>
+          <t>Янгихаёт</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -12414,10 +12416,10 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J130" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -12425,7 +12427,7 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1476</v>
+        <v>1191</v>
       </c>
       <c r="M130" t="n">
         <v>0</v>
@@ -12467,7 +12469,7 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.926335,68.991026</t>
+          <t>https://www.google.com/maps?q=40.950990,68.944456</t>
         </is>
       </c>
     </row>
@@ -12569,7 +12571,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C132" t="n">
         <v>28</v>
@@ -12660,10 +12662,10 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C133" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D133" s="2" t="n">
         <v>40.850739</v>
@@ -12751,7 +12753,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C134" t="n">
         <v>46</v>
@@ -12933,7 +12935,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C136" t="n">
         <v>23</v>
@@ -13115,7 +13117,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C138" t="n">
         <v>54</v>
@@ -13206,7 +13208,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C139" t="n">
         <v>32</v>
@@ -13297,10 +13299,10 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C140" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D140" s="2" t="n">
         <v>40.879789</v>
@@ -13388,7 +13390,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C141" t="n">
         <v>49</v>
@@ -13479,10 +13481,10 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C142" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D142" s="2" t="n">
         <v>40.865328</v>
@@ -13570,7 +13572,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C143" t="n">
         <v>54</v>
@@ -13663,10 +13665,10 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C144" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D144" s="2" t="n">
         <v>40.911195</v>
@@ -13754,10 +13756,10 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C145" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D145" s="2" t="n">
         <v>40.869928</v>
@@ -13845,7 +13847,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C146" t="n">
         <v>26</v>
@@ -14027,7 +14029,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C148" t="n">
         <v>30</v>
@@ -14118,7 +14120,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C149" t="n">
         <v>32</v>
@@ -14212,7 +14214,7 @@
         <v>15</v>
       </c>
       <c r="C150" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D150" s="2" t="n">
         <v>41.601553</v>
@@ -14300,7 +14302,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C151" t="n">
         <v>46</v>
@@ -14391,7 +14393,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C152" t="n">
         <v>35</v>
@@ -14482,7 +14484,7 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C153" t="n">
         <v>45</v>
@@ -14573,10 +14575,10 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C154" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D154" s="2" t="n">
         <v>40.985851</v>
@@ -14664,10 +14666,10 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C155" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D155" s="2" t="n">
         <v>40.864341</v>
@@ -14755,7 +14757,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C156" t="n">
         <v>55</v>
@@ -14940,7 +14942,7 @@
         <v>35</v>
       </c>
       <c r="C158" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D158" s="2" t="n">
         <v>40.809862</v>
@@ -15028,7 +15030,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C159" t="n">
         <v>56</v>
@@ -15122,7 +15124,7 @@
         <v>37</v>
       </c>
       <c r="C160" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D160" s="2" t="n">
         <v>40.960514</v>
@@ -15210,7 +15212,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C161" t="n">
         <v>44</v>
@@ -15306,7 +15308,7 @@
         <v>36</v>
       </c>
       <c r="C162" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D162" s="2" t="n">
         <v>40.830681</v>
@@ -15394,25 +15396,25 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="C163" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>40.908954</v>
+        <v>40.968021</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>68.78631</v>
+        <v>69.967872</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>40.908954, 68.786310</t>
+          <t>40.968021, 69.967872</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Курганча</t>
+          <t>Увак</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -15421,18 +15423,18 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J163" t="n">
-        <v>48.7</v>
+        <v>47.2</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Куйичирчикский район</t>
+          <t>Ахангаранский район</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>1815</v>
+        <v>1066</v>
       </c>
       <c r="M163" t="n">
         <v>0</v>
@@ -15456,7 +15458,7 @@
         <v>0</v>
       </c>
       <c r="T163" t="n">
-        <v>63.5</v>
+        <v>55.2</v>
       </c>
       <c r="U163" t="n">
         <v>0</v>
@@ -15474,7 +15476,7 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.908954,68.786310</t>
+          <t>https://www.google.com/maps?q=40.968021,69.967872</t>
         </is>
       </c>
     </row>
@@ -15485,25 +15487,25 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C164" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>40.771428</v>
+        <v>40.908954</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>68.959765</v>
+        <v>68.78631</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>40.771428, 68.959765</t>
+          <t>40.908954, 68.786310</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Хамзаабад</t>
+          <t>Курганча</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -15512,18 +15514,18 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J164" t="n">
-        <v>49.4</v>
+        <v>48.7</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Аккурганский район</t>
+          <t>Куйичирчикский район</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>1669</v>
+        <v>1815</v>
       </c>
       <c r="M164" t="n">
         <v>0</v>
@@ -15547,7 +15549,7 @@
         <v>0</v>
       </c>
       <c r="T164" t="n">
-        <v>40.3</v>
+        <v>63.5</v>
       </c>
       <c r="U164" t="n">
         <v>0</v>
@@ -15565,7 +15567,7 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.771428,68.959765</t>
+          <t>https://www.google.com/maps?q=40.908954,68.786310</t>
         </is>
       </c>
     </row>
@@ -15576,25 +15578,25 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C165" t="n">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>41.669921</v>
+        <v>40.771428</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>69.95719</v>
+        <v>68.959765</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>41.669921, 69.957190</t>
+          <t>40.771428, 68.959765</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Хумсан</t>
+          <t>Хамзаабад</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -15603,18 +15605,18 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J165" t="n">
-        <v>49.6</v>
+        <v>49.4</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Бостанлыкский район</t>
+          <t>Аккурганский район</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>2001</v>
+        <v>1669</v>
       </c>
       <c r="M165" t="n">
         <v>0</v>
@@ -15632,13 +15634,13 @@
         <v>5</v>
       </c>
       <c r="R165" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S165" t="n">
-        <v>1260</v>
+        <v>0</v>
       </c>
       <c r="T165" t="n">
-        <v>147.5</v>
+        <v>40.3</v>
       </c>
       <c r="U165" t="n">
         <v>0</v>
@@ -15656,7 +15658,7 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.669921,69.957190</t>
+          <t>https://www.google.com/maps?q=40.771428,68.959765</t>
         </is>
       </c>
     </row>
@@ -15667,25 +15669,25 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="C166" t="n">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>40.910344</v>
+        <v>41.669921</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>69.94977299999999</v>
+        <v>69.95719</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>40.910344, 69.949773</t>
+          <t>41.669921, 69.957190</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Сузам</t>
+          <t>Хумсан</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -15694,18 +15696,18 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J166" t="n">
-        <v>50.1</v>
+        <v>49.6</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Ахангаранский район</t>
+          <t>Бостанлыкский район</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>1092</v>
+        <v>2001</v>
       </c>
       <c r="M166" t="n">
         <v>0</v>
@@ -15723,13 +15725,13 @@
         <v>5</v>
       </c>
       <c r="R166" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S166" t="n">
-        <v>0</v>
+        <v>1260</v>
       </c>
       <c r="T166" t="n">
-        <v>55.2</v>
+        <v>147.5</v>
       </c>
       <c r="U166" t="n">
         <v>0</v>
@@ -15747,7 +15749,7 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.910344,69.949773</t>
+          <t>https://www.google.com/maps?q=41.669921,69.957190</t>
         </is>
       </c>
     </row>
@@ -15758,25 +15760,25 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C167" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D167" s="2" t="n">
-        <v>40.937372</v>
+        <v>40.910344</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>68.708319</v>
+        <v>69.94977299999999</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>40.937372, 68.708319</t>
+          <t>40.910344, 69.949773</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Эркин</t>
+          <t>Сузам</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -15785,21 +15787,21 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J167" t="n">
-        <v>50.4</v>
+        <v>50.1</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Чиназский район</t>
+          <t>Ахангаранский район</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>1263</v>
+        <v>1092</v>
       </c>
       <c r="M167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
         <v>0</v>
@@ -15820,7 +15822,7 @@
         <v>0</v>
       </c>
       <c r="T167" t="n">
-        <v>59.7</v>
+        <v>55.2</v>
       </c>
       <c r="U167" t="n">
         <v>0</v>
@@ -15833,12 +15835,12 @@
       </c>
       <c r="X167" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.937372,68.708319</t>
+          <t>https://www.google.com/maps?q=40.910344,69.949773</t>
         </is>
       </c>
     </row>
@@ -15849,25 +15851,25 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C168" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>40.98193</v>
+        <v>40.855974</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>70.027506</v>
+        <v>68.789107</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>40.981930, 70.027506</t>
+          <t>40.855974, 68.789107</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Гульбог</t>
+          <t>Гул</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -15876,18 +15878,18 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J168" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Ахангаранский район</t>
+          <t>Куйичирчикский район</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>2111</v>
+        <v>1336</v>
       </c>
       <c r="M168" t="n">
         <v>0</v>
@@ -15911,7 +15913,7 @@
         <v>0</v>
       </c>
       <c r="T168" t="n">
-        <v>55.2</v>
+        <v>63.5</v>
       </c>
       <c r="U168" t="n">
         <v>0</v>
@@ -15929,7 +15931,7 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.981930,70.027506</t>
+          <t>https://www.google.com/maps?q=40.855974,68.789107</t>
         </is>
       </c>
     </row>
@@ -15940,25 +15942,25 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C169" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>40.854323</v>
+        <v>40.937372</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>68.78514800000001</v>
+        <v>68.708319</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>40.854323, 68.785148</t>
+          <t>40.937372, 68.708319</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Гул</t>
+          <t>Эркин</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -15967,21 +15969,21 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J169" t="n">
-        <v>50.8</v>
+        <v>50.4</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Куйичирчикский район</t>
+          <t>Чиназский район</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>1430</v>
+        <v>1263</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N169" t="n">
         <v>0</v>
@@ -16002,7 +16004,7 @@
         <v>0</v>
       </c>
       <c r="T169" t="n">
-        <v>63.5</v>
+        <v>59.7</v>
       </c>
       <c r="U169" t="n">
         <v>0</v>
@@ -16015,12 +16017,12 @@
       </c>
       <c r="X169" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.854323,68.785148</t>
+          <t>https://www.google.com/maps?q=40.937372,68.708319</t>
         </is>
       </c>
     </row>
@@ -16031,37 +16033,37 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C170" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D170" s="2" t="n">
-        <v>41.120414</v>
+        <v>40.98193</v>
       </c>
       <c r="E170" s="2" t="n">
-        <v>70.096497</v>
+        <v>70.027506</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>41.120414, 70.096497</t>
+          <t>40.981930, 70.027506</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Янгиабад</t>
+          <t>Гульбог</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J170" t="n">
-        <v>51</v>
+        <v>50.6</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -16069,7 +16071,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>2298</v>
+        <v>2111</v>
       </c>
       <c r="M170" t="n">
         <v>0</v>
@@ -16111,7 +16113,7 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.120414,70.096497</t>
+          <t>https://www.google.com/maps?q=40.981930,70.027506</t>
         </is>
       </c>
     </row>
@@ -16122,45 +16124,45 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="C171" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>40.71599</v>
+        <v>41.120414</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>69.111172</v>
+        <v>70.096497</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>40.715990, 69.111172</t>
+          <t>41.120414, 70.096497</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Янгичаулисай</t>
+          <t>Янгиабад</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I171" t="n">
         <v>0.2</v>
       </c>
       <c r="J171" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Букинский район</t>
+          <t>Ахангаранский район</t>
         </is>
       </c>
       <c r="L171" t="n">
-        <v>1331</v>
+        <v>2298</v>
       </c>
       <c r="M171" t="n">
         <v>0</v>
@@ -16184,7 +16186,7 @@
         <v>0</v>
       </c>
       <c r="T171" t="n">
-        <v>39.6</v>
+        <v>55.2</v>
       </c>
       <c r="U171" t="n">
         <v>0</v>
@@ -16202,7 +16204,7 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.715990,69.111172</t>
+          <t>https://www.google.com/maps?q=41.120414,70.096497</t>
         </is>
       </c>
     </row>
@@ -16213,25 +16215,25 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="C172" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>40.700394</v>
+        <v>40.71599</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>69.220406</v>
+        <v>69.111172</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>40.700394, 69.220406</t>
+          <t>40.715990, 69.111172</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Бустон</t>
+          <t>Янгичаулисай</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -16240,10 +16242,10 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J172" t="n">
-        <v>51.7</v>
+        <v>51.1</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -16251,13 +16253,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>973</v>
+        <v>1331</v>
       </c>
       <c r="M172" t="n">
         <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -16288,12 +16290,12 @@
       </c>
       <c r="X172" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.700394,69.220406</t>
+          <t>https://www.google.com/maps?q=40.715990,69.111172</t>
         </is>
       </c>
     </row>
@@ -16304,37 +16306,37 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C173" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>40.976114</v>
+        <v>41.04022</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>70.054822</v>
+        <v>70.089085</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>40.976114, 70.054822</t>
+          <t>41.040220, 70.089085</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Аблык курган</t>
+          <t>14 квартал</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I173" t="n">
         <v>0.4</v>
       </c>
       <c r="J173" t="n">
-        <v>52.9</v>
+        <v>52.5</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -16342,19 +16344,19 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>2688</v>
+        <v>6421</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N173" t="n">
+        <v>3</v>
+      </c>
+      <c r="O173" t="n">
         <v>1</v>
       </c>
-      <c r="O173" t="n">
-        <v>0</v>
-      </c>
       <c r="P173" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q173" t="n">
         <v>5</v>
@@ -16384,7 +16386,7 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.976114,70.054822</t>
+          <t>https://www.google.com/maps?q=41.040220,70.089085</t>
         </is>
       </c>
     </row>
@@ -16395,25 +16397,25 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="C174" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>40.947577</v>
+        <v>40.976114</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>70.033931</v>
+        <v>70.054822</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>40.947577, 70.033931</t>
+          <t>40.976114, 70.054822</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Алдын</t>
+          <t>Аблык курган</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -16422,10 +16424,10 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J174" t="n">
-        <v>53.1</v>
+        <v>52.9</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -16433,19 +16435,19 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>1201</v>
+        <v>2688</v>
       </c>
       <c r="M174" t="n">
         <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
       </c>
       <c r="P174" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q174" t="n">
         <v>5</v>
@@ -16470,12 +16472,12 @@
       </c>
       <c r="X174" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.947577,70.033931</t>
+          <t>https://www.google.com/maps?q=40.976114,70.054822</t>
         </is>
       </c>
     </row>
@@ -16486,25 +16488,25 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C175" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>41.031377</v>
+        <v>40.947577</v>
       </c>
       <c r="E175" s="2" t="n">
-        <v>70.100526</v>
+        <v>70.033931</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>41.031377, 70.100526</t>
+          <t>40.947577, 70.033931</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Дукент</t>
+          <t>Алдын</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -16513,10 +16515,10 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J175" t="n">
-        <v>53.7</v>
+        <v>53.1</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
@@ -16524,19 +16526,19 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>1285</v>
+        <v>1201</v>
       </c>
       <c r="M175" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P175" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q175" t="n">
         <v>5</v>
@@ -16561,12 +16563,12 @@
       </c>
       <c r="X175" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.031377,70.100526</t>
+          <t>https://www.google.com/maps?q=40.947577,70.033931</t>
         </is>
       </c>
     </row>
@@ -16577,7 +16579,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C176" t="n">
         <v>48</v>
@@ -16668,7 +16670,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C177" t="n">
         <v>52</v>
@@ -16759,20 +16761,20 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C178" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>41.689737</v>
+        <v>41.691547</v>
       </c>
       <c r="E178" s="2" t="n">
-        <v>70.057624</v>
+        <v>70.05371700000001</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>41.689737, 70.057624</t>
+          <t>41.691547, 70.053717</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -16786,10 +16788,10 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J178" t="n">
-        <v>57.8</v>
+        <v>57.6</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
@@ -16797,7 +16799,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>1602</v>
+        <v>1633</v>
       </c>
       <c r="M178" t="n">
         <v>0</v>
@@ -16839,7 +16841,7 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.689737,70.057624</t>
+          <t>https://www.google.com/maps?q=41.691547,70.053717</t>
         </is>
       </c>
     </row>
@@ -16850,20 +16852,20 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C179" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>40.644161</v>
+        <v>40.642384</v>
       </c>
       <c r="E179" s="2" t="n">
-        <v>69.214893</v>
+        <v>69.218755</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>40.644161, 69.214893</t>
+          <t>40.642384, 69.218755</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -16877,10 +16879,10 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J179" t="n">
-        <v>58</v>
+        <v>58.2</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
@@ -16888,7 +16890,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>1118</v>
+        <v>1471</v>
       </c>
       <c r="M179" t="n">
         <v>0</v>
@@ -16930,7 +16932,7 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.644161,69.214893</t>
+          <t>https://www.google.com/maps?q=40.642384,69.218755</t>
         </is>
       </c>
     </row>
@@ -16944,7 +16946,7 @@
         <v>4</v>
       </c>
       <c r="C180" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D180" s="2" t="n">
         <v>41.61707</v>
